--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>10.7</v>
+        <v>13.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="G10" t="n">
-        <v>0.66</v>
+        <v>1.07</v>
       </c>
       <c r="H10" t="n">
         <v>0.65</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>2.29</v>
       </c>
       <c r="J10" t="n">
         <v>2.25</v>
@@ -899,7 +899,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>-264819</v>
+        <v>-264788</v>
       </c>
     </row>
     <row r="11">
@@ -919,16 +919,16 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34.8</v>
+        <v>35.1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>2.26</v>
@@ -942,7 +942,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="n">
-        <v>138598</v>
+        <v>138630</v>
       </c>
     </row>
     <row r="13">
@@ -1603,26 +1603,26 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>100</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.55</v>
+        <v>1.13</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>2.29</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33">
@@ -1642,34 +1642,34 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>30</v>
+        <v>36.4</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.32</v>
+        <v>1.44</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.85</v>
+        <v>1.21</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>1.02</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1.46</v>
+        <v>2.29</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>3.41</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>8.33</v>
+        <v>10.75</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>4.29</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-40</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="35">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -449,7 +449,12 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,7 +520,32 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>실현손익합(원)</t>
+          <t>기대값(%/거래)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>기대값(원/거래)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>실현손익합(원,net)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>수수료·세금(원)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>실현손익합(원,gross)</t>
         </is>
       </c>
     </row>
@@ -546,15 +576,30 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
+        <v>-3.964</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-58941</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-176822</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1322</v>
+      </c>
+      <c r="R2" t="n">
         <v>-175500</v>
       </c>
     </row>
@@ -581,23 +626,38 @@
         <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="G3" t="n">
-        <v>7.83</v>
+        <v>7.79</v>
       </c>
       <c r="H3" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="I3" t="n">
-        <v>19.33</v>
+        <v>19.29</v>
       </c>
       <c r="J3" t="n">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="N3" t="n">
+        <v>16263</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="P3" t="n">
+        <v>227688</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2172</v>
+      </c>
+      <c r="R3" t="n">
         <v>229860</v>
       </c>
     </row>
@@ -624,23 +684,38 @@
         <v>28.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="H4" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="I4" t="n">
-        <v>17.39</v>
+        <v>17.35</v>
       </c>
       <c r="J4" t="n">
-        <v>20.07</v>
+        <v>20.1</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
+        <v>-0.727</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-5748</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-224174</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4434</v>
+      </c>
+      <c r="R4" t="n">
         <v>-219740</v>
       </c>
     </row>
@@ -667,23 +742,38 @@
         <v>36.1</v>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="G5" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="H5" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="I5" t="n">
-        <v>13.18</v>
+        <v>13.15</v>
       </c>
       <c r="J5" t="n">
-        <v>5.79</v>
+        <v>5.82</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
+        <v>-0.643</v>
+      </c>
+      <c r="N5" t="n">
+        <v>452</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>27596</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5045</v>
+      </c>
+      <c r="R5" t="n">
         <v>32641</v>
       </c>
     </row>
@@ -710,23 +800,38 @@
         <v>42.9</v>
       </c>
       <c r="F6" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="H6" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="J6" t="n">
-        <v>8.98</v>
+        <v>9.01</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
+        <v>-0.363</v>
+      </c>
+      <c r="N6" t="n">
+        <v>506</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P6" t="n">
+        <v>21236</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5178</v>
+      </c>
+      <c r="R6" t="n">
         <v>26414</v>
       </c>
     </row>
@@ -753,24 +858,39 @@
         <v>58.3</v>
       </c>
       <c r="F7" t="n">
-        <v>14.58</v>
+        <v>8.09</v>
       </c>
       <c r="G7" t="n">
-        <v>8.01</v>
+        <v>7.98</v>
       </c>
       <c r="H7" t="n">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="I7" t="n">
-        <v>11.17</v>
+        <v>11.14</v>
       </c>
       <c r="J7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>396938</v>
+        <v>3.19</v>
+      </c>
+      <c r="N7" t="n">
+        <v>31602</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="P7" t="n">
+        <v>379229</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2168</v>
+      </c>
+      <c r="R7" t="n">
+        <v>381397</v>
       </c>
     </row>
     <row r="8">
@@ -796,24 +916,39 @@
         <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>4.11</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>5.87</v>
+        <v>5.84</v>
       </c>
       <c r="H8" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="I8" t="n">
-        <v>11.12</v>
+        <v>11.09</v>
       </c>
       <c r="J8" t="n">
-        <v>11.74</v>
+        <v>11.77</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>120087</v>
+        <v>1.549</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3280</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>65607</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7203</v>
+      </c>
+      <c r="R8" t="n">
+        <v>72811</v>
       </c>
     </row>
     <row r="9">
@@ -839,24 +974,39 @@
         <v>31.4</v>
       </c>
       <c r="F9" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="G9" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="H9" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="I9" t="n">
-        <v>13.54</v>
+        <v>13.51</v>
       </c>
       <c r="J9" t="n">
-        <v>7.49</v>
+        <v>7.52</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>-7282</v>
+        <v>0.052</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-342</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-17462</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8322</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-9140</v>
       </c>
     </row>
     <row r="10">
@@ -882,24 +1032,39 @@
         <v>13.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.31</v>
+        <v>1.33</v>
       </c>
       <c r="G10" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="H10" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>-264788</v>
+        <v>-0.448</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-7903</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-229180</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>17298</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-211882</v>
       </c>
     </row>
     <row r="11">
@@ -925,24 +1090,39 @@
         <v>35.1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>19.33</v>
+        <v>19.29</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20.07</v>
+        <v>20.1</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="n">
-        <v>138630</v>
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>73719</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>53141</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>126860</v>
       </c>
     </row>
     <row r="13">
@@ -972,17 +1152,32 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
+        <v>-3.964</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-58941</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-176822</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1322</v>
+      </c>
+      <c r="R13" t="n">
         <v>-175500</v>
       </c>
     </row>
@@ -1009,19 +1204,19 @@
         <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="G14" t="n">
-        <v>7.83</v>
+        <v>7.79</v>
       </c>
       <c r="H14" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="I14" t="n">
-        <v>19.33</v>
+        <v>19.29</v>
       </c>
       <c r="J14" t="n">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="K14" t="n">
         <v>2.71</v>
@@ -1030,6 +1225,21 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="N14" t="n">
+        <v>16263</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="P14" t="n">
+        <v>227688</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2172</v>
+      </c>
+      <c r="R14" t="n">
         <v>229860</v>
       </c>
     </row>
@@ -1060,17 +1270,32 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>8.41</v>
+        <v>8.44</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>0.91</v>
       </c>
       <c r="M15" t="n">
+        <v>-3.001</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-21403</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-235428</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2878</v>
+      </c>
+      <c r="R15" t="n">
         <v>-232550</v>
       </c>
     </row>
@@ -1097,19 +1322,19 @@
         <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>7.5</v>
+        <v>7.37</v>
       </c>
       <c r="G16" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="H16" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="I16" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1118,6 +1343,21 @@
         <v>3.33</v>
       </c>
       <c r="M16" t="n">
+        <v>-1.022</v>
+      </c>
+      <c r="N16" t="n">
+        <v>14731</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P16" t="n">
+        <v>58925</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1075</v>
+      </c>
+      <c r="R16" t="n">
         <v>60000</v>
       </c>
     </row>
@@ -1144,19 +1384,19 @@
         <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="G17" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="H17" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="I17" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="J17" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="K17" t="n">
         <v>0.5</v>
@@ -1165,6 +1405,21 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-521</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-4171</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1720</v>
+      </c>
+      <c r="R17" t="n">
         <v>-2451</v>
       </c>
     </row>
@@ -1192,11 +1447,11 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>8.84</v>
+        <v>8.81</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>11.06</v>
+        <v>11.03</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
@@ -1204,6 +1459,19 @@
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="N18" t="n">
+        <v>85744</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>342974</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1131</v>
+      </c>
+      <c r="R18" t="n">
         <v>344105</v>
       </c>
     </row>
@@ -1230,19 +1498,19 @@
         <v>66.7</v>
       </c>
       <c r="F19" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="G19" t="n">
-        <v>6.79</v>
+        <v>6.75</v>
       </c>
       <c r="H19" t="n">
-        <v>9.4</v>
+        <v>9.42</v>
       </c>
       <c r="I19" t="n">
-        <v>11.12</v>
+        <v>11.09</v>
       </c>
       <c r="J19" t="n">
-        <v>11.74</v>
+        <v>11.77</v>
       </c>
       <c r="K19" t="n">
         <v>3.5</v>
@@ -1251,6 +1519,21 @@
         <v>8.5</v>
       </c>
       <c r="M19" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11916</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P19" t="n">
+        <v>71497</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>583</v>
+      </c>
+      <c r="R19" t="n">
         <v>72080</v>
       </c>
     </row>
@@ -1277,19 +1560,19 @@
         <v>40</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>6.38</v>
+        <v>6.34</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19.33</v>
+        <v>19.29</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>11.74</v>
+        <v>11.77</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>2</v>
@@ -1298,6 +1581,21 @@
         <v>1.47</v>
       </c>
       <c r="M20" s="2" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>5693</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>284665</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>10879</v>
+      </c>
+      <c r="R20" s="2" t="n">
         <v>295544</v>
       </c>
     </row>
@@ -1328,7 +1626,16 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="n">
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1359,7 +1666,16 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="n">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1386,19 +1702,19 @@
         <v>55.6</v>
       </c>
       <c r="F26" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="H26" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="I26" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="J26" t="n">
-        <v>7.01</v>
+        <v>7.04</v>
       </c>
       <c r="K26" t="n">
         <v>3</v>
@@ -1407,6 +1723,21 @@
         <v>1.75</v>
       </c>
       <c r="M26" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R26" t="n">
         <v>-4553</v>
       </c>
     </row>
@@ -1433,19 +1764,19 @@
         <v>55.6</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7.01</v>
+        <v>7.04</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>3</v>
@@ -1454,6 +1785,21 @@
         <v>1.75</v>
       </c>
       <c r="M27" s="2" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R27" s="2" t="n">
         <v>-4553</v>
       </c>
     </row>
@@ -1484,18 +1830,33 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>3.41</v>
+        <v>3.49</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-11</v>
+        <v>-2.607</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-8033</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-16066</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>514</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-15552</v>
       </c>
     </row>
     <row r="30">
@@ -1521,19 +1882,19 @@
         <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="H30" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="I30" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="J30" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1542,7 +1903,22 @@
         <v>5.67</v>
       </c>
       <c r="M30" t="n">
-        <v>-33</v>
+        <v>-0.217</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-13310</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-53239</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5930</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-47309</v>
       </c>
     </row>
     <row r="31">
@@ -1572,18 +1948,33 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>5.5</v>
       </c>
       <c r="M31" t="n">
-        <v>-1</v>
+        <v>-0.136</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-2395</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-4791</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2932</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-1859</v>
       </c>
     </row>
     <row r="32">
@@ -1610,11 +2001,11 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
@@ -1622,7 +2013,20 @@
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>37</v>
+        <v>1.042</v>
+      </c>
+      <c r="N32" t="n">
+        <v>16226</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>48677</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4266</v>
+      </c>
+      <c r="R32" t="n">
+        <v>52943</v>
       </c>
     </row>
     <row r="33">
@@ -1648,19 +2052,19 @@
         <v>36.4</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.41</v>
+        <v>3.49</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>10.75</v>
@@ -1669,7 +2073,22 @@
         <v>4.29</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-8</v>
+        <v>-0.293</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>-2311</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>-25419</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>13642</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>-11778</v>
       </c>
     </row>
     <row r="35">
@@ -1695,19 +2114,19 @@
         <v>40.7</v>
       </c>
       <c r="F35" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="G35" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="H35" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="I35" t="n">
-        <v>17.39</v>
+        <v>17.35</v>
       </c>
       <c r="J35" t="n">
-        <v>20.07</v>
+        <v>20.1</v>
       </c>
       <c r="K35" t="n">
         <v>185.95</v>
@@ -1716,6 +2135,21 @@
         <v>187.46</v>
       </c>
       <c r="M35" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="N35" t="n">
+        <v>507</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P35" t="n">
+        <v>13680</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1530</v>
+      </c>
+      <c r="R35" t="n">
         <v>15210</v>
       </c>
     </row>
@@ -1742,19 +2176,19 @@
         <v>37.8</v>
       </c>
       <c r="F36" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="G36" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="H36" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="I36" t="n">
-        <v>13.18</v>
+        <v>13.15</v>
       </c>
       <c r="J36" t="n">
-        <v>5.79</v>
+        <v>5.82</v>
       </c>
       <c r="K36" t="n">
         <v>313.5</v>
@@ -1763,6 +2197,21 @@
         <v>175.2</v>
       </c>
       <c r="M36" t="n">
+        <v>-0.703</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-1271</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="P36" t="n">
+        <v>-57188</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2829</v>
+      </c>
+      <c r="R36" t="n">
         <v>-54359</v>
       </c>
     </row>
@@ -1789,19 +2238,19 @@
         <v>41.9</v>
       </c>
       <c r="F37" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G37" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="H37" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="I37" t="n">
-        <v>8.720000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="J37" t="n">
-        <v>8.98</v>
+        <v>9.01</v>
       </c>
       <c r="K37" t="n">
         <v>247.7</v>
@@ -1810,6 +2259,21 @@
         <v>174.67</v>
       </c>
       <c r="M37" t="n">
+        <v>-0.288</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1187</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>36789</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3306</v>
+      </c>
+      <c r="R37" t="n">
         <v>40095</v>
       </c>
     </row>
@@ -1836,19 +2300,19 @@
         <v>50</v>
       </c>
       <c r="F38" t="n">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="G38" t="n">
-        <v>6.89</v>
+        <v>6.86</v>
       </c>
       <c r="H38" t="n">
-        <v>4.08</v>
+        <v>4.11</v>
       </c>
       <c r="I38" t="n">
-        <v>11.17</v>
+        <v>11.14</v>
       </c>
       <c r="J38" t="n">
-        <v>9.619999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="K38" t="n">
         <v>533.86</v>
@@ -1857,6 +2321,21 @@
         <v>403.59</v>
       </c>
       <c r="M38" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N38" t="n">
+        <v>8720</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="P38" t="n">
+        <v>52321</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>523</v>
+      </c>
+      <c r="R38" t="n">
         <v>52844</v>
       </c>
     </row>
@@ -1883,19 +2362,19 @@
         <v>44.4</v>
       </c>
       <c r="F39" t="n">
-        <v>4.5</v>
+        <v>4.39</v>
       </c>
       <c r="G39" t="n">
-        <v>7.11</v>
+        <v>7.08</v>
       </c>
       <c r="H39" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>7.98</v>
+        <v>7.95</v>
       </c>
       <c r="J39" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="K39" t="n">
         <v>800.2</v>
@@ -1904,6 +2383,21 @@
         <v>60.03</v>
       </c>
       <c r="M39" t="n">
+        <v>2.446</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5075</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P39" t="n">
+        <v>45679</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>661</v>
+      </c>
+      <c r="R39" t="n">
         <v>46340</v>
       </c>
     </row>
@@ -1930,19 +2424,19 @@
         <v>50</v>
       </c>
       <c r="F40" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="G40" t="n">
-        <v>6.07</v>
+        <v>6.04</v>
       </c>
       <c r="H40" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="I40" t="n">
-        <v>13.54</v>
+        <v>13.51</v>
       </c>
       <c r="J40" t="n">
-        <v>4.71</v>
+        <v>4.74</v>
       </c>
       <c r="K40" t="n">
         <v>2281.51</v>
@@ -1951,6 +2445,21 @@
         <v>27.54</v>
       </c>
       <c r="M40" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N40" t="n">
+        <v>851</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P40" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R40" t="n">
         <v>15177</v>
       </c>
     </row>
@@ -1981,17 +2490,32 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>40.94</v>
       </c>
       <c r="M41" t="n">
+        <v>-0.711</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-19138</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-76552</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3052</v>
+      </c>
+      <c r="R41" t="n">
         <v>-73500</v>
       </c>
     </row>
@@ -2018,19 +2542,19 @@
         <v>40.6</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>17.39</v>
+        <v>17.35</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>20.07</v>
+        <v>20.1</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>600.88</v>
@@ -2039,6 +2563,21 @@
         <v>157.85</v>
       </c>
       <c r="M42" s="2" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>28345</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>13462</v>
+      </c>
+      <c r="R42" s="2" t="n">
         <v>41807</v>
       </c>
     </row>
@@ -2069,17 +2608,32 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
         <v>13.35</v>
       </c>
       <c r="M44" t="n">
+        <v>-0.341</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-4880</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>-14641</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1291</v>
+      </c>
+      <c r="R44" t="n">
         <v>-13350</v>
       </c>
     </row>
@@ -2110,17 +2664,32 @@
       </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="n">
         <v>13.35</v>
       </c>
       <c r="M45" s="2" t="n">
+        <v>-0.341</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>-4880</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>-14641</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>1291</v>
+      </c>
+      <c r="R45" s="2" t="n">
         <v>-13350</v>
       </c>
     </row>
@@ -2151,17 +2720,32 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>29.99</v>
       </c>
       <c r="M47" t="n">
+        <v>-0.912</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-138394</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4519</v>
+      </c>
+      <c r="R47" t="n">
         <v>-133875</v>
       </c>
     </row>
@@ -2192,17 +2776,32 @@
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="n">
         <v>29.99</v>
       </c>
       <c r="M48" s="2" t="n">
+        <v>-0.912</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>-138394</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>4519</v>
+      </c>
+      <c r="R48" s="2" t="n">
         <v>-133875</v>
       </c>
     </row>
@@ -2229,19 +2828,19 @@
         <v>11.1</v>
       </c>
       <c r="F50" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="G50" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="H50" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="I50" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="J50" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K50" t="n">
         <v>3.2</v>
@@ -2250,6 +2849,21 @@
         <v>25.93</v>
       </c>
       <c r="M50" t="n">
+        <v>-0.348</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-5363</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-48269</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4169</v>
+      </c>
+      <c r="R50" t="n">
         <v>-44100</v>
       </c>
     </row>
@@ -2276,19 +2890,19 @@
         <v>11.1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>3.2</v>
@@ -2297,6 +2911,21 @@
         <v>25.93</v>
       </c>
       <c r="M51" s="2" t="n">
+        <v>-0.348</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>-5363</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>-48269</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>4169</v>
+      </c>
+      <c r="R51" s="2" t="n">
         <v>-44100</v>
       </c>
     </row>
@@ -2327,7 +2956,16 @@
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="n">
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2358,96 +2996,57 @@
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="n">
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_동시</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M57" t="n">
-        <v>-2400</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>06/29~07/03</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>12</v>
-      </c>
-      <c r="E58" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J58" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2003.43</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2987.95</v>
-      </c>
-      <c r="M58" t="n">
-        <v>27000</v>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2463,38 +3062,47 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.11</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="K59" t="n">
-        <v>4319.93</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
-        <v>1351.81</v>
+        <v>49.85</v>
       </c>
       <c r="M59" t="n">
-        <v>-11230</v>
+        <v>-2.747</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-2426</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-2426</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>26</v>
+      </c>
+      <c r="R59" t="n">
+        <v>-2400</v>
       </c>
     </row>
     <row r="60">
@@ -2510,30 +3118,53 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E60" t="n">
-        <v>100</v>
-      </c>
-      <c r="F60" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4.65</v>
+      </c>
       <c r="G60" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>1.92</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.4</v>
+      </c>
       <c r="I60" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K60" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L60" t="inlineStr"/>
+        <v>2003.43</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2987.95</v>
+      </c>
       <c r="M60" t="n">
-        <v>1700</v>
+        <v>-0.292</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2155</v>
+      </c>
+      <c r="O60" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P60" t="n">
+        <v>25859</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1141</v>
+      </c>
+      <c r="R60" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="61">
@@ -2549,96 +3180,178 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>07/06~07/10</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4319.93</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1351.81</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-2.059</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-3794</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-11383</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>153</v>
+      </c>
+      <c r="R61" t="n">
+        <v>-11230</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>100</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>30</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D63" t="n">
         <v>24</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E63" t="n">
         <v>12.5</v>
       </c>
-      <c r="F61" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J61" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="K61" t="n">
+      <c r="F63" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J63" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K63" t="n">
         <v>24201.59</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L63" t="n">
         <v>27253.11</v>
       </c>
-      <c r="M61" t="n">
+      <c r="M63" t="n">
+        <v>-0.595</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-816</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-19595</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1690</v>
+      </c>
+      <c r="R63" t="n">
         <v>-17905</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="K62" s="2" t="n">
-        <v>9438.73</v>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>18717.88</v>
-      </c>
-      <c r="M62" s="2" t="n">
-        <v>-2835</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ORD_A</t>
+          <t>5minHL_미분류</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2647,24 +3360,55 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>9438.73</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>18717.88</v>
+      </c>
       <c r="M64" s="2" t="n">
-        <v>0</v>
+        <v>-0.611</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>-5876</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>3041</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>-2835</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VOLUME_1</t>
+          <t>KR_TR_ORD_A</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2688,14 +3432,23 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="n">
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VOLUME_2</t>
+          <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2719,14 +3472,23 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="n">
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP1</t>
+          <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2750,14 +3512,23 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="n">
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>KR_TR_VCP1</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -2781,14 +3552,23 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="n">
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_JEO2</t>
+          <t>KR_TR_VCP2</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2812,14 +3592,23 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="n">
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_MA</t>
+          <t>KR_TR_JEO2</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2843,14 +3632,23 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="n">
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>미국VCP</t>
+          <t>KR_TR_MA</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2874,14 +3672,23 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="n">
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>US_TR_ORD_A</t>
+          <t>미국VCP</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -2905,14 +3712,23 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="n">
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_1</t>
+          <t>US_TR_ORD_A</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2936,14 +3752,23 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="n">
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_2</t>
+          <t>US_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2967,14 +3792,23 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="n">
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP1</t>
+          <t>US_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -2998,14 +3832,23 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="n">
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP2</t>
+          <t>US_TR_VCP1</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -3029,14 +3872,23 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="n">
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>US_TR_JEO2</t>
+          <t>US_TR_VCP2</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -3060,14 +3912,23 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="n">
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>US_TR_MA</t>
+          <t>US_TR_JEO2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -3091,14 +3952,23 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="n">
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>US_TR_MA</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -3122,19 +3992,28 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="n">
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>저점사다리</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -3153,14 +4032,23 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="n">
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>저점사다리</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -3184,7 +4072,56 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="n">
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -878,19 +878,19 @@
         <v>3.19</v>
       </c>
       <c r="N7" t="n">
-        <v>31602</v>
+        <v>31601</v>
       </c>
       <c r="O7" t="n">
-        <v>11.33</v>
+        <v>11.32</v>
       </c>
       <c r="P7" t="n">
-        <v>379229</v>
+        <v>379217</v>
       </c>
       <c r="Q7" t="n">
         <v>2168</v>
       </c>
       <c r="R7" t="n">
-        <v>381397</v>
+        <v>381386</v>
       </c>
     </row>
     <row r="8">
@@ -936,19 +936,19 @@
         <v>1.549</v>
       </c>
       <c r="N8" t="n">
-        <v>3280</v>
+        <v>3278</v>
       </c>
       <c r="O8" t="n">
         <v>1.7</v>
       </c>
       <c r="P8" t="n">
-        <v>65607</v>
+        <v>65570</v>
       </c>
       <c r="Q8" t="n">
-        <v>7203</v>
+        <v>7207</v>
       </c>
       <c r="R8" t="n">
-        <v>72811</v>
+        <v>72777</v>
       </c>
     </row>
     <row r="9">
@@ -1000,13 +1000,13 @@
         <v>0.9</v>
       </c>
       <c r="P9" t="n">
-        <v>-17462</v>
+        <v>-17465</v>
       </c>
       <c r="Q9" t="n">
-        <v>8322</v>
+        <v>8324</v>
       </c>
       <c r="R9" t="n">
-        <v>-9140</v>
+        <v>-9141</v>
       </c>
     </row>
     <row r="10">
@@ -1052,19 +1052,19 @@
         <v>-0.448</v>
       </c>
       <c r="N10" t="n">
-        <v>-7903</v>
+        <v>-7902</v>
       </c>
       <c r="O10" t="n">
         <v>0.21</v>
       </c>
       <c r="P10" t="n">
-        <v>-229180</v>
+        <v>-229146</v>
       </c>
       <c r="Q10" t="n">
-        <v>17298</v>
+        <v>17301</v>
       </c>
       <c r="R10" t="n">
-        <v>-211882</v>
+        <v>-211845</v>
       </c>
     </row>
     <row r="11">
@@ -1116,13 +1116,13 @@
         <v>1.05</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>73719</v>
+        <v>73701</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>53141</v>
+        <v>53151</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>126860</v>
+        <v>126852</v>
       </c>
     </row>
     <row r="13">
@@ -1844,19 +1844,19 @@
         <v>-2.607</v>
       </c>
       <c r="N29" t="n">
-        <v>-8033</v>
+        <v>-8039</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-16066</v>
+        <v>-16078</v>
       </c>
       <c r="Q29" t="n">
         <v>514</v>
       </c>
       <c r="R29" t="n">
-        <v>-15552</v>
+        <v>-15563</v>
       </c>
     </row>
     <row r="30">
@@ -1906,19 +1906,19 @@
         <v>-0.217</v>
       </c>
       <c r="N30" t="n">
-        <v>-13310</v>
+        <v>-13319</v>
       </c>
       <c r="O30" t="n">
         <v>0.02</v>
       </c>
       <c r="P30" t="n">
-        <v>-53239</v>
+        <v>-53277</v>
       </c>
       <c r="Q30" t="n">
-        <v>5930</v>
+        <v>5934</v>
       </c>
       <c r="R30" t="n">
-        <v>-47309</v>
+        <v>-47343</v>
       </c>
     </row>
     <row r="31">
@@ -1962,19 +1962,19 @@
         <v>-0.136</v>
       </c>
       <c r="N31" t="n">
-        <v>-2395</v>
+        <v>-2397</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-4791</v>
+        <v>-4794</v>
       </c>
       <c r="Q31" t="n">
-        <v>2932</v>
+        <v>2934</v>
       </c>
       <c r="R31" t="n">
-        <v>-1859</v>
+        <v>-1860</v>
       </c>
     </row>
     <row r="32">
@@ -2016,17 +2016,17 @@
         <v>1.042</v>
       </c>
       <c r="N32" t="n">
-        <v>16226</v>
+        <v>16237</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>48677</v>
+        <v>48711</v>
       </c>
       <c r="Q32" t="n">
-        <v>4266</v>
+        <v>4269</v>
       </c>
       <c r="R32" t="n">
-        <v>52943</v>
+        <v>52980</v>
       </c>
     </row>
     <row r="33">
@@ -2076,19 +2076,19 @@
         <v>-0.293</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-2311</v>
+        <v>-2312</v>
       </c>
       <c r="O33" s="2" t="n">
         <v>0.66</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>-25419</v>
+        <v>-25437</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>13642</v>
+        <v>13651</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>-11778</v>
+        <v>-11786</v>
       </c>
     </row>
     <row r="35">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1068,117 +1068,115 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>통합</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-9939</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-9939</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>198</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-9741</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>271</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="F11" s="2" t="n">
+      <c r="D12" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>4.22</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="I11" s="2" t="n">
+      <c r="H12" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>272</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>73701</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>53151</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>126852</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>주도주</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>06/08~06/12</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-3.964</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-58941</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-176822</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1322</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-175500</v>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>63762</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>53348</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>117111</v>
       </c>
     </row>
     <row r="14">
@@ -1194,53 +1192,47 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>06/15~06/19</t>
+          <t>06/08~06/12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="I14" t="n">
-        <v>19.29</v>
-      </c>
+        <v>3.96</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.71</v>
-      </c>
+        <v>4.35</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.378</v>
+        <v>-3.964</v>
       </c>
       <c r="N14" t="n">
-        <v>16263</v>
+        <v>-58941</v>
       </c>
       <c r="O14" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>227688</v>
+        <v>-176822</v>
       </c>
       <c r="Q14" t="n">
-        <v>2172</v>
+        <v>1322</v>
       </c>
       <c r="R14" t="n">
-        <v>229860</v>
+        <v>-175500</v>
       </c>
     </row>
     <row r="15">
@@ -1256,47 +1248,53 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>06/22~06/26</t>
+          <t>06/15~06/19</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
+        <v>3.69</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.79</v>
+      </c>
       <c r="H15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="I15" t="n">
+        <v>19.29</v>
+      </c>
       <c r="J15" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>4.76</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.71</v>
+      </c>
       <c r="L15" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.001</v>
+        <v>2.378</v>
       </c>
       <c r="N15" t="n">
-        <v>-21403</v>
+        <v>16263</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P15" t="n">
-        <v>-235428</v>
+        <v>227688</v>
       </c>
       <c r="Q15" t="n">
-        <v>2878</v>
+        <v>2172</v>
       </c>
       <c r="R15" t="n">
-        <v>-232550</v>
+        <v>229860</v>
       </c>
     </row>
     <row r="16">
@@ -1312,53 +1310,47 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4.74</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
+        <v>8.44</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>3.33</v>
+        <v>0.91</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.022</v>
+        <v>-3.001</v>
       </c>
       <c r="N16" t="n">
-        <v>14731</v>
+        <v>-21403</v>
       </c>
       <c r="O16" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>58925</v>
+        <v>-235428</v>
       </c>
       <c r="Q16" t="n">
-        <v>1075</v>
+        <v>2878</v>
       </c>
       <c r="R16" t="n">
-        <v>60000</v>
+        <v>-232550</v>
       </c>
     </row>
     <row r="17">
@@ -1374,53 +1366,53 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.67</v>
+        <v>7.37</v>
       </c>
       <c r="G17" t="n">
-        <v>1.34</v>
+        <v>4.74</v>
       </c>
       <c r="H17" t="n">
-        <v>1.38</v>
+        <v>2.94</v>
       </c>
       <c r="I17" t="n">
-        <v>4.21</v>
+        <v>4.74</v>
       </c>
       <c r="J17" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.021</v>
+        <v>-1.022</v>
       </c>
       <c r="N17" t="n">
-        <v>-521</v>
+        <v>14731</v>
       </c>
       <c r="O17" t="n">
-        <v>0.67</v>
+        <v>2.46</v>
       </c>
       <c r="P17" t="n">
-        <v>-4171</v>
+        <v>58925</v>
       </c>
       <c r="Q17" t="n">
-        <v>1720</v>
+        <v>1075</v>
       </c>
       <c r="R17" t="n">
-        <v>-2451</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="18">
@@ -1436,43 +1428,53 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.67</v>
+      </c>
       <c r="G18" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>1.34</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.38</v>
+      </c>
       <c r="I18" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>4.21</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.27</v>
+      </c>
       <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" t="n">
-        <v>8.81</v>
+        <v>-0.021</v>
       </c>
       <c r="N18" t="n">
-        <v>85744</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
+        <v>-521</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.67</v>
+      </c>
       <c r="P18" t="n">
-        <v>342974</v>
+        <v>-4171</v>
       </c>
       <c r="Q18" t="n">
-        <v>1131</v>
+        <v>1720</v>
       </c>
       <c r="R18" t="n">
-        <v>344105</v>
+        <v>-2451</v>
       </c>
     </row>
     <row r="19">
@@ -1488,375 +1490,371 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>07/13~07/17</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="N19" t="n">
+        <v>85744</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>342974</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1131</v>
+      </c>
+      <c r="R19" t="n">
+        <v>344105</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>주도주</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>07/20~07/24</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D20" t="n">
         <v>6</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E20" t="n">
         <v>66.7</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>2.21</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>6.75</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
         <v>9.42</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>11.09</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>11.77</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>3.5</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L20" t="n">
         <v>8.5</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M20" t="n">
         <v>1.361</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N20" t="n">
         <v>11916</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O20" t="n">
         <v>4.43</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P20" t="n">
         <v>71497</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q20" t="n">
         <v>583</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>72080</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>주도주</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D21" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E21" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F21" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>6.34</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>3.31</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I21" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>11.77</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="L21" s="2" t="n">
         <v>1.47</v>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="M21" s="2" t="n">
         <v>0.551</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="N21" s="2" t="n">
         <v>5693</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="O21" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>284665</v>
       </c>
-      <c r="Q20" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>10879</v>
       </c>
-      <c r="R20" s="2" t="n">
+      <c r="R21" s="2" t="n">
         <v>295544</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>ROCKET</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="D23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>ABC-VCP</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D27" t="n">
         <v>9</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>55.6</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G27" t="n">
         <v>1.17</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H27" t="n">
         <v>4.19</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>3.38</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>7.04</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K27" t="n">
         <v>3</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>1.75</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>-744</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O27" t="n">
         <v>0.86</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P27" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q27" t="n">
         <v>2139</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>-4553</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D28" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E28" s="2" t="n">
         <v>55.6</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F28" s="2" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>1.17</v>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="I28" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="J27" s="2" t="n">
+      <c r="J28" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L27" s="2" t="n">
+      <c r="L28" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="M27" s="2" t="n">
+      <c r="M28" s="2" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="N28" s="2" t="n">
         <v>-744</v>
       </c>
-      <c r="O27" s="2" t="n">
+      <c r="O28" s="2" t="n">
         <v>0.86</v>
       </c>
-      <c r="P27" s="2" t="n">
+      <c r="P28" s="2" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q27" s="2" t="n">
+      <c r="Q28" s="2" t="n">
         <v>2139</v>
       </c>
-      <c r="R27" s="2" t="n">
+      <c r="R28" s="2" t="n">
         <v>-4553</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-8039</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>-16078</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>514</v>
-      </c>
-      <c r="R29" t="n">
-        <v>-15563</v>
       </c>
     </row>
     <row r="30">
@@ -1872,53 +1870,47 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.37</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K30" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>5.67</v>
-      </c>
       <c r="M30" t="n">
-        <v>-0.217</v>
+        <v>-2.607</v>
       </c>
       <c r="N30" t="n">
-        <v>-13319</v>
+        <v>-8039</v>
       </c>
       <c r="O30" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-53277</v>
+        <v>-16078</v>
       </c>
       <c r="Q30" t="n">
-        <v>5934</v>
+        <v>514</v>
       </c>
       <c r="R30" t="n">
-        <v>-47343</v>
+        <v>-15563</v>
       </c>
     </row>
     <row r="31">
@@ -1934,47 +1926,53 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J31" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
       <c r="L31" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.136</v>
+        <v>-0.217</v>
       </c>
       <c r="N31" t="n">
-        <v>-2397</v>
+        <v>-13319</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P31" t="n">
-        <v>-4794</v>
+        <v>-53277</v>
       </c>
       <c r="Q31" t="n">
-        <v>2934</v>
+        <v>5934</v>
       </c>
       <c r="R31" t="n">
-        <v>-1860</v>
+        <v>-47343</v>
       </c>
     </row>
     <row r="32">
@@ -1990,167 +1988,161 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-2397</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-4794</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2934</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-1860</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D33" t="n">
         <v>3</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E33" t="n">
         <v>100</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="n">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>1.04</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
         <v>2.2</v>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
         <v>14</v>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
         <v>1.042</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N33" t="n">
         <v>16237</v>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
         <v>48711</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q33" t="n">
         <v>4269</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>52980</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D34" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E34" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F34" s="2" t="n">
         <v>1.16</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="I34" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="J34" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K34" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L33" s="2" t="n">
+      <c r="L34" s="2" t="n">
         <v>4.29</v>
       </c>
-      <c r="M33" s="2" t="n">
+      <c r="M34" s="2" t="n">
         <v>-0.293</v>
       </c>
-      <c r="N33" s="2" t="n">
+      <c r="N34" s="2" t="n">
         <v>-2312</v>
       </c>
-      <c r="O33" s="2" t="n">
+      <c r="O34" s="2" t="n">
         <v>0.66</v>
       </c>
-      <c r="P33" s="2" t="n">
+      <c r="P34" s="2" t="n">
         <v>-25437</v>
       </c>
-      <c r="Q33" s="2" t="n">
+      <c r="Q34" s="2" t="n">
         <v>13651</v>
       </c>
-      <c r="R33" s="2" t="n">
+      <c r="R34" s="2" t="n">
         <v>-11786</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>27</v>
-      </c>
-      <c r="E35" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G35" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H35" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I35" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J35" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L35" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N35" t="n">
-        <v>507</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P35" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R35" t="n">
-        <v>15210</v>
       </c>
     </row>
     <row r="36">
@@ -2166,53 +2158,53 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E36" t="n">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="F36" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="G36" t="n">
-        <v>3.01</v>
+        <v>5.47</v>
       </c>
       <c r="H36" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="I36" t="n">
-        <v>13.15</v>
+        <v>17.35</v>
       </c>
       <c r="J36" t="n">
-        <v>5.82</v>
+        <v>20.1</v>
       </c>
       <c r="K36" t="n">
-        <v>313.5</v>
+        <v>185.95</v>
       </c>
       <c r="L36" t="n">
-        <v>175.2</v>
+        <v>187.46</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.703</v>
+        <v>0.274</v>
       </c>
       <c r="N36" t="n">
-        <v>-1271</v>
+        <v>507</v>
       </c>
       <c r="O36" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="P36" t="n">
-        <v>-57188</v>
+        <v>13680</v>
       </c>
       <c r="Q36" t="n">
-        <v>2829</v>
+        <v>1530</v>
       </c>
       <c r="R36" t="n">
-        <v>-54359</v>
+        <v>15210</v>
       </c>
     </row>
     <row r="37">
@@ -2228,53 +2220,53 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="F37" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="H37" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I37" t="n">
-        <v>8.68</v>
+        <v>13.15</v>
       </c>
       <c r="J37" t="n">
-        <v>9.01</v>
+        <v>5.82</v>
       </c>
       <c r="K37" t="n">
-        <v>247.7</v>
+        <v>313.5</v>
       </c>
       <c r="L37" t="n">
-        <v>174.67</v>
+        <v>175.2</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.288</v>
+        <v>-0.703</v>
       </c>
       <c r="N37" t="n">
-        <v>1187</v>
+        <v>-1271</v>
       </c>
       <c r="O37" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="P37" t="n">
-        <v>36789</v>
+        <v>-57188</v>
       </c>
       <c r="Q37" t="n">
-        <v>3306</v>
+        <v>2829</v>
       </c>
       <c r="R37" t="n">
-        <v>40095</v>
+        <v>-54359</v>
       </c>
     </row>
     <row r="38">
@@ -2290,53 +2282,53 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E38" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="F38" t="n">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="G38" t="n">
-        <v>6.86</v>
+        <v>3.14</v>
       </c>
       <c r="H38" t="n">
-        <v>4.11</v>
+        <v>2.76</v>
       </c>
       <c r="I38" t="n">
-        <v>11.14</v>
+        <v>8.68</v>
       </c>
       <c r="J38" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="K38" t="n">
-        <v>533.86</v>
+        <v>247.7</v>
       </c>
       <c r="L38" t="n">
-        <v>403.59</v>
+        <v>174.67</v>
       </c>
       <c r="M38" t="n">
-        <v>1.375</v>
+        <v>-0.288</v>
       </c>
       <c r="N38" t="n">
-        <v>8720</v>
+        <v>1187</v>
       </c>
       <c r="O38" t="n">
-        <v>3.53</v>
+        <v>1.3</v>
       </c>
       <c r="P38" t="n">
-        <v>52321</v>
+        <v>36789</v>
       </c>
       <c r="Q38" t="n">
-        <v>523</v>
+        <v>3306</v>
       </c>
       <c r="R38" t="n">
-        <v>52844</v>
+        <v>40095</v>
       </c>
     </row>
     <row r="39">
@@ -2352,53 +2344,53 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="G39" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="H39" t="n">
-        <v>1.26</v>
+        <v>4.11</v>
       </c>
       <c r="I39" t="n">
-        <v>7.95</v>
+        <v>11.14</v>
       </c>
       <c r="J39" t="n">
-        <v>2.19</v>
+        <v>9.65</v>
       </c>
       <c r="K39" t="n">
-        <v>800.2</v>
+        <v>533.86</v>
       </c>
       <c r="L39" t="n">
-        <v>60.03</v>
+        <v>403.59</v>
       </c>
       <c r="M39" t="n">
-        <v>2.446</v>
+        <v>1.375</v>
       </c>
       <c r="N39" t="n">
-        <v>5075</v>
+        <v>8720</v>
       </c>
       <c r="O39" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P39" t="n">
-        <v>45679</v>
+        <v>52321</v>
       </c>
       <c r="Q39" t="n">
-        <v>661</v>
+        <v>523</v>
       </c>
       <c r="R39" t="n">
-        <v>46340</v>
+        <v>52844</v>
       </c>
     </row>
     <row r="40">
@@ -2414,53 +2406,53 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F40" t="n">
-        <v>1.14</v>
+        <v>4.39</v>
       </c>
       <c r="G40" t="n">
-        <v>6.04</v>
+        <v>7.08</v>
       </c>
       <c r="H40" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I40" t="n">
-        <v>13.51</v>
+        <v>7.95</v>
       </c>
       <c r="J40" t="n">
-        <v>4.74</v>
+        <v>2.19</v>
       </c>
       <c r="K40" t="n">
-        <v>2281.51</v>
+        <v>800.2</v>
       </c>
       <c r="L40" t="n">
-        <v>27.54</v>
+        <v>60.03</v>
       </c>
       <c r="M40" t="n">
-        <v>1.758</v>
+        <v>2.446</v>
       </c>
       <c r="N40" t="n">
-        <v>851</v>
+        <v>5075</v>
       </c>
       <c r="O40" t="n">
-        <v>1.14</v>
+        <v>3.51</v>
       </c>
       <c r="P40" t="n">
-        <v>13616</v>
+        <v>45679</v>
       </c>
       <c r="Q40" t="n">
-        <v>1561</v>
+        <v>661</v>
       </c>
       <c r="R40" t="n">
-        <v>15177</v>
+        <v>46340</v>
       </c>
     </row>
     <row r="41">
@@ -2476,633 +2468,639 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>16</v>
+      </c>
+      <c r="E41" t="n">
+        <v>50</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I41" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L41" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N41" t="n">
+        <v>851</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P41" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R41" t="n">
+        <v>15177</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D42" t="n">
         <v>4</v>
       </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="n">
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
         <v>0.71</v>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
         <v>0.97</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
         <v>40.94</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M42" t="n">
         <v>-0.711</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N42" t="n">
         <v>-19138</v>
       </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>-76552</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q42" t="n">
         <v>3052</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R42" t="n">
         <v>-73500</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D43" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E43" s="2" t="n">
         <v>40.6</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F43" s="2" t="n">
         <v>1.53</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H43" s="2" t="n">
         <v>2.77</v>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="I43" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="J43" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="K43" s="2" t="n">
         <v>600.88</v>
       </c>
-      <c r="L42" s="2" t="n">
+      <c r="L43" s="2" t="n">
         <v>157.85</v>
       </c>
-      <c r="M42" s="2" t="n">
+      <c r="M43" s="2" t="n">
         <v>0.162</v>
       </c>
-      <c r="N42" s="2" t="n">
+      <c r="N43" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="O42" s="2" t="n">
+      <c r="O43" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="P42" s="2" t="n">
+      <c r="P43" s="2" t="n">
         <v>28345</v>
       </c>
-      <c r="Q42" s="2" t="n">
+      <c r="Q43" s="2" t="n">
         <v>13462</v>
       </c>
-      <c r="R42" s="2" t="n">
+      <c r="R43" s="2" t="n">
         <v>41807</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D45" t="n">
         <v>3</v>
       </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="n">
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
         <v>0.34</v>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="n">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
         <v>0.49</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="n">
         <v>13.35</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M45" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N45" t="n">
         <v>-4880</v>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q45" t="n">
         <v>1291</v>
       </c>
-      <c r="R44" t="n">
+      <c r="R45" t="n">
         <v>-13350</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="n">
+      <c r="E46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="n">
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M45" s="2" t="n">
+      <c r="M46" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N45" s="2" t="n">
+      <c r="N46" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2" t="n">
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q45" s="2" t="n">
+      <c r="Q46" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R45" s="2" t="n">
+      <c r="R46" s="2" t="n">
         <v>-13350</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D48" t="n">
         <v>10</v>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="n">
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
         <v>0.91</v>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="n">
         <v>2.28</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="n">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
         <v>29.99</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M48" t="n">
         <v>-0.912</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N48" t="n">
         <v>-13839</v>
       </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
         <v>-138394</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q48" t="n">
         <v>4519</v>
       </c>
-      <c r="R47" t="n">
+      <c r="R48" t="n">
         <v>-133875</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D49" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="n">
+      <c r="E49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="n">
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="n">
         <v>29.99</v>
       </c>
-      <c r="M48" s="2" t="n">
+      <c r="M49" s="2" t="n">
         <v>-0.912</v>
       </c>
-      <c r="N48" s="2" t="n">
+      <c r="N49" s="2" t="n">
         <v>-13839</v>
       </c>
-      <c r="O48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="n">
+      <c r="O49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="n">
         <v>-138394</v>
       </c>
-      <c r="Q48" s="2" t="n">
+      <c r="Q49" s="2" t="n">
         <v>4519</v>
       </c>
-      <c r="R48" s="2" t="n">
+      <c r="R49" s="2" t="n">
         <v>-133875</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D51" t="n">
         <v>9</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E51" t="n">
         <v>11.1</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F51" t="n">
         <v>1.75</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G51" t="n">
         <v>0.84</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H51" t="n">
         <v>0.5</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I51" t="n">
         <v>0.84</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J51" t="n">
         <v>1.15</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K51" t="n">
         <v>3.2</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L51" t="n">
         <v>25.93</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M51" t="n">
         <v>-0.348</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N51" t="n">
         <v>-5363</v>
       </c>
-      <c r="O50" t="n">
+      <c r="O51" t="n">
         <v>0.22</v>
       </c>
-      <c r="P50" t="n">
+      <c r="P51" t="n">
         <v>-48269</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q51" t="n">
         <v>4169</v>
       </c>
-      <c r="R50" t="n">
+      <c r="R51" t="n">
         <v>-44100</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D52" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E52" s="2" t="n">
         <v>11.1</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F52" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H52" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I52" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="J52" s="2" t="n">
         <v>1.15</v>
       </c>
-      <c r="K51" s="2" t="n">
+      <c r="K52" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="L51" s="2" t="n">
+      <c r="L52" s="2" t="n">
         <v>25.93</v>
       </c>
-      <c r="M51" s="2" t="n">
+      <c r="M52" s="2" t="n">
         <v>-0.348</v>
       </c>
-      <c r="N51" s="2" t="n">
+      <c r="N52" s="2" t="n">
         <v>-5363</v>
       </c>
-      <c r="O51" s="2" t="n">
+      <c r="O52" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="P51" s="2" t="n">
+      <c r="P52" s="2" t="n">
         <v>-48269</v>
       </c>
-      <c r="Q51" s="2" t="n">
+      <c r="Q52" s="2" t="n">
         <v>4169</v>
       </c>
-      <c r="R51" s="2" t="n">
+      <c r="R52" s="2" t="n">
         <v>-44100</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>5minHL</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr"/>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="D54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>5minHL2</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr"/>
-      <c r="O55" s="2" t="inlineStr"/>
-      <c r="P55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="D56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>5minHL_동시</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
-      <c r="O57" s="2" t="inlineStr"/>
-      <c r="P57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M59" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>26</v>
-      </c>
-      <c r="R59" t="n">
-        <v>-2400</v>
+      <c r="D58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3118,53 +3116,47 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1.92</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I60" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K60" t="n">
-        <v>2003.43</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>2987.95</v>
+        <v>49.85</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.292</v>
+        <v>-2.747</v>
       </c>
       <c r="N60" t="n">
-        <v>2155</v>
+        <v>-2426</v>
       </c>
       <c r="O60" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>25859</v>
+        <v>-2426</v>
       </c>
       <c r="Q60" t="n">
-        <v>1141</v>
+        <v>26</v>
       </c>
       <c r="R60" t="n">
-        <v>27000</v>
+        <v>-2400</v>
       </c>
     </row>
     <row r="61">
@@ -3180,53 +3172,53 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E61" t="n">
         <v>33.3</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01</v>
+        <v>4.65</v>
       </c>
       <c r="G61" t="n">
-        <v>0.08</v>
+        <v>1.92</v>
       </c>
       <c r="H61" t="n">
-        <v>3.13</v>
+        <v>1.4</v>
       </c>
       <c r="I61" t="n">
-        <v>0.08</v>
+        <v>4.6</v>
       </c>
       <c r="J61" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="K61" t="n">
-        <v>4319.93</v>
+        <v>2003.43</v>
       </c>
       <c r="L61" t="n">
-        <v>1351.81</v>
+        <v>2987.95</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.059</v>
+        <v>-0.292</v>
       </c>
       <c r="N61" t="n">
-        <v>-3794</v>
+        <v>2155</v>
       </c>
       <c r="O61" t="n">
-        <v>0.01</v>
+        <v>2.33</v>
       </c>
       <c r="P61" t="n">
-        <v>-11383</v>
+        <v>25859</v>
       </c>
       <c r="Q61" t="n">
-        <v>153</v>
+        <v>1141</v>
       </c>
       <c r="R61" t="n">
-        <v>-11230</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="62">
@@ -3242,43 +3234,53 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>100</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G62" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3.13</v>
+      </c>
       <c r="I62" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3.61</v>
+      </c>
       <c r="K62" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
+        <v>4319.93</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1351.81</v>
+      </c>
       <c r="M62" t="n">
-        <v>1.678</v>
+        <v>-2.059</v>
       </c>
       <c r="N62" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O62" t="inlineStr"/>
+        <v>-3794</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.01</v>
+      </c>
       <c r="P62" t="n">
-        <v>1670</v>
+        <v>-11383</v>
       </c>
       <c r="Q62" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="R62" t="n">
-        <v>1700</v>
+        <v>-11230</v>
       </c>
     </row>
     <row r="63">
@@ -3294,641 +3296,709 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>100</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>30</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D64" t="n">
         <v>24</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E64" t="n">
         <v>12.5</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F64" t="n">
         <v>1.08</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G64" t="n">
         <v>1.37</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H64" t="n">
         <v>0.88</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I64" t="n">
         <v>2.51</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J64" t="n">
         <v>7.52</v>
       </c>
-      <c r="K63" t="n">
+      <c r="K64" t="n">
         <v>24201.59</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L64" t="n">
         <v>27253.11</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M64" t="n">
         <v>-0.595</v>
       </c>
-      <c r="N63" t="n">
+      <c r="N64" t="n">
         <v>-816</v>
       </c>
-      <c r="O63" t="n">
+      <c r="O64" t="n">
         <v>0.15</v>
       </c>
-      <c r="P63" t="n">
+      <c r="P64" t="n">
         <v>-19595</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="Q64" t="n">
         <v>1690</v>
       </c>
-      <c r="R63" t="n">
+      <c r="R64" t="n">
         <v>-17905</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D65" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E65" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F65" s="2" t="n">
         <v>3.19</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>1.51</v>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H65" s="2" t="n">
         <v>1.21</v>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="I65" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="J64" s="2" t="n">
+      <c r="J65" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="K64" s="2" t="n">
+      <c r="K65" s="2" t="n">
         <v>9438.73</v>
       </c>
-      <c r="L64" s="2" t="n">
+      <c r="L65" s="2" t="n">
         <v>18717.88</v>
       </c>
-      <c r="M64" s="2" t="n">
+      <c r="M65" s="2" t="n">
         <v>-0.611</v>
       </c>
-      <c r="N64" s="2" t="n">
+      <c r="N65" s="2" t="n">
         <v>-143</v>
       </c>
-      <c r="O64" s="2" t="n">
+      <c r="O65" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="P64" s="2" t="n">
+      <c r="P65" s="2" t="n">
         <v>-5876</v>
       </c>
-      <c r="Q64" s="2" t="n">
+      <c r="Q65" s="2" t="n">
         <v>3041</v>
       </c>
-      <c r="R64" s="2" t="n">
+      <c r="R65" s="2" t="n">
         <v>-2835</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr"/>
-      <c r="P66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="D67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="D69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="D71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP1</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="D73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP2</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="D75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>KR_TR_JEO2</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="D77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>KR_TR_MA</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="D79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>미국VCP</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="D81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="D83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="D85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="D87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="D89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="2" t="n">
-        <v>0</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>5</v>
+      </c>
+      <c r="M91" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-9939</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>-9939</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>198</v>
+      </c>
+      <c r="R91" t="n">
+        <v>-9741</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>US_TR_JEO2</t>
+          <t>US_TR_VCP2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -3942,33 +4012,49 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="n">
+        <v>6.8</v>
+      </c>
       <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="n">
+        <v>6.8</v>
+      </c>
       <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-9939</v>
+      </c>
+      <c r="O92" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P92" s="2" t="n">
-        <v>0</v>
+        <v>-9939</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="R92" s="2" t="n">
-        <v>0</v>
+        <v>-9741</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>US_TR_MA</t>
+          <t>US_TR_JEO2</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4008,7 +4094,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>US_TR_MA</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4048,12 +4134,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>저점사다리</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -4088,7 +4174,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>저점사다리</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4125,6 +4211,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>6.8</v>
+        <v>2.62</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
@@ -1103,22 +1103,22 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>-6.802</v>
+        <v>-2.623</v>
       </c>
       <c r="N11" t="n">
-        <v>-9939</v>
+        <v>-14942</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-9939</v>
+        <v>-44826</v>
       </c>
       <c r="Q11" t="n">
-        <v>198</v>
+        <v>11058</v>
       </c>
       <c r="R11" t="n">
-        <v>-9741</v>
+        <v>-33768</v>
       </c>
     </row>
     <row r="12">
@@ -1138,19 +1138,19 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>4.22</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>19.29</v>
@@ -1161,22 +1161,22 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="n">
-        <v>-0.034</v>
+        <v>-0.038</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>234</v>
+        <v>105</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>63762</v>
+        <v>28876</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>53348</v>
+        <v>64209</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>117111</v>
+        <v>93084</v>
       </c>
     </row>
     <row r="14">
@@ -2084,127 +2084,121 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.534</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-17443</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-34887</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>10861</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-24026</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="G34" s="2" t="n">
+      <c r="D35" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G35" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H34" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I34" s="2" t="n">
+      <c r="H35" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I35" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K35" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L34" s="2" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>-0.293</v>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>-2312</v>
-      </c>
-      <c r="O34" s="2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>-25437</v>
-      </c>
-      <c r="Q34" s="2" t="n">
-        <v>13651</v>
-      </c>
-      <c r="R34" s="2" t="n">
-        <v>-11786</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>27</v>
-      </c>
-      <c r="E36" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G36" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I36" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J36" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L36" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N36" t="n">
-        <v>507</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P36" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R36" t="n">
-        <v>15210</v>
+      <c r="L35" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-4640</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>-60324</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>24512</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>-35812</v>
       </c>
     </row>
     <row r="37">
@@ -2220,53 +2214,53 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E37" t="n">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="F37" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="G37" t="n">
-        <v>3.01</v>
+        <v>5.47</v>
       </c>
       <c r="H37" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="I37" t="n">
-        <v>13.15</v>
+        <v>17.35</v>
       </c>
       <c r="J37" t="n">
-        <v>5.82</v>
+        <v>20.1</v>
       </c>
       <c r="K37" t="n">
-        <v>313.5</v>
+        <v>185.95</v>
       </c>
       <c r="L37" t="n">
-        <v>175.2</v>
+        <v>187.46</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.703</v>
+        <v>0.274</v>
       </c>
       <c r="N37" t="n">
-        <v>-1271</v>
+        <v>507</v>
       </c>
       <c r="O37" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="P37" t="n">
-        <v>-57188</v>
+        <v>13680</v>
       </c>
       <c r="Q37" t="n">
-        <v>2829</v>
+        <v>1530</v>
       </c>
       <c r="R37" t="n">
-        <v>-54359</v>
+        <v>15210</v>
       </c>
     </row>
     <row r="38">
@@ -2282,53 +2276,53 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E38" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="F38" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="G38" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="H38" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I38" t="n">
-        <v>8.68</v>
+        <v>13.15</v>
       </c>
       <c r="J38" t="n">
-        <v>9.01</v>
+        <v>5.82</v>
       </c>
       <c r="K38" t="n">
-        <v>247.7</v>
+        <v>313.5</v>
       </c>
       <c r="L38" t="n">
-        <v>174.67</v>
+        <v>175.2</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.288</v>
+        <v>-0.703</v>
       </c>
       <c r="N38" t="n">
-        <v>1187</v>
+        <v>-1271</v>
       </c>
       <c r="O38" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="P38" t="n">
-        <v>36789</v>
+        <v>-57188</v>
       </c>
       <c r="Q38" t="n">
-        <v>3306</v>
+        <v>2829</v>
       </c>
       <c r="R38" t="n">
-        <v>40095</v>
+        <v>-54359</v>
       </c>
     </row>
     <row r="39">
@@ -2344,53 +2338,53 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="F39" t="n">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="G39" t="n">
-        <v>6.86</v>
+        <v>3.14</v>
       </c>
       <c r="H39" t="n">
-        <v>4.11</v>
+        <v>2.76</v>
       </c>
       <c r="I39" t="n">
-        <v>11.14</v>
+        <v>8.68</v>
       </c>
       <c r="J39" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="K39" t="n">
-        <v>533.86</v>
+        <v>247.7</v>
       </c>
       <c r="L39" t="n">
-        <v>403.59</v>
+        <v>174.67</v>
       </c>
       <c r="M39" t="n">
-        <v>1.375</v>
+        <v>-0.288</v>
       </c>
       <c r="N39" t="n">
-        <v>8720</v>
+        <v>1187</v>
       </c>
       <c r="O39" t="n">
-        <v>3.53</v>
+        <v>1.3</v>
       </c>
       <c r="P39" t="n">
-        <v>52321</v>
+        <v>36789</v>
       </c>
       <c r="Q39" t="n">
-        <v>523</v>
+        <v>3306</v>
       </c>
       <c r="R39" t="n">
-        <v>52844</v>
+        <v>40095</v>
       </c>
     </row>
     <row r="40">
@@ -2406,53 +2400,53 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F40" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="G40" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="H40" t="n">
-        <v>1.26</v>
+        <v>4.11</v>
       </c>
       <c r="I40" t="n">
-        <v>7.95</v>
+        <v>11.14</v>
       </c>
       <c r="J40" t="n">
-        <v>2.19</v>
+        <v>9.65</v>
       </c>
       <c r="K40" t="n">
-        <v>800.2</v>
+        <v>533.86</v>
       </c>
       <c r="L40" t="n">
-        <v>60.03</v>
+        <v>403.59</v>
       </c>
       <c r="M40" t="n">
-        <v>2.446</v>
+        <v>1.375</v>
       </c>
       <c r="N40" t="n">
-        <v>5075</v>
+        <v>8720</v>
       </c>
       <c r="O40" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P40" t="n">
-        <v>45679</v>
+        <v>52321</v>
       </c>
       <c r="Q40" t="n">
-        <v>661</v>
+        <v>523</v>
       </c>
       <c r="R40" t="n">
-        <v>46340</v>
+        <v>52844</v>
       </c>
     </row>
     <row r="41">
@@ -2468,53 +2462,53 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F41" t="n">
-        <v>1.14</v>
+        <v>4.39</v>
       </c>
       <c r="G41" t="n">
-        <v>6.04</v>
+        <v>7.08</v>
       </c>
       <c r="H41" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I41" t="n">
-        <v>13.51</v>
+        <v>7.95</v>
       </c>
       <c r="J41" t="n">
-        <v>4.74</v>
+        <v>2.19</v>
       </c>
       <c r="K41" t="n">
-        <v>2281.51</v>
+        <v>800.2</v>
       </c>
       <c r="L41" t="n">
-        <v>27.54</v>
+        <v>60.03</v>
       </c>
       <c r="M41" t="n">
-        <v>1.758</v>
+        <v>2.446</v>
       </c>
       <c r="N41" t="n">
-        <v>851</v>
+        <v>5075</v>
       </c>
       <c r="O41" t="n">
-        <v>1.14</v>
+        <v>3.51</v>
       </c>
       <c r="P41" t="n">
-        <v>13616</v>
+        <v>45679</v>
       </c>
       <c r="Q41" t="n">
-        <v>1561</v>
+        <v>661</v>
       </c>
       <c r="R41" t="n">
-        <v>15177</v>
+        <v>46340</v>
       </c>
     </row>
     <row r="42">
@@ -2530,633 +2524,639 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>16</v>
+      </c>
+      <c r="E42" t="n">
+        <v>50</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I42" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L42" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N42" t="n">
+        <v>851</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P42" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R42" t="n">
+        <v>15177</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D43" t="n">
         <v>4</v>
       </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="n">
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
         <v>0.71</v>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
         <v>0.97</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
         <v>40.94</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M43" t="n">
         <v>-0.711</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N43" t="n">
         <v>-19138</v>
       </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
         <v>-76552</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q43" t="n">
         <v>3052</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R43" t="n">
         <v>-73500</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D44" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E44" s="2" t="n">
         <v>40.6</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F44" s="2" t="n">
         <v>1.53</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H44" s="2" t="n">
         <v>2.77</v>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="I44" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J43" s="2" t="n">
+      <c r="J44" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K44" s="2" t="n">
         <v>600.88</v>
       </c>
-      <c r="L43" s="2" t="n">
+      <c r="L44" s="2" t="n">
         <v>157.85</v>
       </c>
-      <c r="M43" s="2" t="n">
+      <c r="M44" s="2" t="n">
         <v>0.162</v>
       </c>
-      <c r="N43" s="2" t="n">
+      <c r="N44" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="O43" s="2" t="n">
+      <c r="O44" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="P43" s="2" t="n">
+      <c r="P44" s="2" t="n">
         <v>28345</v>
       </c>
-      <c r="Q43" s="2" t="n">
+      <c r="Q44" s="2" t="n">
         <v>13462</v>
       </c>
-      <c r="R43" s="2" t="n">
+      <c r="R44" s="2" t="n">
         <v>41807</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D46" t="n">
         <v>3</v>
       </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="n">
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="n">
         <v>0.34</v>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="n">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
         <v>0.49</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="n">
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="n">
         <v>13.35</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M46" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N46" t="n">
         <v>-4880</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q46" t="n">
         <v>1291</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R46" t="n">
         <v>-13350</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="n">
+      <c r="E47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="n">
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M46" s="2" t="n">
+      <c r="M47" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N46" s="2" t="n">
+      <c r="N47" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2" t="n">
+      <c r="O47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q46" s="2" t="n">
+      <c r="Q47" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R46" s="2" t="n">
+      <c r="R47" s="2" t="n">
         <v>-13350</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D49" t="n">
         <v>10</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
         <v>0.91</v>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="n">
         <v>2.28</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="n">
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="n">
         <v>29.99</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M49" t="n">
         <v>-0.912</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N49" t="n">
         <v>-13839</v>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
         <v>-138394</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q49" t="n">
         <v>4519</v>
       </c>
-      <c r="R48" t="n">
+      <c r="R49" t="n">
         <v>-133875</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D50" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="n">
+      <c r="E50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="n">
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="n">
         <v>29.99</v>
       </c>
-      <c r="M49" s="2" t="n">
+      <c r="M50" s="2" t="n">
         <v>-0.912</v>
       </c>
-      <c r="N49" s="2" t="n">
+      <c r="N50" s="2" t="n">
         <v>-13839</v>
       </c>
-      <c r="O49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2" t="n">
+      <c r="O50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="n">
         <v>-138394</v>
       </c>
-      <c r="Q49" s="2" t="n">
+      <c r="Q50" s="2" t="n">
         <v>4519</v>
       </c>
-      <c r="R49" s="2" t="n">
+      <c r="R50" s="2" t="n">
         <v>-133875</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D52" t="n">
         <v>9</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E52" t="n">
         <v>11.1</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F52" t="n">
         <v>1.75</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G52" t="n">
         <v>0.84</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H52" t="n">
         <v>0.5</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I52" t="n">
         <v>0.84</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J52" t="n">
         <v>1.15</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K52" t="n">
         <v>3.2</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L52" t="n">
         <v>25.93</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M52" t="n">
         <v>-0.348</v>
       </c>
-      <c r="N51" t="n">
+      <c r="N52" t="n">
         <v>-5363</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O52" t="n">
         <v>0.22</v>
       </c>
-      <c r="P51" t="n">
+      <c r="P52" t="n">
         <v>-48269</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q52" t="n">
         <v>4169</v>
       </c>
-      <c r="R51" t="n">
+      <c r="R52" t="n">
         <v>-44100</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D53" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E53" s="2" t="n">
         <v>11.1</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F53" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="H53" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I53" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="J52" s="2" t="n">
+      <c r="J53" s="2" t="n">
         <v>1.15</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="K53" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="L52" s="2" t="n">
+      <c r="L53" s="2" t="n">
         <v>25.93</v>
       </c>
-      <c r="M52" s="2" t="n">
+      <c r="M53" s="2" t="n">
         <v>-0.348</v>
       </c>
-      <c r="N52" s="2" t="n">
+      <c r="N53" s="2" t="n">
         <v>-5363</v>
       </c>
-      <c r="O52" s="2" t="n">
+      <c r="O53" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="P52" s="2" t="n">
+      <c r="P53" s="2" t="n">
         <v>-48269</v>
       </c>
-      <c r="Q52" s="2" t="n">
+      <c r="Q53" s="2" t="n">
         <v>4169</v>
       </c>
-      <c r="R52" s="2" t="n">
+      <c r="R53" s="2" t="n">
         <v>-44100</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>5minHL</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="D55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>5minHL2</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="D57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>5minHL_동시</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M60" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>26</v>
-      </c>
-      <c r="R60" t="n">
-        <v>-2400</v>
+      <c r="D59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3172,53 +3172,47 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1.92</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I61" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K61" t="n">
-        <v>2003.43</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>2987.95</v>
+        <v>49.85</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.292</v>
+        <v>-2.747</v>
       </c>
       <c r="N61" t="n">
-        <v>2155</v>
+        <v>-2426</v>
       </c>
       <c r="O61" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>25859</v>
+        <v>-2426</v>
       </c>
       <c r="Q61" t="n">
-        <v>1141</v>
+        <v>26</v>
       </c>
       <c r="R61" t="n">
-        <v>27000</v>
+        <v>-2400</v>
       </c>
     </row>
     <row r="62">
@@ -3234,53 +3228,53 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E62" t="n">
         <v>33.3</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01</v>
+        <v>4.65</v>
       </c>
       <c r="G62" t="n">
-        <v>0.08</v>
+        <v>1.92</v>
       </c>
       <c r="H62" t="n">
-        <v>3.13</v>
+        <v>1.4</v>
       </c>
       <c r="I62" t="n">
-        <v>0.08</v>
+        <v>4.6</v>
       </c>
       <c r="J62" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="K62" t="n">
-        <v>4319.93</v>
+        <v>2003.43</v>
       </c>
       <c r="L62" t="n">
-        <v>1351.81</v>
+        <v>2987.95</v>
       </c>
       <c r="M62" t="n">
-        <v>-2.059</v>
+        <v>-0.292</v>
       </c>
       <c r="N62" t="n">
-        <v>-3794</v>
+        <v>2155</v>
       </c>
       <c r="O62" t="n">
-        <v>0.01</v>
+        <v>2.33</v>
       </c>
       <c r="P62" t="n">
-        <v>-11383</v>
+        <v>25859</v>
       </c>
       <c r="Q62" t="n">
-        <v>153</v>
+        <v>1141</v>
       </c>
       <c r="R62" t="n">
-        <v>-11230</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="63">
@@ -3296,43 +3290,53 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>100</v>
-      </c>
-      <c r="F63" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G63" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.13</v>
+      </c>
       <c r="I63" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J63" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3.61</v>
+      </c>
       <c r="K63" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
+        <v>4319.93</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1351.81</v>
+      </c>
       <c r="M63" t="n">
-        <v>1.678</v>
+        <v>-2.059</v>
       </c>
       <c r="N63" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O63" t="inlineStr"/>
+        <v>-3794</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.01</v>
+      </c>
       <c r="P63" t="n">
-        <v>1670</v>
+        <v>-11383</v>
       </c>
       <c r="Q63" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="R63" t="n">
-        <v>1700</v>
+        <v>-11230</v>
       </c>
     </row>
     <row r="64">
@@ -3348,906 +3352,958 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>100</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>30</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D65" t="n">
         <v>24</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E65" t="n">
         <v>12.5</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F65" t="n">
         <v>1.08</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G65" t="n">
         <v>1.37</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H65" t="n">
         <v>0.88</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I65" t="n">
         <v>2.51</v>
       </c>
-      <c r="J64" t="n">
+      <c r="J65" t="n">
         <v>7.52</v>
       </c>
-      <c r="K64" t="n">
+      <c r="K65" t="n">
         <v>24201.59</v>
       </c>
-      <c r="L64" t="n">
+      <c r="L65" t="n">
         <v>27253.11</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M65" t="n">
         <v>-0.595</v>
       </c>
-      <c r="N64" t="n">
+      <c r="N65" t="n">
         <v>-816</v>
       </c>
-      <c r="O64" t="n">
+      <c r="O65" t="n">
         <v>0.15</v>
       </c>
-      <c r="P64" t="n">
+      <c r="P65" t="n">
         <v>-19595</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="Q65" t="n">
         <v>1690</v>
       </c>
-      <c r="R64" t="n">
+      <c r="R65" t="n">
         <v>-17905</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D66" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E66" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F66" s="2" t="n">
         <v>3.19</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>1.51</v>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="H66" s="2" t="n">
         <v>1.21</v>
       </c>
-      <c r="I65" s="2" t="n">
+      <c r="I66" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="J65" s="2" t="n">
+      <c r="J66" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="K65" s="2" t="n">
+      <c r="K66" s="2" t="n">
         <v>9438.73</v>
       </c>
-      <c r="L65" s="2" t="n">
+      <c r="L66" s="2" t="n">
         <v>18717.88</v>
       </c>
-      <c r="M65" s="2" t="n">
+      <c r="M66" s="2" t="n">
         <v>-0.611</v>
       </c>
-      <c r="N65" s="2" t="n">
+      <c r="N66" s="2" t="n">
         <v>-143</v>
       </c>
-      <c r="O65" s="2" t="n">
+      <c r="O66" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="P65" s="2" t="n">
+      <c r="P66" s="2" t="n">
         <v>-5876</v>
       </c>
-      <c r="Q65" s="2" t="n">
+      <c r="Q66" s="2" t="n">
         <v>3041</v>
       </c>
-      <c r="R65" s="2" t="n">
+      <c r="R66" s="2" t="n">
         <v>-2835</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr"/>
-      <c r="O67" s="2" t="inlineStr"/>
-      <c r="P67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="D68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr"/>
-      <c r="O69" s="2" t="inlineStr"/>
-      <c r="P69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="D70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr"/>
-      <c r="P71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="D72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP1</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr"/>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="D74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP2</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr"/>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="D76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>KR_TR_JEO2</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr"/>
-      <c r="O77" s="2" t="inlineStr"/>
-      <c r="P77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="D78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>KR_TR_MA</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr"/>
-      <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="D80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>미국VCP</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr"/>
-      <c r="O81" s="2" t="inlineStr"/>
-      <c r="P81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="D82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
-      <c r="N83" s="2" t="inlineStr"/>
-      <c r="O83" s="2" t="inlineStr"/>
-      <c r="P83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="D84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr"/>
-      <c r="O85" s="2" t="inlineStr"/>
-      <c r="P85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="D86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr"/>
-      <c r="N87" s="2" t="inlineStr"/>
-      <c r="O87" s="2" t="inlineStr"/>
-      <c r="P87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="D88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
-      <c r="N89" s="2" t="inlineStr"/>
-      <c r="O89" s="2" t="inlineStr"/>
-      <c r="P89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="D90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D92" t="n">
         <v>1</v>
       </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="n">
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="n">
         <v>6.8</v>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="n">
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="n">
         <v>6.8</v>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="n">
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="n">
         <v>5</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M92" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N92" t="n">
         <v>-9939</v>
       </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
         <v>-9939</v>
       </c>
-      <c r="Q91" t="n">
+      <c r="Q92" t="n">
         <v>198</v>
       </c>
-      <c r="R91" t="n">
+      <c r="R92" t="n">
         <v>-9741</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D93" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="n">
+      <c r="E93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="n">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="n">
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M92" s="2" t="n">
+      <c r="M93" s="2" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N92" s="2" t="n">
+      <c r="N93" s="2" t="n">
         <v>-9939</v>
       </c>
-      <c r="O92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" s="2" t="n">
+      <c r="O93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="2" t="n">
         <v>-9939</v>
       </c>
-      <c r="Q92" s="2" t="n">
+      <c r="Q93" s="2" t="n">
         <v>198</v>
       </c>
-      <c r="R92" s="2" t="n">
+      <c r="R93" s="2" t="n">
         <v>-9741</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr"/>
-      <c r="O94" s="2" t="inlineStr"/>
-      <c r="P94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="D95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr"/>
-      <c r="P96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="D99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
-      <c r="P100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="D101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="2" t="n">
+      <c r="D103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R103"/>
+  <dimension ref="A1:R104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -858,7 +858,7 @@
         <v>58.3</v>
       </c>
       <c r="F7" t="n">
-        <v>8.09</v>
+        <v>8.1</v>
       </c>
       <c r="G7" t="n">
         <v>7.98</v>
@@ -878,19 +878,19 @@
         <v>3.19</v>
       </c>
       <c r="N7" t="n">
-        <v>31601</v>
+        <v>31606</v>
       </c>
       <c r="O7" t="n">
-        <v>11.32</v>
+        <v>11.34</v>
       </c>
       <c r="P7" t="n">
-        <v>379217</v>
+        <v>379274</v>
       </c>
       <c r="Q7" t="n">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="R7" t="n">
-        <v>381386</v>
+        <v>381441</v>
       </c>
     </row>
     <row r="8">
@@ -936,19 +936,19 @@
         <v>1.549</v>
       </c>
       <c r="N8" t="n">
-        <v>3278</v>
+        <v>3288</v>
       </c>
       <c r="O8" t="n">
         <v>1.7</v>
       </c>
       <c r="P8" t="n">
-        <v>65570</v>
+        <v>65757</v>
       </c>
       <c r="Q8" t="n">
-        <v>7207</v>
+        <v>7187</v>
       </c>
       <c r="R8" t="n">
-        <v>72777</v>
+        <v>72944</v>
       </c>
     </row>
     <row r="9">
@@ -1000,13 +1000,13 @@
         <v>0.9</v>
       </c>
       <c r="P9" t="n">
-        <v>-17465</v>
+        <v>-17448</v>
       </c>
       <c r="Q9" t="n">
-        <v>8324</v>
+        <v>8314</v>
       </c>
       <c r="R9" t="n">
-        <v>-9141</v>
+        <v>-9135</v>
       </c>
     </row>
     <row r="10">
@@ -1052,19 +1052,19 @@
         <v>-0.448</v>
       </c>
       <c r="N10" t="n">
-        <v>-7902</v>
+        <v>-7907</v>
       </c>
       <c r="O10" t="n">
         <v>0.21</v>
       </c>
       <c r="P10" t="n">
-        <v>-229146</v>
+        <v>-229317</v>
       </c>
       <c r="Q10" t="n">
-        <v>17301</v>
+        <v>17286</v>
       </c>
       <c r="R10" t="n">
-        <v>-211845</v>
+        <v>-212031</v>
       </c>
     </row>
     <row r="11">
@@ -1084,41 +1084,45 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>1.94</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.69</v>
+      </c>
       <c r="H11" t="n">
         <v>2.62</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>12.69</v>
+      </c>
       <c r="J11" t="n">
         <v>6.8</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>-2.623</v>
+        <v>1.204</v>
       </c>
       <c r="N11" t="n">
-        <v>-14942</v>
+        <v>-3935</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="P11" t="n">
-        <v>-44826</v>
+        <v>-15741</v>
       </c>
       <c r="Q11" t="n">
-        <v>11058</v>
+        <v>11092</v>
       </c>
       <c r="R11" t="n">
-        <v>-33768</v>
+        <v>-4649</v>
       </c>
     </row>
     <row r="12">
@@ -1138,16 +1142,16 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4.22</v>
+        <v>4.31</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>2.3</v>
@@ -1161,22 +1165,22 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="n">
-        <v>-0.038</v>
+        <v>0.008</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>28876</v>
+        <v>58050</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>64209</v>
+        <v>64195</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>93084</v>
+        <v>122245</v>
       </c>
     </row>
     <row r="14">
@@ -1796,121 +1800,117 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>100</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>12.685</v>
+      </c>
+      <c r="N28" t="n">
+        <v>28927</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>28927</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>73</v>
+      </c>
+      <c r="R28" t="n">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H28" s="2" t="n">
+      <c r="D29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H29" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J28" s="2" t="n">
+      <c r="I29" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J29" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" s="2" t="n">
+      <c r="K29" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L29" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="M28" s="2" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O28" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R28" s="2" t="n">
-        <v>-4553</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-8039</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>-16078</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>514</v>
-      </c>
-      <c r="R30" t="n">
-        <v>-15563</v>
+      <c r="M29" s="2" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>2224</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>22236</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>2211</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>24447</v>
       </c>
     </row>
     <row r="31">
@@ -1926,53 +1926,47 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1.37</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K31" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>5.67</v>
-      </c>
       <c r="M31" t="n">
-        <v>-0.217</v>
+        <v>-2.607</v>
       </c>
       <c r="N31" t="n">
-        <v>-13319</v>
+        <v>-8011</v>
       </c>
       <c r="O31" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-53277</v>
+        <v>-16021</v>
       </c>
       <c r="Q31" t="n">
-        <v>5934</v>
+        <v>513</v>
       </c>
       <c r="R31" t="n">
-        <v>-47343</v>
+        <v>-15508</v>
       </c>
     </row>
     <row r="32">
@@ -1988,47 +1982,53 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H32" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
       <c r="L32" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.136</v>
+        <v>-0.217</v>
       </c>
       <c r="N32" t="n">
-        <v>-2397</v>
+        <v>-13272</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P32" t="n">
-        <v>-4794</v>
+        <v>-53089</v>
       </c>
       <c r="Q32" t="n">
-        <v>2934</v>
+        <v>5913</v>
       </c>
       <c r="R32" t="n">
-        <v>-1860</v>
+        <v>-47176</v>
       </c>
     </row>
     <row r="33">
@@ -2044,43 +2044,47 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>100</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>14</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M33" t="n">
-        <v>1.042</v>
+        <v>-0.136</v>
       </c>
       <c r="N33" t="n">
-        <v>16237</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
+        <v>-2389</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
       <c r="P33" t="n">
-        <v>48711</v>
+        <v>-4777</v>
       </c>
       <c r="Q33" t="n">
-        <v>4269</v>
+        <v>2924</v>
       </c>
       <c r="R33" t="n">
-        <v>52980</v>
+        <v>-1854</v>
       </c>
     </row>
     <row r="34">
@@ -2096,171 +2100,161 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>100</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>14</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N34" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R34" t="n">
+        <v>52794</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D35" t="n">
         <v>2</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="n">
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
         <v>0.53</v>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
         <v>1.01</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
         <v>4.5</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M35" t="n">
         <v>-0.534</v>
       </c>
-      <c r="N34" t="n">
-        <v>-17443</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>-34887</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>10861</v>
-      </c>
-      <c r="R34" t="n">
-        <v>-24026</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="N35" t="n">
+        <v>-17382</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-34764</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>10822</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-23942</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D36" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E36" s="2" t="n">
         <v>30.8</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F36" s="2" t="n">
         <v>1.02</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J36" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K36" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L35" s="2" t="n">
+      <c r="L36" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="M35" s="2" t="n">
+      <c r="M36" s="2" t="n">
         <v>-0.33</v>
       </c>
-      <c r="N35" s="2" t="n">
-        <v>-4640</v>
-      </c>
-      <c r="O35" s="2" t="n">
+      <c r="N36" s="2" t="n">
+        <v>-4624</v>
+      </c>
+      <c r="O36" s="2" t="n">
         <v>0.45</v>
       </c>
-      <c r="P35" s="2" t="n">
-        <v>-60324</v>
-      </c>
-      <c r="Q35" s="2" t="n">
-        <v>24512</v>
-      </c>
-      <c r="R35" s="2" t="n">
-        <v>-35812</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>27</v>
-      </c>
-      <c r="E37" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G37" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I37" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J37" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L37" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N37" t="n">
-        <v>507</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P37" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R37" t="n">
-        <v>15210</v>
+      <c r="P36" s="2" t="n">
+        <v>-60112</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>24426</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>-35686</v>
       </c>
     </row>
     <row r="38">
@@ -2276,53 +2270,53 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E38" t="n">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="F38" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="G38" t="n">
-        <v>3.01</v>
+        <v>5.47</v>
       </c>
       <c r="H38" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="I38" t="n">
-        <v>13.15</v>
+        <v>17.35</v>
       </c>
       <c r="J38" t="n">
-        <v>5.82</v>
+        <v>20.1</v>
       </c>
       <c r="K38" t="n">
-        <v>313.5</v>
+        <v>185.95</v>
       </c>
       <c r="L38" t="n">
-        <v>175.2</v>
+        <v>187.46</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.703</v>
+        <v>0.274</v>
       </c>
       <c r="N38" t="n">
-        <v>-1271</v>
+        <v>507</v>
       </c>
       <c r="O38" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="P38" t="n">
-        <v>-57188</v>
+        <v>13680</v>
       </c>
       <c r="Q38" t="n">
-        <v>2829</v>
+        <v>1530</v>
       </c>
       <c r="R38" t="n">
-        <v>-54359</v>
+        <v>15210</v>
       </c>
     </row>
     <row r="39">
@@ -2338,53 +2332,53 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E39" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="F39" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="G39" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="H39" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I39" t="n">
-        <v>8.68</v>
+        <v>13.15</v>
       </c>
       <c r="J39" t="n">
-        <v>9.01</v>
+        <v>5.82</v>
       </c>
       <c r="K39" t="n">
-        <v>247.7</v>
+        <v>313.5</v>
       </c>
       <c r="L39" t="n">
-        <v>174.67</v>
+        <v>175.2</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.288</v>
+        <v>-0.703</v>
       </c>
       <c r="N39" t="n">
-        <v>1187</v>
+        <v>-1271</v>
       </c>
       <c r="O39" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="P39" t="n">
-        <v>36789</v>
+        <v>-57188</v>
       </c>
       <c r="Q39" t="n">
-        <v>3306</v>
+        <v>2829</v>
       </c>
       <c r="R39" t="n">
-        <v>40095</v>
+        <v>-54359</v>
       </c>
     </row>
     <row r="40">
@@ -2400,53 +2394,53 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E40" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="F40" t="n">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="G40" t="n">
-        <v>6.86</v>
+        <v>3.14</v>
       </c>
       <c r="H40" t="n">
-        <v>4.11</v>
+        <v>2.76</v>
       </c>
       <c r="I40" t="n">
-        <v>11.14</v>
+        <v>8.68</v>
       </c>
       <c r="J40" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="K40" t="n">
-        <v>533.86</v>
+        <v>247.7</v>
       </c>
       <c r="L40" t="n">
-        <v>403.59</v>
+        <v>174.67</v>
       </c>
       <c r="M40" t="n">
-        <v>1.375</v>
+        <v>-0.288</v>
       </c>
       <c r="N40" t="n">
-        <v>8720</v>
+        <v>1187</v>
       </c>
       <c r="O40" t="n">
-        <v>3.53</v>
+        <v>1.3</v>
       </c>
       <c r="P40" t="n">
-        <v>52321</v>
+        <v>36789</v>
       </c>
       <c r="Q40" t="n">
-        <v>523</v>
+        <v>3306</v>
       </c>
       <c r="R40" t="n">
-        <v>52844</v>
+        <v>40095</v>
       </c>
     </row>
     <row r="41">
@@ -2462,53 +2456,53 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F41" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="G41" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="H41" t="n">
-        <v>1.26</v>
+        <v>4.11</v>
       </c>
       <c r="I41" t="n">
-        <v>7.95</v>
+        <v>11.14</v>
       </c>
       <c r="J41" t="n">
-        <v>2.19</v>
+        <v>9.65</v>
       </c>
       <c r="K41" t="n">
-        <v>800.2</v>
+        <v>533.86</v>
       </c>
       <c r="L41" t="n">
-        <v>60.03</v>
+        <v>403.59</v>
       </c>
       <c r="M41" t="n">
-        <v>2.446</v>
+        <v>1.375</v>
       </c>
       <c r="N41" t="n">
-        <v>5075</v>
+        <v>8720</v>
       </c>
       <c r="O41" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P41" t="n">
-        <v>45679</v>
+        <v>52321</v>
       </c>
       <c r="Q41" t="n">
-        <v>661</v>
+        <v>523</v>
       </c>
       <c r="R41" t="n">
-        <v>46340</v>
+        <v>52844</v>
       </c>
     </row>
     <row r="42">
@@ -2524,53 +2518,53 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E42" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F42" t="n">
-        <v>1.14</v>
+        <v>4.39</v>
       </c>
       <c r="G42" t="n">
-        <v>6.04</v>
+        <v>7.08</v>
       </c>
       <c r="H42" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I42" t="n">
-        <v>13.51</v>
+        <v>7.95</v>
       </c>
       <c r="J42" t="n">
-        <v>4.74</v>
+        <v>2.19</v>
       </c>
       <c r="K42" t="n">
-        <v>2281.51</v>
+        <v>800.2</v>
       </c>
       <c r="L42" t="n">
-        <v>27.54</v>
+        <v>60.03</v>
       </c>
       <c r="M42" t="n">
-        <v>1.758</v>
+        <v>2.446</v>
       </c>
       <c r="N42" t="n">
-        <v>851</v>
+        <v>5075</v>
       </c>
       <c r="O42" t="n">
-        <v>1.14</v>
+        <v>3.51</v>
       </c>
       <c r="P42" t="n">
-        <v>13616</v>
+        <v>45679</v>
       </c>
       <c r="Q42" t="n">
-        <v>1561</v>
+        <v>661</v>
       </c>
       <c r="R42" t="n">
-        <v>15177</v>
+        <v>46340</v>
       </c>
     </row>
     <row r="43">
@@ -2586,633 +2580,639 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>16</v>
+      </c>
+      <c r="E43" t="n">
+        <v>50</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I43" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L43" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N43" t="n">
+        <v>851</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P43" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R43" t="n">
+        <v>15177</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D44" t="n">
         <v>4</v>
       </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="n">
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="n">
         <v>0.71</v>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
         <v>0.97</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="n">
         <v>40.94</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M44" t="n">
         <v>-0.711</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N44" t="n">
         <v>-19138</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>-76552</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q44" t="n">
         <v>3052</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R44" t="n">
         <v>-73500</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D45" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E45" s="2" t="n">
         <v>40.6</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F45" s="2" t="n">
         <v>1.53</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>2.77</v>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="I45" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="J45" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K45" s="2" t="n">
         <v>600.88</v>
       </c>
-      <c r="L44" s="2" t="n">
+      <c r="L45" s="2" t="n">
         <v>157.85</v>
       </c>
-      <c r="M44" s="2" t="n">
+      <c r="M45" s="2" t="n">
         <v>0.162</v>
       </c>
-      <c r="N44" s="2" t="n">
+      <c r="N45" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="O44" s="2" t="n">
+      <c r="O45" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="P44" s="2" t="n">
+      <c r="P45" s="2" t="n">
         <v>28345</v>
       </c>
-      <c r="Q44" s="2" t="n">
+      <c r="Q45" s="2" t="n">
         <v>13462</v>
       </c>
-      <c r="R44" s="2" t="n">
+      <c r="R45" s="2" t="n">
         <v>41807</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D47" t="n">
         <v>3</v>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="n">
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
         <v>0.34</v>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="n">
         <v>0.49</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="n">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="n">
         <v>13.35</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M47" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N46" t="n">
+      <c r="N47" t="n">
         <v>-4880</v>
       </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q47" t="n">
         <v>1291</v>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>-13350</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="n">
+      <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="n">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="n">
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M47" s="2" t="n">
+      <c r="M48" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N47" s="2" t="n">
+      <c r="N48" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="2" t="n">
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q47" s="2" t="n">
+      <c r="Q48" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R47" s="2" t="n">
+      <c r="R48" s="2" t="n">
         <v>-13350</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D50" t="n">
         <v>10</v>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="n">
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
         <v>0.91</v>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
         <v>2.28</v>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="n">
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="n">
         <v>29.99</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M50" t="n">
         <v>-0.912</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N50" t="n">
         <v>-13839</v>
       </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
         <v>-138394</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q50" t="n">
         <v>4519</v>
       </c>
-      <c r="R49" t="n">
+      <c r="R50" t="n">
         <v>-133875</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D51" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="n">
+      <c r="E51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="n">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="n">
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="n">
         <v>29.99</v>
       </c>
-      <c r="M50" s="2" t="n">
+      <c r="M51" s="2" t="n">
         <v>-0.912</v>
       </c>
-      <c r="N50" s="2" t="n">
+      <c r="N51" s="2" t="n">
         <v>-13839</v>
       </c>
-      <c r="O50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2" t="n">
+      <c r="O51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="n">
         <v>-138394</v>
       </c>
-      <c r="Q50" s="2" t="n">
+      <c r="Q51" s="2" t="n">
         <v>4519</v>
       </c>
-      <c r="R50" s="2" t="n">
+      <c r="R51" s="2" t="n">
         <v>-133875</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D53" t="n">
         <v>9</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E53" t="n">
         <v>11.1</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F53" t="n">
         <v>1.75</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G53" t="n">
         <v>0.84</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H53" t="n">
         <v>0.5</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I53" t="n">
         <v>0.84</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J53" t="n">
         <v>1.15</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K53" t="n">
         <v>3.2</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L53" t="n">
         <v>25.93</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M53" t="n">
         <v>-0.348</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N53" t="n">
         <v>-5363</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O53" t="n">
         <v>0.22</v>
       </c>
-      <c r="P52" t="n">
+      <c r="P53" t="n">
         <v>-48269</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="Q53" t="n">
         <v>4169</v>
       </c>
-      <c r="R52" t="n">
+      <c r="R53" t="n">
         <v>-44100</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D54" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E54" s="2" t="n">
         <v>11.1</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F54" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H54" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="I54" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="J53" s="2" t="n">
+      <c r="J54" s="2" t="n">
         <v>1.15</v>
       </c>
-      <c r="K53" s="2" t="n">
+      <c r="K54" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="L53" s="2" t="n">
+      <c r="L54" s="2" t="n">
         <v>25.93</v>
       </c>
-      <c r="M53" s="2" t="n">
+      <c r="M54" s="2" t="n">
         <v>-0.348</v>
       </c>
-      <c r="N53" s="2" t="n">
+      <c r="N54" s="2" t="n">
         <v>-5363</v>
       </c>
-      <c r="O53" s="2" t="n">
+      <c r="O54" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="P53" s="2" t="n">
+      <c r="P54" s="2" t="n">
         <v>-48269</v>
       </c>
-      <c r="Q53" s="2" t="n">
+      <c r="Q54" s="2" t="n">
         <v>4169</v>
       </c>
-      <c r="R53" s="2" t="n">
+      <c r="R54" s="2" t="n">
         <v>-44100</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>5minHL</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr"/>
-      <c r="O55" s="2" t="inlineStr"/>
-      <c r="P55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="D56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>5minHL2</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
-      <c r="O57" s="2" t="inlineStr"/>
-      <c r="P57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="D58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>5minHL_동시</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
-      <c r="O59" s="2" t="inlineStr"/>
-      <c r="P59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M61" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N61" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>26</v>
-      </c>
-      <c r="R61" t="n">
-        <v>-2400</v>
+      <c r="D60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3228,53 +3228,47 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1.92</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I62" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2003.43</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>2987.95</v>
+        <v>49.85</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.292</v>
+        <v>-2.747</v>
       </c>
       <c r="N62" t="n">
-        <v>2155</v>
+        <v>-2426</v>
       </c>
       <c r="O62" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>25859</v>
+        <v>-2426</v>
       </c>
       <c r="Q62" t="n">
-        <v>1141</v>
+        <v>26</v>
       </c>
       <c r="R62" t="n">
-        <v>27000</v>
+        <v>-2400</v>
       </c>
     </row>
     <row r="63">
@@ -3290,53 +3284,53 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E63" t="n">
         <v>33.3</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01</v>
+        <v>4.65</v>
       </c>
       <c r="G63" t="n">
-        <v>0.08</v>
+        <v>1.92</v>
       </c>
       <c r="H63" t="n">
-        <v>3.13</v>
+        <v>1.4</v>
       </c>
       <c r="I63" t="n">
-        <v>0.08</v>
+        <v>4.6</v>
       </c>
       <c r="J63" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="K63" t="n">
-        <v>4319.93</v>
+        <v>2003.43</v>
       </c>
       <c r="L63" t="n">
-        <v>1351.81</v>
+        <v>2987.95</v>
       </c>
       <c r="M63" t="n">
-        <v>-2.059</v>
+        <v>-0.292</v>
       </c>
       <c r="N63" t="n">
-        <v>-3794</v>
+        <v>2155</v>
       </c>
       <c r="O63" t="n">
-        <v>0.01</v>
+        <v>2.33</v>
       </c>
       <c r="P63" t="n">
-        <v>-11383</v>
+        <v>25859</v>
       </c>
       <c r="Q63" t="n">
-        <v>153</v>
+        <v>1141</v>
       </c>
       <c r="R63" t="n">
-        <v>-11230</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="64">
@@ -3352,43 +3346,53 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>100</v>
-      </c>
-      <c r="F64" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G64" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3.13</v>
+      </c>
       <c r="I64" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3.61</v>
+      </c>
       <c r="K64" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
+        <v>4319.93</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1351.81</v>
+      </c>
       <c r="M64" t="n">
-        <v>1.678</v>
+        <v>-2.059</v>
       </c>
       <c r="N64" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O64" t="inlineStr"/>
+        <v>-3794</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.01</v>
+      </c>
       <c r="P64" t="n">
-        <v>1670</v>
+        <v>-11383</v>
       </c>
       <c r="Q64" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="R64" t="n">
-        <v>1700</v>
+        <v>-11230</v>
       </c>
     </row>
     <row r="65">
@@ -3404,906 +3408,958 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>100</v>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>30</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D66" t="n">
         <v>24</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E66" t="n">
         <v>12.5</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F66" t="n">
         <v>1.08</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G66" t="n">
         <v>1.37</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H66" t="n">
         <v>0.88</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I66" t="n">
         <v>2.51</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J66" t="n">
         <v>7.52</v>
       </c>
-      <c r="K65" t="n">
+      <c r="K66" t="n">
         <v>24201.59</v>
       </c>
-      <c r="L65" t="n">
+      <c r="L66" t="n">
         <v>27253.11</v>
       </c>
-      <c r="M65" t="n">
+      <c r="M66" t="n">
         <v>-0.595</v>
       </c>
-      <c r="N65" t="n">
+      <c r="N66" t="n">
         <v>-816</v>
       </c>
-      <c r="O65" t="n">
+      <c r="O66" t="n">
         <v>0.15</v>
       </c>
-      <c r="P65" t="n">
+      <c r="P66" t="n">
         <v>-19595</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="Q66" t="n">
         <v>1690</v>
       </c>
-      <c r="R65" t="n">
+      <c r="R66" t="n">
         <v>-17905</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D67" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E67" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F67" s="2" t="n">
         <v>3.19</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>1.51</v>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="H67" s="2" t="n">
         <v>1.21</v>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="I67" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="J66" s="2" t="n">
+      <c r="J67" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="K66" s="2" t="n">
+      <c r="K67" s="2" t="n">
         <v>9438.73</v>
       </c>
-      <c r="L66" s="2" t="n">
+      <c r="L67" s="2" t="n">
         <v>18717.88</v>
       </c>
-      <c r="M66" s="2" t="n">
+      <c r="M67" s="2" t="n">
         <v>-0.611</v>
       </c>
-      <c r="N66" s="2" t="n">
+      <c r="N67" s="2" t="n">
         <v>-143</v>
       </c>
-      <c r="O66" s="2" t="n">
+      <c r="O67" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="P66" s="2" t="n">
+      <c r="P67" s="2" t="n">
         <v>-5876</v>
       </c>
-      <c r="Q66" s="2" t="n">
+      <c r="Q67" s="2" t="n">
         <v>3041</v>
       </c>
-      <c r="R66" s="2" t="n">
+      <c r="R67" s="2" t="n">
         <v>-2835</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="D69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="D71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="D73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP1</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="D75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP2</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="D77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>KR_TR_JEO2</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="D79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>KR_TR_MA</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="D81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>미국VCP</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="D83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="D85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="D87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="D89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="D91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D93" t="n">
         <v>1</v>
       </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="n">
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="n">
         <v>6.8</v>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="n">
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="n">
         <v>6.8</v>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="n">
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="n">
         <v>5</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M93" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N92" t="n">
-        <v>-9939</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>-9939</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>198</v>
-      </c>
-      <c r="R92" t="n">
-        <v>-9741</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="N93" t="n">
+        <v>-9904</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>-9904</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>197</v>
+      </c>
+      <c r="R93" t="n">
+        <v>-9707</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="n">
+      <c r="E94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="n">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="n">
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M93" s="2" t="n">
+      <c r="M94" s="2" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N93" s="2" t="n">
-        <v>-9939</v>
-      </c>
-      <c r="O93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" s="2" t="n">
-        <v>-9939</v>
-      </c>
-      <c r="Q93" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="R93" s="2" t="n">
-        <v>-9741</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="N94" s="2" t="n">
+        <v>-9904</v>
+      </c>
+      <c r="O94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>-9904</v>
+      </c>
+      <c r="Q94" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>-9707</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr"/>
-      <c r="O95" s="2" t="inlineStr"/>
-      <c r="P95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="D96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
-      <c r="O97" s="2" t="inlineStr"/>
-      <c r="P97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="D98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
-      <c r="O99" s="2" t="inlineStr"/>
-      <c r="P99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
-      <c r="P101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="D102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
-      <c r="P103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" s="2" t="n">
+      <c r="D104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R104"/>
+  <dimension ref="A1:R105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1084,45 +1084,45 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="F11" t="n">
-        <v>1.94</v>
+        <v>0.86</v>
       </c>
       <c r="G11" t="n">
         <v>12.69</v>
       </c>
       <c r="H11" t="n">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="I11" t="n">
         <v>12.69</v>
       </c>
       <c r="J11" t="n">
-        <v>6.8</v>
+        <v>10.01</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>1.204</v>
+        <v>-1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>-3935</v>
+        <v>-23305</v>
       </c>
       <c r="O11" t="n">
-        <v>0.65</v>
+        <v>0.17</v>
       </c>
       <c r="P11" t="n">
-        <v>-15741</v>
+        <v>-139830</v>
       </c>
       <c r="Q11" t="n">
-        <v>11092</v>
+        <v>15047</v>
       </c>
       <c r="R11" t="n">
-        <v>-4649</v>
+        <v>-124782</v>
       </c>
     </row>
     <row r="12">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>4.31</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>19.29</v>
@@ -1165,22 +1165,22 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="n">
-        <v>0.008</v>
+        <v>-0.033</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>211</v>
+        <v>-238</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>58050</v>
+        <v>-66039</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>64195</v>
+        <v>68150</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>122245</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="14">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -2166,33 +2166,33 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0.53</v>
+        <v>0.86</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.534</v>
+        <v>-0.864</v>
       </c>
       <c r="N35" t="n">
-        <v>-17382</v>
+        <v>-29079</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-34764</v>
+        <v>-87237</v>
       </c>
       <c r="Q35" t="n">
-        <v>10822</v>
+        <v>13827</v>
       </c>
       <c r="R35" t="n">
-        <v>-23942</v>
+        <v>-73410</v>
       </c>
     </row>
     <row r="36">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>30.8</v>
+        <v>28.6</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1.02</v>
+        <v>0.77</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>1.12</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>2.2</v>
@@ -2236,25 +2236,25 @@
         <v>10.75</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.416</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-4624</v>
+        <v>-8042</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>0.45</v>
+        <v>0.31</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>-60112</v>
+        <v>-112585</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>24426</v>
+        <v>27430</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>-35686</v>
+        <v>-85155</v>
       </c>
     </row>
     <row r="38">
@@ -3892,474 +3892,546 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="n">
+        <v>3</v>
+      </c>
+      <c r="M85" t="n">
+        <v>-10.012</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-71616</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>-71616</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>951</v>
+      </c>
+      <c r="R85" t="n">
+        <v>-70665</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_A</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr"/>
-      <c r="O85" s="2" t="inlineStr"/>
-      <c r="P85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="D86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-10.012</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>-71616</v>
+      </c>
+      <c r="O86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="2" t="n">
+        <v>-71616</v>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>951</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>-70665</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr"/>
-      <c r="N87" s="2" t="inlineStr"/>
-      <c r="O87" s="2" t="inlineStr"/>
-      <c r="P87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="D88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
-      <c r="N89" s="2" t="inlineStr"/>
-      <c r="O89" s="2" t="inlineStr"/>
-      <c r="P89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="D90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr"/>
-      <c r="O91" s="2" t="inlineStr"/>
-      <c r="P91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="D92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="n">
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="n">
         <v>6.8</v>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="n">
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="n">
         <v>6.8</v>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="n">
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="n">
         <v>5</v>
       </c>
-      <c r="M93" t="n">
+      <c r="M94" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N94" t="n">
         <v>-9904</v>
       </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
         <v>-9904</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="Q94" t="n">
         <v>197</v>
       </c>
-      <c r="R93" t="n">
+      <c r="R94" t="n">
         <v>-9707</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="n">
+      <c r="E95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="n">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="n">
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M94" s="2" t="n">
+      <c r="M95" s="2" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N94" s="2" t="n">
+      <c r="N95" s="2" t="n">
         <v>-9904</v>
       </c>
-      <c r="O94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" s="2" t="n">
+      <c r="O95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="2" t="n">
         <v>-9904</v>
       </c>
-      <c r="Q94" s="2" t="n">
+      <c r="Q95" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="R94" s="2" t="n">
+      <c r="R95" s="2" t="n">
         <v>-9707</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr"/>
-      <c r="P96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="D99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
-      <c r="P100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="D101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="D103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr"/>
-      <c r="P104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" s="2" t="n">
+      <c r="D105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>16.7</v>
+        <v>28.6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.86</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>12.69</v>
+        <v>8.56</v>
       </c>
       <c r="H11" t="n">
         <v>3.88</v>
@@ -1107,22 +1107,22 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>-1.12</v>
+        <v>-0.327</v>
       </c>
       <c r="N11" t="n">
-        <v>-23305</v>
+        <v>-7689</v>
       </c>
       <c r="O11" t="n">
-        <v>0.17</v>
+        <v>0.68</v>
       </c>
       <c r="P11" t="n">
-        <v>-139830</v>
+        <v>-53824</v>
       </c>
       <c r="Q11" t="n">
-        <v>15047</v>
+        <v>15642</v>
       </c>
       <c r="R11" t="n">
-        <v>-124782</v>
+        <v>-38182</v>
       </c>
     </row>
     <row r="12">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>4.31</v>
@@ -1165,22 +1165,22 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="n">
-        <v>-0.033</v>
+        <v>-0.017</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-238</v>
+        <v>72</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>-66039</v>
+        <v>19966</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>68150</v>
+        <v>68745</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>2111</v>
+        <v>88711</v>
       </c>
     </row>
     <row r="14">
@@ -1816,14 +1816,14 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>100</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>12.69</v>
+        <v>8.56</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
@@ -1831,24 +1831,24 @@
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>12.685</v>
+        <v>8.56</v>
       </c>
       <c r="N28" t="n">
-        <v>28927</v>
+        <v>57466</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>28927</v>
+        <v>114933</v>
       </c>
       <c r="Q28" t="n">
-        <v>73</v>
+        <v>667</v>
       </c>
       <c r="R28" t="n">
-        <v>29000</v>
+        <v>115600</v>
       </c>
     </row>
     <row r="29">
@@ -1868,16 +1868,16 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.97</v>
+        <v>1.84</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>4.19</v>
@@ -1889,28 +1889,28 @@
         <v>7.04</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>1.75</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.177</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2224</v>
+        <v>9840</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>1.46</v>
+        <v>3.23</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>22236</v>
+        <v>108241</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>2211</v>
+        <v>2806</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>24447</v>
+        <v>111047</v>
       </c>
     </row>
     <row r="31">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>36.1</v>
+        <v>38.2</v>
       </c>
       <c r="F5" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="G5" t="n">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="I5" t="n">
         <v>13.15</v>
@@ -759,22 +759,22 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-0.643</v>
+        <v>-0.67</v>
       </c>
       <c r="N5" t="n">
-        <v>452</v>
+        <v>572</v>
       </c>
       <c r="O5" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P5" t="n">
-        <v>27596</v>
+        <v>31442</v>
       </c>
       <c r="Q5" t="n">
-        <v>5045</v>
+        <v>4659</v>
       </c>
       <c r="R5" t="n">
-        <v>32641</v>
+        <v>36101</v>
       </c>
     </row>
     <row r="6">
@@ -968,19 +968,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>31.4</v>
+        <v>44.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1.97</v>
+        <v>1.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3.64</v>
+        <v>4.17</v>
       </c>
       <c r="H9" t="n">
-        <v>1.59</v>
+        <v>3.17</v>
       </c>
       <c r="I9" t="n">
         <v>13.51</v>
@@ -991,22 +991,22 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>0.052</v>
+        <v>0.116</v>
       </c>
       <c r="N9" t="n">
-        <v>-342</v>
+        <v>-427</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="P9" t="n">
-        <v>-17448</v>
+        <v>-12396</v>
       </c>
       <c r="Q9" t="n">
-        <v>8314</v>
+        <v>6681</v>
       </c>
       <c r="R9" t="n">
-        <v>-9135</v>
+        <v>-5715</v>
       </c>
     </row>
     <row r="10">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>13.8</v>
+        <v>17.9</v>
       </c>
       <c r="F10" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="G10" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="I10" t="n">
         <v>2.2</v>
@@ -1052,19 +1052,19 @@
         <v>-0.448</v>
       </c>
       <c r="N10" t="n">
-        <v>-7907</v>
+        <v>-6707</v>
       </c>
       <c r="O10" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="P10" t="n">
-        <v>-229317</v>
+        <v>-187786</v>
       </c>
       <c r="Q10" t="n">
-        <v>17286</v>
+        <v>15579</v>
       </c>
       <c r="R10" t="n">
-        <v>-212031</v>
+        <v>-172206</v>
       </c>
     </row>
     <row r="11">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>34.9</v>
+        <v>37.8</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4.31</v>
+        <v>4.4</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>19.29</v>
@@ -1165,22 +1165,22 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="n">
-        <v>-0.017</v>
+        <v>-0.005</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>72</v>
+        <v>283</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>19966</v>
+        <v>70396</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>68745</v>
+        <v>65020</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>88711</v>
+        <v>135416</v>
       </c>
     </row>
     <row r="14">
@@ -1738,297 +1738,219 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TV알림</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D29" t="n">
         <v>9</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E29" t="n">
         <v>55.6</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F29" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G29" t="n">
         <v>1.17</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H29" t="n">
         <v>4.19</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I29" t="n">
         <v>3.38</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J29" t="n">
         <v>7.04</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K29" t="n">
         <v>3</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L29" t="n">
         <v>1.75</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M29" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N29" t="n">
         <v>-744</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O29" t="n">
         <v>0.86</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P29" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q29" t="n">
         <v>2139</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R29" t="n">
         <v>-4553</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D30" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E30" t="n">
         <v>100</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="n">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
         <v>8.56</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
         <v>12.69</v>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
         <v>4.5</v>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
         <v>8.56</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N30" t="n">
         <v>57466</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
         <v>114933</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q30" t="n">
         <v>667</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R30" t="n">
         <v>115600</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D31" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E31" s="2" t="n">
         <v>63.6</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F31" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="I31" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="J31" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K31" s="2" t="n">
         <v>3.43</v>
       </c>
-      <c r="L29" s="2" t="n">
+      <c r="L31" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="M31" s="2" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="N31" s="2" t="n">
         <v>9840</v>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="O31" s="2" t="n">
         <v>3.23</v>
       </c>
-      <c r="P29" s="2" t="n">
+      <c r="P31" s="2" t="n">
         <v>108241</v>
       </c>
-      <c r="Q29" s="2" t="n">
+      <c r="Q31" s="2" t="n">
         <v>2806</v>
       </c>
-      <c r="R29" s="2" t="n">
+      <c r="R31" s="2" t="n">
         <v>111047</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>513</v>
-      </c>
-      <c r="R31" t="n">
-        <v>-15508</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="n">
-        <v>25</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M32" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P32" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R32" t="n">
-        <v>-47176</v>
       </c>
     </row>
     <row r="33">
@@ -2044,7 +1966,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2058,33 +1980,33 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0.14</v>
+        <v>2.61</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>0.16</v>
+        <v>3.49</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.136</v>
+        <v>-2.607</v>
       </c>
       <c r="N33" t="n">
-        <v>-2389</v>
+        <v>-8011</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-4777</v>
+        <v>-16021</v>
       </c>
       <c r="Q33" t="n">
-        <v>2924</v>
+        <v>513</v>
       </c>
       <c r="R33" t="n">
-        <v>-1854</v>
+        <v>-15508</v>
       </c>
     </row>
     <row r="34">
@@ -2100,43 +2022,53 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>100</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K34" t="n">
-        <v>14</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M34" t="n">
-        <v>1.042</v>
+        <v>-0.217</v>
       </c>
       <c r="N34" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
+        <v>-13272</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P34" t="n">
-        <v>48540</v>
+        <v>-53089</v>
       </c>
       <c r="Q34" t="n">
-        <v>4254</v>
+        <v>5913</v>
       </c>
       <c r="R34" t="n">
-        <v>52794</v>
+        <v>-47176</v>
       </c>
     </row>
     <row r="35">
@@ -2152,11 +2084,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -2166,219 +2098,203 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-2389</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-4777</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2924</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-1854</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>14</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N36" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R36" t="n">
+        <v>52794</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
         <v>4.67</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M37" t="n">
         <v>-0.864</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N37" t="n">
         <v>-29079</v>
       </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>-87237</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q37" t="n">
         <v>13827</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R37" t="n">
         <v>-73410</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D38" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E38" s="2" t="n">
         <v>28.6</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F38" s="2" t="n">
         <v>0.77</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>1.03</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I38" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J38" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K38" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L36" s="2" t="n">
+      <c r="L38" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="M38" s="2" t="n">
         <v>-0.416</v>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="N38" s="2" t="n">
         <v>-8042</v>
       </c>
-      <c r="O36" s="2" t="n">
+      <c r="O38" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="P36" s="2" t="n">
+      <c r="P38" s="2" t="n">
         <v>-112585</v>
       </c>
-      <c r="Q36" s="2" t="n">
+      <c r="Q38" s="2" t="n">
         <v>27430</v>
       </c>
-      <c r="R36" s="2" t="n">
+      <c r="R38" s="2" t="n">
         <v>-85155</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>27</v>
-      </c>
-      <c r="E38" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H38" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I38" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J38" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L38" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N38" t="n">
-        <v>507</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P38" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R38" t="n">
-        <v>15210</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>06/29~07/03</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>45</v>
-      </c>
-      <c r="E39" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G39" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I39" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="J39" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="K39" t="n">
-        <v>313.5</v>
-      </c>
-      <c r="L39" t="n">
-        <v>175.2</v>
-      </c>
-      <c r="M39" t="n">
-        <v>-0.703</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-1271</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="P39" t="n">
-        <v>-57188</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2829</v>
-      </c>
-      <c r="R39" t="n">
-        <v>-54359</v>
       </c>
     </row>
     <row r="40">
@@ -2394,53 +2310,53 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E40" t="n">
-        <v>41.9</v>
+        <v>40.7</v>
       </c>
       <c r="F40" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="G40" t="n">
-        <v>3.14</v>
+        <v>5.47</v>
       </c>
       <c r="H40" t="n">
-        <v>2.76</v>
+        <v>3.29</v>
       </c>
       <c r="I40" t="n">
-        <v>8.68</v>
+        <v>17.35</v>
       </c>
       <c r="J40" t="n">
-        <v>9.01</v>
+        <v>20.1</v>
       </c>
       <c r="K40" t="n">
-        <v>247.7</v>
+        <v>185.95</v>
       </c>
       <c r="L40" t="n">
-        <v>174.67</v>
+        <v>187.46</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.288</v>
+        <v>0.274</v>
       </c>
       <c r="N40" t="n">
-        <v>1187</v>
+        <v>507</v>
       </c>
       <c r="O40" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="P40" t="n">
-        <v>36789</v>
+        <v>13680</v>
       </c>
       <c r="Q40" t="n">
-        <v>3306</v>
+        <v>1530</v>
       </c>
       <c r="R40" t="n">
-        <v>40095</v>
+        <v>15210</v>
       </c>
     </row>
     <row r="41">
@@ -2456,53 +2372,53 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>37.8</v>
       </c>
       <c r="F41" t="n">
-        <v>3.53</v>
+        <v>1.11</v>
       </c>
       <c r="G41" t="n">
-        <v>6.86</v>
+        <v>3.01</v>
       </c>
       <c r="H41" t="n">
-        <v>4.11</v>
+        <v>2.96</v>
       </c>
       <c r="I41" t="n">
-        <v>11.14</v>
+        <v>13.15</v>
       </c>
       <c r="J41" t="n">
-        <v>9.65</v>
+        <v>5.82</v>
       </c>
       <c r="K41" t="n">
-        <v>533.86</v>
+        <v>313.5</v>
       </c>
       <c r="L41" t="n">
-        <v>403.59</v>
+        <v>175.2</v>
       </c>
       <c r="M41" t="n">
-        <v>1.375</v>
+        <v>-0.703</v>
       </c>
       <c r="N41" t="n">
-        <v>8720</v>
+        <v>-1271</v>
       </c>
       <c r="O41" t="n">
-        <v>3.53</v>
+        <v>0.67</v>
       </c>
       <c r="P41" t="n">
-        <v>52321</v>
+        <v>-57188</v>
       </c>
       <c r="Q41" t="n">
-        <v>523</v>
+        <v>2829</v>
       </c>
       <c r="R41" t="n">
-        <v>52844</v>
+        <v>-54359</v>
       </c>
     </row>
     <row r="42">
@@ -2518,53 +2434,53 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E42" t="n">
-        <v>44.4</v>
+        <v>41.9</v>
       </c>
       <c r="F42" t="n">
-        <v>4.39</v>
+        <v>1.8</v>
       </c>
       <c r="G42" t="n">
-        <v>7.08</v>
+        <v>3.14</v>
       </c>
       <c r="H42" t="n">
-        <v>1.26</v>
+        <v>2.76</v>
       </c>
       <c r="I42" t="n">
-        <v>7.95</v>
+        <v>8.68</v>
       </c>
       <c r="J42" t="n">
-        <v>2.19</v>
+        <v>9.01</v>
       </c>
       <c r="K42" t="n">
-        <v>800.2</v>
+        <v>247.7</v>
       </c>
       <c r="L42" t="n">
-        <v>60.03</v>
+        <v>174.67</v>
       </c>
       <c r="M42" t="n">
-        <v>2.446</v>
+        <v>-0.288</v>
       </c>
       <c r="N42" t="n">
-        <v>5075</v>
+        <v>1187</v>
       </c>
       <c r="O42" t="n">
-        <v>3.51</v>
+        <v>1.3</v>
       </c>
       <c r="P42" t="n">
-        <v>45679</v>
+        <v>36789</v>
       </c>
       <c r="Q42" t="n">
-        <v>661</v>
+        <v>3306</v>
       </c>
       <c r="R42" t="n">
-        <v>46340</v>
+        <v>40095</v>
       </c>
     </row>
     <row r="43">
@@ -2580,53 +2496,53 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
         <v>50</v>
       </c>
       <c r="F43" t="n">
-        <v>1.14</v>
+        <v>3.53</v>
       </c>
       <c r="G43" t="n">
-        <v>6.04</v>
+        <v>6.86</v>
       </c>
       <c r="H43" t="n">
-        <v>2.52</v>
+        <v>4.11</v>
       </c>
       <c r="I43" t="n">
-        <v>13.51</v>
+        <v>11.14</v>
       </c>
       <c r="J43" t="n">
-        <v>4.74</v>
+        <v>9.65</v>
       </c>
       <c r="K43" t="n">
-        <v>2281.51</v>
+        <v>533.86</v>
       </c>
       <c r="L43" t="n">
-        <v>27.54</v>
+        <v>403.59</v>
       </c>
       <c r="M43" t="n">
-        <v>1.758</v>
+        <v>1.375</v>
       </c>
       <c r="N43" t="n">
-        <v>851</v>
+        <v>8720</v>
       </c>
       <c r="O43" t="n">
-        <v>1.14</v>
+        <v>3.53</v>
       </c>
       <c r="P43" t="n">
-        <v>13616</v>
+        <v>52321</v>
       </c>
       <c r="Q43" t="n">
-        <v>1561</v>
+        <v>523</v>
       </c>
       <c r="R43" t="n">
-        <v>15177</v>
+        <v>52844</v>
       </c>
     </row>
     <row r="44">
@@ -2642,633 +2558,645 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="G44" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I44" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K44" t="n">
+        <v>800.2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2.446</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5075</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P44" t="n">
+        <v>45679</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>661</v>
+      </c>
+      <c r="R44" t="n">
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>16</v>
+      </c>
+      <c r="E45" t="n">
+        <v>50</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I45" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J45" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L45" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N45" t="n">
+        <v>851</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P45" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R45" t="n">
+        <v>15177</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>600.88</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>163.85</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>104898</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>10409</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>115307</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>삼닉v3_저2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
-        <v>40.94</v>
-      </c>
-      <c r="M44" t="n">
-        <v>-0.711</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-19138</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>-76552</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3052</v>
-      </c>
-      <c r="R44" t="n">
-        <v>-73500</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-0.341</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-4880</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-14641</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1291</v>
+      </c>
+      <c r="R48" t="n">
+        <v>-13350</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>삼닉v3_저2</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>600.88</v>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>157.85</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>28345</v>
-      </c>
-      <c r="Q45" s="2" t="n">
-        <v>13462</v>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>41807</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>삼닉v3_저2</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="D49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>-0.341</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>-4880</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>-14641</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>1291</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>-13350</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="M47" t="n">
-        <v>-0.341</v>
-      </c>
-      <c r="N47" t="n">
-        <v>-4880</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>-14641</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1291</v>
-      </c>
-      <c r="R47" t="n">
-        <v>-13350</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>삼닉v3_저2</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-0.912</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-138394</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>4519</v>
+      </c>
+      <c r="R51" t="n">
+        <v>-133875</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>-0.341</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>-4880</v>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="n">
-        <v>-14641</v>
-      </c>
-      <c r="Q48" s="2" t="n">
-        <v>1291</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>-13350</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="D52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>-0.912</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>-138394</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>4519</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>-133875</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>삼닉v3_MA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M50" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>-138394</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4519</v>
-      </c>
-      <c r="R50" t="n">
-        <v>-133875</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="D54" t="n">
+        <v>12</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K54" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="L54" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-0.461</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-6941</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-83290</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>5515</v>
+      </c>
+      <c r="R54" t="n">
+        <v>-77775</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>삼닉v3_MA</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>-138394</v>
-      </c>
-      <c r="Q51" s="2" t="n">
-        <v>4519</v>
-      </c>
-      <c r="R51" s="2" t="n">
-        <v>-133875</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>삼닉v3_MA</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="D55" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>-0.461</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>-6941</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>-83290</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>5515</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>-77775</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>5minHL</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>9</v>
-      </c>
-      <c r="E53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="K53" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L53" t="n">
-        <v>25.93</v>
-      </c>
-      <c r="M53" t="n">
-        <v>-0.348</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-5363</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="P53" t="n">
-        <v>-48269</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>4169</v>
-      </c>
-      <c r="R53" t="n">
-        <v>-44100</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>삼닉v3_MA</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>5minHL2</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>25.93</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>-0.348</v>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>-5363</v>
-      </c>
-      <c r="O54" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>-48269</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>4169</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>-44100</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>5minHL</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="D59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_동시</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>5minHL2</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>5minHL_동시</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M62" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N62" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>26</v>
-      </c>
-      <c r="R62" t="n">
-        <v>-2400</v>
+      <c r="D61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3284,53 +3212,47 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1.92</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I63" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2003.43</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>2987.95</v>
+        <v>49.85</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.292</v>
+        <v>-2.747</v>
       </c>
       <c r="N63" t="n">
-        <v>2155</v>
+        <v>-2426</v>
       </c>
       <c r="O63" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>25859</v>
+        <v>-2426</v>
       </c>
       <c r="Q63" t="n">
-        <v>1141</v>
+        <v>26</v>
       </c>
       <c r="R63" t="n">
-        <v>27000</v>
+        <v>-2400</v>
       </c>
     </row>
     <row r="64">
@@ -3346,53 +3268,53 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="G64" t="n">
-        <v>0.08</v>
+        <v>2.47</v>
       </c>
       <c r="H64" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="I64" t="n">
-        <v>0.08</v>
+        <v>4.6</v>
       </c>
       <c r="J64" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="K64" t="n">
-        <v>4319.93</v>
+        <v>1279.97</v>
       </c>
       <c r="L64" t="n">
-        <v>1351.81</v>
+        <v>875.09</v>
       </c>
       <c r="M64" t="n">
-        <v>-2.059</v>
+        <v>-0.191</v>
       </c>
       <c r="N64" t="n">
-        <v>-3794</v>
+        <v>4951</v>
       </c>
       <c r="O64" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="P64" t="n">
-        <v>-11383</v>
+        <v>29704</v>
       </c>
       <c r="Q64" t="n">
-        <v>153</v>
+        <v>756</v>
       </c>
       <c r="R64" t="n">
-        <v>-11230</v>
+        <v>30460</v>
       </c>
     </row>
     <row r="65">
@@ -3408,43 +3330,53 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>100</v>
-      </c>
-      <c r="F65" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G65" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3.13</v>
+      </c>
       <c r="I65" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J65" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.61</v>
+      </c>
       <c r="K65" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L65" t="inlineStr"/>
+        <v>4319.93</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1351.81</v>
+      </c>
       <c r="M65" t="n">
-        <v>1.678</v>
+        <v>-2.059</v>
       </c>
       <c r="N65" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O65" t="inlineStr"/>
+        <v>-3794</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.01</v>
+      </c>
       <c r="P65" t="n">
-        <v>1670</v>
+        <v>-11383</v>
       </c>
       <c r="Q65" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="R65" t="n">
-        <v>1700</v>
+        <v>-11230</v>
       </c>
     </row>
     <row r="66">
@@ -3460,978 +3392,1024 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>30</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>24</v>
-      </c>
-      <c r="E66" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F66" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I66" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="J66" t="n">
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="n">
         <v>7.52</v>
       </c>
-      <c r="K66" t="n">
-        <v>24201.59</v>
-      </c>
-      <c r="L66" t="n">
-        <v>27253.11</v>
-      </c>
-      <c r="M66" t="n">
-        <v>-0.595</v>
-      </c>
-      <c r="N66" t="n">
-        <v>-816</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P66" t="n">
-        <v>-19595</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1690</v>
-      </c>
-      <c r="R66" t="n">
-        <v>-17905</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>5756.96</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-7272</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-14543</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>58</v>
+      </c>
+      <c r="R67" t="n">
+        <v>-14485</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="I67" s="2" t="n">
+      <c r="D68" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I68" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="J67" s="2" t="n">
+      <c r="J68" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="K67" s="2" t="n">
-        <v>9438.73</v>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>18717.88</v>
-      </c>
-      <c r="M67" s="2" t="n">
-        <v>-0.611</v>
-      </c>
-      <c r="N67" s="2" t="n">
-        <v>-143</v>
-      </c>
-      <c r="O67" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P67" s="2" t="n">
-        <v>-5876</v>
-      </c>
-      <c r="Q67" s="2" t="n">
-        <v>3041</v>
-      </c>
-      <c r="R67" s="2" t="n">
-        <v>-2835</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="K68" s="2" t="n">
+        <v>1633.99</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>2111.58</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>-1.689</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>3022</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>1023</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>4045</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr"/>
-      <c r="O69" s="2" t="inlineStr"/>
-      <c r="P69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="D70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr"/>
-      <c r="P71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="D72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr"/>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="D74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP1</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr"/>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="D76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP2</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr"/>
-      <c r="O77" s="2" t="inlineStr"/>
-      <c r="P77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="D78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>KR_TR_JEO2</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr"/>
-      <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="D80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>KR_TR_MA</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr"/>
-      <c r="O81" s="2" t="inlineStr"/>
-      <c r="P81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="D82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>미국VCP</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
-      <c r="N83" s="2" t="inlineStr"/>
-      <c r="O83" s="2" t="inlineStr"/>
-      <c r="P83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="D84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D86" t="n">
         <v>1</v>
       </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="n">
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="n">
         <v>10.01</v>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="n">
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="n">
         <v>10.01</v>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="n">
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="n">
         <v>3</v>
       </c>
-      <c r="M85" t="n">
+      <c r="M86" t="n">
         <v>-10.012</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N86" t="n">
         <v>-71616</v>
       </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
         <v>-71616</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="Q86" t="n">
         <v>951</v>
       </c>
-      <c r="R85" t="n">
+      <c r="R86" t="n">
         <v>-70665</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
+      <c r="D87" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="n">
+      <c r="E87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="n">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="n">
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M86" s="2" t="n">
+      <c r="M87" s="2" t="n">
         <v>-10.012</v>
       </c>
-      <c r="N86" s="2" t="n">
+      <c r="N87" s="2" t="n">
         <v>-71616</v>
       </c>
-      <c r="O86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" s="2" t="n">
+      <c r="O87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="2" t="n">
         <v>-71616</v>
       </c>
-      <c r="Q86" s="2" t="n">
+      <c r="Q87" s="2" t="n">
         <v>951</v>
       </c>
-      <c r="R86" s="2" t="n">
+      <c r="R87" s="2" t="n">
         <v>-70665</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="D89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="D91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr"/>
-      <c r="P92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="D93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D95" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="n">
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="n">
         <v>6.8</v>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="n">
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="n">
         <v>6.8</v>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="n">
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="n">
         <v>5</v>
       </c>
-      <c r="M94" t="n">
+      <c r="M95" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N95" t="n">
         <v>-9904</v>
       </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
         <v>-9904</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="Q95" t="n">
         <v>197</v>
       </c>
-      <c r="R94" t="n">
+      <c r="R95" t="n">
         <v>-9707</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n">
+      <c r="D96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="n">
+      <c r="E96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="n">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="n">
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M95" s="2" t="n">
+      <c r="M96" s="2" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N95" s="2" t="n">
+      <c r="N96" s="2" t="n">
         <v>-9904</v>
       </c>
-      <c r="O95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="2" t="n">
+      <c r="O96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="2" t="n">
         <v>-9904</v>
       </c>
-      <c r="Q95" s="2" t="n">
+      <c r="Q96" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="R95" s="2" t="n">
+      <c r="R96" s="2" t="n">
         <v>-9707</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
-      <c r="O97" s="2" t="inlineStr"/>
-      <c r="P97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="D98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
-      <c r="O99" s="2" t="inlineStr"/>
-      <c r="P99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
-      <c r="P101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="D102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
-      <c r="P103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="D104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr"/>
-      <c r="O105" s="2" t="inlineStr"/>
-      <c r="P105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" s="2" t="n">
+      <c r="D106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R106"/>
+  <dimension ref="A1:S118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -455,6 +455,7 @@
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,6 +549,11 @@
           <t>실현손익합(원,gross)</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>환율(USDKRW)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -602,6 +608,9 @@
       <c r="R2" t="n">
         <v>-175500</v>
       </c>
+      <c r="S2" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -660,6 +669,9 @@
       <c r="R3" t="n">
         <v>229860</v>
       </c>
+      <c r="S3" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -718,6 +730,9 @@
       <c r="R4" t="n">
         <v>-219740</v>
       </c>
+      <c r="S4" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -776,6 +791,9 @@
       <c r="R5" t="n">
         <v>36101</v>
       </c>
+      <c r="S5" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -834,6 +852,9 @@
       <c r="R6" t="n">
         <v>26414</v>
       </c>
+      <c r="S6" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -892,6 +913,9 @@
       <c r="R7" t="n">
         <v>381441</v>
       </c>
+      <c r="S7" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -950,6 +974,9 @@
       <c r="R8" t="n">
         <v>72944</v>
       </c>
+      <c r="S8" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1008,6 +1035,9 @@
       <c r="R9" t="n">
         <v>-5715</v>
       </c>
+      <c r="S9" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1066,6 +1096,9 @@
       <c r="R10" t="n">
         <v>-172206</v>
       </c>
+      <c r="S10" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1090,7 +1123,7 @@
         <v>28.6</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
         <v>8.56</v>
@@ -1110,19 +1143,22 @@
         <v>-0.327</v>
       </c>
       <c r="N11" t="n">
-        <v>-7689</v>
+        <v>-7621</v>
       </c>
       <c r="O11" t="n">
         <v>0.68</v>
       </c>
       <c r="P11" t="n">
-        <v>-53824</v>
+        <v>-53347</v>
       </c>
       <c r="Q11" t="n">
-        <v>15642</v>
+        <v>15600</v>
       </c>
       <c r="R11" t="n">
-        <v>-38182</v>
+        <v>-37747</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1411</v>
       </c>
     </row>
     <row r="12">
@@ -1168,20 +1204,21 @@
         <v>-0.005</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>1.04</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>70396</v>
+        <v>70873</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>65020</v>
+        <v>64978</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>135416</v>
-      </c>
+        <v>135851</v>
+      </c>
+      <c r="S12" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1238,6 +1275,9 @@
       <c r="R14" t="n">
         <v>-175500</v>
       </c>
+      <c r="S14" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1299,6 +1339,9 @@
       </c>
       <c r="R15" t="n">
         <v>229860</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1415</v>
       </c>
     </row>
     <row r="16">
@@ -1356,6 +1399,9 @@
       <c r="R16" t="n">
         <v>-232550</v>
       </c>
+      <c r="S16" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1418,6 +1464,9 @@
       <c r="R17" t="n">
         <v>60000</v>
       </c>
+      <c r="S17" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1479,6 +1528,9 @@
       </c>
       <c r="R18" t="n">
         <v>-2451</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1415</v>
       </c>
     </row>
     <row r="19">
@@ -1532,6 +1584,9 @@
       <c r="R19" t="n">
         <v>344105</v>
       </c>
+      <c r="S19" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1594,6 +1649,9 @@
       <c r="R20" t="n">
         <v>72080</v>
       </c>
+      <c r="S20" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1656,6 +1714,7 @@
       <c r="R21" s="2" t="n">
         <v>295544</v>
       </c>
+      <c r="S21" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1696,6 +1755,7 @@
       <c r="R23" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S23" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1736,6 +1796,7 @@
       <c r="R25" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S25" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1776,6 +1837,7 @@
       <c r="R27" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S27" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1837,6 +1899,9 @@
       </c>
       <c r="R29" t="n">
         <v>-4553</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1415</v>
       </c>
     </row>
     <row r="30">
@@ -1890,6 +1955,9 @@
       <c r="R30" t="n">
         <v>115600</v>
       </c>
+      <c r="S30" t="n">
+        <v>1411</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1952,6 +2020,7 @@
       <c r="R31" s="2" t="n">
         <v>111047</v>
       </c>
+      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2008,6 +2077,9 @@
       <c r="R33" t="n">
         <v>-15508</v>
       </c>
+      <c r="S33" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2069,6 +2141,9 @@
       </c>
       <c r="R34" t="n">
         <v>-47176</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1415</v>
       </c>
     </row>
     <row r="35">
@@ -2126,6 +2201,9 @@
       <c r="R35" t="n">
         <v>-1854</v>
       </c>
+      <c r="S35" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2178,6 +2256,9 @@
       <c r="R36" t="n">
         <v>52794</v>
       </c>
+      <c r="S36" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2220,19 +2301,22 @@
         <v>-0.864</v>
       </c>
       <c r="N37" t="n">
-        <v>-29079</v>
+        <v>-28997</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-87237</v>
+        <v>-86990</v>
       </c>
       <c r="Q37" t="n">
-        <v>13827</v>
+        <v>13787</v>
       </c>
       <c r="R37" t="n">
-        <v>-73410</v>
+        <v>-73203</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1411</v>
       </c>
     </row>
     <row r="38">
@@ -2282,20 +2366,21 @@
         <v>-0.416</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-8042</v>
+        <v>-8024</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>0.31</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>-112585</v>
+        <v>-112338</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>27430</v>
+        <v>27391</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-85155</v>
-      </c>
+        <v>-84947</v>
+      </c>
+      <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2358,6 +2443,9 @@
       <c r="R40" t="n">
         <v>15210</v>
       </c>
+      <c r="S40" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2420,6 +2508,9 @@
       <c r="R41" t="n">
         <v>-54359</v>
       </c>
+      <c r="S41" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2482,6 +2573,9 @@
       <c r="R42" t="n">
         <v>40095</v>
       </c>
+      <c r="S42" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2544,6 +2638,9 @@
       <c r="R43" t="n">
         <v>52844</v>
       </c>
+      <c r="S43" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2606,6 +2703,9 @@
       <c r="R44" t="n">
         <v>46340</v>
       </c>
+      <c r="S44" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2668,6 +2768,9 @@
       <c r="R45" t="n">
         <v>15177</v>
       </c>
+      <c r="S45" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2730,6 +2833,7 @@
       <c r="R46" s="2" t="n">
         <v>115307</v>
       </c>
+      <c r="S46" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2786,6 +2890,9 @@
       <c r="R48" t="n">
         <v>-13350</v>
       </c>
+      <c r="S48" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2842,6 +2949,7 @@
       <c r="R49" s="2" t="n">
         <v>-13350</v>
       </c>
+      <c r="S49" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2898,6 +3006,9 @@
       <c r="R51" t="n">
         <v>-133875</v>
       </c>
+      <c r="S51" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2954,6 +3065,7 @@
       <c r="R52" s="2" t="n">
         <v>-133875</v>
       </c>
+      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3016,6 +3128,9 @@
       <c r="R54" t="n">
         <v>-77775</v>
       </c>
+      <c r="S54" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3078,11 +3193,12 @@
       <c r="R55" s="2" t="n">
         <v>-77775</v>
       </c>
+      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>5minHL</t>
+          <t>삼닉v3_미분류</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3118,11 +3234,12 @@
       <c r="R57" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>5minHL2</t>
+          <t>5minHL</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3158,11 +3275,12 @@
       <c r="R59" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>5minHL_동시</t>
+          <t>5minHL2</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3198,124 +3316,48 @@
       <c r="R61" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S61" s="2" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_동시</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M63" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N63" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>26</v>
-      </c>
-      <c r="R63" t="n">
-        <v>-2400</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>06/29~07/03</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>6</v>
-      </c>
-      <c r="E64" t="n">
-        <v>50</v>
-      </c>
-      <c r="F64" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G64" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="H64" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I64" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J64" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1279.97</v>
-      </c>
-      <c r="L64" t="n">
-        <v>875.09</v>
-      </c>
-      <c r="M64" t="n">
-        <v>-0.191</v>
-      </c>
-      <c r="N64" t="n">
-        <v>4951</v>
-      </c>
-      <c r="O64" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P64" t="n">
-        <v>29704</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>756</v>
-      </c>
-      <c r="R64" t="n">
-        <v>30460</v>
-      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3330,53 +3372,50 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0.08</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.08</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="K65" t="n">
-        <v>4319.93</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
-        <v>1351.81</v>
+        <v>49.85</v>
       </c>
       <c r="M65" t="n">
-        <v>-2.059</v>
+        <v>-2.747</v>
       </c>
       <c r="N65" t="n">
-        <v>-3794</v>
+        <v>-2426</v>
       </c>
       <c r="O65" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>-11383</v>
+        <v>-2426</v>
       </c>
       <c r="Q65" t="n">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="R65" t="n">
-        <v>-11230</v>
+        <v>-2400</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1415</v>
       </c>
     </row>
     <row r="66">
@@ -3392,43 +3431,56 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>100</v>
-      </c>
-      <c r="F66" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.93</v>
+      </c>
       <c r="G66" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>2.47</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2.85</v>
+      </c>
       <c r="I66" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K66" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L66" t="inlineStr"/>
+        <v>1279.97</v>
+      </c>
+      <c r="L66" t="n">
+        <v>875.09</v>
+      </c>
       <c r="M66" t="n">
-        <v>1.678</v>
+        <v>-0.191</v>
       </c>
       <c r="N66" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O66" t="inlineStr"/>
+        <v>4951</v>
+      </c>
+      <c r="O66" t="n">
+        <v>2.93</v>
+      </c>
       <c r="P66" t="n">
-        <v>1670</v>
+        <v>29704</v>
       </c>
       <c r="Q66" t="n">
-        <v>30</v>
+        <v>756</v>
       </c>
       <c r="R66" t="n">
-        <v>1700</v>
+        <v>30460</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1415</v>
       </c>
     </row>
     <row r="67">
@@ -3444,120 +3496,181 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>07/06~07/10</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="K67" t="n">
+        <v>4319.93</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1351.81</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-2.059</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-3794</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-11383</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>153</v>
+      </c>
+      <c r="R67" t="n">
+        <v>-11230</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>100</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>30</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1700</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D69" t="n">
         <v>2</v>
       </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="n">
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="n">
         <v>6.78</v>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="n">
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="n">
         <v>7.52</v>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="n">
         <v>5756.96</v>
       </c>
-      <c r="M67" t="n">
+      <c r="M69" t="n">
         <v>-6.785</v>
       </c>
-      <c r="N67" t="n">
+      <c r="N69" t="n">
         <v>-7272</v>
       </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
         <v>-14543</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="Q69" t="n">
         <v>58</v>
       </c>
-      <c r="R67" t="n">
+      <c r="R69" t="n">
         <v>-14485</v>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>1633.99</v>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>2111.58</v>
-      </c>
-      <c r="M68" s="2" t="n">
-        <v>-1.689</v>
-      </c>
-      <c r="N68" s="2" t="n">
-        <v>232</v>
-      </c>
-      <c r="O68" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P68" s="2" t="n">
-        <v>3022</v>
-      </c>
-      <c r="Q68" s="2" t="n">
-        <v>1023</v>
-      </c>
-      <c r="R68" s="2" t="n">
-        <v>4045</v>
+      <c r="S69" t="n">
+        <v>1415</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ORD_A</t>
+          <t>5minHL_미분류</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3566,33 +3679,56 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>1633.99</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>2111.58</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>-1.689</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>1.07</v>
+      </c>
       <c r="P70" s="2" t="n">
-        <v>0</v>
+        <v>3022</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="R70" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>4045</v>
+      </c>
+      <c r="S70" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VOLUME_1</t>
+          <t>KR_TR_ORD_A</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3628,11 +3764,12 @@
       <c r="R72" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S72" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VOLUME_2</t>
+          <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3668,11 +3805,12 @@
       <c r="R74" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S74" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP1</t>
+          <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3708,11 +3846,12 @@
       <c r="R76" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S76" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>KR_TR_VCP1</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3748,11 +3887,12 @@
       <c r="R78" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S78" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_JEO2</t>
+          <t>KR_TR_VCP2</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -3788,11 +3928,12 @@
       <c r="R80" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S80" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_MA</t>
+          <t>KR_TR_JEO2</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3828,11 +3969,12 @@
       <c r="R82" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S82" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>미국VCP</t>
+          <t>KR_TR_MA</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -3868,163 +4010,153 @@
       <c r="R84" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S84" s="2" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_ADD1</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>미국VCP</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D90" t="n">
         <v>1</v>
       </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="n">
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="n">
         <v>10.01</v>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="n">
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="n">
         <v>10.01</v>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="n">
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="n">
         <v>3</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M90" t="n">
         <v>-10.012</v>
       </c>
-      <c r="N86" t="n">
-        <v>-71616</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>-71616</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>951</v>
-      </c>
-      <c r="R86" t="n">
-        <v>-70665</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_A</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>-71616</v>
-      </c>
-      <c r="O87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="2" t="n">
-        <v>-71616</v>
-      </c>
-      <c r="Q87" s="2" t="n">
-        <v>951</v>
-      </c>
-      <c r="R87" s="2" t="n">
-        <v>-70665</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VOLUME_1</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
-      <c r="N89" s="2" t="inlineStr"/>
-      <c r="O89" s="2" t="inlineStr"/>
-      <c r="P89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" s="2" t="n">
-        <v>0</v>
+      <c r="N90" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>949</v>
+      </c>
+      <c r="R90" t="n">
+        <v>-70465</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1411</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_2</t>
+          <t>US_TR_ORD_A</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4038,33 +4170,50 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="n">
+        <v>10.01</v>
+      </c>
       <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="n">
+        <v>10.01</v>
+      </c>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr"/>
-      <c r="O91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-10.012</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="O91" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P91" s="2" t="n">
-        <v>0</v>
+        <v>-71414</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>0</v>
+        <v>949</v>
       </c>
       <c r="R91" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>-70465</v>
+      </c>
+      <c r="S91" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP1</t>
+          <t>US_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4100,163 +4249,153 @@
       <c r="R93" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S93" s="2" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VOLUME_2</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP1</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D99" t="n">
         <v>1</v>
       </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="n">
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
         <v>6.8</v>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="n">
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
         <v>6.8</v>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="n">
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
         <v>5</v>
       </c>
-      <c r="M95" t="n">
+      <c r="M99" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N95" t="n">
-        <v>-9904</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>-9904</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>197</v>
-      </c>
-      <c r="R95" t="n">
-        <v>-9707</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>-6.802</v>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>-9904</v>
-      </c>
-      <c r="O96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="2" t="n">
-        <v>-9904</v>
-      </c>
-      <c r="Q96" s="2" t="n">
-        <v>197</v>
-      </c>
-      <c r="R96" s="2" t="n">
-        <v>-9707</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" s="2" t="n">
-        <v>0</v>
+      <c r="N99" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>196</v>
+      </c>
+      <c r="R99" t="n">
+        <v>-9679</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1411</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>US_TR_MA</t>
+          <t>US_TR_VCP2</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4270,33 +4409,50 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="n">
+        <v>6.8</v>
+      </c>
       <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="n">
+        <v>6.8</v>
+      </c>
       <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P100" s="2" t="n">
-        <v>0</v>
+        <v>-9876</v>
       </c>
       <c r="Q100" s="2" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="R100" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>-9679</v>
+      </c>
+      <c r="S100" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>US_TR_JEO2</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -4332,16 +4488,17 @@
       <c r="R102" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S102" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>저점사다리</t>
+          <t>US_TR_MA</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4372,16 +4529,17 @@
       <c r="R104" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S104" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>US_TR_ADD1</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4412,6 +4570,253 @@
       <c r="R106" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="S106" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_LOW</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>미국수동</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S118"/>
+  <dimension ref="A1:S122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>58.3</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>8.1</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>7.98</v>
       </c>
       <c r="H7" t="n">
-        <v>3.51</v>
+        <v>4.11</v>
       </c>
       <c r="I7" t="n">
         <v>11.14</v>
@@ -896,22 +896,22 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>3.19</v>
+        <v>4.349</v>
       </c>
       <c r="N7" t="n">
-        <v>31606</v>
+        <v>39530</v>
       </c>
       <c r="O7" t="n">
-        <v>11.34</v>
+        <v>20.14</v>
       </c>
       <c r="P7" t="n">
-        <v>379274</v>
+        <v>395295</v>
       </c>
       <c r="Q7" t="n">
-        <v>2167</v>
+        <v>1654</v>
       </c>
       <c r="R7" t="n">
-        <v>381441</v>
+        <v>396949</v>
       </c>
       <c r="S7" t="n">
         <v>1415</v>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>56.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>3.14</v>
       </c>
       <c r="G8" t="n">
-        <v>5.84</v>
+        <v>6.33</v>
       </c>
       <c r="H8" t="n">
-        <v>2.74</v>
+        <v>3.59</v>
       </c>
       <c r="I8" t="n">
         <v>11.09</v>
@@ -957,22 +957,22 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>1.549</v>
+        <v>1.991</v>
       </c>
       <c r="N8" t="n">
-        <v>3288</v>
+        <v>7428</v>
       </c>
       <c r="O8" t="n">
-        <v>1.7</v>
+        <v>4.04</v>
       </c>
       <c r="P8" t="n">
-        <v>65757</v>
+        <v>118846</v>
       </c>
       <c r="Q8" t="n">
-        <v>7187</v>
+        <v>1274</v>
       </c>
       <c r="R8" t="n">
-        <v>72944</v>
+        <v>120120</v>
       </c>
       <c r="S8" t="n">
         <v>1415</v>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>44.8</v>
+        <v>44.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="G9" t="n">
-        <v>4.17</v>
+        <v>6.04</v>
       </c>
       <c r="H9" t="n">
-        <v>3.17</v>
+        <v>3.37</v>
       </c>
       <c r="I9" t="n">
         <v>13.51</v>
@@ -1018,22 +1018,22 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>0.116</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-427</v>
+        <v>-52</v>
       </c>
       <c r="O9" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="P9" t="n">
-        <v>-12396</v>
+        <v>-927</v>
       </c>
       <c r="Q9" t="n">
-        <v>6681</v>
+        <v>1619</v>
       </c>
       <c r="R9" t="n">
-        <v>-5715</v>
+        <v>692</v>
       </c>
       <c r="S9" t="n">
         <v>1415</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>17.9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>1.15</v>
+        <v>0.64</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8</v>
+        <v>0.44</v>
       </c>
       <c r="H10" t="n">
         <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2</v>
+        <v>0.84</v>
       </c>
       <c r="J10" t="n">
         <v>2.28</v>
@@ -1079,22 +1079,22 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>-0.448</v>
+        <v>-0.627</v>
       </c>
       <c r="N10" t="n">
-        <v>-6707</v>
+        <v>-9453</v>
       </c>
       <c r="O10" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="P10" t="n">
-        <v>-187786</v>
+        <v>-236325</v>
       </c>
       <c r="Q10" t="n">
-        <v>15579</v>
+        <v>11325</v>
       </c>
       <c r="R10" t="n">
-        <v>-172206</v>
+        <v>-225000</v>
       </c>
       <c r="S10" t="n">
         <v>1415</v>
@@ -1117,45 +1117,41 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="G11" t="n">
-        <v>8.56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="I11" t="n">
-        <v>12.69</v>
-      </c>
+        <v>8.41</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>10.01</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>-0.327</v>
+        <v>-8.407</v>
       </c>
       <c r="N11" t="n">
-        <v>-7621</v>
+        <v>-40645</v>
       </c>
       <c r="O11" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-53347</v>
+        <v>-81290</v>
       </c>
       <c r="Q11" t="n">
-        <v>15600</v>
+        <v>1145</v>
       </c>
       <c r="R11" t="n">
-        <v>-37747</v>
+        <v>-80145</v>
       </c>
       <c r="S11" t="n">
         <v>1411</v>
@@ -1178,19 +1174,19 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>37.8</v>
+        <v>37.1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>19.29</v>
@@ -1201,22 +1197,22 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="n">
-        <v>-0.005</v>
+        <v>-0.007</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>70873</v>
+        <v>74969</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>64978</v>
+        <v>34782</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>135851</v>
+        <v>109751</v>
       </c>
       <c r="S12" s="2" t="inlineStr"/>
     </row>
@@ -1706,10 +1702,10 @@
         <v>1.5</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>284665</v>
+        <v>284663</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>10879</v>
+        <v>10881</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>295544</v>
@@ -1842,63 +1838,63 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>2X단타</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E29" t="n">
-        <v>55.6</v>
+        <v>40.7</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="G29" t="n">
-        <v>1.17</v>
+        <v>5.47</v>
       </c>
       <c r="H29" t="n">
-        <v>4.19</v>
+        <v>3.29</v>
       </c>
       <c r="I29" t="n">
-        <v>3.38</v>
+        <v>17.35</v>
       </c>
       <c r="J29" t="n">
-        <v>7.04</v>
+        <v>20.1</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>185.95</v>
       </c>
       <c r="L29" t="n">
-        <v>1.75</v>
+        <v>187.46</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.213</v>
+        <v>0.274</v>
       </c>
       <c r="N29" t="n">
-        <v>-744</v>
+        <v>507</v>
       </c>
       <c r="O29" t="n">
-        <v>0.86</v>
+        <v>1.14</v>
       </c>
       <c r="P29" t="n">
-        <v>-6692</v>
+        <v>13680</v>
       </c>
       <c r="Q29" t="n">
-        <v>2139</v>
+        <v>1530</v>
       </c>
       <c r="R29" t="n">
-        <v>-4553</v>
+        <v>15210</v>
       </c>
       <c r="S29" t="n">
         <v>1415</v>
@@ -1907,175 +1903,258 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>2X단타</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+        <v>37.8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.11</v>
+      </c>
       <c r="G30" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>3.01</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.96</v>
+      </c>
       <c r="I30" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
+        <v>13.15</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.82</v>
+      </c>
       <c r="K30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>313.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>175.2</v>
+      </c>
       <c r="M30" t="n">
-        <v>8.56</v>
+        <v>-0.703</v>
       </c>
       <c r="N30" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
+        <v>-1271</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.67</v>
+      </c>
       <c r="P30" t="n">
-        <v>114933</v>
+        <v>-57188</v>
       </c>
       <c r="Q30" t="n">
-        <v>667</v>
+        <v>2829</v>
       </c>
       <c r="R30" t="n">
-        <v>115600</v>
+        <v>-54359</v>
       </c>
       <c r="S30" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>9840</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>108241</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>2806</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>111047</v>
-      </c>
-      <c r="S31" s="2" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>07/06~07/10</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>31</v>
+      </c>
+      <c r="E31" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="K31" t="n">
+        <v>247.7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>174.67</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-0.288</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1187</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>36789</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3306</v>
+      </c>
+      <c r="R31" t="n">
+        <v>40095</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>07/13~07/17</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>50</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="I32" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="J32" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="K32" t="n">
+        <v>533.86</v>
+      </c>
+      <c r="L32" t="n">
+        <v>403.59</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8720</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="P32" t="n">
+        <v>52321</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>523</v>
+      </c>
+      <c r="R32" t="n">
+        <v>52844</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>2X단타</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
+        <v>4.39</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7.08</v>
+      </c>
       <c r="H33" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
+        <v>1.26</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7.95</v>
+      </c>
       <c r="J33" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
+        <v>2.19</v>
+      </c>
+      <c r="K33" t="n">
+        <v>800.2</v>
+      </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>60.03</v>
       </c>
       <c r="M33" t="n">
-        <v>-2.607</v>
+        <v>2.446</v>
       </c>
       <c r="N33" t="n">
-        <v>-8011</v>
+        <v>5075</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P33" t="n">
-        <v>-16021</v>
+        <v>45679</v>
       </c>
       <c r="Q33" t="n">
-        <v>513</v>
+        <v>661</v>
       </c>
       <c r="R33" t="n">
-        <v>-15508</v>
+        <v>46340</v>
       </c>
       <c r="S33" t="n">
         <v>1415</v>
@@ -2084,196 +2163,145 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>2X단타</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F34" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="G34" t="n">
-        <v>1.37</v>
+        <v>6.04</v>
       </c>
       <c r="H34" t="n">
-        <v>0.74</v>
+        <v>2.52</v>
       </c>
       <c r="I34" t="n">
-        <v>1.37</v>
+        <v>13.51</v>
       </c>
       <c r="J34" t="n">
-        <v>1.32</v>
+        <v>4.74</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>2281.51</v>
       </c>
       <c r="L34" t="n">
-        <v>5.67</v>
+        <v>27.54</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.217</v>
+        <v>1.758</v>
       </c>
       <c r="N34" t="n">
-        <v>-13272</v>
+        <v>851</v>
       </c>
       <c r="O34" t="n">
-        <v>0.02</v>
+        <v>1.14</v>
       </c>
       <c r="P34" t="n">
-        <v>-53089</v>
+        <v>13616</v>
       </c>
       <c r="Q34" t="n">
-        <v>5913</v>
+        <v>1561</v>
       </c>
       <c r="R34" t="n">
-        <v>-47176</v>
+        <v>15177</v>
       </c>
       <c r="S34" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>-0.136</v>
-      </c>
-      <c r="N35" t="n">
-        <v>-2389</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>-4777</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2924</v>
-      </c>
-      <c r="R35" t="n">
-        <v>-1854</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" t="n">
-        <v>100</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>14</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
-        <v>1.042</v>
-      </c>
-      <c r="N36" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>48540</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4254</v>
-      </c>
-      <c r="R36" t="n">
-        <v>52794</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1415</v>
-      </c>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>600.88</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>163.85</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>104897</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>10410</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>115307</v>
+      </c>
+      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>삼닉v3_저2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2287,47 +2315,47 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0.86</v>
+        <v>0.34</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>1.53</v>
+        <v>0.49</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>4.67</v>
+        <v>13.35</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.864</v>
+        <v>-0.341</v>
       </c>
       <c r="N37" t="n">
-        <v>-28997</v>
+        <v>-4880</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-86990</v>
+        <v>-14641</v>
       </c>
       <c r="Q37" t="n">
-        <v>13787</v>
+        <v>1291</v>
       </c>
       <c r="R37" t="n">
-        <v>-73203</v>
+        <v>-13350</v>
       </c>
       <c r="S37" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>삼닉v3_저2</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2336,56 +2364,50 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>1.12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>2.2</v>
-      </c>
+        <v>0.34</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>10.75</v>
-      </c>
+        <v>0.49</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="n">
-        <v>4.4</v>
+        <v>13.35</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.416</v>
+        <v>-0.341</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-8024</v>
+        <v>-4880</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>-112338</v>
+        <v>-14641</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>27391</v>
+        <v>1291</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-84947</v>
+        <v>-13350</v>
       </c>
       <c r="S38" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2X단타</t>
+          <t>삼닉v3_추세</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2395,192 +2417,113 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>06/22~06/26</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G40" t="n">
-        <v>5.47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I40" t="n">
-        <v>17.35</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>185.95</v>
-      </c>
+        <v>2.28</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>187.46</v>
+        <v>29.99</v>
       </c>
       <c r="M40" t="n">
-        <v>0.274</v>
+        <v>-0.912</v>
       </c>
       <c r="N40" t="n">
-        <v>507</v>
+        <v>-13839</v>
       </c>
       <c r="O40" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>13680</v>
+        <v>-138394</v>
       </c>
       <c r="Q40" t="n">
-        <v>1530</v>
+        <v>4519</v>
       </c>
       <c r="R40" t="n">
-        <v>15210</v>
+        <v>-133875</v>
       </c>
       <c r="S40" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>06/29~07/03</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>45</v>
-      </c>
-      <c r="E41" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G41" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I41" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="J41" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="K41" t="n">
-        <v>313.5</v>
-      </c>
-      <c r="L41" t="n">
-        <v>175.2</v>
-      </c>
-      <c r="M41" t="n">
-        <v>-0.703</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-1271</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="P41" t="n">
-        <v>-57188</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2829</v>
-      </c>
-      <c r="R41" t="n">
-        <v>-54359</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>07/06~07/10</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>31</v>
-      </c>
-      <c r="E42" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G42" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I42" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="J42" t="n">
-        <v>9.01</v>
-      </c>
-      <c r="K42" t="n">
-        <v>247.7</v>
-      </c>
-      <c r="L42" t="n">
-        <v>174.67</v>
-      </c>
-      <c r="M42" t="n">
-        <v>-0.288</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1187</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P42" t="n">
-        <v>36789</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3306</v>
-      </c>
-      <c r="R42" t="n">
-        <v>40095</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1415</v>
-      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>-0.912</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>-138394</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>4519</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>-133875</v>
+      </c>
+      <c r="S41" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2X단타</t>
+          <t>삼닉v3_MA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2590,192 +2533,125 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E43" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="F43" t="n">
-        <v>3.53</v>
+        <v>0.72</v>
       </c>
       <c r="G43" t="n">
-        <v>6.86</v>
+        <v>0.44</v>
       </c>
       <c r="H43" t="n">
-        <v>4.11</v>
+        <v>0.64</v>
       </c>
       <c r="I43" t="n">
-        <v>11.14</v>
+        <v>0.84</v>
       </c>
       <c r="J43" t="n">
-        <v>9.65</v>
+        <v>1.81</v>
       </c>
       <c r="K43" t="n">
-        <v>533.86</v>
+        <v>14.12</v>
       </c>
       <c r="L43" t="n">
-        <v>403.59</v>
+        <v>26.24</v>
       </c>
       <c r="M43" t="n">
-        <v>1.375</v>
+        <v>-0.461</v>
       </c>
       <c r="N43" t="n">
-        <v>8720</v>
+        <v>-6941</v>
       </c>
       <c r="O43" t="n">
-        <v>3.53</v>
+        <v>0.14</v>
       </c>
       <c r="P43" t="n">
-        <v>52321</v>
+        <v>-83290</v>
       </c>
       <c r="Q43" t="n">
-        <v>523</v>
+        <v>5515</v>
       </c>
       <c r="R43" t="n">
-        <v>52844</v>
+        <v>-77775</v>
       </c>
       <c r="S43" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>삼닉v3_MA</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>9</v>
-      </c>
-      <c r="E44" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="F44" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="G44" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I44" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="K44" t="n">
-        <v>800.2</v>
-      </c>
-      <c r="L44" t="n">
-        <v>60.03</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="N44" t="n">
-        <v>5075</v>
-      </c>
-      <c r="O44" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P44" t="n">
-        <v>45679</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>661</v>
-      </c>
-      <c r="R44" t="n">
-        <v>46340</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>16</v>
-      </c>
-      <c r="E45" t="n">
-        <v>50</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="G45" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I45" t="n">
-        <v>13.51</v>
-      </c>
-      <c r="J45" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2281.51</v>
-      </c>
-      <c r="L45" t="n">
-        <v>27.54</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1.758</v>
-      </c>
-      <c r="N45" t="n">
-        <v>851</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P45" t="n">
-        <v>13616</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1561</v>
-      </c>
-      <c r="R45" t="n">
-        <v>15177</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1415</v>
-      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>-0.461</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-6941</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>-83290</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>5515</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>-77775</v>
+      </c>
+      <c r="S44" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2X단타</t>
+          <t>삼닉v3_미분류</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2789,231 +2665,116 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>600.88</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>163.85</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>783</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>1.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="n">
-        <v>104898</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>10409</v>
+        <v>0</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>115307</v>
+        <v>0</v>
       </c>
       <c r="S46" s="2" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>삼닉v3_저2</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>5minHL</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="M48" t="n">
-        <v>-0.341</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-4880</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>-14641</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1291</v>
-      </c>
-      <c r="R48" t="n">
-        <v>-13350</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>삼닉v3_저2</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>5minHL2</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>-0.341</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>-4880</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>-14641</v>
-      </c>
-      <c r="Q49" s="2" t="n">
-        <v>1291</v>
-      </c>
-      <c r="R49" s="2" t="n">
-        <v>-13350</v>
-      </c>
-      <c r="S49" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M51" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N51" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>-138394</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4519</v>
-      </c>
-      <c r="R51" t="n">
-        <v>-133875</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>삼닉v3_추세</t>
+          <t>5minHL_동시</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3027,50 +2788,34 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="n">
-        <v>0.91</v>
-      </c>
+      <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="n">
-        <v>2.28</v>
-      </c>
+      <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M52" s="2" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N52" s="2" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O52" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="n">
-        <v>-138394</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>4519</v>
+        <v>0</v>
       </c>
       <c r="R52" s="2" t="n">
-        <v>-133875</v>
+        <v>0</v>
       </c>
       <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>삼닉v3_MA</t>
+          <t>5minHL_미분류</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3080,166 +2825,300 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.44</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.84</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="K54" t="n">
-        <v>14.12</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>26.24</v>
+        <v>49.85</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.461</v>
+        <v>-2.747</v>
       </c>
       <c r="N54" t="n">
-        <v>-6941</v>
+        <v>-2426</v>
       </c>
       <c r="O54" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-83290</v>
+        <v>-2426</v>
       </c>
       <c r="Q54" t="n">
-        <v>5515</v>
+        <v>26</v>
       </c>
       <c r="R54" t="n">
-        <v>-77775</v>
+        <v>-2400</v>
       </c>
       <c r="S54" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>삼닉v3_MA</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>26.24</v>
-      </c>
-      <c r="M55" s="2" t="n">
-        <v>-0.461</v>
-      </c>
-      <c r="N55" s="2" t="n">
-        <v>-6941</v>
-      </c>
-      <c r="O55" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>-83290</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>5515</v>
-      </c>
-      <c r="R55" s="2" t="n">
-        <v>-77775</v>
-      </c>
-      <c r="S55" s="2" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>06/29~07/03</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>50</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1279.97</v>
+      </c>
+      <c r="L55" t="n">
+        <v>875.09</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-0.191</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4951</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P55" t="n">
+        <v>29704</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>756</v>
+      </c>
+      <c r="R55" t="n">
+        <v>30460</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>07/06~07/10</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4319.93</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1351.81</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-2.059</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-3794</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-11383</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>153</v>
+      </c>
+      <c r="R56" t="n">
+        <v>-11230</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>삼닉v3_미분류</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
-      <c r="O57" s="2" t="inlineStr"/>
-      <c r="P57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>100</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>30</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1700</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>5756.96</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-7272</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-14543</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>58</v>
+      </c>
+      <c r="R58" t="n">
+        <v>-14485</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>5minHL</t>
+          <t>5minHL_미분류</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3253,39 +3132,61 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
-      <c r="O59" s="2" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>1633.99</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>2111.58</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>-1.689</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>1.07</v>
+      </c>
       <c r="P59" s="2" t="n">
-        <v>0</v>
+        <v>3022</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>0</v>
+        <v>4045</v>
       </c>
       <c r="S59" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>5minHL2</t>
+          <t>KR_TR_ORD_A</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3321,12 +3222,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>5minHL_동시</t>
+          <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3360,539 +3261,355 @@
       <c r="S63" s="2" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_VOLUME_2</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_VCP1</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_MA</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_ADD1</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>미국VCP</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
         <v>1</v>
       </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M65" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N65" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>26</v>
-      </c>
-      <c r="R65" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>06/29~07/03</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>6</v>
-      </c>
-      <c r="E66" t="n">
-        <v>50</v>
-      </c>
-      <c r="F66" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G66" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I66" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J66" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1279.97</v>
-      </c>
-      <c r="L66" t="n">
-        <v>875.09</v>
-      </c>
-      <c r="M66" t="n">
-        <v>-0.191</v>
-      </c>
-      <c r="N66" t="n">
-        <v>4951</v>
-      </c>
-      <c r="O66" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P66" t="n">
-        <v>29704</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>756</v>
-      </c>
-      <c r="R66" t="n">
-        <v>30460</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>07/06~07/10</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="n">
         <v>3</v>
       </c>
-      <c r="E67" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H67" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J67" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="K67" t="n">
-        <v>4319.93</v>
-      </c>
-      <c r="L67" t="n">
-        <v>1351.81</v>
-      </c>
-      <c r="M67" t="n">
-        <v>-2.059</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-3794</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P67" t="n">
-        <v>-11383</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>153</v>
-      </c>
-      <c r="R67" t="n">
-        <v>-11230</v>
-      </c>
-      <c r="S67" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="n">
-        <v>100</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="n">
-        <v>1.678</v>
-      </c>
-      <c r="N68" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="n">
-        <v>1670</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>30</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1700</v>
-      </c>
-      <c r="S68" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="n">
-        <v>5756.96</v>
-      </c>
-      <c r="M69" t="n">
-        <v>-6.785</v>
-      </c>
-      <c r="N69" t="n">
-        <v>-7272</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>-14543</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>58</v>
-      </c>
-      <c r="R69" t="n">
-        <v>-14485</v>
-      </c>
-      <c r="S69" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>1633.99</v>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>2111.58</v>
-      </c>
-      <c r="M70" s="2" t="n">
-        <v>-1.689</v>
-      </c>
-      <c r="N70" s="2" t="n">
-        <v>232</v>
-      </c>
-      <c r="O70" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P70" s="2" t="n">
-        <v>3022</v>
-      </c>
-      <c r="Q70" s="2" t="n">
-        <v>1023</v>
-      </c>
-      <c r="R70" s="2" t="n">
-        <v>4045</v>
-      </c>
-      <c r="S70" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>KR_TR_ORD_A</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>KR_TR_VOLUME_1</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>KR_TR_VOLUME_2</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>KR_TR_VCP1</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="2" t="inlineStr"/>
+      <c r="M79" t="n">
+        <v>-10.012</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>949</v>
+      </c>
+      <c r="R79" t="n">
+        <v>-70465</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1411</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>US_TR_ORD_A</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -3906,34 +3623,50 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="n">
+        <v>10.01</v>
+      </c>
       <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="n">
+        <v>10.01</v>
+      </c>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-10.012</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P80" s="2" t="n">
-        <v>0</v>
+        <v>-71414</v>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>0</v>
+        <v>949</v>
       </c>
       <c r="R80" s="2" t="n">
-        <v>0</v>
+        <v>-70465</v>
       </c>
       <c r="S80" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_JEO2</t>
+          <t>US_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3974,7 +3707,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_MA</t>
+          <t>US_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4015,7 +3748,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ADD1</t>
+          <t>US_TR_VCP1</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4054,109 +3787,125 @@
       <c r="S86" s="2" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>미국VCP</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="n">
+        <v>5</v>
+      </c>
+      <c r="M88" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>196</v>
+      </c>
+      <c r="R88" t="n">
+        <v>-9679</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_A</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
+      <c r="D89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="n">
-        <v>3</v>
-      </c>
-      <c r="M90" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N90" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>949</v>
-      </c>
-      <c r="R90" t="n">
-        <v>-70465</v>
-      </c>
-      <c r="S90" t="n">
-        <v>1411</v>
-      </c>
+      <c r="E89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="O89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>-9679</v>
+      </c>
+      <c r="S89" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>US_TR_ORD_A</t>
+          <t>US_TR_JEO2</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4170,50 +3919,34 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="n">
-        <v>10.01</v>
-      </c>
+      <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="n">
-        <v>10.01</v>
-      </c>
+      <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="O91" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
       <c r="P91" s="2" t="n">
-        <v>-71414</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>949</v>
+        <v>0</v>
       </c>
       <c r="R91" s="2" t="n">
-        <v>-70465</v>
+        <v>0</v>
       </c>
       <c r="S91" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_1</t>
+          <t>US_TR_MA</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4254,7 +3987,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_2</t>
+          <t>US_TR_ADD1</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4295,7 +4028,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP1</t>
+          <t>US_TR_LEGACY</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4334,289 +4067,429 @@
       <c r="S97" s="2" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_LOW</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>07/13~07/17</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" t="n">
+        <v>-2.607</v>
+      </c>
+      <c r="N105" t="n">
+        <v>-8011</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>-16021</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>513</v>
+      </c>
+      <c r="R105" t="n">
+        <v>-15508</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" t="n">
+        <v>25</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="M106" t="n">
+        <v>-0.217</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-13272</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P106" t="n">
+        <v>-53089</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>5913</v>
+      </c>
+      <c r="R106" t="n">
+        <v>-47176</v>
+      </c>
+      <c r="S106" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M107" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="N107" t="n">
+        <v>-2389</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>-4777</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>2924</v>
+      </c>
+      <c r="R107" t="n">
+        <v>-1854</v>
+      </c>
+      <c r="S107" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" t="n">
+        <v>100</v>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>14</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N108" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R108" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S108" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="n">
-        <v>5</v>
-      </c>
-      <c r="M99" t="n">
-        <v>-6.802</v>
-      </c>
-      <c r="N99" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>196</v>
-      </c>
-      <c r="R99" t="n">
-        <v>-9679</v>
-      </c>
-      <c r="S99" t="n">
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M109" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R109" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S109" t="n">
         <v>1411</v>
       </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>-6.802</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="O100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="2" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>-9679</v>
-      </c>
-      <c r="S100" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr"/>
-      <c r="P104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_ADD1</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr"/>
-      <c r="P106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
-      <c r="P108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_TREND</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -4630,80 +4503,175 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-0.416</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>-8024</v>
+      </c>
+      <c r="O110" s="2" t="n">
+        <v>0.31</v>
+      </c>
       <c r="P110" s="2" t="n">
-        <v>0</v>
+        <v>-112337</v>
       </c>
       <c r="Q110" s="2" t="n">
-        <v>0</v>
+        <v>27391</v>
       </c>
       <c r="R110" s="2" t="n">
-        <v>0</v>
+        <v>-84947</v>
       </c>
       <c r="S110" s="2" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_LOW</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" s="2" t="inlineStr"/>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-      <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="2" t="inlineStr"/>
-      <c r="O112" s="2" t="inlineStr"/>
-      <c r="P112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" s="2" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>9</v>
+      </c>
+      <c r="E112" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H112" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I112" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J112" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N112" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P112" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R112" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" t="n">
+        <v>100</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N113" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>667</v>
+      </c>
+      <c r="R113" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1411</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4712,111 +4680,312 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="2" t="inlineStr"/>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="2" t="inlineStr"/>
-      <c r="O114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>9840</v>
+      </c>
+      <c r="O114" s="2" t="n">
+        <v>3.23</v>
+      </c>
       <c r="P114" s="2" t="n">
-        <v>0</v>
+        <v>108241</v>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>0</v>
+        <v>2806</v>
       </c>
       <c r="R114" s="2" t="n">
-        <v>0</v>
+        <v>111047</v>
       </c>
       <c r="S114" s="2" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr"/>
-      <c r="O116" s="2" t="inlineStr"/>
-      <c r="P116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" s="2" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>9</v>
+      </c>
+      <c r="E116" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H116" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I116" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J116" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K116" t="n">
+        <v>3</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M116" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N116" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P116" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R116" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="n">
+        <v>100</v>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N117" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>667</v>
+      </c>
+      <c r="R117" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1411</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>9840</v>
+      </c>
+      <c r="O118" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="P118" s="2" t="n">
+        <v>108241</v>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>2806</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>111047</v>
+      </c>
+      <c r="S118" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>미국수동</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" s="2" t="inlineStr"/>
-      <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
-      <c r="M118" s="2" t="inlineStr"/>
-      <c r="N118" s="2" t="inlineStr"/>
-      <c r="O118" s="2" t="inlineStr"/>
-      <c r="P118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" s="2" t="inlineStr"/>
+      <c r="D122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S122"/>
+  <dimension ref="A1:S124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1158,122 +1158,116 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>통합</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6421</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>27249</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1115</v>
+      </c>
+      <c r="R12" t="n">
+        <v>28365</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>224</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="H12" s="2" t="n">
+      <c r="D13" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="H13" s="2" t="n">
         <v>2.75</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>335</v>
-      </c>
-      <c r="O12" s="2" t="n">
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="O13" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="P12" s="2" t="n">
-        <v>74969</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>34782</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>109751</v>
-      </c>
-      <c r="S12" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>주도주</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>06/08~06/12</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-3.964</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-58941</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-176822</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1322</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-175500</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1415</v>
-      </c>
+      <c r="P13" s="2" t="n">
+        <v>102218</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>35897</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>138116</v>
+      </c>
+      <c r="S13" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1288,53 +1282,47 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>06/15~06/19</t>
+          <t>06/08~06/12</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="G15" t="n">
-        <v>7.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="I15" t="n">
-        <v>19.29</v>
-      </c>
+        <v>3.96</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.71</v>
-      </c>
+        <v>4.35</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.378</v>
+        <v>-3.964</v>
       </c>
       <c r="N15" t="n">
-        <v>16263</v>
+        <v>-58941</v>
       </c>
       <c r="O15" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>227688</v>
+        <v>-176822</v>
       </c>
       <c r="Q15" t="n">
-        <v>2172</v>
+        <v>1322</v>
       </c>
       <c r="R15" t="n">
-        <v>229860</v>
+        <v>-175500</v>
       </c>
       <c r="S15" t="n">
         <v>1415</v>
@@ -1353,47 +1341,53 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>06/22~06/26</t>
+          <t>06/15~06/19</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+        <v>3.69</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.79</v>
+      </c>
       <c r="H16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="I16" t="n">
+        <v>19.29</v>
+      </c>
       <c r="J16" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>4.76</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.71</v>
+      </c>
       <c r="L16" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.001</v>
+        <v>2.378</v>
       </c>
       <c r="N16" t="n">
-        <v>-21403</v>
+        <v>16263</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P16" t="n">
-        <v>-235428</v>
+        <v>227688</v>
       </c>
       <c r="Q16" t="n">
-        <v>2878</v>
+        <v>2172</v>
       </c>
       <c r="R16" t="n">
-        <v>-232550</v>
+        <v>229860</v>
       </c>
       <c r="S16" t="n">
         <v>1415</v>
@@ -1412,53 +1406,47 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I17" t="n">
-        <v>4.74</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
+        <v>8.44</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>3.33</v>
+        <v>0.91</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.022</v>
+        <v>-3.001</v>
       </c>
       <c r="N17" t="n">
-        <v>14731</v>
+        <v>-21403</v>
       </c>
       <c r="O17" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>58925</v>
+        <v>-235428</v>
       </c>
       <c r="Q17" t="n">
-        <v>1075</v>
+        <v>2878</v>
       </c>
       <c r="R17" t="n">
-        <v>60000</v>
+        <v>-232550</v>
       </c>
       <c r="S17" t="n">
         <v>1415</v>
@@ -1477,53 +1465,53 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>0.67</v>
+        <v>7.37</v>
       </c>
       <c r="G18" t="n">
-        <v>1.34</v>
+        <v>4.74</v>
       </c>
       <c r="H18" t="n">
-        <v>1.38</v>
+        <v>2.94</v>
       </c>
       <c r="I18" t="n">
-        <v>4.21</v>
+        <v>4.74</v>
       </c>
       <c r="J18" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.021</v>
+        <v>-1.022</v>
       </c>
       <c r="N18" t="n">
-        <v>-521</v>
+        <v>14731</v>
       </c>
       <c r="O18" t="n">
-        <v>0.67</v>
+        <v>2.46</v>
       </c>
       <c r="P18" t="n">
-        <v>-4171</v>
+        <v>58925</v>
       </c>
       <c r="Q18" t="n">
-        <v>1720</v>
+        <v>1075</v>
       </c>
       <c r="R18" t="n">
-        <v>-2451</v>
+        <v>60000</v>
       </c>
       <c r="S18" t="n">
         <v>1415</v>
@@ -1542,43 +1530,53 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.67</v>
+      </c>
       <c r="G19" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>1.34</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.38</v>
+      </c>
       <c r="I19" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>4.21</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.27</v>
+      </c>
       <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" t="n">
-        <v>8.81</v>
+        <v>-0.021</v>
       </c>
       <c r="N19" t="n">
-        <v>85744</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
+        <v>-521</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.67</v>
+      </c>
       <c r="P19" t="n">
-        <v>342974</v>
+        <v>-4171</v>
       </c>
       <c r="Q19" t="n">
-        <v>1131</v>
+        <v>1720</v>
       </c>
       <c r="R19" t="n">
-        <v>344105</v>
+        <v>-2451</v>
       </c>
       <c r="S19" t="n">
         <v>1415</v>
@@ -1597,308 +1595,298 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.21</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="H20" t="n">
-        <v>9.42</v>
-      </c>
+        <v>8.81</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="J20" t="n">
-        <v>11.77</v>
-      </c>
+        <v>11.03</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>8.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>1.361</v>
+        <v>8.81</v>
       </c>
       <c r="N20" t="n">
-        <v>11916</v>
-      </c>
-      <c r="O20" t="n">
-        <v>4.43</v>
-      </c>
+        <v>85744</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>71497</v>
+        <v>342974</v>
       </c>
       <c r="Q20" t="n">
-        <v>583</v>
+        <v>1131</v>
       </c>
       <c r="R20" t="n">
-        <v>72080</v>
+        <v>344105</v>
       </c>
       <c r="S20" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>주도주</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="J21" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="N21" t="n">
+        <v>11916</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P21" t="n">
+        <v>71497</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>583</v>
+      </c>
+      <c r="R21" t="n">
+        <v>72080</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>주도주</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D22" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E22" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F22" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G22" s="2" t="n">
         <v>6.34</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>3.31</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="I22" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>11.77</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>1.47</v>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="M22" s="2" t="n">
         <v>0.551</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="N22" s="2" t="n">
         <v>5693</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="O22" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>284663</v>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>10881</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="R22" s="2" t="n">
         <v>295544</v>
       </c>
-      <c r="S21" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>ROCKET</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>ABC-VCP</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>TV알림</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>27</v>
-      </c>
-      <c r="E29" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H29" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I29" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J29" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L29" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N29" t="n">
-        <v>507</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P29" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R29" t="n">
-        <v>15210</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1913,53 +1901,53 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="F30" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="G30" t="n">
-        <v>3.01</v>
+        <v>5.47</v>
       </c>
       <c r="H30" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="I30" t="n">
-        <v>13.15</v>
+        <v>17.35</v>
       </c>
       <c r="J30" t="n">
-        <v>5.82</v>
+        <v>20.1</v>
       </c>
       <c r="K30" t="n">
-        <v>313.5</v>
+        <v>185.95</v>
       </c>
       <c r="L30" t="n">
-        <v>175.2</v>
+        <v>187.46</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.703</v>
+        <v>0.274</v>
       </c>
       <c r="N30" t="n">
-        <v>-1271</v>
+        <v>507</v>
       </c>
       <c r="O30" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="P30" t="n">
-        <v>-57188</v>
+        <v>13680</v>
       </c>
       <c r="Q30" t="n">
-        <v>2829</v>
+        <v>1530</v>
       </c>
       <c r="R30" t="n">
-        <v>-54359</v>
+        <v>15210</v>
       </c>
       <c r="S30" t="n">
         <v>1415</v>
@@ -1978,53 +1966,53 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E31" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="G31" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="H31" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I31" t="n">
-        <v>8.68</v>
+        <v>13.15</v>
       </c>
       <c r="J31" t="n">
-        <v>9.01</v>
+        <v>5.82</v>
       </c>
       <c r="K31" t="n">
-        <v>247.7</v>
+        <v>313.5</v>
       </c>
       <c r="L31" t="n">
-        <v>174.67</v>
+        <v>175.2</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.288</v>
+        <v>-0.703</v>
       </c>
       <c r="N31" t="n">
-        <v>1187</v>
+        <v>-1271</v>
       </c>
       <c r="O31" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="P31" t="n">
-        <v>36789</v>
+        <v>-57188</v>
       </c>
       <c r="Q31" t="n">
-        <v>3306</v>
+        <v>2829</v>
       </c>
       <c r="R31" t="n">
-        <v>40095</v>
+        <v>-54359</v>
       </c>
       <c r="S31" t="n">
         <v>1415</v>
@@ -2043,53 +2031,53 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E32" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="F32" t="n">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="G32" t="n">
-        <v>6.86</v>
+        <v>3.14</v>
       </c>
       <c r="H32" t="n">
-        <v>4.11</v>
+        <v>2.76</v>
       </c>
       <c r="I32" t="n">
-        <v>11.14</v>
+        <v>8.68</v>
       </c>
       <c r="J32" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="K32" t="n">
-        <v>533.86</v>
+        <v>247.7</v>
       </c>
       <c r="L32" t="n">
-        <v>403.59</v>
+        <v>174.67</v>
       </c>
       <c r="M32" t="n">
-        <v>1.375</v>
+        <v>-0.288</v>
       </c>
       <c r="N32" t="n">
-        <v>8720</v>
+        <v>1187</v>
       </c>
       <c r="O32" t="n">
-        <v>3.53</v>
+        <v>1.3</v>
       </c>
       <c r="P32" t="n">
-        <v>52321</v>
+        <v>36789</v>
       </c>
       <c r="Q32" t="n">
-        <v>523</v>
+        <v>3306</v>
       </c>
       <c r="R32" t="n">
-        <v>52844</v>
+        <v>40095</v>
       </c>
       <c r="S32" t="n">
         <v>1415</v>
@@ -2108,53 +2096,53 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="G33" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="H33" t="n">
-        <v>1.26</v>
+        <v>4.11</v>
       </c>
       <c r="I33" t="n">
-        <v>7.95</v>
+        <v>11.14</v>
       </c>
       <c r="J33" t="n">
-        <v>2.19</v>
+        <v>9.65</v>
       </c>
       <c r="K33" t="n">
-        <v>800.2</v>
+        <v>533.86</v>
       </c>
       <c r="L33" t="n">
-        <v>60.03</v>
+        <v>403.59</v>
       </c>
       <c r="M33" t="n">
-        <v>2.446</v>
+        <v>1.375</v>
       </c>
       <c r="N33" t="n">
-        <v>5075</v>
+        <v>8720</v>
       </c>
       <c r="O33" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P33" t="n">
-        <v>45679</v>
+        <v>52321</v>
       </c>
       <c r="Q33" t="n">
-        <v>661</v>
+        <v>523</v>
       </c>
       <c r="R33" t="n">
-        <v>46340</v>
+        <v>52844</v>
       </c>
       <c r="S33" t="n">
         <v>1415</v>
@@ -2173,703 +2161,709 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F34" t="n">
-        <v>1.14</v>
+        <v>4.39</v>
       </c>
       <c r="G34" t="n">
-        <v>6.04</v>
+        <v>7.08</v>
       </c>
       <c r="H34" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>13.51</v>
+        <v>7.95</v>
       </c>
       <c r="J34" t="n">
-        <v>4.74</v>
+        <v>2.19</v>
       </c>
       <c r="K34" t="n">
-        <v>2281.51</v>
+        <v>800.2</v>
       </c>
       <c r="L34" t="n">
-        <v>27.54</v>
+        <v>60.03</v>
       </c>
       <c r="M34" t="n">
-        <v>1.758</v>
+        <v>2.446</v>
       </c>
       <c r="N34" t="n">
-        <v>851</v>
+        <v>5075</v>
       </c>
       <c r="O34" t="n">
-        <v>1.14</v>
+        <v>3.51</v>
       </c>
       <c r="P34" t="n">
-        <v>13616</v>
+        <v>45679</v>
       </c>
       <c r="Q34" t="n">
-        <v>1561</v>
+        <v>661</v>
       </c>
       <c r="R34" t="n">
-        <v>15177</v>
+        <v>46340</v>
       </c>
       <c r="S34" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>16</v>
+      </c>
+      <c r="E35" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I35" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L35" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N35" t="n">
+        <v>851</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P35" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R35" t="n">
+        <v>15177</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D36" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E36" s="2" t="n">
         <v>41.8</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F36" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>2.87</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J36" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K36" s="2" t="n">
         <v>600.88</v>
       </c>
-      <c r="L35" s="2" t="n">
+      <c r="L36" s="2" t="n">
         <v>163.85</v>
       </c>
-      <c r="M35" s="2" t="n">
+      <c r="M36" s="2" t="n">
         <v>0.188</v>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="N36" s="2" t="n">
         <v>783</v>
       </c>
-      <c r="O35" s="2" t="n">
+      <c r="O36" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="P35" s="2" t="n">
+      <c r="P36" s="2" t="n">
         <v>104897</v>
       </c>
-      <c r="Q35" s="2" t="n">
+      <c r="Q36" s="2" t="n">
         <v>10410</v>
       </c>
-      <c r="R35" s="2" t="n">
+      <c r="R36" s="2" t="n">
         <v>115307</v>
       </c>
-      <c r="S35" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D38" t="n">
         <v>3</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="n">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
         <v>0.34</v>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
         <v>0.49</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
         <v>13.35</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M38" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N38" t="n">
         <v>-4880</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q38" t="n">
         <v>1291</v>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>-13350</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S38" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="n">
+      <c r="E39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="n">
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M38" s="2" t="n">
+      <c r="M39" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="N39" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="2" t="n">
+      <c r="O39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q38" s="2" t="n">
+      <c r="Q39" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R38" s="2" t="n">
+      <c r="R39" s="2" t="n">
         <v>-13350</v>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D41" t="n">
         <v>10</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="n">
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="n">
         <v>0.91</v>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
         <v>2.28</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
         <v>29.99</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M41" t="n">
         <v>-0.912</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N41" t="n">
         <v>-13839</v>
       </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>-138394</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q41" t="n">
         <v>4519</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R41" t="n">
         <v>-133875</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S41" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D42" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="n">
+      <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="n">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="n">
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="n">
         <v>29.99</v>
       </c>
-      <c r="M41" s="2" t="n">
+      <c r="M42" s="2" t="n">
         <v>-0.912</v>
       </c>
-      <c r="N41" s="2" t="n">
+      <c r="N42" s="2" t="n">
         <v>-13839</v>
       </c>
-      <c r="O41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2" t="n">
+      <c r="O42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2" t="n">
         <v>-138394</v>
       </c>
-      <c r="Q41" s="2" t="n">
+      <c r="Q42" s="2" t="n">
         <v>4519</v>
       </c>
-      <c r="R41" s="2" t="n">
+      <c r="R42" s="2" t="n">
         <v>-133875</v>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D44" t="n">
         <v>12</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E44" t="n">
         <v>16.7</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F44" t="n">
         <v>0.72</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G44" t="n">
         <v>0.44</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H44" t="n">
         <v>0.64</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I44" t="n">
         <v>0.84</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J44" t="n">
         <v>1.81</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K44" t="n">
         <v>14.12</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L44" t="n">
         <v>26.24</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M44" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N44" t="n">
         <v>-6941</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O44" t="n">
         <v>0.14</v>
       </c>
-      <c r="P43" t="n">
+      <c r="P44" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q44" t="n">
         <v>5515</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R44" t="n">
         <v>-77775</v>
       </c>
-      <c r="S43" t="n">
+      <c r="S44" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D45" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E45" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F45" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>0.64</v>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="I45" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="J45" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K45" s="2" t="n">
         <v>14.12</v>
       </c>
-      <c r="L44" s="2" t="n">
+      <c r="L45" s="2" t="n">
         <v>26.24</v>
       </c>
-      <c r="M44" s="2" t="n">
+      <c r="M45" s="2" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N44" s="2" t="n">
+      <c r="N45" s="2" t="n">
         <v>-6941</v>
       </c>
-      <c r="O44" s="2" t="n">
+      <c r="O45" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="P44" s="2" t="n">
+      <c r="P45" s="2" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q44" s="2" t="n">
+      <c r="Q45" s="2" t="n">
         <v>5515</v>
       </c>
-      <c r="R44" s="2" t="n">
+      <c r="R45" s="2" t="n">
         <v>-77775</v>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_미분류</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="D47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>5minHL</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="D49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>5minHL2</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="D51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>5minHL_동시</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M54" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N54" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>26</v>
-      </c>
-      <c r="R54" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="S54" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2884,53 +2878,47 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G55" t="n">
-        <v>2.47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I55" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1279.97</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>875.09</v>
+        <v>49.85</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.191</v>
+        <v>-2.747</v>
       </c>
       <c r="N55" t="n">
-        <v>4951</v>
+        <v>-2426</v>
       </c>
       <c r="O55" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>29704</v>
+        <v>-2426</v>
       </c>
       <c r="Q55" t="n">
-        <v>756</v>
+        <v>26</v>
       </c>
       <c r="R55" t="n">
-        <v>30460</v>
+        <v>-2400</v>
       </c>
       <c r="S55" t="n">
         <v>1415</v>
@@ -2949,53 +2937,53 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="G56" t="n">
-        <v>0.08</v>
+        <v>2.47</v>
       </c>
       <c r="H56" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="I56" t="n">
-        <v>0.08</v>
+        <v>4.6</v>
       </c>
       <c r="J56" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="K56" t="n">
-        <v>4319.93</v>
+        <v>1279.97</v>
       </c>
       <c r="L56" t="n">
-        <v>1351.81</v>
+        <v>875.09</v>
       </c>
       <c r="M56" t="n">
-        <v>-2.059</v>
+        <v>-0.191</v>
       </c>
       <c r="N56" t="n">
-        <v>-3794</v>
+        <v>4951</v>
       </c>
       <c r="O56" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="P56" t="n">
-        <v>-11383</v>
+        <v>29704</v>
       </c>
       <c r="Q56" t="n">
-        <v>153</v>
+        <v>756</v>
       </c>
       <c r="R56" t="n">
-        <v>-11230</v>
+        <v>30460</v>
       </c>
       <c r="S56" t="n">
         <v>1415</v>
@@ -3014,43 +3002,53 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>100</v>
-      </c>
-      <c r="F57" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G57" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.13</v>
+      </c>
       <c r="I57" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.61</v>
+      </c>
       <c r="K57" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
+        <v>4319.93</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1351.81</v>
+      </c>
       <c r="M57" t="n">
-        <v>1.678</v>
+        <v>-2.059</v>
       </c>
       <c r="N57" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O57" t="inlineStr"/>
+        <v>-3794</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.01</v>
+      </c>
       <c r="P57" t="n">
-        <v>1670</v>
+        <v>-11383</v>
       </c>
       <c r="Q57" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="R57" t="n">
-        <v>1700</v>
+        <v>-11230</v>
       </c>
       <c r="S57" t="n">
         <v>1415</v>
@@ -3069,201 +3067,270 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
-        <v>5756.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>-6.785</v>
+        <v>1.678</v>
       </c>
       <c r="N58" t="n">
-        <v>-7272</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
+        <v>1670</v>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>-14543</v>
+        <v>1670</v>
       </c>
       <c r="Q58" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="R58" t="n">
-        <v>-14485</v>
+        <v>1700</v>
       </c>
       <c r="S58" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>5756.96</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-7272</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-14543</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>58</v>
+      </c>
+      <c r="R59" t="n">
+        <v>-14485</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D60" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E60" s="2" t="n">
         <v>38.5</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F60" s="2" t="n">
         <v>1.71</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H60" s="2" t="n">
         <v>3.89</v>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="I60" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="J59" s="2" t="n">
+      <c r="J60" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="K59" s="2" t="n">
+      <c r="K60" s="2" t="n">
         <v>1633.99</v>
       </c>
-      <c r="L59" s="2" t="n">
+      <c r="L60" s="2" t="n">
         <v>2111.58</v>
       </c>
-      <c r="M59" s="2" t="n">
+      <c r="M60" s="2" t="n">
         <v>-1.689</v>
       </c>
-      <c r="N59" s="2" t="n">
+      <c r="N60" s="2" t="n">
         <v>232</v>
       </c>
-      <c r="O59" s="2" t="n">
+      <c r="O60" s="2" t="n">
         <v>1.07</v>
       </c>
-      <c r="P59" s="2" t="n">
+      <c r="P60" s="2" t="n">
         <v>3022</v>
       </c>
-      <c r="Q59" s="2" t="n">
+      <c r="Q60" s="2" t="n">
         <v>1023</v>
       </c>
-      <c r="R59" s="2" t="n">
+      <c r="R60" s="2" t="n">
         <v>4045</v>
       </c>
-      <c r="S59" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="S60" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr"/>
-      <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="D62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr"/>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>100</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>7</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="N64" t="n">
+        <v>6421</v>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>6421</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>149</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6570</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VOLUME_2</t>
+          <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3277,34 +3344,46 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr"/>
-      <c r="N65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>6421</v>
+      </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="n">
-        <v>0</v>
+        <v>6421</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="R65" s="2" t="n">
-        <v>0</v>
+        <v>6570</v>
       </c>
       <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP1</t>
+          <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3345,7 +3424,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>KR_TR_VCP1</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3386,7 +3465,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_JEO2</t>
+          <t>KR_TR_VCP2</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3427,7 +3506,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_MA</t>
+          <t>KR_TR_JEO2</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3468,7 +3547,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ADD1</t>
+          <t>KR_TR_MA</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3509,7 +3588,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>미국VCP</t>
+          <t>KR_TR_ADD1</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3548,125 +3627,109 @@
       <c r="S77" s="2" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>미국VCP</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D81" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="n">
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="n">
         <v>10.01</v>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="n">
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="n">
         <v>10.01</v>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="n">
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="n">
         <v>3</v>
       </c>
-      <c r="M79" t="n">
+      <c r="M81" t="n">
         <v>-10.012</v>
       </c>
-      <c r="N79" t="n">
+      <c r="N81" t="n">
         <v>-71414</v>
       </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
         <v>-71414</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="Q81" t="n">
         <v>949</v>
       </c>
-      <c r="R79" t="n">
+      <c r="R81" t="n">
         <v>-70465</v>
       </c>
-      <c r="S79" t="n">
+      <c r="S81" t="n">
         <v>1411</v>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_A</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N80" s="2" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="O80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="2" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="Q80" s="2" t="n">
-        <v>949</v>
-      </c>
-      <c r="R80" s="2" t="n">
-        <v>-70465</v>
-      </c>
-      <c r="S80" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_1</t>
+          <t>US_TR_ORD_A</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3680,34 +3743,50 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="n">
+        <v>10.01</v>
+      </c>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="n">
+        <v>10.01</v>
+      </c>
       <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-10.012</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P82" s="2" t="n">
-        <v>0</v>
+        <v>-53512</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>0</v>
+        <v>1679</v>
       </c>
       <c r="R82" s="2" t="n">
-        <v>0</v>
+        <v>-51833</v>
       </c>
       <c r="S82" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_2</t>
+          <t>US_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -3748,7 +3827,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP1</t>
+          <t>US_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -3787,125 +3866,109 @@
       <c r="S86" s="2" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP1</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D90" t="n">
         <v>1</v>
       </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="n">
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="n">
         <v>6.8</v>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="n">
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="n">
         <v>6.8</v>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="n">
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="n">
         <v>5</v>
       </c>
-      <c r="M88" t="n">
+      <c r="M90" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N90" t="n">
         <v>-9876</v>
       </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
         <v>-9876</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="Q90" t="n">
         <v>196</v>
       </c>
-      <c r="R88" t="n">
+      <c r="R90" t="n">
         <v>-9679</v>
       </c>
-      <c r="S88" t="n">
+      <c r="S90" t="n">
         <v>1411</v>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>-6.802</v>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="O89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" s="2" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="Q89" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="R89" s="2" t="n">
-        <v>-9679</v>
-      </c>
-      <c r="S89" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>US_TR_JEO2</t>
+          <t>US_TR_VCP2</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -3919,34 +3982,50 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="n">
+        <v>6.8</v>
+      </c>
       <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="n">
+        <v>6.8</v>
+      </c>
       <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr"/>
-      <c r="O91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="O91" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P91" s="2" t="n">
-        <v>0</v>
+        <v>-6552</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="R91" s="2" t="n">
-        <v>0</v>
+        <v>-6283</v>
       </c>
       <c r="S91" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>US_TR_MA</t>
+          <t>US_TR_JEO2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -3987,7 +4066,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>US_TR_ADD1</t>
+          <t>US_TR_MA</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4015,20 +4094,20 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="n">
-        <v>0</v>
+        <v>-398</v>
       </c>
       <c r="Q95" s="2" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="R95" s="2" t="n">
-        <v>0</v>
+        <v>-233</v>
       </c>
       <c r="S95" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY</t>
+          <t>US_TR_ADD1</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4069,7 +4148,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_TREND</t>
+          <t>US_TR_LEGACY</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4110,7 +4189,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_LOW</t>
+          <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -4151,12 +4230,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>저점사다리</t>
+          <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4190,128 +4269,45 @@
       <c r="S103" s="2" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="n">
-        <v>1</v>
-      </c>
-      <c r="M105" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N105" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>513</v>
-      </c>
-      <c r="R105" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S105" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>4</v>
-      </c>
-      <c r="E106" t="n">
-        <v>25</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G106" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I106" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J106" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K106" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M106" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P106" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R106" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S106" t="n">
-        <v>1415</v>
-      </c>
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4326,7 +4322,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4340,33 +4336,33 @@
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>0.14</v>
+        <v>2.61</v>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
-        <v>0.16</v>
+        <v>3.49</v>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-0.136</v>
+        <v>-2.607</v>
       </c>
       <c r="N107" t="n">
-        <v>-2389</v>
+        <v>-8011</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>-4777</v>
+        <v>-16021</v>
       </c>
       <c r="Q107" t="n">
-        <v>2924</v>
+        <v>513</v>
       </c>
       <c r="R107" t="n">
-        <v>-1854</v>
+        <v>-15508</v>
       </c>
       <c r="S107" t="n">
         <v>1415</v>
@@ -4385,43 +4381,53 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E108" t="n">
-        <v>100</v>
-      </c>
-      <c r="F108" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G108" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I108" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J108" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K108" t="n">
-        <v>14</v>
-      </c>
-      <c r="L108" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L108" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M108" t="n">
-        <v>1.042</v>
+        <v>-0.217</v>
       </c>
       <c r="N108" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O108" t="inlineStr"/>
+        <v>-13272</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P108" t="n">
-        <v>48540</v>
+        <v>-53089</v>
       </c>
       <c r="Q108" t="n">
-        <v>4254</v>
+        <v>5913</v>
       </c>
       <c r="R108" t="n">
-        <v>52794</v>
+        <v>-47176</v>
       </c>
       <c r="S108" t="n">
         <v>1415</v>
@@ -4440,11 +4446,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -4454,461 +4460,512 @@
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M109" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-2389</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>-4777</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>2924</v>
+      </c>
+      <c r="R109" t="n">
+        <v>-1854</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>100</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>14</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N110" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R110" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="n">
         <v>4.67</v>
       </c>
-      <c r="M109" t="n">
+      <c r="M111" t="n">
         <v>-0.864</v>
       </c>
-      <c r="N109" t="n">
+      <c r="N111" t="n">
         <v>-28997</v>
       </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
         <v>-86990</v>
       </c>
-      <c r="Q109" t="n">
+      <c r="Q111" t="n">
         <v>13787</v>
       </c>
-      <c r="R109" t="n">
+      <c r="R111" t="n">
         <v>-73203</v>
       </c>
-      <c r="S109" t="n">
+      <c r="S111" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n">
+      <c r="D112" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E110" s="2" t="n">
+      <c r="E112" s="2" t="n">
         <v>28.6</v>
       </c>
-      <c r="F110" s="2" t="n">
+      <c r="F112" s="2" t="n">
         <v>0.77</v>
       </c>
-      <c r="G110" s="2" t="n">
+      <c r="G112" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H110" s="2" t="n">
+      <c r="H112" s="2" t="n">
         <v>1.03</v>
       </c>
-      <c r="I110" s="2" t="n">
+      <c r="I112" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J110" s="2" t="n">
+      <c r="J112" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K110" s="2" t="n">
+      <c r="K112" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L110" s="2" t="n">
+      <c r="L112" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="M110" s="2" t="n">
+      <c r="M112" s="2" t="n">
         <v>-0.416</v>
       </c>
-      <c r="N110" s="2" t="n">
+      <c r="N112" s="2" t="n">
         <v>-8024</v>
       </c>
-      <c r="O110" s="2" t="n">
+      <c r="O112" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="P110" s="2" t="n">
+      <c r="P112" s="2" t="n">
         <v>-112337</v>
       </c>
-      <c r="Q110" s="2" t="n">
+      <c r="Q112" s="2" t="n">
         <v>27391</v>
       </c>
-      <c r="R110" s="2" t="n">
+      <c r="R112" s="2" t="n">
         <v>-84947</v>
       </c>
-      <c r="S110" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="S112" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D112" t="n">
+      <c r="D114" t="n">
         <v>9</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E114" t="n">
         <v>55.6</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F114" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G114" t="n">
         <v>1.17</v>
       </c>
-      <c r="H112" t="n">
+      <c r="H114" t="n">
         <v>4.19</v>
       </c>
-      <c r="I112" t="n">
+      <c r="I114" t="n">
         <v>3.38</v>
       </c>
-      <c r="J112" t="n">
+      <c r="J114" t="n">
         <v>7.04</v>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="n">
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N112" t="n">
+      <c r="N114" t="n">
         <v>-744</v>
       </c>
-      <c r="O112" t="n">
+      <c r="O114" t="n">
         <v>0.86</v>
       </c>
-      <c r="P112" t="n">
+      <c r="P114" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q112" t="n">
+      <c r="Q114" t="n">
         <v>2139</v>
       </c>
-      <c r="R112" t="n">
+      <c r="R114" t="n">
         <v>-4553</v>
       </c>
-      <c r="S112" t="n">
+      <c r="S114" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D115" t="n">
         <v>2</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E115" t="n">
         <v>100</v>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="n">
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="n">
         <v>8.56</v>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="n">
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="n">
         <v>12.69</v>
       </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="n">
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="n">
         <v>8.56</v>
       </c>
-      <c r="N113" t="n">
+      <c r="N115" t="n">
         <v>57466</v>
       </c>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="n">
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="n">
         <v>114933</v>
       </c>
-      <c r="Q113" t="n">
+      <c r="Q115" t="n">
         <v>667</v>
       </c>
-      <c r="R113" t="n">
+      <c r="R115" t="n">
         <v>115600</v>
       </c>
-      <c r="S113" t="n">
+      <c r="S115" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D116" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E116" s="2" t="n">
         <v>63.6</v>
       </c>
-      <c r="F114" s="2" t="n">
+      <c r="F116" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="G114" s="2" t="n">
+      <c r="G116" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H114" s="2" t="n">
+      <c r="H116" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I114" s="2" t="n">
+      <c r="I116" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J114" s="2" t="n">
+      <c r="J116" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="n">
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="N114" s="2" t="n">
+      <c r="N116" s="2" t="n">
         <v>9840</v>
       </c>
-      <c r="O114" s="2" t="n">
+      <c r="O116" s="2" t="n">
         <v>3.23</v>
       </c>
-      <c r="P114" s="2" t="n">
+      <c r="P116" s="2" t="n">
         <v>108241</v>
       </c>
-      <c r="Q114" s="2" t="n">
+      <c r="Q116" s="2" t="n">
         <v>2806</v>
       </c>
-      <c r="R114" s="2" t="n">
+      <c r="R116" s="2" t="n">
         <v>111047</v>
       </c>
-      <c r="S114" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="S116" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D116" t="n">
+      <c r="D118" t="n">
         <v>9</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E118" t="n">
         <v>55.6</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F118" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G116" t="n">
+      <c r="G118" t="n">
         <v>1.17</v>
       </c>
-      <c r="H116" t="n">
+      <c r="H118" t="n">
         <v>4.19</v>
       </c>
-      <c r="I116" t="n">
+      <c r="I118" t="n">
         <v>3.38</v>
       </c>
-      <c r="J116" t="n">
+      <c r="J118" t="n">
         <v>7.04</v>
       </c>
-      <c r="K116" t="n">
+      <c r="K118" t="n">
         <v>3</v>
       </c>
-      <c r="L116" t="n">
+      <c r="L118" t="n">
         <v>1.75</v>
       </c>
-      <c r="M116" t="n">
+      <c r="M118" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N116" t="n">
+      <c r="N118" t="n">
         <v>-744</v>
       </c>
-      <c r="O116" t="n">
+      <c r="O118" t="n">
         <v>0.86</v>
       </c>
-      <c r="P116" t="n">
+      <c r="P118" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q116" t="n">
+      <c r="Q118" t="n">
         <v>2139</v>
       </c>
-      <c r="R116" t="n">
+      <c r="R118" t="n">
         <v>-4553</v>
       </c>
-      <c r="S116" t="n">
+      <c r="S118" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D117" t="n">
+      <c r="D119" t="n">
         <v>2</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E119" t="n">
         <v>100</v>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="n">
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="n">
         <v>8.56</v>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="n">
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="n">
         <v>12.69</v>
       </c>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="n">
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="n">
         <v>4.5</v>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="n">
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
         <v>8.56</v>
       </c>
-      <c r="N117" t="n">
+      <c r="N119" t="n">
         <v>57466</v>
       </c>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="n">
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="n">
         <v>114933</v>
       </c>
-      <c r="Q117" t="n">
+      <c r="Q119" t="n">
         <v>667</v>
       </c>
-      <c r="R117" t="n">
+      <c r="R119" t="n">
         <v>115600</v>
       </c>
-      <c r="S117" t="n">
+      <c r="S119" t="n">
         <v>1411</v>
       </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="N118" s="2" t="n">
-        <v>9840</v>
-      </c>
-      <c r="O118" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="P118" s="2" t="n">
-        <v>108241</v>
-      </c>
-      <c r="Q118" s="2" t="n">
-        <v>2806</v>
-      </c>
-      <c r="R118" s="2" t="n">
-        <v>111047</v>
-      </c>
-      <c r="S118" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -4922,39 +4979,61 @@
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="inlineStr"/>
-      <c r="N120" s="2" t="inlineStr"/>
-      <c r="O120" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>9840</v>
+      </c>
+      <c r="O120" s="2" t="n">
+        <v>3.23</v>
+      </c>
       <c r="P120" s="2" t="n">
-        <v>0</v>
+        <v>108241</v>
       </c>
       <c r="Q120" s="2" t="n">
-        <v>0</v>
+        <v>2806</v>
       </c>
       <c r="R120" s="2" t="n">
-        <v>0</v>
+        <v>111047</v>
       </c>
       <c r="S120" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -4987,6 +5066,47 @@
       </c>
       <c r="S122" s="2" t="inlineStr"/>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S124"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1174,40 +1174,48 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.34</v>
+      </c>
       <c r="G12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>4.68</v>
+      </c>
       <c r="I12" t="n">
         <v>1.3</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>4.74</v>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>1.299</v>
+        <v>-2.688</v>
       </c>
       <c r="N12" t="n">
-        <v>6421</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
+        <v>-10620</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.17</v>
+      </c>
       <c r="P12" t="n">
-        <v>27249</v>
+        <v>-2132</v>
       </c>
       <c r="Q12" t="n">
-        <v>1115</v>
+        <v>3880</v>
       </c>
       <c r="R12" t="n">
-        <v>28365</v>
+        <v>1748</v>
       </c>
       <c r="S12" t="n">
-        <v>1415</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="13">
@@ -1227,19 +1235,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>4.61</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>19.29</v>
@@ -1250,22 +1258,22 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="n">
-        <v>-0.002</v>
+        <v>-0.043</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>362</v>
+        <v>190</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>102218</v>
+        <v>72837</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>35897</v>
+        <v>38662</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>138116</v>
+        <v>111499</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -3324,7 +3332,7 @@
         <v>6570</v>
       </c>
       <c r="S64" t="n">
-        <v>1415</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="65">
@@ -3727,387 +3735,464 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="n">
+        <v>7</v>
+      </c>
+      <c r="M82" t="n">
+        <v>-4.743</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-23740</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>18371</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2014</v>
+      </c>
+      <c r="R82" t="n">
+        <v>20385</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_A</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
+      <c r="D83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-7.378</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>-47577</v>
+      </c>
+      <c r="O83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>-53043</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>2963</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>-50080</v>
+      </c>
+      <c r="S83" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VOLUME_1</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VOLUME_2</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP1</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="O82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="2" t="n">
-        <v>-53512</v>
-      </c>
-      <c r="Q82" s="2" t="n">
-        <v>1679</v>
-      </c>
-      <c r="R82" s="2" t="n">
-        <v>-51833</v>
-      </c>
-      <c r="S82" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VOLUME_1</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>5</v>
+      </c>
+      <c r="M91" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>196</v>
+      </c>
+      <c r="R91" t="n">
+        <v>-9679</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VOLUME_2</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="D92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="O92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>-21862</v>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>1317</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>-20544</v>
+      </c>
+      <c r="S92" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VCP1</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="D94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
         <v>1</v>
       </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="n">
-        <v>5</v>
-      </c>
-      <c r="M90" t="n">
-        <v>-6.802</v>
-      </c>
-      <c r="N90" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>196</v>
-      </c>
-      <c r="R90" t="n">
-        <v>-9679</v>
-      </c>
-      <c r="S90" t="n">
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="n">
+        <v>4</v>
+      </c>
+      <c r="M96" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-14540</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>-14938</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>595</v>
+      </c>
+      <c r="R96" t="n">
+        <v>-14343</v>
+      </c>
+      <c r="S96" t="n">
         <v>1411</v>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>-6.802</v>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="O91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" s="2" t="n">
-        <v>-6552</v>
-      </c>
-      <c r="Q91" s="2" t="n">
-        <v>268</v>
-      </c>
-      <c r="R91" s="2" t="n">
-        <v>-6283</v>
-      </c>
-      <c r="S91" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr"/>
-      <c r="O93" s="2" t="inlineStr"/>
-      <c r="P93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr"/>
-      <c r="O95" s="2" t="inlineStr"/>
-      <c r="P95" s="2" t="n">
-        <v>-398</v>
-      </c>
-      <c r="Q95" s="2" t="n">
-        <v>165</v>
-      </c>
-      <c r="R95" s="2" t="n">
-        <v>-233</v>
-      </c>
-      <c r="S95" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>US_TR_ADD1</t>
+          <t>US_TR_MA</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4121,34 +4206,50 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="n">
+        <v>4.62</v>
+      </c>
       <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="n">
+        <v>4.62</v>
+      </c>
       <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
-      <c r="O97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-14540</v>
+      </c>
+      <c r="O97" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P97" s="2" t="n">
-        <v>0</v>
+        <v>-14938</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="R97" s="2" t="n">
-        <v>0</v>
+        <v>-14343</v>
       </c>
       <c r="S97" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY</t>
+          <t>US_TR_ADD1</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4189,7 +4290,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_TREND</t>
+          <t>US_TR_LEGACY</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -4228,269 +4329,214 @@
       <c r="S101" s="2" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>5</v>
+      </c>
+      <c r="E103" t="n">
+        <v>40</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I103" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J103" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="N103" t="n">
+        <v>334</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P103" t="n">
+        <v>16603</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>2615</v>
+      </c>
+      <c r="R103" t="n">
+        <v>19218</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>334</v>
+      </c>
+      <c r="O104" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P104" s="2" t="n">
+        <v>16603</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>2615</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>19218</v>
+      </c>
+      <c r="S104" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
-      <c r="P103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="D106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr"/>
-      <c r="O105" s="2" t="inlineStr"/>
-      <c r="P105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>2</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="n">
-        <v>1</v>
-      </c>
-      <c r="M107" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N107" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>513</v>
-      </c>
-      <c r="R107" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S107" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>4</v>
-      </c>
-      <c r="E108" t="n">
-        <v>25</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G108" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I108" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J108" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K108" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M108" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N108" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P108" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R108" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S108" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>2</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M109" t="n">
-        <v>-0.136</v>
-      </c>
-      <c r="N109" t="n">
-        <v>-2389</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
-        <v>-4777</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>2924</v>
-      </c>
-      <c r="R109" t="n">
-        <v>-1854</v>
-      </c>
-      <c r="S109" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4505,43 +4551,47 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>100</v>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="n">
-        <v>14</v>
-      </c>
-      <c r="L110" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="n">
+        <v>1</v>
+      </c>
       <c r="M110" t="n">
-        <v>1.042</v>
+        <v>-2.607</v>
       </c>
       <c r="N110" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O110" t="inlineStr"/>
+        <v>-8011</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
       <c r="P110" t="n">
-        <v>48540</v>
+        <v>-16021</v>
       </c>
       <c r="Q110" t="n">
-        <v>4254</v>
+        <v>513</v>
       </c>
       <c r="R110" t="n">
-        <v>52794</v>
+        <v>-15508</v>
       </c>
       <c r="S110" t="n">
         <v>1415</v>
@@ -4560,552 +4610,731 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D111" t="n">
+        <v>4</v>
+      </c>
+      <c r="E111" t="n">
+        <v>25</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="M111" t="n">
+        <v>-0.217</v>
+      </c>
+      <c r="N111" t="n">
+        <v>-13272</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P111" t="n">
+        <v>-53089</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>5913</v>
+      </c>
+      <c r="R111" t="n">
+        <v>-47176</v>
+      </c>
+      <c r="S111" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M112" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="N112" t="n">
+        <v>-2389</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>-4777</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>2924</v>
+      </c>
+      <c r="R112" t="n">
+        <v>-1854</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
         <v>3</v>
       </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="M111" t="n">
-        <v>-0.864</v>
-      </c>
-      <c r="N111" t="n">
-        <v>-28997</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>-86990</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>13787</v>
-      </c>
-      <c r="R111" t="n">
-        <v>-73203</v>
-      </c>
-      <c r="S111" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="n">
+      <c r="E113" t="n">
+        <v>100</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
         <v>14</v>
       </c>
-      <c r="E112" s="2" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>-0.416</v>
-      </c>
-      <c r="N112" s="2" t="n">
-        <v>-8024</v>
-      </c>
-      <c r="O112" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="P112" s="2" t="n">
-        <v>-112337</v>
-      </c>
-      <c r="Q112" s="2" t="n">
-        <v>27391</v>
-      </c>
-      <c r="R112" s="2" t="n">
-        <v>-84947</v>
-      </c>
-      <c r="S112" s="2" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N113" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R113" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M114" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R114" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-0.416</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-8024</v>
+      </c>
+      <c r="O115" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="P115" s="2" t="n">
+        <v>-112337</v>
+      </c>
+      <c r="Q115" s="2" t="n">
+        <v>27391</v>
+      </c>
+      <c r="R115" s="2" t="n">
+        <v>-84947</v>
+      </c>
+      <c r="S115" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D114" t="n">
+      <c r="D117" t="n">
         <v>9</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E117" t="n">
         <v>55.6</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F117" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G117" t="n">
         <v>1.17</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H117" t="n">
         <v>4.19</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I117" t="n">
         <v>3.38</v>
       </c>
-      <c r="J114" t="n">
+      <c r="J117" t="n">
         <v>7.04</v>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="n">
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N114" t="n">
+      <c r="N117" t="n">
         <v>-744</v>
       </c>
-      <c r="O114" t="n">
+      <c r="O117" t="n">
         <v>0.86</v>
       </c>
-      <c r="P114" t="n">
+      <c r="P117" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q114" t="n">
+      <c r="Q117" t="n">
         <v>2139</v>
       </c>
-      <c r="R114" t="n">
+      <c r="R117" t="n">
         <v>-4553</v>
       </c>
-      <c r="S114" t="n">
+      <c r="S117" t="n">
         <v>1415</v>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>2</v>
-      </c>
-      <c r="E115" t="n">
-        <v>100</v>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N115" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>667</v>
-      </c>
-      <c r="R115" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S115" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="N116" s="2" t="n">
-        <v>9840</v>
-      </c>
-      <c r="O116" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="P116" s="2" t="n">
-        <v>108241</v>
-      </c>
-      <c r="Q116" s="2" t="n">
-        <v>2806</v>
-      </c>
-      <c r="R116" s="2" t="n">
-        <v>111047</v>
-      </c>
-      <c r="S116" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" t="n">
+        <v>100</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N118" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>667</v>
+      </c>
+      <c r="R118" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>9840</v>
+      </c>
+      <c r="O119" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="P119" s="2" t="n">
+        <v>108241</v>
+      </c>
+      <c r="Q119" s="2" t="n">
+        <v>2806</v>
+      </c>
+      <c r="R119" s="2" t="n">
+        <v>111047</v>
+      </c>
+      <c r="S119" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D118" t="n">
+      <c r="D121" t="n">
         <v>9</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E121" t="n">
         <v>55.6</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F121" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G121" t="n">
         <v>1.17</v>
       </c>
-      <c r="H118" t="n">
+      <c r="H121" t="n">
         <v>4.19</v>
       </c>
-      <c r="I118" t="n">
+      <c r="I121" t="n">
         <v>3.38</v>
       </c>
-      <c r="J118" t="n">
+      <c r="J121" t="n">
         <v>7.04</v>
       </c>
-      <c r="K118" t="n">
+      <c r="K121" t="n">
         <v>3</v>
       </c>
-      <c r="L118" t="n">
+      <c r="L121" t="n">
         <v>1.75</v>
       </c>
-      <c r="M118" t="n">
+      <c r="M121" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N118" t="n">
+      <c r="N121" t="n">
         <v>-744</v>
       </c>
-      <c r="O118" t="n">
+      <c r="O121" t="n">
         <v>0.86</v>
       </c>
-      <c r="P118" t="n">
+      <c r="P121" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q118" t="n">
+      <c r="Q121" t="n">
         <v>2139</v>
       </c>
-      <c r="R118" t="n">
+      <c r="R121" t="n">
         <v>-4553</v>
       </c>
-      <c r="S118" t="n">
+      <c r="S121" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D119" t="n">
+      <c r="D122" t="n">
         <v>2</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E122" t="n">
         <v>100</v>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="n">
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="n">
         <v>8.56</v>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="n">
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="n">
         <v>12.69</v>
       </c>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="n">
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="n">
         <v>4.5</v>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="n">
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="n">
         <v>8.56</v>
       </c>
-      <c r="N119" t="n">
+      <c r="N122" t="n">
         <v>57466</v>
       </c>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="n">
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="n">
         <v>114933</v>
       </c>
-      <c r="Q119" t="n">
+      <c r="Q122" t="n">
         <v>667</v>
       </c>
-      <c r="R119" t="n">
+      <c r="R122" t="n">
         <v>115600</v>
       </c>
-      <c r="S119" t="n">
+      <c r="S122" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D120" s="2" t="n">
+      <c r="D123" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E120" s="2" t="n">
+      <c r="E123" s="2" t="n">
         <v>63.6</v>
       </c>
-      <c r="F120" s="2" t="n">
+      <c r="F123" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="G120" s="2" t="n">
+      <c r="G123" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H120" s="2" t="n">
+      <c r="H123" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I120" s="2" t="n">
+      <c r="I123" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J120" s="2" t="n">
+      <c r="J123" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K120" s="2" t="n">
+      <c r="K123" s="2" t="n">
         <v>3.43</v>
       </c>
-      <c r="L120" s="2" t="n">
+      <c r="L123" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="M120" s="2" t="n">
+      <c r="M123" s="2" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="N120" s="2" t="n">
+      <c r="N123" s="2" t="n">
         <v>9840</v>
       </c>
-      <c r="O120" s="2" t="n">
+      <c r="O123" s="2" t="n">
         <v>3.23</v>
       </c>
-      <c r="P120" s="2" t="n">
+      <c r="P123" s="2" t="n">
         <v>108241</v>
       </c>
-      <c r="Q120" s="2" t="n">
+      <c r="Q123" s="2" t="n">
         <v>2806</v>
       </c>
-      <c r="R120" s="2" t="n">
+      <c r="R123" s="2" t="n">
         <v>111047</v>
       </c>
-      <c r="S120" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="S123" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="2" t="inlineStr"/>
-      <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="2" t="inlineStr"/>
-      <c r="N122" s="2" t="inlineStr"/>
-      <c r="O122" s="2" t="inlineStr"/>
-      <c r="P122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="D125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="2" t="inlineStr"/>
-      <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr"/>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr"/>
-      <c r="M124" s="2" t="inlineStr"/>
-      <c r="N124" s="2" t="inlineStr"/>
-      <c r="O124" s="2" t="inlineStr"/>
-      <c r="P124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" s="2" t="inlineStr"/>
+      <c r="D127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1200,22 +1200,22 @@
         <v>-2.688</v>
       </c>
       <c r="N12" t="n">
-        <v>-10620</v>
+        <v>-10629</v>
       </c>
       <c r="O12" t="n">
         <v>0.17</v>
       </c>
       <c r="P12" t="n">
-        <v>-2132</v>
+        <v>-2138</v>
       </c>
       <c r="Q12" t="n">
-        <v>3880</v>
+        <v>3882</v>
       </c>
       <c r="R12" t="n">
-        <v>1748</v>
+        <v>1744</v>
       </c>
       <c r="S12" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="13">
@@ -1267,13 +1267,13 @@
         <v>1.03</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>72837</v>
+        <v>72831</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>38662</v>
+        <v>38664</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>111499</v>
+        <v>111495</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -3332,7 +3332,7 @@
         <v>6570</v>
       </c>
       <c r="S64" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="65">
@@ -3775,22 +3775,22 @@
         <v>-4.743</v>
       </c>
       <c r="N82" t="n">
-        <v>-23740</v>
+        <v>-23757</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>18371</v>
+        <v>18384</v>
       </c>
       <c r="Q82" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="R82" t="n">
-        <v>20385</v>
+        <v>20400</v>
       </c>
       <c r="S82" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="83">
@@ -3834,19 +3834,19 @@
         <v>-7.378</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-47577</v>
+        <v>-47585</v>
       </c>
       <c r="O83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>-53043</v>
+        <v>-53030</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>2963</v>
+        <v>2965</v>
       </c>
       <c r="R83" s="2" t="n">
-        <v>-50080</v>
+        <v>-50065</v>
       </c>
       <c r="S83" s="2" t="inlineStr"/>
     </row>
@@ -4079,13 +4079,13 @@
         <v>0</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>-21862</v>
+        <v>-21870</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="R92" s="2" t="n">
-        <v>-20544</v>
+        <v>-20551</v>
       </c>
       <c r="S92" s="2" t="inlineStr"/>
     </row>
@@ -4171,22 +4171,22 @@
         <v>-4.62</v>
       </c>
       <c r="N96" t="n">
-        <v>-14540</v>
+        <v>-14551</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>-14938</v>
+        <v>-14948</v>
       </c>
       <c r="Q96" t="n">
         <v>595</v>
       </c>
       <c r="R96" t="n">
-        <v>-14343</v>
+        <v>-14353</v>
       </c>
       <c r="S96" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="97">
@@ -4230,19 +4230,19 @@
         <v>-4.62</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-14540</v>
+        <v>-14551</v>
       </c>
       <c r="O97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>-14938</v>
+        <v>-14948</v>
       </c>
       <c r="Q97" s="2" t="n">
         <v>595</v>
       </c>
       <c r="R97" s="2" t="n">
-        <v>-14343</v>
+        <v>-14353</v>
       </c>
       <c r="S97" s="2" t="inlineStr"/>
     </row>
@@ -4381,16 +4381,16 @@
         <v>1.07</v>
       </c>
       <c r="P103" t="n">
-        <v>16603</v>
+        <v>16615</v>
       </c>
       <c r="Q103" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="R103" t="n">
-        <v>19218</v>
+        <v>19231</v>
       </c>
       <c r="S103" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="104">
@@ -4446,13 +4446,13 @@
         <v>1.07</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>16603</v>
+        <v>16615</v>
       </c>
       <c r="Q104" s="2" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="R104" s="2" t="n">
-        <v>19218</v>
+        <v>19231</v>
       </c>
       <c r="S104" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S127"/>
+  <dimension ref="A1:S128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1200,22 +1200,22 @@
         <v>-2.688</v>
       </c>
       <c r="N12" t="n">
-        <v>-10629</v>
+        <v>-10611</v>
       </c>
       <c r="O12" t="n">
         <v>0.17</v>
       </c>
       <c r="P12" t="n">
-        <v>-2138</v>
+        <v>137916</v>
       </c>
       <c r="Q12" t="n">
-        <v>3882</v>
+        <v>4715</v>
       </c>
       <c r="R12" t="n">
-        <v>1744</v>
+        <v>142631</v>
       </c>
       <c r="S12" t="n">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="13">
@@ -1267,13 +1267,13 @@
         <v>1.03</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>72831</v>
+        <v>212885</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>38664</v>
+        <v>39497</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>111495</v>
+        <v>252382</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -2339,13 +2339,13 @@
         <v>1.2</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>104897</v>
+        <v>244938</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>10410</v>
+        <v>11249</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>115307</v>
+        <v>256187</v>
       </c>
       <c r="S36" s="2" t="inlineStr"/>
     </row>
@@ -3332,7 +3332,7 @@
         <v>6570</v>
       </c>
       <c r="S64" t="n">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="65">
@@ -3775,22 +3775,22 @@
         <v>-4.743</v>
       </c>
       <c r="N82" t="n">
-        <v>-23757</v>
+        <v>-23723</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>18384</v>
+        <v>18358</v>
       </c>
       <c r="Q82" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="R82" t="n">
-        <v>20400</v>
+        <v>20371</v>
       </c>
       <c r="S82" t="n">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="83">
@@ -3834,19 +3834,19 @@
         <v>-7.378</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-47585</v>
+        <v>-47568</v>
       </c>
       <c r="O83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>-53030</v>
+        <v>-53056</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>2965</v>
+        <v>2962</v>
       </c>
       <c r="R83" s="2" t="n">
-        <v>-50065</v>
+        <v>-50094</v>
       </c>
       <c r="S83" s="2" t="inlineStr"/>
     </row>
@@ -4079,13 +4079,13 @@
         <v>0</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>-21870</v>
+        <v>-21853</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="R92" s="2" t="n">
-        <v>-20551</v>
+        <v>-20536</v>
       </c>
       <c r="S92" s="2" t="inlineStr"/>
     </row>
@@ -4171,22 +4171,22 @@
         <v>-4.62</v>
       </c>
       <c r="N96" t="n">
-        <v>-14551</v>
+        <v>-14530</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>-14948</v>
+        <v>-14927</v>
       </c>
       <c r="Q96" t="n">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="R96" t="n">
-        <v>-14353</v>
+        <v>-14333</v>
       </c>
       <c r="S96" t="n">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="97">
@@ -4230,19 +4230,19 @@
         <v>-4.62</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-14551</v>
+        <v>-14530</v>
       </c>
       <c r="O97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>-14948</v>
+        <v>-14927</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="R97" s="2" t="n">
-        <v>-14353</v>
+        <v>-14333</v>
       </c>
       <c r="S97" s="2" t="inlineStr"/>
     </row>
@@ -4288,314 +4288,330 @@
       <c r="S99" s="2" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>-10.495</v>
+      </c>
+      <c r="N101" t="n">
+        <v>-40657</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>-40657</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>514</v>
+      </c>
+      <c r="R101" t="n">
+        <v>-40143</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
-      <c r="P101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="D102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-10.495</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-40657</v>
+      </c>
+      <c r="O102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>-40657</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>514</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>-40143</v>
+      </c>
+      <c r="S102" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D103" t="n">
-        <v>5</v>
-      </c>
-      <c r="E103" t="n">
-        <v>40</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="G103" t="n">
+      <c r="D104" t="n">
+        <v>6</v>
+      </c>
+      <c r="E104" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G104" t="n">
         <v>4.75</v>
       </c>
-      <c r="H103" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="I103" t="n">
+      <c r="H104" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I104" t="n">
         <v>7.6</v>
       </c>
-      <c r="J103" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="N103" t="n">
-        <v>334</v>
-      </c>
-      <c r="O103" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P103" t="n">
-        <v>16615</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>2616</v>
-      </c>
-      <c r="R103" t="n">
-        <v>19231</v>
-      </c>
-      <c r="S103" t="n">
-        <v>1412</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="J104" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>-0.845</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-2493</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="P104" t="n">
+        <v>10636</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>2745</v>
+      </c>
+      <c r="R104" t="n">
+        <v>13381</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="G104" s="2" t="n">
+      <c r="D105" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G105" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="H104" s="2" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="I104" s="2" t="n">
+      <c r="H105" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I105" s="2" t="n">
         <v>7.6</v>
       </c>
-      <c r="J104" s="2" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="N104" s="2" t="n">
-        <v>334</v>
-      </c>
-      <c r="O104" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P104" s="2" t="n">
-        <v>16615</v>
-      </c>
-      <c r="Q104" s="2" t="n">
-        <v>2616</v>
-      </c>
-      <c r="R104" s="2" t="n">
-        <v>19231</v>
-      </c>
-      <c r="S104" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="J105" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-0.845</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-2493</v>
+      </c>
+      <c r="O105" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="P105" s="2" t="n">
+        <v>10636</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>2745</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>13381</v>
+      </c>
+      <c r="S105" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr"/>
-      <c r="P106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="D107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
-      <c r="P108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>2</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="n">
-        <v>1</v>
-      </c>
-      <c r="M110" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N110" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>513</v>
-      </c>
-      <c r="R110" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S110" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4610,53 +4626,47 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G111" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I111" t="n">
-        <v>1.37</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K111" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="n">
         <v>1</v>
       </c>
-      <c r="L111" t="n">
-        <v>5.67</v>
-      </c>
       <c r="M111" t="n">
-        <v>-0.217</v>
+        <v>-2.607</v>
       </c>
       <c r="N111" t="n">
-        <v>-13272</v>
+        <v>-8011</v>
       </c>
       <c r="O111" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>-53089</v>
+        <v>-16021</v>
       </c>
       <c r="Q111" t="n">
-        <v>5913</v>
+        <v>513</v>
       </c>
       <c r="R111" t="n">
-        <v>-47176</v>
+        <v>-15508</v>
       </c>
       <c r="S111" t="n">
         <v>1415</v>
@@ -4675,47 +4685,53 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H112" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I112" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J112" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K112" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1</v>
+      </c>
       <c r="L112" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M112" t="n">
-        <v>-0.136</v>
+        <v>-0.217</v>
       </c>
       <c r="N112" t="n">
-        <v>-2389</v>
+        <v>-13272</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P112" t="n">
-        <v>-4777</v>
+        <v>-53089</v>
       </c>
       <c r="Q112" t="n">
-        <v>2924</v>
+        <v>5913</v>
       </c>
       <c r="R112" t="n">
-        <v>-1854</v>
+        <v>-47176</v>
       </c>
       <c r="S112" t="n">
         <v>1415</v>
@@ -4734,43 +4750,47 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>100</v>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="n">
-        <v>14</v>
-      </c>
-      <c r="L113" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M113" t="n">
-        <v>1.042</v>
+        <v>-0.136</v>
       </c>
       <c r="N113" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O113" t="inlineStr"/>
+        <v>-2389</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
       <c r="P113" t="n">
-        <v>48540</v>
+        <v>-4777</v>
       </c>
       <c r="Q113" t="n">
-        <v>4254</v>
+        <v>2924</v>
       </c>
       <c r="R113" t="n">
-        <v>52794</v>
+        <v>-1854</v>
       </c>
       <c r="S113" t="n">
         <v>1415</v>
@@ -4789,175 +4809,169 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>3</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="n">
+        <v>100</v>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="n">
+        <v>14</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N114" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R114" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="n">
         <v>0.86</v>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="n">
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="n">
         <v>1.53</v>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="n">
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="n">
         <v>4.67</v>
       </c>
-      <c r="M114" t="n">
+      <c r="M115" t="n">
         <v>-0.864</v>
       </c>
-      <c r="N114" t="n">
+      <c r="N115" t="n">
         <v>-28997</v>
       </c>
-      <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" t="n">
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
         <v>-86990</v>
       </c>
-      <c r="Q114" t="n">
+      <c r="Q115" t="n">
         <v>13787</v>
       </c>
-      <c r="R114" t="n">
+      <c r="R115" t="n">
         <v>-73203</v>
       </c>
-      <c r="S114" t="n">
+      <c r="S115" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D115" s="2" t="n">
+      <c r="D116" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E116" s="2" t="n">
         <v>28.6</v>
       </c>
-      <c r="F115" s="2" t="n">
+      <c r="F116" s="2" t="n">
         <v>0.77</v>
       </c>
-      <c r="G115" s="2" t="n">
+      <c r="G116" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H115" s="2" t="n">
+      <c r="H116" s="2" t="n">
         <v>1.03</v>
       </c>
-      <c r="I115" s="2" t="n">
+      <c r="I116" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J116" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K115" s="2" t="n">
+      <c r="K116" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L115" s="2" t="n">
+      <c r="L116" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="M115" s="2" t="n">
+      <c r="M116" s="2" t="n">
         <v>-0.416</v>
       </c>
-      <c r="N115" s="2" t="n">
+      <c r="N116" s="2" t="n">
         <v>-8024</v>
       </c>
-      <c r="O115" s="2" t="n">
+      <c r="O116" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="P115" s="2" t="n">
+      <c r="P116" s="2" t="n">
         <v>-112337</v>
       </c>
-      <c r="Q115" s="2" t="n">
+      <c r="Q116" s="2" t="n">
         <v>27391</v>
       </c>
-      <c r="R115" s="2" t="n">
+      <c r="R116" s="2" t="n">
         <v>-84947</v>
       </c>
-      <c r="S115" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>9</v>
-      </c>
-      <c r="E117" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G117" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H117" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I117" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J117" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N117" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P117" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R117" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S117" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S116" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4972,169 +4986,165 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E118" t="n">
-        <v>100</v>
-      </c>
-      <c r="F118" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G118" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H118" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I118" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J118" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J118" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N118" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P118" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R118" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="n">
+        <v>100</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="n">
         <v>8.56</v>
       </c>
-      <c r="N118" t="n">
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N119" t="n">
         <v>57466</v>
       </c>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="n">
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="n">
         <v>114933</v>
       </c>
-      <c r="Q118" t="n">
+      <c r="Q119" t="n">
         <v>667</v>
       </c>
-      <c r="R118" t="n">
+      <c r="R119" t="n">
         <v>115600</v>
       </c>
-      <c r="S118" t="n">
+      <c r="S119" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D119" s="2" t="n">
+      <c r="D120" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E119" s="2" t="n">
+      <c r="E120" s="2" t="n">
         <v>63.6</v>
       </c>
-      <c r="F119" s="2" t="n">
+      <c r="F120" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="G119" s="2" t="n">
+      <c r="G120" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H119" s="2" t="n">
+      <c r="H120" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I119" s="2" t="n">
+      <c r="I120" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J119" s="2" t="n">
+      <c r="J120" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="inlineStr"/>
-      <c r="M119" s="2" t="n">
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="N119" s="2" t="n">
+      <c r="N120" s="2" t="n">
         <v>9840</v>
       </c>
-      <c r="O119" s="2" t="n">
+      <c r="O120" s="2" t="n">
         <v>3.23</v>
       </c>
-      <c r="P119" s="2" t="n">
+      <c r="P120" s="2" t="n">
         <v>108241</v>
       </c>
-      <c r="Q119" s="2" t="n">
+      <c r="Q120" s="2" t="n">
         <v>2806</v>
       </c>
-      <c r="R119" s="2" t="n">
+      <c r="R120" s="2" t="n">
         <v>111047</v>
       </c>
-      <c r="S119" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>9</v>
-      </c>
-      <c r="E121" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G121" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H121" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I121" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J121" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K121" t="n">
-        <v>3</v>
-      </c>
-      <c r="L121" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M121" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N121" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P121" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R121" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S121" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S120" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5149,192 +5159,257 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>9</v>
+      </c>
+      <c r="E122" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H122" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I122" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J122" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P122" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R122" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D122" t="n">
+      <c r="D123" t="n">
         <v>2</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E123" t="n">
         <v>100</v>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="n">
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="n">
         <v>8.56</v>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="n">
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="n">
         <v>12.69</v>
       </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="n">
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="n">
         <v>4.5</v>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="n">
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
         <v>8.56</v>
       </c>
-      <c r="N122" t="n">
+      <c r="N123" t="n">
         <v>57466</v>
       </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="n">
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="n">
         <v>114933</v>
       </c>
-      <c r="Q122" t="n">
+      <c r="Q123" t="n">
         <v>667</v>
       </c>
-      <c r="R122" t="n">
+      <c r="R123" t="n">
         <v>115600</v>
       </c>
-      <c r="S122" t="n">
+      <c r="S123" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D123" s="2" t="n">
+      <c r="D124" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E123" s="2" t="n">
+      <c r="E124" s="2" t="n">
         <v>63.6</v>
       </c>
-      <c r="F123" s="2" t="n">
+      <c r="F124" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="G123" s="2" t="n">
+      <c r="G124" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H123" s="2" t="n">
+      <c r="H124" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I123" s="2" t="n">
+      <c r="I124" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J123" s="2" t="n">
+      <c r="J124" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K123" s="2" t="n">
+      <c r="K124" s="2" t="n">
         <v>3.43</v>
       </c>
-      <c r="L123" s="2" t="n">
+      <c r="L124" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="M123" s="2" t="n">
+      <c r="M124" s="2" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="N123" s="2" t="n">
+      <c r="N124" s="2" t="n">
         <v>9840</v>
       </c>
-      <c r="O123" s="2" t="n">
+      <c r="O124" s="2" t="n">
         <v>3.23</v>
       </c>
-      <c r="P123" s="2" t="n">
+      <c r="P124" s="2" t="n">
         <v>108241</v>
       </c>
-      <c r="Q123" s="2" t="n">
+      <c r="Q124" s="2" t="n">
         <v>2806</v>
       </c>
-      <c r="R123" s="2" t="n">
+      <c r="R124" s="2" t="n">
         <v>111047</v>
       </c>
-      <c r="S123" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="S124" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="2" t="inlineStr"/>
-      <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-      <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="2" t="inlineStr"/>
-      <c r="M125" s="2" t="inlineStr"/>
-      <c r="N125" s="2" t="inlineStr"/>
-      <c r="O125" s="2" t="inlineStr"/>
-      <c r="P125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="D126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="2" t="inlineStr"/>
-      <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-      <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="2" t="inlineStr"/>
-      <c r="M127" s="2" t="inlineStr"/>
-      <c r="N127" s="2" t="inlineStr"/>
-      <c r="O127" s="2" t="inlineStr"/>
-      <c r="P127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" s="2" t="inlineStr"/>
+      <c r="D128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S128"/>
+  <dimension ref="A1:S129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1174,22 +1174,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="H12" t="n">
         <v>4.68</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
         <v>4.74</v>
@@ -1197,22 +1197,22 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>-2.688</v>
+        <v>-1.491</v>
       </c>
       <c r="N12" t="n">
-        <v>-10611</v>
+        <v>-7373</v>
       </c>
       <c r="O12" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="P12" t="n">
-        <v>137916</v>
+        <v>140257</v>
       </c>
       <c r="Q12" t="n">
-        <v>4715</v>
+        <v>4749</v>
       </c>
       <c r="R12" t="n">
-        <v>142631</v>
+        <v>145006</v>
       </c>
       <c r="S12" t="n">
         <v>1410</v>
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>2.78</v>
@@ -1258,22 +1258,22 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="n">
-        <v>-0.043</v>
+        <v>-0.033</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1.03</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>212885</v>
+        <v>215226</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>39497</v>
+        <v>39531</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>252382</v>
+        <v>254757</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -4573,104 +4573,112 @@
       <c r="S107" s="2" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>100</v>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N109" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>34</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr"/>
-      <c r="O109" s="2" t="inlineStr"/>
-      <c r="P109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="n">
+      <c r="D110" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M111" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N111" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>513</v>
-      </c>
-      <c r="R111" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S111" t="n">
-        <v>1415</v>
-      </c>
+      <c r="E110" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S110" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4685,53 +4693,47 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G112" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I112" t="n">
-        <v>1.37</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K112" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="n">
         <v>1</v>
       </c>
-      <c r="L112" t="n">
-        <v>5.67</v>
-      </c>
       <c r="M112" t="n">
-        <v>-0.217</v>
+        <v>-2.607</v>
       </c>
       <c r="N112" t="n">
-        <v>-13272</v>
+        <v>-8011</v>
       </c>
       <c r="O112" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>-53089</v>
+        <v>-16021</v>
       </c>
       <c r="Q112" t="n">
-        <v>5913</v>
+        <v>513</v>
       </c>
       <c r="R112" t="n">
-        <v>-47176</v>
+        <v>-15508</v>
       </c>
       <c r="S112" t="n">
         <v>1415</v>
@@ -4750,47 +4752,53 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H113" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I113" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J113" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K113" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1</v>
+      </c>
       <c r="L113" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M113" t="n">
-        <v>-0.136</v>
+        <v>-0.217</v>
       </c>
       <c r="N113" t="n">
-        <v>-2389</v>
+        <v>-13272</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P113" t="n">
-        <v>-4777</v>
+        <v>-53089</v>
       </c>
       <c r="Q113" t="n">
-        <v>2924</v>
+        <v>5913</v>
       </c>
       <c r="R113" t="n">
-        <v>-1854</v>
+        <v>-47176</v>
       </c>
       <c r="S113" t="n">
         <v>1415</v>
@@ -4809,43 +4817,47 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" t="n">
-        <v>100</v>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="n">
-        <v>14</v>
-      </c>
-      <c r="L114" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M114" t="n">
-        <v>1.042</v>
+        <v>-0.136</v>
       </c>
       <c r="N114" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O114" t="inlineStr"/>
+        <v>-2389</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
       <c r="P114" t="n">
-        <v>48540</v>
+        <v>-4777</v>
       </c>
       <c r="Q114" t="n">
-        <v>4254</v>
+        <v>2924</v>
       </c>
       <c r="R114" t="n">
-        <v>52794</v>
+        <v>-1854</v>
       </c>
       <c r="S114" t="n">
         <v>1415</v>
@@ -4864,175 +4876,169 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D115" t="n">
         <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="n">
+        <v>100</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>14</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N115" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R115" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="n">
         <v>0.86</v>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="n">
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="n">
         <v>1.53</v>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="n">
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="n">
         <v>4.67</v>
       </c>
-      <c r="M115" t="n">
+      <c r="M116" t="n">
         <v>-0.864</v>
       </c>
-      <c r="N115" t="n">
+      <c r="N116" t="n">
         <v>-28997</v>
       </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
         <v>-86990</v>
       </c>
-      <c r="Q115" t="n">
+      <c r="Q116" t="n">
         <v>13787</v>
       </c>
-      <c r="R115" t="n">
+      <c r="R116" t="n">
         <v>-73203</v>
       </c>
-      <c r="S115" t="n">
+      <c r="S116" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n">
+      <c r="D117" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>28.6</v>
       </c>
-      <c r="F116" s="2" t="n">
+      <c r="F117" s="2" t="n">
         <v>0.77</v>
       </c>
-      <c r="G116" s="2" t="n">
+      <c r="G117" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H116" s="2" t="n">
+      <c r="H117" s="2" t="n">
         <v>1.03</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K116" s="2" t="n">
+      <c r="K117" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L116" s="2" t="n">
+      <c r="L117" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="M116" s="2" t="n">
+      <c r="M117" s="2" t="n">
         <v>-0.416</v>
       </c>
-      <c r="N116" s="2" t="n">
+      <c r="N117" s="2" t="n">
         <v>-8024</v>
       </c>
-      <c r="O116" s="2" t="n">
+      <c r="O117" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="P116" s="2" t="n">
+      <c r="P117" s="2" t="n">
         <v>-112337</v>
       </c>
-      <c r="Q116" s="2" t="n">
+      <c r="Q117" s="2" t="n">
         <v>27391</v>
       </c>
-      <c r="R116" s="2" t="n">
+      <c r="R117" s="2" t="n">
         <v>-84947</v>
       </c>
-      <c r="S116" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>9</v>
-      </c>
-      <c r="E118" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G118" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H118" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I118" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J118" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N118" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P118" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R118" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S118" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S117" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5047,169 +5053,165 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E119" t="n">
-        <v>100</v>
-      </c>
-      <c r="F119" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G119" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H119" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I119" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J119" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J119" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N119" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P119" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R119" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="n">
+        <v>100</v>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="n">
         <v>8.56</v>
       </c>
-      <c r="N119" t="n">
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N120" t="n">
         <v>57466</v>
       </c>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="n">
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="n">
         <v>114933</v>
       </c>
-      <c r="Q119" t="n">
+      <c r="Q120" t="n">
         <v>667</v>
       </c>
-      <c r="R119" t="n">
+      <c r="R120" t="n">
         <v>115600</v>
       </c>
-      <c r="S119" t="n">
+      <c r="S120" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D120" s="2" t="n">
+      <c r="D121" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E120" s="2" t="n">
+      <c r="E121" s="2" t="n">
         <v>63.6</v>
       </c>
-      <c r="F120" s="2" t="n">
+      <c r="F121" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="G120" s="2" t="n">
+      <c r="G121" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H120" s="2" t="n">
+      <c r="H121" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I120" s="2" t="n">
+      <c r="I121" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J120" s="2" t="n">
+      <c r="J121" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="n">
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="N120" s="2" t="n">
+      <c r="N121" s="2" t="n">
         <v>9840</v>
       </c>
-      <c r="O120" s="2" t="n">
+      <c r="O121" s="2" t="n">
         <v>3.23</v>
       </c>
-      <c r="P120" s="2" t="n">
+      <c r="P121" s="2" t="n">
         <v>108241</v>
       </c>
-      <c r="Q120" s="2" t="n">
+      <c r="Q121" s="2" t="n">
         <v>2806</v>
       </c>
-      <c r="R120" s="2" t="n">
+      <c r="R121" s="2" t="n">
         <v>111047</v>
       </c>
-      <c r="S120" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>9</v>
-      </c>
-      <c r="E122" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F122" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G122" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H122" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I122" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J122" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K122" t="n">
-        <v>3</v>
-      </c>
-      <c r="L122" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M122" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N122" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P122" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R122" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S122" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S121" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5224,192 +5226,257 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>9</v>
+      </c>
+      <c r="E123" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H123" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I123" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J123" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K123" t="n">
+        <v>3</v>
+      </c>
+      <c r="L123" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M123" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P123" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R123" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D123" t="n">
+      <c r="D124" t="n">
         <v>2</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E124" t="n">
         <v>100</v>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="n">
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="n">
         <v>8.56</v>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="n">
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="n">
         <v>12.69</v>
       </c>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="n">
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="n">
         <v>4.5</v>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="n">
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
         <v>8.56</v>
       </c>
-      <c r="N123" t="n">
+      <c r="N124" t="n">
         <v>57466</v>
       </c>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="n">
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="n">
         <v>114933</v>
       </c>
-      <c r="Q123" t="n">
+      <c r="Q124" t="n">
         <v>667</v>
       </c>
-      <c r="R123" t="n">
+      <c r="R124" t="n">
         <v>115600</v>
       </c>
-      <c r="S123" t="n">
+      <c r="S124" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D124" s="2" t="n">
+      <c r="D125" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E124" s="2" t="n">
+      <c r="E125" s="2" t="n">
         <v>63.6</v>
       </c>
-      <c r="F124" s="2" t="n">
+      <c r="F125" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="G124" s="2" t="n">
+      <c r="G125" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H124" s="2" t="n">
+      <c r="H125" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I124" s="2" t="n">
+      <c r="I125" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J124" s="2" t="n">
+      <c r="J125" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K124" s="2" t="n">
+      <c r="K125" s="2" t="n">
         <v>3.43</v>
       </c>
-      <c r="L124" s="2" t="n">
+      <c r="L125" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="M124" s="2" t="n">
+      <c r="M125" s="2" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="N124" s="2" t="n">
+      <c r="N125" s="2" t="n">
         <v>9840</v>
       </c>
-      <c r="O124" s="2" t="n">
+      <c r="O125" s="2" t="n">
         <v>3.23</v>
       </c>
-      <c r="P124" s="2" t="n">
+      <c r="P125" s="2" t="n">
         <v>108241</v>
       </c>
-      <c r="Q124" s="2" t="n">
+      <c r="Q125" s="2" t="n">
         <v>2806</v>
       </c>
-      <c r="R124" s="2" t="n">
+      <c r="R125" s="2" t="n">
         <v>111047</v>
       </c>
-      <c r="S124" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="S125" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" s="2" t="inlineStr"/>
-      <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr"/>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-      <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="2" t="inlineStr"/>
-      <c r="N126" s="2" t="inlineStr"/>
-      <c r="O126" s="2" t="inlineStr"/>
-      <c r="P126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="D127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="inlineStr"/>
-      <c r="M128" s="2" t="inlineStr"/>
-      <c r="N128" s="2" t="inlineStr"/>
-      <c r="O128" s="2" t="inlineStr"/>
-      <c r="P128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" s="2" t="inlineStr"/>
+      <c r="D129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr"/>
+      <c r="P129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S129"/>
+  <dimension ref="A1:S130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1174,48 +1174,48 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="F12" t="n">
-        <v>0.23</v>
+        <v>0.55</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="H12" t="n">
-        <v>4.68</v>
+        <v>4.32</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>4.34</v>
       </c>
       <c r="J12" t="n">
-        <v>4.74</v>
+        <v>6.17</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>-1.491</v>
+        <v>-2.134</v>
       </c>
       <c r="N12" t="n">
-        <v>-7373</v>
+        <v>-5991</v>
       </c>
       <c r="O12" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="P12" t="n">
-        <v>140257</v>
+        <v>82374</v>
       </c>
       <c r="Q12" t="n">
-        <v>4749</v>
+        <v>8820</v>
       </c>
       <c r="R12" t="n">
-        <v>145006</v>
+        <v>91194</v>
       </c>
       <c r="S12" t="n">
-        <v>1410</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="13">
@@ -1235,19 +1235,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37.3</v>
+        <v>36.8</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4.58</v>
+        <v>4.52</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>19.29</v>
@@ -1258,22 +1258,22 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="n">
-        <v>-0.033</v>
+        <v>-0.141</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>199</v>
+        <v>-62</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>215226</v>
+        <v>157343</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>39531</v>
+        <v>43602</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>254757</v>
+        <v>200945</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -3332,7 +3332,7 @@
         <v>6570</v>
       </c>
       <c r="S64" t="n">
-        <v>1410</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="65">
@@ -3751,46 +3751,52 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
+        <v>0.16</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.66</v>
+      </c>
       <c r="H82" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="I82" t="inlineStr"/>
+        <v>5.31</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.66</v>
+      </c>
       <c r="J82" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="K82" t="inlineStr"/>
+        <v>5.74</v>
+      </c>
+      <c r="K82" t="n">
+        <v>14</v>
+      </c>
       <c r="L82" t="n">
-        <v>7</v>
+        <v>3.67</v>
       </c>
       <c r="M82" t="n">
-        <v>-4.743</v>
+        <v>-3.817</v>
       </c>
       <c r="N82" t="n">
-        <v>-23723</v>
+        <v>-13745</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P82" t="n">
-        <v>18358</v>
+        <v>-7777</v>
       </c>
       <c r="Q82" t="n">
-        <v>2013</v>
+        <v>4042</v>
       </c>
       <c r="R82" t="n">
-        <v>20371</v>
+        <v>-3735</v>
       </c>
       <c r="S82" t="n">
-        <v>1410</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="83">
@@ -3810,43 +3816,49 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="2" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>0.66</v>
+      </c>
       <c r="H83" s="2" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
+        <v>6.49</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0.66</v>
+      </c>
       <c r="J83" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="K83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="n">
+        <v>14</v>
+      </c>
       <c r="L83" s="2" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>-7.378</v>
+        <v>-5.056</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-47568</v>
+        <v>-25279</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>-53056</v>
+        <v>-79191</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>2962</v>
+        <v>4991</v>
       </c>
       <c r="R83" s="2" t="n">
-        <v>-50094</v>
+        <v>-74200</v>
       </c>
       <c r="S83" s="2" t="inlineStr"/>
     </row>
@@ -4033,711 +4045,723 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="H92" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="I92" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="J92" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="K92" t="n">
+        <v>14</v>
+      </c>
+      <c r="L92" t="n">
+        <v>2</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="N92" t="n">
+        <v>3676</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P92" t="n">
+        <v>-3971</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>2041</v>
+      </c>
+      <c r="R92" t="n">
+        <v>-1930</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D93" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1.058</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="O93" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P93" s="2" t="n">
+        <v>-13847</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>2237</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>-11609</v>
+      </c>
+      <c r="S93" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>6</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-3.784</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-9114</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>-54681</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1715</v>
+      </c>
+      <c r="R97" t="n">
+        <v>-52966</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-3.784</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>-9114</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>-54681</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>1715</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>-52966</v>
+      </c>
+      <c r="S98" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_ADD1</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
         <v>1</v>
       </c>
-      <c r="E92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>-6.802</v>
-      </c>
-      <c r="N92" s="2" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="O92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" s="2" t="n">
-        <v>-21853</v>
-      </c>
-      <c r="Q92" s="2" t="n">
-        <v>1316</v>
-      </c>
-      <c r="R92" s="2" t="n">
-        <v>-20536</v>
-      </c>
-      <c r="S92" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>-10.495</v>
+      </c>
+      <c r="N102" t="n">
+        <v>-40484</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>-40484</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>512</v>
+      </c>
+      <c r="R102" t="n">
+        <v>-39972</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr"/>
-      <c r="O94" s="2" t="inlineStr"/>
-      <c r="P94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
+      <c r="D103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-10.495</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-40484</v>
+      </c>
+      <c r="O103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="2" t="n">
+        <v>-40484</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>-39972</v>
+      </c>
+      <c r="S103" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D105" t="n">
+        <v>7</v>
+      </c>
+      <c r="E105" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G105" t="n">
+        <v>6</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I105" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="J105" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1867</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P105" t="n">
+        <v>36110</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>3239</v>
+      </c>
+      <c r="R105" t="n">
+        <v>39349</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>1867</v>
+      </c>
+      <c r="O106" s="2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P106" s="2" t="n">
+        <v>36110</v>
+      </c>
+      <c r="Q106" s="2" t="n">
+        <v>3239</v>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>39349</v>
+      </c>
+      <c r="S106" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_LOW</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
         <v>1</v>
       </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="n">
-        <v>4</v>
-      </c>
-      <c r="M96" t="n">
-        <v>-4.62</v>
-      </c>
-      <c r="N96" t="n">
-        <v>-14530</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>-14927</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>594</v>
-      </c>
-      <c r="R96" t="n">
-        <v>-14333</v>
-      </c>
-      <c r="S96" t="n">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="E110" t="n">
+        <v>100</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N110" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>34</v>
+      </c>
+      <c r="R110" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n">
+      <c r="D111" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>-4.62</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>-14530</v>
-      </c>
-      <c r="O97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="2" t="n">
-        <v>-14927</v>
-      </c>
-      <c r="Q97" s="2" t="n">
-        <v>594</v>
-      </c>
-      <c r="R97" s="2" t="n">
-        <v>-14333</v>
-      </c>
-      <c r="S97" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_ADD1</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
-      <c r="O99" s="2" t="inlineStr"/>
-      <c r="P99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>-10.495</v>
-      </c>
-      <c r="N101" t="n">
-        <v>-40657</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>-40657</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>514</v>
-      </c>
-      <c r="R101" t="n">
-        <v>-40143</v>
-      </c>
-      <c r="S101" t="n">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>-10.495</v>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>-40657</v>
-      </c>
-      <c r="O102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" s="2" t="n">
-        <v>-40657</v>
-      </c>
-      <c r="Q102" s="2" t="n">
-        <v>514</v>
-      </c>
-      <c r="R102" s="2" t="n">
-        <v>-40143</v>
-      </c>
-      <c r="S102" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>6</v>
-      </c>
-      <c r="E104" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F104" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="G104" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="H104" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I104" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J104" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>-0.845</v>
-      </c>
-      <c r="N104" t="n">
-        <v>-2493</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="P104" t="n">
-        <v>10636</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>2745</v>
-      </c>
-      <c r="R104" t="n">
-        <v>13381</v>
-      </c>
-      <c r="S104" t="n">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>-0.845</v>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>-2493</v>
-      </c>
-      <c r="O105" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="P105" s="2" t="n">
-        <v>10636</v>
-      </c>
-      <c r="Q105" s="2" t="n">
-        <v>2745</v>
-      </c>
-      <c r="R105" s="2" t="n">
-        <v>13381</v>
-      </c>
-      <c r="S105" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_LOW</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
-      <c r="N107" s="2" t="inlineStr"/>
-      <c r="O107" s="2" t="inlineStr"/>
-      <c r="P107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" t="n">
+      <c r="E111" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="n">
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="n">
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="n">
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="n">
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N109" t="n">
+      <c r="N111" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="n">
+      <c r="O111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q109" t="n">
+      <c r="Q111" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R109" t="n">
+      <c r="R111" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S109" t="n">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr"/>
-      <c r="K110" s="2" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N110" s="2" t="n">
-        <v>2341</v>
-      </c>
-      <c r="O110" s="2" t="inlineStr"/>
-      <c r="P110" s="2" t="n">
-        <v>2341</v>
-      </c>
-      <c r="Q110" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="R110" s="2" t="n">
-        <v>2375</v>
-      </c>
-      <c r="S110" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>2</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="n">
-        <v>1</v>
-      </c>
-      <c r="M112" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N112" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>513</v>
-      </c>
-      <c r="R112" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S112" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S111" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4752,53 +4776,47 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G113" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I113" t="n">
-        <v>1.37</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K113" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="n">
         <v>1</v>
       </c>
-      <c r="L113" t="n">
-        <v>5.67</v>
-      </c>
       <c r="M113" t="n">
-        <v>-0.217</v>
+        <v>-2.607</v>
       </c>
       <c r="N113" t="n">
-        <v>-13272</v>
+        <v>-8011</v>
       </c>
       <c r="O113" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>-53089</v>
+        <v>-16021</v>
       </c>
       <c r="Q113" t="n">
-        <v>5913</v>
+        <v>513</v>
       </c>
       <c r="R113" t="n">
-        <v>-47176</v>
+        <v>-15508</v>
       </c>
       <c r="S113" t="n">
         <v>1415</v>
@@ -4817,47 +4835,53 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H114" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I114" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J114" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K114" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1</v>
+      </c>
       <c r="L114" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.136</v>
+        <v>-0.217</v>
       </c>
       <c r="N114" t="n">
-        <v>-2389</v>
+        <v>-13272</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P114" t="n">
-        <v>-4777</v>
+        <v>-53089</v>
       </c>
       <c r="Q114" t="n">
-        <v>2924</v>
+        <v>5913</v>
       </c>
       <c r="R114" t="n">
-        <v>-1854</v>
+        <v>-47176</v>
       </c>
       <c r="S114" t="n">
         <v>1415</v>
@@ -4876,43 +4900,47 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>100</v>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="n">
-        <v>14</v>
-      </c>
-      <c r="L115" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M115" t="n">
-        <v>1.042</v>
+        <v>-0.136</v>
       </c>
       <c r="N115" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O115" t="inlineStr"/>
+        <v>-2389</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
       <c r="P115" t="n">
-        <v>48540</v>
+        <v>-4777</v>
       </c>
       <c r="Q115" t="n">
-        <v>4254</v>
+        <v>2924</v>
       </c>
       <c r="R115" t="n">
-        <v>52794</v>
+        <v>-1854</v>
       </c>
       <c r="S115" t="n">
         <v>1415</v>
@@ -4931,175 +4959,169 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D116" t="n">
         <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="n">
+        <v>100</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="n">
+        <v>14</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N116" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R116" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>3</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="n">
         <v>0.86</v>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="n">
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="n">
         <v>1.53</v>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="n">
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="n">
         <v>4.67</v>
       </c>
-      <c r="M116" t="n">
+      <c r="M117" t="n">
         <v>-0.864</v>
       </c>
-      <c r="N116" t="n">
+      <c r="N117" t="n">
         <v>-28997</v>
       </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
         <v>-86990</v>
       </c>
-      <c r="Q116" t="n">
+      <c r="Q117" t="n">
         <v>13787</v>
       </c>
-      <c r="R116" t="n">
+      <c r="R117" t="n">
         <v>-73203</v>
       </c>
-      <c r="S116" t="n">
+      <c r="S117" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D117" s="2" t="n">
+      <c r="D118" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E118" s="2" t="n">
         <v>28.6</v>
       </c>
-      <c r="F117" s="2" t="n">
+      <c r="F118" s="2" t="n">
         <v>0.77</v>
       </c>
-      <c r="G117" s="2" t="n">
+      <c r="G118" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H117" s="2" t="n">
+      <c r="H118" s="2" t="n">
         <v>1.03</v>
       </c>
-      <c r="I117" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J118" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K117" s="2" t="n">
+      <c r="K118" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L117" s="2" t="n">
+      <c r="L118" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="M117" s="2" t="n">
+      <c r="M118" s="2" t="n">
         <v>-0.416</v>
       </c>
-      <c r="N117" s="2" t="n">
+      <c r="N118" s="2" t="n">
         <v>-8024</v>
       </c>
-      <c r="O117" s="2" t="n">
+      <c r="O118" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="P117" s="2" t="n">
+      <c r="P118" s="2" t="n">
         <v>-112337</v>
       </c>
-      <c r="Q117" s="2" t="n">
+      <c r="Q118" s="2" t="n">
         <v>27391</v>
       </c>
-      <c r="R117" s="2" t="n">
+      <c r="R118" s="2" t="n">
         <v>-84947</v>
       </c>
-      <c r="S117" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>9</v>
-      </c>
-      <c r="E119" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G119" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H119" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I119" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J119" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N119" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P119" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R119" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S119" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S118" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5114,169 +5136,165 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E120" t="n">
-        <v>100</v>
-      </c>
-      <c r="F120" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G120" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H120" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H120" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I120" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J120" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J120" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P120" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R120" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" t="n">
+        <v>100</v>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="n">
         <v>8.56</v>
       </c>
-      <c r="N120" t="n">
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N121" t="n">
         <v>57466</v>
       </c>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="n">
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="n">
         <v>114933</v>
       </c>
-      <c r="Q120" t="n">
+      <c r="Q121" t="n">
         <v>667</v>
       </c>
-      <c r="R120" t="n">
+      <c r="R121" t="n">
         <v>115600</v>
       </c>
-      <c r="S120" t="n">
+      <c r="S121" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D121" s="2" t="n">
+      <c r="D122" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E121" s="2" t="n">
+      <c r="E122" s="2" t="n">
         <v>63.6</v>
       </c>
-      <c r="F121" s="2" t="n">
+      <c r="F122" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="G121" s="2" t="n">
+      <c r="G122" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H121" s="2" t="n">
+      <c r="H122" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I121" s="2" t="n">
+      <c r="I122" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J121" s="2" t="n">
+      <c r="J122" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="2" t="inlineStr"/>
-      <c r="M121" s="2" t="n">
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="N121" s="2" t="n">
+      <c r="N122" s="2" t="n">
         <v>9840</v>
       </c>
-      <c r="O121" s="2" t="n">
+      <c r="O122" s="2" t="n">
         <v>3.23</v>
       </c>
-      <c r="P121" s="2" t="n">
+      <c r="P122" s="2" t="n">
         <v>108241</v>
       </c>
-      <c r="Q121" s="2" t="n">
+      <c r="Q122" s="2" t="n">
         <v>2806</v>
       </c>
-      <c r="R121" s="2" t="n">
+      <c r="R122" s="2" t="n">
         <v>111047</v>
       </c>
-      <c r="S121" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>9</v>
-      </c>
-      <c r="E123" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F123" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G123" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H123" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I123" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J123" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K123" t="n">
-        <v>3</v>
-      </c>
-      <c r="L123" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M123" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N123" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P123" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R123" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S123" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S122" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5291,192 +5309,257 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>9</v>
+      </c>
+      <c r="E124" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H124" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I124" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J124" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K124" t="n">
+        <v>3</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M124" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N124" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P124" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R124" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S124" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D124" t="n">
+      <c r="D125" t="n">
         <v>2</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E125" t="n">
         <v>100</v>
       </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="n">
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="n">
         <v>8.56</v>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="n">
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="n">
         <v>12.69</v>
       </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="n">
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="n">
         <v>4.5</v>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="n">
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
         <v>8.56</v>
       </c>
-      <c r="N124" t="n">
+      <c r="N125" t="n">
         <v>57466</v>
       </c>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="n">
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="n">
         <v>114933</v>
       </c>
-      <c r="Q124" t="n">
+      <c r="Q125" t="n">
         <v>667</v>
       </c>
-      <c r="R124" t="n">
+      <c r="R125" t="n">
         <v>115600</v>
       </c>
-      <c r="S124" t="n">
+      <c r="S125" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D125" s="2" t="n">
+      <c r="D126" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E126" s="2" t="n">
         <v>63.6</v>
       </c>
-      <c r="F125" s="2" t="n">
+      <c r="F126" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="G125" s="2" t="n">
+      <c r="G126" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H125" s="2" t="n">
+      <c r="H126" s="2" t="n">
         <v>4.19</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I126" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J126" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="K125" s="2" t="n">
+      <c r="K126" s="2" t="n">
         <v>3.43</v>
       </c>
-      <c r="L125" s="2" t="n">
+      <c r="L126" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="M125" s="2" t="n">
+      <c r="M126" s="2" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="N125" s="2" t="n">
+      <c r="N126" s="2" t="n">
         <v>9840</v>
       </c>
-      <c r="O125" s="2" t="n">
+      <c r="O126" s="2" t="n">
         <v>3.23</v>
       </c>
-      <c r="P125" s="2" t="n">
+      <c r="P126" s="2" t="n">
         <v>108241</v>
       </c>
-      <c r="Q125" s="2" t="n">
+      <c r="Q126" s="2" t="n">
         <v>2806</v>
       </c>
-      <c r="R125" s="2" t="n">
+      <c r="R126" s="2" t="n">
         <v>111047</v>
       </c>
-      <c r="S125" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="S126" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="2" t="inlineStr"/>
-      <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-      <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="2" t="inlineStr"/>
-      <c r="M127" s="2" t="inlineStr"/>
-      <c r="N127" s="2" t="inlineStr"/>
-      <c r="O127" s="2" t="inlineStr"/>
-      <c r="P127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="D128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="2" t="inlineStr"/>
-      <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-      <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="inlineStr"/>
-      <c r="M129" s="2" t="inlineStr"/>
-      <c r="N129" s="2" t="inlineStr"/>
-      <c r="O129" s="2" t="inlineStr"/>
-      <c r="P129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" s="2" t="inlineStr"/>
+      <c r="D130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr"/>
+      <c r="P130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1206,13 +1206,13 @@
         <v>0.27</v>
       </c>
       <c r="P12" t="n">
-        <v>82374</v>
+        <v>65248</v>
       </c>
       <c r="Q12" t="n">
-        <v>8820</v>
+        <v>8946</v>
       </c>
       <c r="R12" t="n">
-        <v>91194</v>
+        <v>74194</v>
       </c>
       <c r="S12" t="n">
         <v>1404</v>
@@ -1267,13 +1267,13 @@
         <v>0.99</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>157343</v>
+        <v>140217</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>43602</v>
+        <v>43728</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>200945</v>
+        <v>183945</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -1763,13 +1763,13 @@
         <v>1.5</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>284663</v>
+        <v>267537</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>10881</v>
+        <v>11007</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>295544</v>
+        <v>278544</v>
       </c>
       <c r="S22" s="2" t="inlineStr"/>
     </row>
@@ -5286,13 +5286,13 @@
         <v>3.23</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>108241</v>
+        <v>58081</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>2806</v>
+        <v>2966</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>111047</v>
+        <v>61047</v>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
     </row>
@@ -5469,13 +5469,13 @@
         <v>3.23</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>108241</v>
+        <v>58081</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>2806</v>
+        <v>2966</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>111047</v>
+        <v>61047</v>
       </c>
       <c r="S126" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1174,19 +1174,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>33.3</v>
+        <v>38.1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="G12" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="H12" t="n">
-        <v>4.32</v>
+        <v>3.76</v>
       </c>
       <c r="I12" t="n">
         <v>4.34</v>
@@ -1197,25 +1197,25 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>-2.134</v>
+        <v>-1.601</v>
       </c>
       <c r="N12" t="n">
-        <v>-5991</v>
+        <v>-3838</v>
       </c>
       <c r="O12" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="P12" t="n">
-        <v>65248</v>
+        <v>81615</v>
       </c>
       <c r="Q12" t="n">
-        <v>8946</v>
+        <v>11748</v>
       </c>
       <c r="R12" t="n">
-        <v>74194</v>
+        <v>93363</v>
       </c>
       <c r="S12" t="n">
-        <v>1404</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="13">
@@ -1235,19 +1235,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>36.8</v>
+        <v>37.1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4.52</v>
+        <v>4.41</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>19.29</v>
@@ -1258,22 +1258,22 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="n">
-        <v>-0.141</v>
+        <v>-0.144</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-62</v>
+        <v>-23</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>140217</v>
+        <v>156584</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>43728</v>
+        <v>46530</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>183945</v>
+        <v>203114</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -3332,7 +3332,7 @@
         <v>6570</v>
       </c>
       <c r="S64" t="n">
-        <v>1404</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="65">
@@ -3751,22 +3751,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E82" t="n">
-        <v>25</v>
+        <v>44.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="G82" t="n">
-        <v>0.66</v>
+        <v>1.18</v>
       </c>
       <c r="H82" t="n">
-        <v>5.31</v>
+        <v>4.28</v>
       </c>
       <c r="I82" t="n">
-        <v>0.66</v>
+        <v>3.2</v>
       </c>
       <c r="J82" t="n">
         <v>5.74</v>
@@ -3775,28 +3775,28 @@
         <v>14</v>
       </c>
       <c r="L82" t="n">
-        <v>3.67</v>
+        <v>5.6</v>
       </c>
       <c r="M82" t="n">
-        <v>-3.817</v>
+        <v>-1.851</v>
       </c>
       <c r="N82" t="n">
-        <v>-13745</v>
+        <v>-4960</v>
       </c>
       <c r="O82" t="n">
-        <v>0.05</v>
+        <v>0.34</v>
       </c>
       <c r="P82" t="n">
-        <v>-7777</v>
+        <v>-16484</v>
       </c>
       <c r="Q82" t="n">
-        <v>4042</v>
+        <v>6506</v>
       </c>
       <c r="R82" t="n">
-        <v>-3735</v>
+        <v>-9978</v>
       </c>
       <c r="S82" t="n">
-        <v>1404</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="83">
@@ -3816,22 +3816,22 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.66</v>
+        <v>1.18</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>6.49</v>
+        <v>5.23</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.66</v>
+        <v>3.2</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>10.01</v>
@@ -3840,25 +3840,25 @@
         <v>14</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>3.5</v>
+        <v>5.17</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>-5.056</v>
+        <v>-2.668</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-25279</v>
+        <v>-11605</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>-79191</v>
+        <v>-87898</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>4991</v>
+        <v>7455</v>
       </c>
       <c r="R83" s="2" t="n">
-        <v>-74200</v>
+        <v>-80443</v>
       </c>
       <c r="S83" s="2" t="inlineStr"/>
     </row>
@@ -4061,19 +4061,19 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>0.99</v>
+        <v>1.67</v>
       </c>
       <c r="G92" t="n">
         <v>3.59</v>
       </c>
       <c r="H92" t="n">
-        <v>4.61</v>
+        <v>2.42</v>
       </c>
       <c r="I92" t="n">
         <v>4.34</v>
@@ -4085,28 +4085,28 @@
         <v>14</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="M92" t="n">
-        <v>0.856</v>
+        <v>0.587</v>
       </c>
       <c r="N92" t="n">
-        <v>3676</v>
+        <v>2177</v>
       </c>
       <c r="O92" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="P92" t="n">
-        <v>-3971</v>
+        <v>19858</v>
       </c>
       <c r="Q92" t="n">
-        <v>2041</v>
+        <v>2417</v>
       </c>
       <c r="R92" t="n">
-        <v>-1930</v>
+        <v>22274</v>
       </c>
       <c r="S92" t="n">
-        <v>1404</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="93">
@@ -4126,19 +4126,19 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>3.59</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>5.71</v>
+        <v>3.88</v>
       </c>
       <c r="I93" s="2" t="n">
         <v>4.34</v>
@@ -4150,25 +4150,25 @@
         <v>14</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>3.5</v>
+        <v>4.67</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>-1.058</v>
+        <v>-0.891</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>288</v>
+        <v>-234</v>
       </c>
       <c r="O93" s="2" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="P93" s="2" t="n">
-        <v>-13847</v>
+        <v>9982</v>
       </c>
       <c r="Q93" s="2" t="n">
-        <v>2237</v>
+        <v>2613</v>
       </c>
       <c r="R93" s="2" t="n">
-        <v>-11609</v>
+        <v>12595</v>
       </c>
       <c r="S93" s="2" t="inlineStr"/>
     </row>
@@ -4254,22 +4254,22 @@
         <v>-3.784</v>
       </c>
       <c r="N97" t="n">
-        <v>-9114</v>
+        <v>-8906</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>-54681</v>
+        <v>-53435</v>
       </c>
       <c r="Q97" t="n">
-        <v>1715</v>
+        <v>1676</v>
       </c>
       <c r="R97" t="n">
-        <v>-52966</v>
+        <v>-51759</v>
       </c>
       <c r="S97" t="n">
-        <v>1404</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="98">
@@ -4313,19 +4313,19 @@
         <v>-3.784</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-9114</v>
+        <v>-8906</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="2" t="n">
-        <v>-54681</v>
+        <v>-53435</v>
       </c>
       <c r="Q98" s="2" t="n">
-        <v>1715</v>
+        <v>1676</v>
       </c>
       <c r="R98" s="2" t="n">
-        <v>-52966</v>
+        <v>-51759</v>
       </c>
       <c r="S98" s="2" t="inlineStr"/>
     </row>
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>10.49</v>
+        <v>7.15</v>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
@@ -4405,28 +4405,28 @@
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-10.495</v>
+        <v>-7.145</v>
       </c>
       <c r="N102" t="n">
-        <v>-40484</v>
+        <v>-27425</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>-40484</v>
+        <v>-54849</v>
       </c>
       <c r="Q102" t="n">
-        <v>512</v>
+        <v>1053</v>
       </c>
       <c r="R102" t="n">
-        <v>-39972</v>
+        <v>-53796</v>
       </c>
       <c r="S102" t="n">
-        <v>1404</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="103">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="n">
-        <v>10.49</v>
+        <v>7.15</v>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="n">
@@ -4464,25 +4464,25 @@
       </c>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>-10.495</v>
+        <v>-7.145</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-40484</v>
+        <v>-27425</v>
       </c>
       <c r="O103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="2" t="n">
-        <v>-40484</v>
+        <v>-54849</v>
       </c>
       <c r="Q103" s="2" t="n">
-        <v>512</v>
+        <v>1053</v>
       </c>
       <c r="R103" s="2" t="n">
-        <v>-39972</v>
+        <v>-53796</v>
       </c>
       <c r="S103" s="2" t="inlineStr"/>
     </row>
@@ -4503,52 +4503,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E105" t="n">
-        <v>42.9</v>
+        <v>53.8</v>
       </c>
       <c r="F105" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="G105" t="n">
-        <v>6</v>
+        <v>7.78</v>
       </c>
       <c r="H105" t="n">
-        <v>3.65</v>
+        <v>2.66</v>
       </c>
       <c r="I105" t="n">
-        <v>8.49</v>
+        <v>16.31</v>
       </c>
       <c r="J105" t="n">
         <v>5.68</v>
       </c>
       <c r="K105" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L105" t="n">
         <v>0.33</v>
       </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
       <c r="M105" t="n">
-        <v>0.489</v>
+        <v>2.964</v>
       </c>
       <c r="N105" t="n">
-        <v>1867</v>
+        <v>3611</v>
       </c>
       <c r="O105" t="n">
-        <v>1.33</v>
+        <v>2.16</v>
       </c>
       <c r="P105" t="n">
-        <v>36110</v>
+        <v>129001</v>
       </c>
       <c r="Q105" t="n">
-        <v>3239</v>
+        <v>5832</v>
       </c>
       <c r="R105" t="n">
-        <v>39349</v>
+        <v>134833</v>
       </c>
       <c r="S105" t="n">
-        <v>1404</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="106">
@@ -4568,49 +4568,49 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>42.9</v>
+        <v>53.8</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>6</v>
+        <v>7.78</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>3.65</v>
+        <v>2.66</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>8.49</v>
+        <v>16.31</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>5.68</v>
       </c>
       <c r="K106" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L106" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M106" s="2" t="n">
-        <v>0.489</v>
+        <v>2.964</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>1867</v>
+        <v>3611</v>
       </c>
       <c r="O106" s="2" t="n">
-        <v>1.33</v>
+        <v>2.16</v>
       </c>
       <c r="P106" s="2" t="n">
-        <v>36110</v>
+        <v>129001</v>
       </c>
       <c r="Q106" s="2" t="n">
-        <v>3239</v>
+        <v>5832</v>
       </c>
       <c r="R106" s="2" t="n">
-        <v>39349</v>
+        <v>134833</v>
       </c>
       <c r="S106" s="2" t="inlineStr"/>
     </row>
@@ -4707,7 +4707,7 @@
         <v>2375</v>
       </c>
       <c r="S110" t="n">
-        <v>1404</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="111">
@@ -5286,13 +5286,13 @@
         <v>3.23</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>58081</v>
+        <v>56575</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>2966</v>
+        <v>2972</v>
       </c>
       <c r="R122" s="2" t="n">
-        <v>61047</v>
+        <v>59547</v>
       </c>
       <c r="S122" s="2" t="inlineStr"/>
     </row>
@@ -5469,13 +5469,13 @@
         <v>3.23</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>58081</v>
+        <v>56575</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>2966</v>
+        <v>2972</v>
       </c>
       <c r="R126" s="2" t="n">
-        <v>61047</v>
+        <v>59547</v>
       </c>
       <c r="S126" s="2" t="inlineStr"/>
     </row>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S130"/>
+  <dimension ref="A1:S134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1174,22 +1174,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>38.1</v>
+        <v>37.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="G12" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="H12" t="n">
-        <v>3.76</v>
+        <v>3.61</v>
       </c>
       <c r="I12" t="n">
-        <v>4.34</v>
+        <v>4.87</v>
       </c>
       <c r="J12" t="n">
         <v>6.17</v>
@@ -1197,22 +1197,22 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>-1.601</v>
+        <v>-1.414</v>
       </c>
       <c r="N12" t="n">
-        <v>-3838</v>
+        <v>-3417</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="P12" t="n">
-        <v>81615</v>
+        <v>27405</v>
       </c>
       <c r="Q12" t="n">
-        <v>11748</v>
+        <v>13257</v>
       </c>
       <c r="R12" t="n">
-        <v>93363</v>
+        <v>40662</v>
       </c>
       <c r="S12" t="n">
         <v>1372</v>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>37.1</v>
@@ -1244,10 +1244,10 @@
         <v>1.69</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>19.29</v>
@@ -1261,19 +1261,19 @@
         <v>-0.144</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-23</v>
+        <v>-28</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>156584</v>
+        <v>102374</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>46530</v>
+        <v>48039</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>203114</v>
+        <v>150413</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -1711,255 +1711,255 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>주도주</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4036</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8073</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>427</v>
+      </c>
+      <c r="R22" t="n">
+        <v>8500</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>주도주</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="I22" s="2" t="n">
+      <c r="D23" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>11.77</v>
       </c>
-      <c r="K22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>5693</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>267537</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>11007</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>278544</v>
-      </c>
-      <c r="S22" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="K23" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>5630</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>292736</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>11308</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>304044</v>
+      </c>
+      <c r="S23" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>ROCKET</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>ABC-VCP</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>TV알림</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>27</v>
-      </c>
-      <c r="E30" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H30" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I30" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J30" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L30" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N30" t="n">
-        <v>507</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P30" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R30" t="n">
-        <v>15210</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1974,53 +1974,53 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="F31" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="G31" t="n">
-        <v>3.01</v>
+        <v>5.47</v>
       </c>
       <c r="H31" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="I31" t="n">
-        <v>13.15</v>
+        <v>17.35</v>
       </c>
       <c r="J31" t="n">
-        <v>5.82</v>
+        <v>20.1</v>
       </c>
       <c r="K31" t="n">
-        <v>313.5</v>
+        <v>185.95</v>
       </c>
       <c r="L31" t="n">
-        <v>175.2</v>
+        <v>187.46</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.703</v>
+        <v>0.274</v>
       </c>
       <c r="N31" t="n">
-        <v>-1271</v>
+        <v>507</v>
       </c>
       <c r="O31" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>-57188</v>
+        <v>13680</v>
       </c>
       <c r="Q31" t="n">
-        <v>2829</v>
+        <v>1530</v>
       </c>
       <c r="R31" t="n">
-        <v>-54359</v>
+        <v>15210</v>
       </c>
       <c r="S31" t="n">
         <v>1415</v>
@@ -2039,53 +2039,53 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E32" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="F32" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="G32" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="H32" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I32" t="n">
-        <v>8.68</v>
+        <v>13.15</v>
       </c>
       <c r="J32" t="n">
-        <v>9.01</v>
+        <v>5.82</v>
       </c>
       <c r="K32" t="n">
-        <v>247.7</v>
+        <v>313.5</v>
       </c>
       <c r="L32" t="n">
-        <v>174.67</v>
+        <v>175.2</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.288</v>
+        <v>-0.703</v>
       </c>
       <c r="N32" t="n">
-        <v>1187</v>
+        <v>-1271</v>
       </c>
       <c r="O32" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="P32" t="n">
-        <v>36789</v>
+        <v>-57188</v>
       </c>
       <c r="Q32" t="n">
-        <v>3306</v>
+        <v>2829</v>
       </c>
       <c r="R32" t="n">
-        <v>40095</v>
+        <v>-54359</v>
       </c>
       <c r="S32" t="n">
         <v>1415</v>
@@ -2104,53 +2104,53 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E33" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="F33" t="n">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="G33" t="n">
-        <v>6.86</v>
+        <v>3.14</v>
       </c>
       <c r="H33" t="n">
-        <v>4.11</v>
+        <v>2.76</v>
       </c>
       <c r="I33" t="n">
-        <v>11.14</v>
+        <v>8.68</v>
       </c>
       <c r="J33" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="K33" t="n">
-        <v>533.86</v>
+        <v>247.7</v>
       </c>
       <c r="L33" t="n">
-        <v>403.59</v>
+        <v>174.67</v>
       </c>
       <c r="M33" t="n">
-        <v>1.375</v>
+        <v>-0.288</v>
       </c>
       <c r="N33" t="n">
-        <v>8720</v>
+        <v>1187</v>
       </c>
       <c r="O33" t="n">
-        <v>3.53</v>
+        <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>52321</v>
+        <v>36789</v>
       </c>
       <c r="Q33" t="n">
-        <v>523</v>
+        <v>3306</v>
       </c>
       <c r="R33" t="n">
-        <v>52844</v>
+        <v>40095</v>
       </c>
       <c r="S33" t="n">
         <v>1415</v>
@@ -2169,53 +2169,53 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F34" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="G34" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="H34" t="n">
-        <v>1.26</v>
+        <v>4.11</v>
       </c>
       <c r="I34" t="n">
-        <v>7.95</v>
+        <v>11.14</v>
       </c>
       <c r="J34" t="n">
-        <v>2.19</v>
+        <v>9.65</v>
       </c>
       <c r="K34" t="n">
-        <v>800.2</v>
+        <v>533.86</v>
       </c>
       <c r="L34" t="n">
-        <v>60.03</v>
+        <v>403.59</v>
       </c>
       <c r="M34" t="n">
-        <v>2.446</v>
+        <v>1.375</v>
       </c>
       <c r="N34" t="n">
-        <v>5075</v>
+        <v>8720</v>
       </c>
       <c r="O34" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P34" t="n">
-        <v>45679</v>
+        <v>52321</v>
       </c>
       <c r="Q34" t="n">
-        <v>661</v>
+        <v>523</v>
       </c>
       <c r="R34" t="n">
-        <v>46340</v>
+        <v>52844</v>
       </c>
       <c r="S34" t="n">
         <v>1415</v>
@@ -2234,485 +2234,546 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F35" t="n">
-        <v>1.14</v>
+        <v>4.39</v>
       </c>
       <c r="G35" t="n">
-        <v>6.04</v>
+        <v>7.08</v>
       </c>
       <c r="H35" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I35" t="n">
-        <v>13.51</v>
+        <v>7.95</v>
       </c>
       <c r="J35" t="n">
-        <v>4.74</v>
+        <v>2.19</v>
       </c>
       <c r="K35" t="n">
-        <v>2281.51</v>
+        <v>800.2</v>
       </c>
       <c r="L35" t="n">
-        <v>27.54</v>
+        <v>60.03</v>
       </c>
       <c r="M35" t="n">
-        <v>1.758</v>
+        <v>2.446</v>
       </c>
       <c r="N35" t="n">
-        <v>851</v>
+        <v>5075</v>
       </c>
       <c r="O35" t="n">
-        <v>1.14</v>
+        <v>3.51</v>
       </c>
       <c r="P35" t="n">
-        <v>13616</v>
+        <v>45679</v>
       </c>
       <c r="Q35" t="n">
-        <v>1561</v>
+        <v>661</v>
       </c>
       <c r="R35" t="n">
-        <v>15177</v>
+        <v>46340</v>
       </c>
       <c r="S35" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>16</v>
+      </c>
+      <c r="E36" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I36" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L36" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N36" t="n">
+        <v>851</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P36" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R36" t="n">
+        <v>15177</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D37" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E37" s="2" t="n">
         <v>41.8</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F37" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>2.87</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I37" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J37" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K37" s="2" t="n">
         <v>600.88</v>
       </c>
-      <c r="L36" s="2" t="n">
+      <c r="L37" s="2" t="n">
         <v>163.85</v>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="M37" s="2" t="n">
         <v>0.188</v>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="N37" s="2" t="n">
         <v>783</v>
       </c>
-      <c r="O36" s="2" t="n">
+      <c r="O37" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="P36" s="2" t="n">
-        <v>244938</v>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>11249</v>
-      </c>
-      <c r="R36" s="2" t="n">
-        <v>256187</v>
-      </c>
-      <c r="S36" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="P37" s="2" t="n">
+        <v>175011</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>11975</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>186986</v>
+      </c>
+      <c r="S37" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D39" t="n">
         <v>3</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="n">
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
         <v>0.34</v>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
         <v>0.49</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
         <v>13.35</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M39" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N39" t="n">
         <v>-4880</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q39" t="n">
         <v>1291</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>-13350</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S39" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="n">
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="n">
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M39" s="2" t="n">
+      <c r="M40" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="N40" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2" t="n">
+      <c r="O40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q39" s="2" t="n">
+      <c r="Q40" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R39" s="2" t="n">
+      <c r="R40" s="2" t="n">
         <v>-13350</v>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D42" t="n">
         <v>10</v>
       </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="n">
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
         <v>0.91</v>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
         <v>2.28</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
         <v>29.99</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M42" t="n">
         <v>-0.912</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N42" t="n">
         <v>-13839</v>
       </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>-138394</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q42" t="n">
         <v>4519</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R42" t="n">
         <v>-133875</v>
       </c>
-      <c r="S41" t="n">
+      <c r="S42" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-0.588</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-9482</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-9482</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>482</v>
+      </c>
+      <c r="R43" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="n">
+      <c r="D44" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="2" t="n">
-        <v>-138394</v>
-      </c>
-      <c r="Q42" s="2" t="n">
-        <v>4519</v>
-      </c>
-      <c r="R42" s="2" t="n">
-        <v>-133875</v>
-      </c>
-      <c r="S42" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="n">
+        <v>29.54</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>-0.883</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-13443</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>-147876</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>5001</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>-142875</v>
+      </c>
+      <c r="S44" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D46" t="n">
         <v>12</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E46" t="n">
         <v>16.7</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F46" t="n">
         <v>0.72</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G46" t="n">
         <v>0.44</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H46" t="n">
         <v>0.64</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I46" t="n">
         <v>0.84</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J46" t="n">
         <v>1.81</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K46" t="n">
         <v>14.12</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L46" t="n">
         <v>26.24</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M46" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N46" t="n">
         <v>-6941</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O46" t="n">
         <v>0.14</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P46" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q46" t="n">
         <v>5515</v>
       </c>
-      <c r="R44" t="n">
+      <c r="R46" t="n">
         <v>-77775</v>
       </c>
-      <c r="S44" t="n">
+      <c r="S46" t="n">
         <v>1415</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>삼닉v3_MA</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>26.24</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>-0.461</v>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>-6941</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>-83290</v>
-      </c>
-      <c r="Q45" s="2" t="n">
-        <v>5515</v>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>-77775</v>
-      </c>
-      <c r="S45" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>삼닉v3_미분류</t>
+          <t>삼닉v3_MA</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2726,34 +2787,56 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>-0.461</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>-6941</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>0.14</v>
+      </c>
       <c r="P47" s="2" t="n">
-        <v>0</v>
+        <v>-83290</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>0</v>
+        <v>5515</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>0</v>
+        <v>-77775</v>
       </c>
       <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>5minHL</t>
+          <t>삼닉v3_미분류</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2794,7 +2877,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>5minHL2</t>
+          <t>5minHL</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2835,7 +2918,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>5minHL_동시</t>
+          <t>5minHL2</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2874,128 +2957,45 @@
       <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_동시</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M55" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>26</v>
-      </c>
-      <c r="R55" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="S55" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>06/29~07/03</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>6</v>
-      </c>
-      <c r="E56" t="n">
-        <v>50</v>
-      </c>
-      <c r="F56" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G56" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="H56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I56" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1279.97</v>
-      </c>
-      <c r="L56" t="n">
-        <v>875.09</v>
-      </c>
-      <c r="M56" t="n">
-        <v>-0.191</v>
-      </c>
-      <c r="N56" t="n">
-        <v>4951</v>
-      </c>
-      <c r="O56" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P56" t="n">
-        <v>29704</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>756</v>
-      </c>
-      <c r="R56" t="n">
-        <v>30460</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1415</v>
-      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3010,53 +3010,47 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.08</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.08</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="K57" t="n">
-        <v>4319.93</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>1351.81</v>
+        <v>49.85</v>
       </c>
       <c r="M57" t="n">
-        <v>-2.059</v>
+        <v>-2.747</v>
       </c>
       <c r="N57" t="n">
-        <v>-3794</v>
+        <v>-2426</v>
       </c>
       <c r="O57" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>-11383</v>
+        <v>-2426</v>
       </c>
       <c r="Q57" t="n">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="R57" t="n">
-        <v>-11230</v>
+        <v>-2400</v>
       </c>
       <c r="S57" t="n">
         <v>1415</v>
@@ -3075,43 +3069,53 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>100</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.93</v>
+      </c>
       <c r="G58" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>2.47</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2.85</v>
+      </c>
       <c r="I58" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K58" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L58" t="inlineStr"/>
+        <v>1279.97</v>
+      </c>
+      <c r="L58" t="n">
+        <v>875.09</v>
+      </c>
       <c r="M58" t="n">
-        <v>1.678</v>
+        <v>-0.191</v>
       </c>
       <c r="N58" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O58" t="inlineStr"/>
+        <v>4951</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2.93</v>
+      </c>
       <c r="P58" t="n">
-        <v>1670</v>
+        <v>29704</v>
       </c>
       <c r="Q58" t="n">
-        <v>30</v>
+        <v>756</v>
       </c>
       <c r="R58" t="n">
-        <v>1700</v>
+        <v>30460</v>
       </c>
       <c r="S58" t="n">
         <v>1415</v>
@@ -3130,268 +3134,335 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.08</v>
+      </c>
       <c r="H59" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
+        <v>3.13</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.08</v>
+      </c>
       <c r="J59" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
+        <v>3.61</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4319.93</v>
+      </c>
       <c r="L59" t="n">
-        <v>5756.96</v>
+        <v>1351.81</v>
       </c>
       <c r="M59" t="n">
-        <v>-6.785</v>
+        <v>-2.059</v>
       </c>
       <c r="N59" t="n">
-        <v>-7272</v>
+        <v>-3794</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P59" t="n">
-        <v>-14543</v>
+        <v>-11383</v>
       </c>
       <c r="Q59" t="n">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="R59" t="n">
-        <v>-14485</v>
+        <v>-11230</v>
       </c>
       <c r="S59" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J60" s="2" t="n">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>100</v>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1670</v>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>30</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1700</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
         <v>7.52</v>
       </c>
-      <c r="K60" s="2" t="n">
-        <v>1633.99</v>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>2111.58</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>-1.689</v>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>232</v>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>3022</v>
-      </c>
-      <c r="Q60" s="2" t="n">
-        <v>1023</v>
-      </c>
-      <c r="R60" s="2" t="n">
-        <v>4045</v>
-      </c>
-      <c r="S60" s="2" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>5756.96</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-7272</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-14543</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>58</v>
+      </c>
+      <c r="R61" t="n">
+        <v>-14485</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>1633.99</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>2111.58</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>-1.689</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>3022</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>1023</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>4045</v>
+      </c>
+      <c r="S62" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
           <t>KR_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="D64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E66" t="n">
         <v>100</v>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="n">
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
         <v>1.3</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="n">
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
         <v>1.3</v>
       </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="n">
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
         <v>7</v>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="n">
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="n">
         <v>1.299</v>
       </c>
-      <c r="N64" t="n">
+      <c r="N66" t="n">
         <v>6421</v>
       </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="n">
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
         <v>6421</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="Q66" t="n">
         <v>149</v>
       </c>
-      <c r="R64" t="n">
+      <c r="R66" t="n">
         <v>6570</v>
       </c>
-      <c r="S64" t="n">
+      <c r="S66" t="n">
         <v>1372</v>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>KR_TR_VOLUME_1</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="n">
-        <v>1.299</v>
-      </c>
-      <c r="N65" s="2" t="n">
-        <v>6421</v>
-      </c>
-      <c r="O65" s="2" t="inlineStr"/>
-      <c r="P65" s="2" t="n">
-        <v>6421</v>
-      </c>
-      <c r="Q65" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="R65" s="2" t="n">
-        <v>6570</v>
-      </c>
-      <c r="S65" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VOLUME_2</t>
+          <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3405,34 +3476,46 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>6421</v>
+      </c>
       <c r="O67" s="2" t="inlineStr"/>
       <c r="P67" s="2" t="n">
-        <v>0</v>
+        <v>6421</v>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="R67" s="2" t="n">
-        <v>0</v>
+        <v>6570</v>
       </c>
       <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP1</t>
+          <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3473,7 +3556,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>KR_TR_VCP1</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3514,7 +3597,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_JEO2</t>
+          <t>KR_TR_VCP2</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3555,7 +3638,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_MA</t>
+          <t>KR_TR_JEO2</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3596,7 +3679,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_ADD1</t>
+          <t>KR_TR_MA</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3637,7 +3720,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>미국VCP</t>
+          <t>KR_TR_ADD1</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -3676,196 +3759,174 @@
       <c r="S79" s="2" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>미국VCP</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D83" t="n">
         <v>1</v>
       </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="n">
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="n">
         <v>10.01</v>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="n">
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="n">
         <v>10.01</v>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="n">
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="n">
         <v>3</v>
       </c>
-      <c r="M81" t="n">
+      <c r="M83" t="n">
         <v>-10.012</v>
       </c>
-      <c r="N81" t="n">
+      <c r="N83" t="n">
         <v>-71414</v>
       </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
         <v>-71414</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="Q83" t="n">
         <v>949</v>
       </c>
-      <c r="R81" t="n">
+      <c r="R83" t="n">
         <v>-70465</v>
       </c>
-      <c r="S81" t="n">
+      <c r="S83" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D84" t="n">
         <v>9</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E84" t="n">
         <v>44.4</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F84" t="n">
         <v>0.42</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G84" t="n">
         <v>1.18</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H84" t="n">
         <v>4.28</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I84" t="n">
         <v>3.2</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J84" t="n">
         <v>5.74</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K84" t="n">
         <v>14</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L84" t="n">
         <v>5.6</v>
       </c>
-      <c r="M82" t="n">
+      <c r="M84" t="n">
         <v>-1.851</v>
       </c>
-      <c r="N82" t="n">
+      <c r="N84" t="n">
         <v>-4960</v>
       </c>
-      <c r="O82" t="n">
+      <c r="O84" t="n">
         <v>0.34</v>
       </c>
-      <c r="P82" t="n">
+      <c r="P84" t="n">
         <v>-16484</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="Q84" t="n">
         <v>6506</v>
       </c>
-      <c r="R82" t="n">
+      <c r="R84" t="n">
         <v>-9978</v>
       </c>
-      <c r="S82" t="n">
+      <c r="S84" t="n">
         <v>1372</v>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_A</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>-2.668</v>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>-11605</v>
-      </c>
-      <c r="O83" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P83" s="2" t="n">
-        <v>-87898</v>
-      </c>
-      <c r="Q83" s="2" t="n">
-        <v>7455</v>
-      </c>
-      <c r="R83" s="2" t="n">
-        <v>-80443</v>
-      </c>
-      <c r="S83" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_1</t>
+          <t>US_TR_ORD_A</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -3879,34 +3940,56 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr"/>
-      <c r="O85" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-2.668</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-11605</v>
+      </c>
+      <c r="O85" s="2" t="n">
+        <v>0.16</v>
+      </c>
       <c r="P85" s="2" t="n">
-        <v>0</v>
+        <v>-87898</v>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>0</v>
+        <v>7455</v>
       </c>
       <c r="R85" s="2" t="n">
-        <v>0</v>
+        <v>-80443</v>
       </c>
       <c r="S85" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_2</t>
+          <t>US_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -3947,7 +4030,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP1</t>
+          <t>US_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -3986,906 +4069,823 @@
       <c r="S89" s="2" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP1</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D93" t="n">
         <v>1</v>
       </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="n">
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="n">
         <v>6.8</v>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="n">
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="n">
         <v>6.8</v>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="n">
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="n">
         <v>5</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M93" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N93" t="n">
         <v>-9876</v>
       </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
         <v>-9876</v>
       </c>
-      <c r="Q91" t="n">
+      <c r="Q93" t="n">
         <v>196</v>
       </c>
-      <c r="R91" t="n">
+      <c r="R93" t="n">
         <v>-9679</v>
       </c>
-      <c r="S91" t="n">
+      <c r="S93" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D94" t="n">
         <v>4</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E94" t="n">
         <v>50</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F94" t="n">
         <v>1.67</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G94" t="n">
         <v>3.59</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H94" t="n">
         <v>2.42</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I94" t="n">
         <v>4.34</v>
       </c>
-      <c r="J92" t="n">
+      <c r="J94" t="n">
         <v>4.61</v>
       </c>
-      <c r="K92" t="n">
+      <c r="K94" t="n">
         <v>14</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L94" t="n">
         <v>4.5</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M94" t="n">
         <v>0.587</v>
       </c>
-      <c r="N92" t="n">
+      <c r="N94" t="n">
         <v>2177</v>
       </c>
-      <c r="O92" t="n">
+      <c r="O94" t="n">
         <v>1.67</v>
       </c>
-      <c r="P92" t="n">
+      <c r="P94" t="n">
         <v>19858</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="Q94" t="n">
         <v>2417</v>
       </c>
-      <c r="R92" t="n">
+      <c r="R94" t="n">
         <v>22274</v>
       </c>
-      <c r="S92" t="n">
+      <c r="S94" t="n">
         <v>1372</v>
       </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>-0.891</v>
-      </c>
-      <c r="N93" s="2" t="n">
-        <v>-234</v>
-      </c>
-      <c r="O93" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="P93" s="2" t="n">
-        <v>9982</v>
-      </c>
-      <c r="Q93" s="2" t="n">
-        <v>2613</v>
-      </c>
-      <c r="R93" s="2" t="n">
-        <v>12595</v>
-      </c>
-      <c r="S93" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-0.891</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-234</v>
+      </c>
+      <c r="O95" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P95" s="2" t="n">
+        <v>9982</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>2613</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>12595</v>
+      </c>
+      <c r="S95" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr"/>
-      <c r="O95" s="2" t="inlineStr"/>
-      <c r="P95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D99" t="n">
         <v>6</v>
       </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="n">
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
         <v>3.78</v>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="n">
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
         <v>6.17</v>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="n">
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
         <v>8</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M99" t="n">
         <v>-3.784</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N99" t="n">
         <v>-8906</v>
       </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
         <v>-53435</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="Q99" t="n">
         <v>1676</v>
       </c>
-      <c r="R97" t="n">
+      <c r="R99" t="n">
         <v>-51759</v>
       </c>
-      <c r="S97" t="n">
+      <c r="S99" t="n">
         <v>1372</v>
       </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>-3.784</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>-8906</v>
-      </c>
-      <c r="O98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="2" t="n">
-        <v>-53435</v>
-      </c>
-      <c r="Q98" s="2" t="n">
-        <v>1676</v>
-      </c>
-      <c r="R98" s="2" t="n">
-        <v>-51759</v>
-      </c>
-      <c r="S98" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-3.784</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>-8906</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>-53435</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>1676</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>-51759</v>
+      </c>
+      <c r="S100" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
-      <c r="P100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="D102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D104" t="n">
         <v>2</v>
       </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="n">
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="n">
         <v>7.15</v>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="n">
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="n">
         <v>10.49</v>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="n">
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="n">
         <v>1</v>
       </c>
-      <c r="M102" t="n">
+      <c r="M104" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N102" t="n">
+      <c r="N104" t="n">
         <v>-27425</v>
       </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
         <v>-54849</v>
       </c>
-      <c r="Q102" t="n">
+      <c r="Q104" t="n">
         <v>1053</v>
       </c>
-      <c r="R102" t="n">
+      <c r="R104" t="n">
         <v>-53796</v>
       </c>
-      <c r="S102" t="n">
+      <c r="S104" t="n">
         <v>1372</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D105" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="n">
+      <c r="E105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="n">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="n">
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M103" s="2" t="n">
+      <c r="M105" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N103" s="2" t="n">
+      <c r="N105" s="2" t="n">
         <v>-27425</v>
       </c>
-      <c r="O103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" s="2" t="n">
+      <c r="O105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="2" t="n">
         <v>-54849</v>
       </c>
-      <c r="Q103" s="2" t="n">
+      <c r="Q105" s="2" t="n">
         <v>1053</v>
       </c>
-      <c r="R103" s="2" t="n">
+      <c r="R105" s="2" t="n">
         <v>-53796</v>
       </c>
-      <c r="S103" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="S105" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D107" t="n">
         <v>13</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E107" t="n">
         <v>53.8</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F107" t="n">
         <v>1.85</v>
       </c>
-      <c r="G105" t="n">
+      <c r="G107" t="n">
         <v>7.78</v>
       </c>
-      <c r="H105" t="n">
+      <c r="H107" t="n">
         <v>2.66</v>
       </c>
-      <c r="I105" t="n">
+      <c r="I107" t="n">
         <v>16.31</v>
       </c>
-      <c r="J105" t="n">
+      <c r="J107" t="n">
         <v>5.68</v>
       </c>
-      <c r="K105" t="n">
+      <c r="K107" t="n">
         <v>0.29</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L107" t="n">
         <v>0.33</v>
       </c>
-      <c r="M105" t="n">
+      <c r="M107" t="n">
         <v>2.964</v>
       </c>
-      <c r="N105" t="n">
+      <c r="N107" t="n">
         <v>3611</v>
       </c>
-      <c r="O105" t="n">
+      <c r="O107" t="n">
         <v>2.16</v>
       </c>
-      <c r="P105" t="n">
+      <c r="P107" t="n">
         <v>129001</v>
       </c>
-      <c r="Q105" t="n">
+      <c r="Q107" t="n">
         <v>5832</v>
       </c>
-      <c r="R105" t="n">
+      <c r="R107" t="n">
         <v>134833</v>
       </c>
-      <c r="S105" t="n">
+      <c r="S107" t="n">
         <v>1372</v>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>3611</v>
-      </c>
-      <c r="O106" s="2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="P106" s="2" t="n">
-        <v>129001</v>
-      </c>
-      <c r="Q106" s="2" t="n">
-        <v>5832</v>
-      </c>
-      <c r="R106" s="2" t="n">
-        <v>134833</v>
-      </c>
-      <c r="S106" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>3611</v>
+      </c>
+      <c r="O108" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P108" s="2" t="n">
+        <v>129001</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>5832</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>134833</v>
+      </c>
+      <c r="S108" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
-      <c r="P108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="D110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D110" t="n">
+      <c r="D112" t="n">
         <v>1</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E112" t="n">
         <v>100</v>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="n">
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="n">
         <v>2.1</v>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="n">
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="n">
         <v>2.1</v>
       </c>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="n">
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="n">
         <v>52.73</v>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="n">
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="n">
         <v>2.102</v>
       </c>
-      <c r="N110" t="n">
+      <c r="N112" t="n">
         <v>2341</v>
       </c>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="n">
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="n">
         <v>2341</v>
       </c>
-      <c r="Q110" t="n">
+      <c r="Q112" t="n">
         <v>34</v>
       </c>
-      <c r="R110" t="n">
+      <c r="R112" t="n">
         <v>2375</v>
       </c>
-      <c r="S110" t="n">
+      <c r="S112" t="n">
         <v>1372</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n">
+      <c r="D113" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E111" s="2" t="n">
+      <c r="E113" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="n">
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="n">
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="2" t="n">
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="2" t="n">
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N111" s="2" t="n">
+      <c r="N113" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O111" s="2" t="inlineStr"/>
-      <c r="P111" s="2" t="n">
+      <c r="O113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q111" s="2" t="n">
+      <c r="Q113" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R111" s="2" t="n">
+      <c r="R113" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S111" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>2</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="n">
-        <v>1</v>
-      </c>
-      <c r="M113" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N113" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>513</v>
-      </c>
-      <c r="R113" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S113" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>4</v>
-      </c>
-      <c r="E114" t="n">
-        <v>25</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I114" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J114" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K114" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M114" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N114" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O114" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P114" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R114" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S114" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S113" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4914,33 +4914,33 @@
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>0.14</v>
+        <v>2.61</v>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>0.16</v>
+        <v>3.49</v>
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.136</v>
+        <v>-2.607</v>
       </c>
       <c r="N115" t="n">
-        <v>-2389</v>
+        <v>-8011</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>-4777</v>
+        <v>-16021</v>
       </c>
       <c r="Q115" t="n">
-        <v>2924</v>
+        <v>513</v>
       </c>
       <c r="R115" t="n">
-        <v>-1854</v>
+        <v>-15508</v>
       </c>
       <c r="S115" t="n">
         <v>1415</v>
@@ -4959,43 +4959,53 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E116" t="n">
-        <v>100</v>
-      </c>
-      <c r="F116" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G116" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I116" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J116" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K116" t="n">
-        <v>14</v>
-      </c>
-      <c r="L116" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L116" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M116" t="n">
-        <v>1.042</v>
+        <v>-0.217</v>
       </c>
       <c r="N116" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O116" t="inlineStr"/>
+        <v>-13272</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P116" t="n">
-        <v>48540</v>
+        <v>-53089</v>
       </c>
       <c r="Q116" t="n">
-        <v>4254</v>
+        <v>5913</v>
       </c>
       <c r="R116" t="n">
-        <v>52794</v>
+        <v>-47176</v>
       </c>
       <c r="S116" t="n">
         <v>1415</v>
@@ -5014,11 +5024,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -5028,538 +5038,768 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M117" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="N117" t="n">
+        <v>-2389</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>-4777</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>2924</v>
+      </c>
+      <c r="R117" t="n">
+        <v>-1854</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3</v>
+      </c>
+      <c r="E118" t="n">
+        <v>100</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>14</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N118" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R118" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="n">
         <v>4.67</v>
       </c>
-      <c r="M117" t="n">
+      <c r="M119" t="n">
         <v>-0.864</v>
       </c>
-      <c r="N117" t="n">
+      <c r="N119" t="n">
         <v>-28997</v>
       </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
         <v>-86990</v>
       </c>
-      <c r="Q117" t="n">
+      <c r="Q119" t="n">
         <v>13787</v>
       </c>
-      <c r="R117" t="n">
+      <c r="R119" t="n">
         <v>-73203</v>
       </c>
-      <c r="S117" t="n">
+      <c r="S119" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D118" s="2" t="n">
+      <c r="D120" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E118" s="2" t="n">
+      <c r="E120" s="2" t="n">
         <v>28.6</v>
       </c>
-      <c r="F118" s="2" t="n">
+      <c r="F120" s="2" t="n">
         <v>0.77</v>
       </c>
-      <c r="G118" s="2" t="n">
+      <c r="G120" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H118" s="2" t="n">
+      <c r="H120" s="2" t="n">
         <v>1.03</v>
       </c>
-      <c r="I118" s="2" t="n">
+      <c r="I120" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J118" s="2" t="n">
+      <c r="J120" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K118" s="2" t="n">
+      <c r="K120" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L118" s="2" t="n">
+      <c r="L120" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="M118" s="2" t="n">
+      <c r="M120" s="2" t="n">
         <v>-0.416</v>
       </c>
-      <c r="N118" s="2" t="n">
+      <c r="N120" s="2" t="n">
         <v>-8024</v>
       </c>
-      <c r="O118" s="2" t="n">
+      <c r="O120" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="P118" s="2" t="n">
+      <c r="P120" s="2" t="n">
         <v>-112337</v>
       </c>
-      <c r="Q118" s="2" t="n">
+      <c r="Q120" s="2" t="n">
         <v>27391</v>
       </c>
-      <c r="R118" s="2" t="n">
+      <c r="R120" s="2" t="n">
         <v>-84947</v>
       </c>
-      <c r="S118" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="S120" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D120" t="n">
+      <c r="D122" t="n">
         <v>9</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E122" t="n">
         <v>55.6</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F122" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G122" t="n">
         <v>1.17</v>
       </c>
-      <c r="H120" t="n">
+      <c r="H122" t="n">
         <v>4.19</v>
       </c>
-      <c r="I120" t="n">
+      <c r="I122" t="n">
         <v>3.38</v>
       </c>
-      <c r="J120" t="n">
+      <c r="J122" t="n">
         <v>7.04</v>
       </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="n">
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N120" t="n">
+      <c r="N122" t="n">
         <v>-744</v>
       </c>
-      <c r="O120" t="n">
+      <c r="O122" t="n">
         <v>0.86</v>
       </c>
-      <c r="P120" t="n">
+      <c r="P122" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q120" t="n">
+      <c r="Q122" t="n">
         <v>2139</v>
       </c>
-      <c r="R120" t="n">
+      <c r="R122" t="n">
         <v>-4553</v>
       </c>
-      <c r="S120" t="n">
+      <c r="S122" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D121" t="n">
+      <c r="D123" t="n">
         <v>2</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E123" t="n">
         <v>100</v>
       </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="n">
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="n">
         <v>8.56</v>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="n">
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="n">
         <v>12.69</v>
       </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="n">
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
         <v>8.56</v>
       </c>
-      <c r="N121" t="n">
+      <c r="N123" t="n">
         <v>57466</v>
       </c>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="n">
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="n">
         <v>114933</v>
       </c>
-      <c r="Q121" t="n">
+      <c r="Q123" t="n">
         <v>667</v>
       </c>
-      <c r="R121" t="n">
+      <c r="R123" t="n">
         <v>115600</v>
       </c>
-      <c r="S121" t="n">
+      <c r="S123" t="n">
         <v>1411</v>
       </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="2" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="N122" s="2" t="n">
-        <v>9840</v>
-      </c>
-      <c r="O122" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="P122" s="2" t="n">
-        <v>56575</v>
-      </c>
-      <c r="Q122" s="2" t="n">
-        <v>2972</v>
-      </c>
-      <c r="R122" s="2" t="n">
-        <v>59547</v>
-      </c>
-      <c r="S122" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N124" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>257</v>
+      </c>
+      <c r="R124" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S124" t="n">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>2846</v>
+      </c>
+      <c r="O125" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P125" s="2" t="n">
+        <v>34154</v>
+      </c>
+      <c r="Q125" s="2" t="n">
+        <v>3063</v>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>37217</v>
+      </c>
+      <c r="S125" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D124" t="n">
+      <c r="D127" t="n">
         <v>9</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E127" t="n">
         <v>55.6</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F127" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G127" t="n">
         <v>1.17</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H127" t="n">
         <v>4.19</v>
       </c>
-      <c r="I124" t="n">
+      <c r="I127" t="n">
         <v>3.38</v>
       </c>
-      <c r="J124" t="n">
+      <c r="J127" t="n">
         <v>7.04</v>
       </c>
-      <c r="K124" t="n">
+      <c r="K127" t="n">
         <v>3</v>
       </c>
-      <c r="L124" t="n">
+      <c r="L127" t="n">
         <v>1.75</v>
       </c>
-      <c r="M124" t="n">
+      <c r="M127" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N124" t="n">
+      <c r="N127" t="n">
         <v>-744</v>
       </c>
-      <c r="O124" t="n">
+      <c r="O127" t="n">
         <v>0.86</v>
       </c>
-      <c r="P124" t="n">
+      <c r="P127" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q124" t="n">
+      <c r="Q127" t="n">
         <v>2139</v>
       </c>
-      <c r="R124" t="n">
+      <c r="R127" t="n">
         <v>-4553</v>
       </c>
-      <c r="S124" t="n">
+      <c r="S127" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D125" t="n">
+      <c r="D128" t="n">
         <v>2</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E128" t="n">
         <v>100</v>
       </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="n">
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="n">
         <v>8.56</v>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="n">
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="n">
         <v>12.69</v>
       </c>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="n">
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="n">
         <v>4.5</v>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="n">
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="n">
         <v>8.56</v>
       </c>
-      <c r="N125" t="n">
+      <c r="N128" t="n">
         <v>57466</v>
       </c>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="n">
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="n">
         <v>114933</v>
       </c>
-      <c r="Q125" t="n">
+      <c r="Q128" t="n">
         <v>667</v>
       </c>
-      <c r="R125" t="n">
+      <c r="R128" t="n">
         <v>115600</v>
       </c>
-      <c r="S125" t="n">
+      <c r="S128" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>9840</v>
-      </c>
-      <c r="O126" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="P126" s="2" t="n">
-        <v>56575</v>
-      </c>
-      <c r="Q126" s="2" t="n">
-        <v>2972</v>
-      </c>
-      <c r="R126" s="2" t="n">
-        <v>59547</v>
-      </c>
-      <c r="S126" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>미국수동</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="inlineStr"/>
-      <c r="M128" s="2" t="inlineStr"/>
-      <c r="N128" s="2" t="inlineStr"/>
-      <c r="O128" s="2" t="inlineStr"/>
-      <c r="P128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" s="2" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="n">
+        <v>3</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>257</v>
+      </c>
+      <c r="R129" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1372</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>2846</v>
+      </c>
+      <c r="O130" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P130" s="2" t="n">
+        <v>34154</v>
+      </c>
+      <c r="Q130" s="2" t="n">
+        <v>3063</v>
+      </c>
+      <c r="R130" s="2" t="n">
+        <v>37217</v>
+      </c>
+      <c r="S130" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>미국수동</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr"/>
+      <c r="P132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="2" t="inlineStr"/>
-      <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-      <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="inlineStr"/>
-      <c r="M130" s="2" t="inlineStr"/>
-      <c r="N130" s="2" t="inlineStr"/>
-      <c r="O130" s="2" t="inlineStr"/>
-      <c r="P130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" s="2" t="inlineStr"/>
+      <c r="D134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr"/>
+      <c r="P134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S131"/>
+  <dimension ref="A1:S135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1174,22 +1174,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>34.8</v>
+        <v>38.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="G12" t="n">
-        <v>1.91</v>
+        <v>2.79</v>
       </c>
       <c r="H12" t="n">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="I12" t="n">
-        <v>4.34</v>
+        <v>7.7</v>
       </c>
       <c r="J12" t="n">
         <v>6.17</v>
@@ -1197,22 +1197,22 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>-1.504</v>
+        <v>-1.024</v>
       </c>
       <c r="N12" t="n">
-        <v>-4200</v>
+        <v>-1869</v>
       </c>
       <c r="O12" t="n">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="P12" t="n">
-        <v>-4301</v>
+        <v>46804</v>
       </c>
       <c r="Q12" t="n">
-        <v>13463</v>
+        <v>14145</v>
       </c>
       <c r="R12" t="n">
-        <v>9162</v>
+        <v>60950</v>
       </c>
       <c r="S12" t="n">
         <v>1372</v>
@@ -1235,19 +1235,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>36.8</v>
+        <v>37.2</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4.41</v>
+        <v>4.45</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>19.29</v>
@@ -1258,22 +1258,22 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="n">
-        <v>-0.147</v>
+        <v>-0.113</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-88</v>
+        <v>106</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>70668</v>
+        <v>121773</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>48245</v>
+        <v>48927</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>118913</v>
+        <v>170701</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -1711,255 +1711,255 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>주도주</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4036</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8073</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>427</v>
+      </c>
+      <c r="R22" t="n">
+        <v>8500</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>주도주</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="I22" s="2" t="n">
+      <c r="D23" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>11.77</v>
       </c>
-      <c r="K22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>5693</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>267537</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>11007</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>278544</v>
-      </c>
-      <c r="S22" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="K23" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>5630</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>292736</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>11308</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>304044</v>
+      </c>
+      <c r="S23" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>ROCKET</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>ABC-VCP</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>TV알림</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>27</v>
-      </c>
-      <c r="E30" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H30" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I30" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J30" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L30" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N30" t="n">
-        <v>507</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P30" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R30" t="n">
-        <v>15210</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1974,53 +1974,53 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="F31" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="G31" t="n">
-        <v>3.01</v>
+        <v>5.47</v>
       </c>
       <c r="H31" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="I31" t="n">
-        <v>13.15</v>
+        <v>17.35</v>
       </c>
       <c r="J31" t="n">
-        <v>5.82</v>
+        <v>20.1</v>
       </c>
       <c r="K31" t="n">
-        <v>313.5</v>
+        <v>185.95</v>
       </c>
       <c r="L31" t="n">
-        <v>175.2</v>
+        <v>187.46</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.703</v>
+        <v>0.274</v>
       </c>
       <c r="N31" t="n">
-        <v>-1271</v>
+        <v>507</v>
       </c>
       <c r="O31" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>-57188</v>
+        <v>13680</v>
       </c>
       <c r="Q31" t="n">
-        <v>2829</v>
+        <v>1530</v>
       </c>
       <c r="R31" t="n">
-        <v>-54359</v>
+        <v>15210</v>
       </c>
       <c r="S31" t="n">
         <v>1415</v>
@@ -2039,53 +2039,53 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E32" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="F32" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="G32" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="H32" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I32" t="n">
-        <v>8.68</v>
+        <v>13.15</v>
       </c>
       <c r="J32" t="n">
-        <v>9.01</v>
+        <v>5.82</v>
       </c>
       <c r="K32" t="n">
-        <v>247.7</v>
+        <v>313.5</v>
       </c>
       <c r="L32" t="n">
-        <v>174.67</v>
+        <v>175.2</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.288</v>
+        <v>-0.703</v>
       </c>
       <c r="N32" t="n">
-        <v>1187</v>
+        <v>-1271</v>
       </c>
       <c r="O32" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="P32" t="n">
-        <v>36789</v>
+        <v>-57188</v>
       </c>
       <c r="Q32" t="n">
-        <v>3306</v>
+        <v>2829</v>
       </c>
       <c r="R32" t="n">
-        <v>40095</v>
+        <v>-54359</v>
       </c>
       <c r="S32" t="n">
         <v>1415</v>
@@ -2104,53 +2104,53 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E33" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="F33" t="n">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="G33" t="n">
-        <v>6.86</v>
+        <v>3.14</v>
       </c>
       <c r="H33" t="n">
-        <v>4.11</v>
+        <v>2.76</v>
       </c>
       <c r="I33" t="n">
-        <v>11.14</v>
+        <v>8.68</v>
       </c>
       <c r="J33" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="K33" t="n">
-        <v>533.86</v>
+        <v>247.7</v>
       </c>
       <c r="L33" t="n">
-        <v>403.59</v>
+        <v>174.67</v>
       </c>
       <c r="M33" t="n">
-        <v>1.375</v>
+        <v>-0.288</v>
       </c>
       <c r="N33" t="n">
-        <v>8720</v>
+        <v>1187</v>
       </c>
       <c r="O33" t="n">
-        <v>3.53</v>
+        <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>52321</v>
+        <v>36789</v>
       </c>
       <c r="Q33" t="n">
-        <v>523</v>
+        <v>3306</v>
       </c>
       <c r="R33" t="n">
-        <v>52844</v>
+        <v>40095</v>
       </c>
       <c r="S33" t="n">
         <v>1415</v>
@@ -2169,53 +2169,53 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F34" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="G34" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="H34" t="n">
-        <v>1.26</v>
+        <v>4.11</v>
       </c>
       <c r="I34" t="n">
-        <v>7.95</v>
+        <v>11.14</v>
       </c>
       <c r="J34" t="n">
-        <v>2.19</v>
+        <v>9.65</v>
       </c>
       <c r="K34" t="n">
-        <v>800.2</v>
+        <v>533.86</v>
       </c>
       <c r="L34" t="n">
-        <v>60.03</v>
+        <v>403.59</v>
       </c>
       <c r="M34" t="n">
-        <v>2.446</v>
+        <v>1.375</v>
       </c>
       <c r="N34" t="n">
-        <v>5075</v>
+        <v>8720</v>
       </c>
       <c r="O34" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P34" t="n">
-        <v>45679</v>
+        <v>52321</v>
       </c>
       <c r="Q34" t="n">
-        <v>661</v>
+        <v>523</v>
       </c>
       <c r="R34" t="n">
-        <v>46340</v>
+        <v>52844</v>
       </c>
       <c r="S34" t="n">
         <v>1415</v>
@@ -2234,295 +2234,301 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F35" t="n">
-        <v>1.14</v>
+        <v>4.39</v>
       </c>
       <c r="G35" t="n">
-        <v>6.04</v>
+        <v>7.08</v>
       </c>
       <c r="H35" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I35" t="n">
-        <v>13.51</v>
+        <v>7.95</v>
       </c>
       <c r="J35" t="n">
-        <v>4.74</v>
+        <v>2.19</v>
       </c>
       <c r="K35" t="n">
-        <v>2281.51</v>
+        <v>800.2</v>
       </c>
       <c r="L35" t="n">
-        <v>27.54</v>
+        <v>60.03</v>
       </c>
       <c r="M35" t="n">
-        <v>1.758</v>
+        <v>2.446</v>
       </c>
       <c r="N35" t="n">
-        <v>851</v>
+        <v>5075</v>
       </c>
       <c r="O35" t="n">
-        <v>1.14</v>
+        <v>3.51</v>
       </c>
       <c r="P35" t="n">
-        <v>13616</v>
+        <v>45679</v>
       </c>
       <c r="Q35" t="n">
-        <v>1561</v>
+        <v>661</v>
       </c>
       <c r="R35" t="n">
-        <v>15177</v>
+        <v>46340</v>
       </c>
       <c r="S35" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>16</v>
+      </c>
+      <c r="E36" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I36" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L36" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N36" t="n">
+        <v>851</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P36" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R36" t="n">
+        <v>15177</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D37" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E37" s="2" t="n">
         <v>41.8</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F37" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>2.87</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I37" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J37" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K37" s="2" t="n">
         <v>600.88</v>
       </c>
-      <c r="L36" s="2" t="n">
+      <c r="L37" s="2" t="n">
         <v>163.85</v>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="M37" s="2" t="n">
         <v>0.188</v>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="N37" s="2" t="n">
         <v>783</v>
       </c>
-      <c r="O36" s="2" t="n">
+      <c r="O37" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="P36" s="2" t="n">
+      <c r="P37" s="2" t="n">
         <v>175011</v>
       </c>
-      <c r="Q36" s="2" t="n">
+      <c r="Q37" s="2" t="n">
         <v>11975</v>
       </c>
-      <c r="R36" s="2" t="n">
+      <c r="R37" s="2" t="n">
         <v>186986</v>
       </c>
-      <c r="S36" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D39" t="n">
         <v>3</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="n">
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
         <v>0.34</v>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
         <v>0.49</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
         <v>13.35</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M39" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N39" t="n">
         <v>-4880</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q39" t="n">
         <v>1291</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>-13350</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S39" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="n">
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="n">
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M39" s="2" t="n">
+      <c r="M40" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="N40" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2" t="n">
+      <c r="O40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q39" s="2" t="n">
+      <c r="Q40" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R39" s="2" t="n">
+      <c r="R40" s="2" t="n">
         <v>-13350</v>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M41" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>-138394</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>4519</v>
-      </c>
-      <c r="R41" t="n">
-        <v>-133875</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S40" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2537,11 +2543,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -2551,445 +2557,445 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>0.49</v>
+        <v>0.91</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>0.59</v>
+        <v>2.28</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-0.912</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-138394</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4519</v>
+      </c>
+      <c r="R42" t="n">
+        <v>-133875</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
         <v>27.47</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M43" t="n">
         <v>-0.486</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N43" t="n">
         <v>-7995</v>
       </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
         <v>-15989</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q43" t="n">
         <v>989</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R43" t="n">
         <v>-15000</v>
       </c>
-      <c r="S42" t="n">
+      <c r="S43" t="n">
         <v>1372</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D44" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="n">
+      <c r="E44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="n">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="n">
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="n">
         <v>29.57</v>
       </c>
-      <c r="M43" s="2" t="n">
+      <c r="M44" s="2" t="n">
         <v>-0.841</v>
       </c>
-      <c r="N43" s="2" t="n">
+      <c r="N44" s="2" t="n">
         <v>-12865</v>
       </c>
-      <c r="O43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="2" t="n">
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
         <v>-154383</v>
       </c>
-      <c r="Q43" s="2" t="n">
+      <c r="Q44" s="2" t="n">
         <v>5508</v>
       </c>
-      <c r="R43" s="2" t="n">
+      <c r="R44" s="2" t="n">
         <v>-148875</v>
       </c>
-      <c r="S43" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D46" t="n">
         <v>12</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E46" t="n">
         <v>16.7</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F46" t="n">
         <v>0.72</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G46" t="n">
         <v>0.44</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H46" t="n">
         <v>0.64</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I46" t="n">
         <v>0.84</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J46" t="n">
         <v>1.81</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K46" t="n">
         <v>14.12</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L46" t="n">
         <v>26.24</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M46" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N46" t="n">
         <v>-6941</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O46" t="n">
         <v>0.14</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P46" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q46" t="n">
         <v>5515</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R46" t="n">
         <v>-77775</v>
       </c>
-      <c r="S45" t="n">
+      <c r="S46" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D47" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E47" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F47" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H47" s="2" t="n">
         <v>0.64</v>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="I47" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="J47" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K47" s="2" t="n">
         <v>14.12</v>
       </c>
-      <c r="L46" s="2" t="n">
+      <c r="L47" s="2" t="n">
         <v>26.24</v>
       </c>
-      <c r="M46" s="2" t="n">
+      <c r="M47" s="2" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N46" s="2" t="n">
+      <c r="N47" s="2" t="n">
         <v>-6941</v>
       </c>
-      <c r="O46" s="2" t="n">
+      <c r="O47" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="P46" s="2" t="n">
+      <c r="P47" s="2" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q46" s="2" t="n">
+      <c r="Q47" s="2" t="n">
         <v>5515</v>
       </c>
-      <c r="R46" s="2" t="n">
+      <c r="R47" s="2" t="n">
         <v>-77775</v>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="S47" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_미분류</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="D49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>5minHL</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="D51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>5minHL2</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="D53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>5minHL_동시</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M56" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N56" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>26</v>
-      </c>
-      <c r="R56" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3004,53 +3010,47 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G57" t="n">
-        <v>2.47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I57" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1279.97</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>875.09</v>
+        <v>49.85</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.191</v>
+        <v>-2.747</v>
       </c>
       <c r="N57" t="n">
-        <v>4951</v>
+        <v>-2426</v>
       </c>
       <c r="O57" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>29704</v>
+        <v>-2426</v>
       </c>
       <c r="Q57" t="n">
-        <v>756</v>
+        <v>26</v>
       </c>
       <c r="R57" t="n">
-        <v>30460</v>
+        <v>-2400</v>
       </c>
       <c r="S57" t="n">
         <v>1415</v>
@@ -3069,53 +3069,53 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08</v>
+        <v>2.47</v>
       </c>
       <c r="H58" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="I58" t="n">
-        <v>0.08</v>
+        <v>4.6</v>
       </c>
       <c r="J58" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="K58" t="n">
-        <v>4319.93</v>
+        <v>1279.97</v>
       </c>
       <c r="L58" t="n">
-        <v>1351.81</v>
+        <v>875.09</v>
       </c>
       <c r="M58" t="n">
-        <v>-2.059</v>
+        <v>-0.191</v>
       </c>
       <c r="N58" t="n">
-        <v>-3794</v>
+        <v>4951</v>
       </c>
       <c r="O58" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="P58" t="n">
-        <v>-11383</v>
+        <v>29704</v>
       </c>
       <c r="Q58" t="n">
-        <v>153</v>
+        <v>756</v>
       </c>
       <c r="R58" t="n">
-        <v>-11230</v>
+        <v>30460</v>
       </c>
       <c r="S58" t="n">
         <v>1415</v>
@@ -3134,43 +3134,53 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>100</v>
-      </c>
-      <c r="F59" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G59" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3.13</v>
+      </c>
       <c r="I59" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.61</v>
+      </c>
       <c r="K59" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
+        <v>4319.93</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1351.81</v>
+      </c>
       <c r="M59" t="n">
-        <v>1.678</v>
+        <v>-2.059</v>
       </c>
       <c r="N59" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O59" t="inlineStr"/>
+        <v>-3794</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.01</v>
+      </c>
       <c r="P59" t="n">
-        <v>1670</v>
+        <v>-11383</v>
       </c>
       <c r="Q59" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="R59" t="n">
-        <v>1700</v>
+        <v>-11230</v>
       </c>
       <c r="S59" t="n">
         <v>1415</v>
@@ -3189,609 +3199,605 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="n">
-        <v>5756.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>-6.785</v>
+        <v>1.678</v>
       </c>
       <c r="N60" t="n">
-        <v>-7272</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
+        <v>1670</v>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>-14543</v>
+        <v>1670</v>
       </c>
       <c r="Q60" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="R60" t="n">
-        <v>-14485</v>
+        <v>1700</v>
       </c>
       <c r="S60" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>5756.96</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-7272</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-14543</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>58</v>
+      </c>
+      <c r="R61" t="n">
+        <v>-14485</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D62" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E62" s="2" t="n">
         <v>38.5</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F62" s="2" t="n">
         <v>1.71</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="H62" s="2" t="n">
         <v>3.89</v>
       </c>
-      <c r="I61" s="2" t="n">
+      <c r="I62" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="J61" s="2" t="n">
+      <c r="J62" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="K61" s="2" t="n">
+      <c r="K62" s="2" t="n">
         <v>1633.99</v>
       </c>
-      <c r="L61" s="2" t="n">
+      <c r="L62" s="2" t="n">
         <v>2111.58</v>
       </c>
-      <c r="M61" s="2" t="n">
+      <c r="M62" s="2" t="n">
         <v>-1.689</v>
       </c>
-      <c r="N61" s="2" t="n">
+      <c r="N62" s="2" t="n">
         <v>232</v>
       </c>
-      <c r="O61" s="2" t="n">
+      <c r="O62" s="2" t="n">
         <v>1.07</v>
       </c>
-      <c r="P61" s="2" t="n">
+      <c r="P62" s="2" t="n">
         <v>3022</v>
       </c>
-      <c r="Q61" s="2" t="n">
+      <c r="Q62" s="2" t="n">
         <v>1023</v>
       </c>
-      <c r="R61" s="2" t="n">
+      <c r="R62" s="2" t="n">
         <v>4045</v>
       </c>
-      <c r="S61" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="S62" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr"/>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="D64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D66" t="n">
         <v>1</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E66" t="n">
         <v>100</v>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="n">
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
         <v>1.3</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="n">
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
         <v>1.3</v>
       </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="n">
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
         <v>7</v>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="n">
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="n">
         <v>1.299</v>
       </c>
-      <c r="N65" t="n">
+      <c r="N66" t="n">
         <v>6421</v>
       </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="n">
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
         <v>6421</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="Q66" t="n">
         <v>149</v>
       </c>
-      <c r="R65" t="n">
+      <c r="R66" t="n">
         <v>6570</v>
       </c>
-      <c r="S65" t="n">
+      <c r="S66" t="n">
         <v>1372</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E67" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="n">
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="n">
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="n">
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="n">
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="n">
         <v>1.299</v>
       </c>
-      <c r="N66" s="2" t="n">
+      <c r="N67" s="2" t="n">
         <v>6421</v>
       </c>
-      <c r="O66" s="2" t="inlineStr"/>
-      <c r="P66" s="2" t="n">
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="n">
         <v>6421</v>
       </c>
-      <c r="Q66" s="2" t="n">
+      <c r="Q67" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="R66" s="2" t="n">
+      <c r="R67" s="2" t="n">
         <v>6570</v>
       </c>
-      <c r="S66" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="S67" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="D69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP1</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="D71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP2</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="D73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>KR_TR_JEO2</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="D75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>KR_TR_MA</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="D77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ADD1</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="D79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>미국VCP</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_A</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="n">
-        <v>3</v>
-      </c>
-      <c r="M82" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N82" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>949</v>
-      </c>
-      <c r="R82" t="n">
-        <v>-70465</v>
-      </c>
-      <c r="S82" t="n">
-        <v>1411</v>
-      </c>
+      <c r="D81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3806,302 +3812,302 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="n">
+        <v>3</v>
+      </c>
+      <c r="M83" t="n">
+        <v>-10.012</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>949</v>
+      </c>
+      <c r="R83" t="n">
+        <v>-70465</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_A</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>9</v>
-      </c>
-      <c r="E83" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H83" t="n">
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="n">
+        <v>50</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H84" t="n">
         <v>4.28</v>
       </c>
-      <c r="I83" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J83" t="n">
+      <c r="I84" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J84" t="n">
         <v>5.74</v>
       </c>
-      <c r="K83" t="n">
-        <v>14</v>
-      </c>
-      <c r="L83" t="n">
+      <c r="K84" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L84" t="n">
         <v>5.6</v>
       </c>
-      <c r="M83" t="n">
-        <v>-1.851</v>
-      </c>
-      <c r="N83" t="n">
-        <v>-4960</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="P83" t="n">
-        <v>-16484</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>6506</v>
-      </c>
-      <c r="R83" t="n">
-        <v>-9978</v>
-      </c>
-      <c r="S83" t="n">
+      <c r="M84" t="n">
+        <v>-0.896</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-471</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P84" t="n">
+        <v>9422</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>6887</v>
+      </c>
+      <c r="R84" t="n">
+        <v>16310</v>
+      </c>
+      <c r="S84" t="n">
         <v>1372</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D84" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H84" s="2" t="n">
+      <c r="D85" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H85" s="2" t="n">
         <v>5.23</v>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J84" s="2" t="n">
+      <c r="I85" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J85" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="K84" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="L84" s="2" t="n">
+      <c r="K85" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L85" s="2" t="n">
         <v>5.17</v>
       </c>
-      <c r="M84" s="2" t="n">
-        <v>-2.668</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>-11605</v>
-      </c>
-      <c r="O84" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P84" s="2" t="n">
-        <v>-87898</v>
-      </c>
-      <c r="Q84" s="2" t="n">
-        <v>7455</v>
-      </c>
-      <c r="R84" s="2" t="n">
-        <v>-80443</v>
-      </c>
-      <c r="S84" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="M85" s="2" t="n">
+        <v>-1.725</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-6920</v>
+      </c>
+      <c r="O85" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P85" s="2" t="n">
+        <v>-61992</v>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>7836</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>-54155</v>
+      </c>
+      <c r="S85" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="D87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>US_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="D89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP1</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="n">
-        <v>5</v>
-      </c>
-      <c r="M92" t="n">
-        <v>-6.802</v>
-      </c>
-      <c r="N92" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>196</v>
-      </c>
-      <c r="R92" t="n">
-        <v>-9679</v>
-      </c>
-      <c r="S92" t="n">
-        <v>1411</v>
-      </c>
+      <c r="D91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4116,770 +4122,770 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="n">
+        <v>5</v>
+      </c>
+      <c r="M93" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="N93" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>-9876</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>196</v>
+      </c>
+      <c r="R93" t="n">
+        <v>-9679</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D94" t="n">
         <v>4</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E94" t="n">
         <v>50</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F94" t="n">
         <v>1.67</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G94" t="n">
         <v>3.59</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H94" t="n">
         <v>2.42</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I94" t="n">
         <v>4.34</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J94" t="n">
         <v>4.61</v>
       </c>
-      <c r="K93" t="n">
+      <c r="K94" t="n">
         <v>14</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L94" t="n">
         <v>4.5</v>
       </c>
-      <c r="M93" t="n">
+      <c r="M94" t="n">
         <v>0.587</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N94" t="n">
         <v>2177</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O94" t="n">
         <v>1.67</v>
       </c>
-      <c r="P93" t="n">
+      <c r="P94" t="n">
         <v>19858</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="Q94" t="n">
         <v>2417</v>
       </c>
-      <c r="R93" t="n">
+      <c r="R94" t="n">
         <v>22274</v>
       </c>
-      <c r="S93" t="n">
+      <c r="S94" t="n">
         <v>1372</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D95" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E94" s="2" t="n">
+      <c r="E95" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F94" s="2" t="n">
+      <c r="F95" s="2" t="n">
         <v>1.42</v>
       </c>
-      <c r="G94" s="2" t="n">
+      <c r="G95" s="2" t="n">
         <v>3.59</v>
       </c>
-      <c r="H94" s="2" t="n">
+      <c r="H95" s="2" t="n">
         <v>3.88</v>
       </c>
-      <c r="I94" s="2" t="n">
+      <c r="I95" s="2" t="n">
         <v>4.34</v>
       </c>
-      <c r="J94" s="2" t="n">
+      <c r="J95" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="K94" s="2" t="n">
+      <c r="K95" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="L94" s="2" t="n">
+      <c r="L95" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="M94" s="2" t="n">
+      <c r="M95" s="2" t="n">
         <v>-0.891</v>
       </c>
-      <c r="N94" s="2" t="n">
+      <c r="N95" s="2" t="n">
         <v>-234</v>
       </c>
-      <c r="O94" s="2" t="n">
+      <c r="O95" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="P94" s="2" t="n">
+      <c r="P95" s="2" t="n">
         <v>9982</v>
       </c>
-      <c r="Q94" s="2" t="n">
+      <c r="Q95" s="2" t="n">
         <v>2613</v>
       </c>
-      <c r="R94" s="2" t="n">
+      <c r="R95" s="2" t="n">
         <v>12595</v>
       </c>
-      <c r="S94" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="S95" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr"/>
-      <c r="P96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D99" t="n">
         <v>6</v>
       </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="n">
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
         <v>3.78</v>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="n">
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
         <v>6.17</v>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="n">
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
         <v>8</v>
       </c>
-      <c r="M98" t="n">
+      <c r="M99" t="n">
         <v>-3.784</v>
       </c>
-      <c r="N98" t="n">
+      <c r="N99" t="n">
         <v>-8906</v>
       </c>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="n">
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
         <v>-53435</v>
       </c>
-      <c r="Q98" t="n">
+      <c r="Q99" t="n">
         <v>1676</v>
       </c>
-      <c r="R98" t="n">
+      <c r="R99" t="n">
         <v>-51759</v>
       </c>
-      <c r="S98" t="n">
+      <c r="S99" t="n">
         <v>1372</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n">
+      <c r="D100" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="n">
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="n">
         <v>3.78</v>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="n">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="n">
         <v>6.17</v>
       </c>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="n">
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M99" s="2" t="n">
+      <c r="M100" s="2" t="n">
         <v>-3.784</v>
       </c>
-      <c r="N99" s="2" t="n">
+      <c r="N100" s="2" t="n">
         <v>-8906</v>
       </c>
-      <c r="O99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="2" t="n">
+      <c r="O100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="2" t="n">
         <v>-53435</v>
       </c>
-      <c r="Q99" s="2" t="n">
+      <c r="Q100" s="2" t="n">
         <v>1676</v>
       </c>
-      <c r="R99" s="2" t="n">
+      <c r="R100" s="2" t="n">
         <v>-51759</v>
       </c>
-      <c r="S99" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="S100" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
-      <c r="P101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="D102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D104" t="n">
         <v>2</v>
       </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="n">
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="n">
         <v>7.15</v>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="n">
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="n">
         <v>10.49</v>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="n">
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="n">
         <v>1</v>
       </c>
-      <c r="M103" t="n">
+      <c r="M104" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N103" t="n">
+      <c r="N104" t="n">
         <v>-27425</v>
       </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
         <v>-54849</v>
       </c>
-      <c r="Q103" t="n">
+      <c r="Q104" t="n">
         <v>1053</v>
       </c>
-      <c r="R103" t="n">
+      <c r="R104" t="n">
         <v>-53796</v>
       </c>
-      <c r="S103" t="n">
+      <c r="S104" t="n">
         <v>1372</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n">
+      <c r="D105" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="n">
+      <c r="E105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="n">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="n">
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M104" s="2" t="n">
+      <c r="M105" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N104" s="2" t="n">
+      <c r="N105" s="2" t="n">
         <v>-27425</v>
       </c>
-      <c r="O104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" s="2" t="n">
+      <c r="O105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="2" t="n">
         <v>-54849</v>
       </c>
-      <c r="Q104" s="2" t="n">
+      <c r="Q105" s="2" t="n">
         <v>1053</v>
       </c>
-      <c r="R104" s="2" t="n">
+      <c r="R105" s="2" t="n">
         <v>-53796</v>
       </c>
-      <c r="S104" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="S105" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D107" t="n">
         <v>13</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E107" t="n">
         <v>53.8</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F107" t="n">
         <v>1.85</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G107" t="n">
         <v>7.78</v>
       </c>
-      <c r="H106" t="n">
+      <c r="H107" t="n">
         <v>2.66</v>
       </c>
-      <c r="I106" t="n">
+      <c r="I107" t="n">
         <v>16.31</v>
       </c>
-      <c r="J106" t="n">
+      <c r="J107" t="n">
         <v>5.68</v>
       </c>
-      <c r="K106" t="n">
+      <c r="K107" t="n">
         <v>0.29</v>
       </c>
-      <c r="L106" t="n">
+      <c r="L107" t="n">
         <v>0.33</v>
       </c>
-      <c r="M106" t="n">
+      <c r="M107" t="n">
         <v>2.964</v>
       </c>
-      <c r="N106" t="n">
+      <c r="N107" t="n">
         <v>3611</v>
       </c>
-      <c r="O106" t="n">
+      <c r="O107" t="n">
         <v>2.16</v>
       </c>
-      <c r="P106" t="n">
-        <v>129001</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>5832</v>
-      </c>
-      <c r="R106" t="n">
-        <v>134833</v>
-      </c>
-      <c r="S106" t="n">
+      <c r="P107" t="n">
+        <v>137378</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>5906</v>
+      </c>
+      <c r="R107" t="n">
+        <v>143285</v>
+      </c>
+      <c r="S107" t="n">
         <v>1372</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D107" s="2" t="n">
+      <c r="D108" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E107" s="2" t="n">
+      <c r="E108" s="2" t="n">
         <v>53.8</v>
       </c>
-      <c r="F107" s="2" t="n">
+      <c r="F108" s="2" t="n">
         <v>1.85</v>
       </c>
-      <c r="G107" s="2" t="n">
+      <c r="G108" s="2" t="n">
         <v>7.78</v>
       </c>
-      <c r="H107" s="2" t="n">
+      <c r="H108" s="2" t="n">
         <v>2.66</v>
       </c>
-      <c r="I107" s="2" t="n">
+      <c r="I108" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J107" s="2" t="n">
+      <c r="J108" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K107" s="2" t="n">
+      <c r="K108" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="L107" s="2" t="n">
+      <c r="L108" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="M107" s="2" t="n">
+      <c r="M108" s="2" t="n">
         <v>2.964</v>
       </c>
-      <c r="N107" s="2" t="n">
+      <c r="N108" s="2" t="n">
         <v>3611</v>
       </c>
-      <c r="O107" s="2" t="n">
+      <c r="O108" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="P107" s="2" t="n">
-        <v>129001</v>
-      </c>
-      <c r="Q107" s="2" t="n">
-        <v>5832</v>
-      </c>
-      <c r="R107" s="2" t="n">
-        <v>134833</v>
-      </c>
-      <c r="S107" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="P108" s="2" t="n">
+        <v>137378</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>5906</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>143285</v>
+      </c>
+      <c r="S108" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr"/>
-      <c r="O109" s="2" t="inlineStr"/>
-      <c r="P109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="D110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D111" t="n">
+      <c r="D112" t="n">
         <v>1</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E112" t="n">
         <v>100</v>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="n">
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="n">
         <v>2.1</v>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="n">
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="n">
         <v>2.1</v>
       </c>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="n">
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="n">
         <v>52.73</v>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="n">
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="n">
         <v>2.102</v>
       </c>
-      <c r="N111" t="n">
+      <c r="N112" t="n">
         <v>2341</v>
       </c>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="n">
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="n">
         <v>2341</v>
       </c>
-      <c r="Q111" t="n">
+      <c r="Q112" t="n">
         <v>34</v>
       </c>
-      <c r="R111" t="n">
+      <c r="R112" t="n">
         <v>2375</v>
       </c>
-      <c r="S111" t="n">
+      <c r="S112" t="n">
         <v>1372</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D112" s="2" t="n">
+      <c r="D113" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E112" s="2" t="n">
+      <c r="E113" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="n">
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="n">
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J112" s="2" t="inlineStr"/>
-      <c r="K112" s="2" t="n">
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="n">
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N112" s="2" t="n">
+      <c r="N113" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O112" s="2" t="inlineStr"/>
-      <c r="P112" s="2" t="n">
+      <c r="O113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q112" s="2" t="n">
+      <c r="Q113" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R112" s="2" t="n">
+      <c r="R113" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S112" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>2</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="n">
-        <v>1</v>
-      </c>
-      <c r="M114" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N114" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>513</v>
-      </c>
-      <c r="R114" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S114" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S113" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4894,53 +4900,47 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G115" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I115" t="n">
-        <v>1.37</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K115" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="n">
         <v>1</v>
       </c>
-      <c r="L115" t="n">
-        <v>5.67</v>
-      </c>
       <c r="M115" t="n">
-        <v>-0.217</v>
+        <v>-2.607</v>
       </c>
       <c r="N115" t="n">
-        <v>-13272</v>
+        <v>-8011</v>
       </c>
       <c r="O115" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>-53089</v>
+        <v>-16021</v>
       </c>
       <c r="Q115" t="n">
-        <v>5913</v>
+        <v>513</v>
       </c>
       <c r="R115" t="n">
-        <v>-47176</v>
+        <v>-15508</v>
       </c>
       <c r="S115" t="n">
         <v>1415</v>
@@ -4959,47 +4959,53 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H116" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I116" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J116" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K116" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1</v>
+      </c>
       <c r="L116" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.136</v>
+        <v>-0.217</v>
       </c>
       <c r="N116" t="n">
-        <v>-2389</v>
+        <v>-13272</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P116" t="n">
-        <v>-4777</v>
+        <v>-53089</v>
       </c>
       <c r="Q116" t="n">
-        <v>2924</v>
+        <v>5913</v>
       </c>
       <c r="R116" t="n">
-        <v>-1854</v>
+        <v>-47176</v>
       </c>
       <c r="S116" t="n">
         <v>1415</v>
@@ -5018,43 +5024,47 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>100</v>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="n">
-        <v>14</v>
-      </c>
-      <c r="L117" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M117" t="n">
-        <v>1.042</v>
+        <v>-0.136</v>
       </c>
       <c r="N117" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O117" t="inlineStr"/>
+        <v>-2389</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
       <c r="P117" t="n">
-        <v>48540</v>
+        <v>-4777</v>
       </c>
       <c r="Q117" t="n">
-        <v>4254</v>
+        <v>2924</v>
       </c>
       <c r="R117" t="n">
-        <v>52794</v>
+        <v>-1854</v>
       </c>
       <c r="S117" t="n">
         <v>1415</v>
@@ -5073,552 +5083,782 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D118" t="n">
         <v>3</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="n">
+        <v>100</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>14</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N118" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R118" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="n">
         <v>0.86</v>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="n">
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="n">
         <v>1.53</v>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="n">
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="n">
         <v>4.67</v>
       </c>
-      <c r="M118" t="n">
+      <c r="M119" t="n">
         <v>-0.864</v>
       </c>
-      <c r="N118" t="n">
+      <c r="N119" t="n">
         <v>-28997</v>
       </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
         <v>-86990</v>
       </c>
-      <c r="Q118" t="n">
+      <c r="Q119" t="n">
         <v>13787</v>
       </c>
-      <c r="R118" t="n">
+      <c r="R119" t="n">
         <v>-73203</v>
       </c>
-      <c r="S118" t="n">
+      <c r="S119" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>3</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-0.867</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-29167</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>-29167</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>2948</v>
+      </c>
+      <c r="R120" t="n">
+        <v>-26219</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D119" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="G119" s="2" t="n">
+      <c r="D121" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G121" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H119" s="2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I119" s="2" t="n">
+      <c r="H121" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I121" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J119" s="2" t="n">
+      <c r="J121" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K119" s="2" t="n">
+      <c r="K121" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L119" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>-0.416</v>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>-8024</v>
-      </c>
-      <c r="O119" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="P119" s="2" t="n">
-        <v>-112337</v>
-      </c>
-      <c r="Q119" s="2" t="n">
-        <v>27391</v>
-      </c>
-      <c r="R119" s="2" t="n">
-        <v>-84947</v>
-      </c>
-      <c r="S119" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="L121" s="2" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-0.446</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-9434</v>
+      </c>
+      <c r="O121" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P121" s="2" t="n">
+        <v>-141504</v>
+      </c>
+      <c r="Q121" s="2" t="n">
+        <v>30339</v>
+      </c>
+      <c r="R121" s="2" t="n">
+        <v>-111166</v>
+      </c>
+      <c r="S121" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D121" t="n">
+      <c r="D123" t="n">
         <v>9</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E123" t="n">
         <v>55.6</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F123" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G123" t="n">
         <v>1.17</v>
       </c>
-      <c r="H121" t="n">
+      <c r="H123" t="n">
         <v>4.19</v>
       </c>
-      <c r="I121" t="n">
+      <c r="I123" t="n">
         <v>3.38</v>
       </c>
-      <c r="J121" t="n">
+      <c r="J123" t="n">
         <v>7.04</v>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="n">
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N121" t="n">
+      <c r="N123" t="n">
         <v>-744</v>
       </c>
-      <c r="O121" t="n">
+      <c r="O123" t="n">
         <v>0.86</v>
       </c>
-      <c r="P121" t="n">
+      <c r="P123" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q121" t="n">
+      <c r="Q123" t="n">
         <v>2139</v>
       </c>
-      <c r="R121" t="n">
+      <c r="R123" t="n">
         <v>-4553</v>
       </c>
-      <c r="S121" t="n">
+      <c r="S123" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D122" t="n">
+      <c r="D124" t="n">
         <v>2</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E124" t="n">
         <v>100</v>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="n">
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="n">
         <v>8.56</v>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="n">
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="n">
         <v>12.69</v>
       </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="n">
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
         <v>8.56</v>
       </c>
-      <c r="N122" t="n">
+      <c r="N124" t="n">
         <v>57466</v>
       </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="n">
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="n">
         <v>114933</v>
       </c>
-      <c r="Q122" t="n">
+      <c r="Q124" t="n">
         <v>667</v>
       </c>
-      <c r="R122" t="n">
+      <c r="R124" t="n">
         <v>115600</v>
       </c>
-      <c r="S122" t="n">
+      <c r="S124" t="n">
         <v>1411</v>
       </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="2" t="inlineStr"/>
-      <c r="M123" s="2" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="N123" s="2" t="n">
-        <v>9840</v>
-      </c>
-      <c r="O123" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="P123" s="2" t="n">
-        <v>56575</v>
-      </c>
-      <c r="Q123" s="2" t="n">
-        <v>2972</v>
-      </c>
-      <c r="R123" s="2" t="n">
-        <v>59547</v>
-      </c>
-      <c r="S123" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>257</v>
+      </c>
+      <c r="R125" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>2846</v>
+      </c>
+      <c r="O126" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P126" s="2" t="n">
+        <v>34154</v>
+      </c>
+      <c r="Q126" s="2" t="n">
+        <v>3063</v>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>37217</v>
+      </c>
+      <c r="S126" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>07/27~07/31</t>
         </is>
       </c>
-      <c r="D125" t="n">
+      <c r="D128" t="n">
         <v>9</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E128" t="n">
         <v>55.6</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F128" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G125" t="n">
+      <c r="G128" t="n">
         <v>1.17</v>
       </c>
-      <c r="H125" t="n">
+      <c r="H128" t="n">
         <v>4.19</v>
       </c>
-      <c r="I125" t="n">
+      <c r="I128" t="n">
         <v>3.38</v>
       </c>
-      <c r="J125" t="n">
+      <c r="J128" t="n">
         <v>7.04</v>
       </c>
-      <c r="K125" t="n">
+      <c r="K128" t="n">
         <v>3</v>
       </c>
-      <c r="L125" t="n">
+      <c r="L128" t="n">
         <v>1.75</v>
       </c>
-      <c r="M125" t="n">
+      <c r="M128" t="n">
         <v>-1.213</v>
       </c>
-      <c r="N125" t="n">
+      <c r="N128" t="n">
         <v>-744</v>
       </c>
-      <c r="O125" t="n">
+      <c r="O128" t="n">
         <v>0.86</v>
       </c>
-      <c r="P125" t="n">
+      <c r="P128" t="n">
         <v>-6692</v>
       </c>
-      <c r="Q125" t="n">
+      <c r="Q128" t="n">
         <v>2139</v>
       </c>
-      <c r="R125" t="n">
+      <c r="R128" t="n">
         <v>-4553</v>
       </c>
-      <c r="S125" t="n">
+      <c r="S128" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D126" t="n">
+      <c r="D129" t="n">
         <v>2</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E129" t="n">
         <v>100</v>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="n">
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="n">
         <v>8.56</v>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="n">
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="n">
         <v>12.69</v>
       </c>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="n">
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="n">
         <v>4.5</v>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="n">
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="n">
         <v>8.56</v>
       </c>
-      <c r="N126" t="n">
+      <c r="N129" t="n">
         <v>57466</v>
       </c>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="n">
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="n">
         <v>114933</v>
       </c>
-      <c r="Q126" t="n">
+      <c r="Q129" t="n">
         <v>667</v>
       </c>
-      <c r="R126" t="n">
+      <c r="R129" t="n">
         <v>115600</v>
       </c>
-      <c r="S126" t="n">
+      <c r="S129" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="N127" s="2" t="n">
-        <v>9840</v>
-      </c>
-      <c r="O127" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="P127" s="2" t="n">
-        <v>56575</v>
-      </c>
-      <c r="Q127" s="2" t="n">
-        <v>2972</v>
-      </c>
-      <c r="R127" s="2" t="n">
-        <v>59547</v>
-      </c>
-      <c r="S127" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>미국수동</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="2" t="inlineStr"/>
-      <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-      <c r="K129" s="2" t="inlineStr"/>
-      <c r="L129" s="2" t="inlineStr"/>
-      <c r="M129" s="2" t="inlineStr"/>
-      <c r="N129" s="2" t="inlineStr"/>
-      <c r="O129" s="2" t="inlineStr"/>
-      <c r="P129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" s="2" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="n">
+        <v>3</v>
+      </c>
+      <c r="M130" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N130" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>257</v>
+      </c>
+      <c r="R130" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1372</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>2846</v>
+      </c>
+      <c r="O131" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P131" s="2" t="n">
+        <v>34154</v>
+      </c>
+      <c r="Q131" s="2" t="n">
+        <v>3063</v>
+      </c>
+      <c r="R131" s="2" t="n">
+        <v>37217</v>
+      </c>
+      <c r="S131" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>미국수동</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr"/>
+      <c r="O133" s="2" t="inlineStr"/>
+      <c r="P133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="2" t="inlineStr"/>
-      <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-      <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="inlineStr"/>
-      <c r="M131" s="2" t="inlineStr"/>
-      <c r="N131" s="2" t="inlineStr"/>
-      <c r="O131" s="2" t="inlineStr"/>
-      <c r="P131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" s="2" t="inlineStr"/>
+      <c r="D135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr"/>
+      <c r="O135" s="2" t="inlineStr"/>
+      <c r="P135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1200,22 +1200,22 @@
         <v>-1.024</v>
       </c>
       <c r="N12" t="n">
-        <v>-1869</v>
+        <v>-1880</v>
       </c>
       <c r="O12" t="n">
         <v>0.73</v>
       </c>
       <c r="P12" t="n">
-        <v>46804</v>
+        <v>46663</v>
       </c>
       <c r="Q12" t="n">
-        <v>14145</v>
+        <v>14209</v>
       </c>
       <c r="R12" t="n">
-        <v>60950</v>
+        <v>60873</v>
       </c>
       <c r="S12" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="13">
@@ -1261,19 +1261,19 @@
         <v>-0.113</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1.02</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>121773</v>
+        <v>121632</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>48927</v>
+        <v>48991</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>170701</v>
+        <v>170624</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -1772,7 +1772,7 @@
         <v>8500</v>
       </c>
       <c r="S22" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="23">
@@ -2645,7 +2645,7 @@
         <v>-15000</v>
       </c>
       <c r="S43" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="44">
@@ -3456,7 +3456,7 @@
         <v>6570</v>
       </c>
       <c r="S66" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="67">
@@ -3905,22 +3905,22 @@
         <v>-0.896</v>
       </c>
       <c r="N84" t="n">
-        <v>-471</v>
+        <v>-474</v>
       </c>
       <c r="O84" t="n">
         <v>0.93</v>
       </c>
       <c r="P84" t="n">
-        <v>9422</v>
+        <v>9477</v>
       </c>
       <c r="Q84" t="n">
-        <v>6887</v>
+        <v>6927</v>
       </c>
       <c r="R84" t="n">
-        <v>16310</v>
+        <v>16405</v>
       </c>
       <c r="S84" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="85">
@@ -3970,19 +3970,19 @@
         <v>-1.725</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-6920</v>
+        <v>-6923</v>
       </c>
       <c r="O85" s="2" t="n">
         <v>0.45</v>
       </c>
       <c r="P85" s="2" t="n">
-        <v>-61992</v>
+        <v>-61937</v>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>7836</v>
+        <v>7876</v>
       </c>
       <c r="R85" s="2" t="n">
-        <v>-54155</v>
+        <v>-54060</v>
       </c>
       <c r="S85" s="2" t="inlineStr"/>
     </row>
@@ -4215,22 +4215,22 @@
         <v>0.587</v>
       </c>
       <c r="N94" t="n">
-        <v>2177</v>
+        <v>2190</v>
       </c>
       <c r="O94" t="n">
         <v>1.67</v>
       </c>
       <c r="P94" t="n">
-        <v>19858</v>
+        <v>19973</v>
       </c>
       <c r="Q94" t="n">
-        <v>2417</v>
+        <v>2431</v>
       </c>
       <c r="R94" t="n">
-        <v>22274</v>
+        <v>22404</v>
       </c>
       <c r="S94" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="95">
@@ -4256,7 +4256,7 @@
         <v>40</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>3.59</v>
@@ -4280,19 +4280,19 @@
         <v>-0.891</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-234</v>
+        <v>-224</v>
       </c>
       <c r="O95" s="2" t="n">
         <v>0.95</v>
       </c>
       <c r="P95" s="2" t="n">
-        <v>9982</v>
+        <v>10097</v>
       </c>
       <c r="Q95" s="2" t="n">
-        <v>2613</v>
+        <v>2627</v>
       </c>
       <c r="R95" s="2" t="n">
-        <v>12595</v>
+        <v>12725</v>
       </c>
       <c r="S95" s="2" t="inlineStr"/>
     </row>
@@ -4378,22 +4378,22 @@
         <v>-3.784</v>
       </c>
       <c r="N99" t="n">
-        <v>-8906</v>
+        <v>-8958</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>-53435</v>
+        <v>-53747</v>
       </c>
       <c r="Q99" t="n">
-        <v>1676</v>
+        <v>1686</v>
       </c>
       <c r="R99" t="n">
-        <v>-51759</v>
+        <v>-52060</v>
       </c>
       <c r="S99" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="100">
@@ -4437,19 +4437,19 @@
         <v>-3.784</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-8906</v>
+        <v>-8958</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="2" t="n">
-        <v>-53435</v>
+        <v>-53747</v>
       </c>
       <c r="Q100" s="2" t="n">
-        <v>1676</v>
+        <v>1686</v>
       </c>
       <c r="R100" s="2" t="n">
-        <v>-51759</v>
+        <v>-52060</v>
       </c>
       <c r="S100" s="2" t="inlineStr"/>
     </row>
@@ -4535,22 +4535,22 @@
         <v>-7.145</v>
       </c>
       <c r="N104" t="n">
-        <v>-27425</v>
+        <v>-27585</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>-54849</v>
+        <v>-55169</v>
       </c>
       <c r="Q104" t="n">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="R104" t="n">
-        <v>-53796</v>
+        <v>-54110</v>
       </c>
       <c r="S104" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="105">
@@ -4594,19 +4594,19 @@
         <v>-7.145</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-27425</v>
+        <v>-27585</v>
       </c>
       <c r="O105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>-54849</v>
+        <v>-55169</v>
       </c>
       <c r="Q105" s="2" t="n">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="R105" s="2" t="n">
-        <v>-53796</v>
+        <v>-54110</v>
       </c>
       <c r="S105" s="2" t="inlineStr"/>
     </row>
@@ -4657,22 +4657,22 @@
         <v>2.964</v>
       </c>
       <c r="N107" t="n">
-        <v>3611</v>
+        <v>3632</v>
       </c>
       <c r="O107" t="n">
         <v>2.16</v>
       </c>
       <c r="P107" t="n">
-        <v>137378</v>
+        <v>138180</v>
       </c>
       <c r="Q107" t="n">
-        <v>5906</v>
+        <v>5941</v>
       </c>
       <c r="R107" t="n">
-        <v>143285</v>
+        <v>144120</v>
       </c>
       <c r="S107" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="108">
@@ -4722,19 +4722,19 @@
         <v>2.964</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>3611</v>
+        <v>3632</v>
       </c>
       <c r="O108" s="2" t="n">
         <v>2.16</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>137378</v>
+        <v>138180</v>
       </c>
       <c r="Q108" s="2" t="n">
-        <v>5906</v>
+        <v>5941</v>
       </c>
       <c r="R108" s="2" t="n">
-        <v>143285</v>
+        <v>144120</v>
       </c>
       <c r="S108" s="2" t="inlineStr"/>
     </row>
@@ -4831,7 +4831,7 @@
         <v>2375</v>
       </c>
       <c r="S112" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="113">
@@ -5225,22 +5225,22 @@
         <v>-0.867</v>
       </c>
       <c r="N120" t="n">
-        <v>-29167</v>
+        <v>-29337</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>-29167</v>
+        <v>-29337</v>
       </c>
       <c r="Q120" t="n">
-        <v>2948</v>
+        <v>2965</v>
       </c>
       <c r="R120" t="n">
-        <v>-26219</v>
+        <v>-26372</v>
       </c>
       <c r="S120" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="121">
@@ -5266,7 +5266,7 @@
         <v>26.7</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>1.12</v>
@@ -5290,19 +5290,19 @@
         <v>-0.446</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-9434</v>
+        <v>-9445</v>
       </c>
       <c r="O121" s="2" t="n">
         <v>0.26</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>-141504</v>
+        <v>-141674</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>30339</v>
+        <v>30356</v>
       </c>
       <c r="R121" s="2" t="n">
-        <v>-111166</v>
+        <v>-111319</v>
       </c>
       <c r="S121" s="2" t="inlineStr"/>
     </row>
@@ -5474,7 +5474,7 @@
         <v>-73830</v>
       </c>
       <c r="S125" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="126">
@@ -5712,7 +5712,7 @@
         <v>-73830</v>
       </c>
       <c r="S130" t="n">
-        <v>1372</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="131">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S135"/>
+  <dimension ref="A1:S136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1174,19 +1174,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>38.5</v>
+        <v>35.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="G12" t="n">
         <v>2.79</v>
       </c>
       <c r="H12" t="n">
-        <v>3.41</v>
+        <v>3.18</v>
       </c>
       <c r="I12" t="n">
         <v>7.7</v>
@@ -1197,25 +1197,25 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>-1.024</v>
+        <v>-1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>-1880</v>
+        <v>-3277</v>
       </c>
       <c r="O12" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="P12" t="n">
-        <v>46663</v>
+        <v>-10474</v>
       </c>
       <c r="Q12" t="n">
-        <v>14209</v>
+        <v>17894</v>
       </c>
       <c r="R12" t="n">
-        <v>60873</v>
+        <v>7421</v>
       </c>
       <c r="S12" t="n">
-        <v>1380</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="13">
@@ -1235,19 +1235,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37.2</v>
+        <v>36.9</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>4.45</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>19.29</v>
@@ -1258,22 +1258,22 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="n">
-        <v>-0.113</v>
+        <v>-0.123</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>104</v>
+        <v>-67</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>121632</v>
+        <v>64495</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>48991</v>
+        <v>52676</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>170624</v>
+        <v>117172</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -1772,7 +1772,7 @@
         <v>8500</v>
       </c>
       <c r="S22" t="n">
-        <v>1380</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="23">
@@ -2645,7 +2645,7 @@
         <v>-15000</v>
       </c>
       <c r="S43" t="n">
-        <v>1380</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="44">
@@ -3456,7 +3456,7 @@
         <v>6570</v>
       </c>
       <c r="S66" t="n">
-        <v>1380</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="67">
@@ -3905,22 +3905,22 @@
         <v>-0.896</v>
       </c>
       <c r="N84" t="n">
-        <v>-474</v>
+        <v>-471</v>
       </c>
       <c r="O84" t="n">
         <v>0.93</v>
       </c>
       <c r="P84" t="n">
-        <v>9477</v>
+        <v>9429</v>
       </c>
       <c r="Q84" t="n">
-        <v>6927</v>
+        <v>6892</v>
       </c>
       <c r="R84" t="n">
-        <v>16405</v>
+        <v>16322</v>
       </c>
       <c r="S84" t="n">
-        <v>1380</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="85">
@@ -3970,19 +3970,19 @@
         <v>-1.725</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-6923</v>
+        <v>-6921</v>
       </c>
       <c r="O85" s="2" t="n">
         <v>0.45</v>
       </c>
       <c r="P85" s="2" t="n">
-        <v>-61937</v>
+        <v>-61985</v>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>7876</v>
+        <v>7841</v>
       </c>
       <c r="R85" s="2" t="n">
-        <v>-54060</v>
+        <v>-54143</v>
       </c>
       <c r="S85" s="2" t="inlineStr"/>
     </row>
@@ -4215,22 +4215,22 @@
         <v>0.587</v>
       </c>
       <c r="N94" t="n">
-        <v>2190</v>
+        <v>2178</v>
       </c>
       <c r="O94" t="n">
         <v>1.67</v>
       </c>
       <c r="P94" t="n">
-        <v>19973</v>
+        <v>5736</v>
       </c>
       <c r="Q94" t="n">
-        <v>2431</v>
+        <v>3250</v>
       </c>
       <c r="R94" t="n">
-        <v>22404</v>
+        <v>8986</v>
       </c>
       <c r="S94" t="n">
-        <v>1380</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="95">
@@ -4256,7 +4256,7 @@
         <v>40</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>3.59</v>
@@ -4280,671 +4280,687 @@
         <v>-0.891</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-224</v>
+        <v>-232</v>
       </c>
       <c r="O95" s="2" t="n">
         <v>0.95</v>
       </c>
       <c r="P95" s="2" t="n">
-        <v>10097</v>
+        <v>-4140</v>
       </c>
       <c r="Q95" s="2" t="n">
-        <v>2627</v>
+        <v>3446</v>
       </c>
       <c r="R95" s="2" t="n">
-        <v>12725</v>
+        <v>-693</v>
       </c>
       <c r="S95" s="2" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-2.131</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-41586</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>-41586</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>2702</v>
+      </c>
+      <c r="R97" t="n">
+        <v>-38883</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_JEO2</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
-      <c r="O97" s="2" t="inlineStr"/>
-      <c r="P97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="D98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-2.131</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>-41586</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>-41586</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>2702</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>-38883</v>
+      </c>
+      <c r="S98" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v>6</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="n">
+      <c r="D100" t="n">
+        <v>7</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="n">
         <v>6.17</v>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="n">
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="n">
         <v>8</v>
       </c>
-      <c r="M99" t="n">
-        <v>-3.784</v>
-      </c>
-      <c r="N99" t="n">
-        <v>-8958</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>-53747</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>1686</v>
-      </c>
-      <c r="R99" t="n">
-        <v>-52060</v>
-      </c>
-      <c r="S99" t="n">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="M100" t="n">
+        <v>-3.337</v>
+      </c>
+      <c r="N100" t="n">
+        <v>-7859</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>-55013</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1884</v>
+      </c>
+      <c r="R100" t="n">
+        <v>-53128</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="n">
+      <c r="D101" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="n">
         <v>6.17</v>
       </c>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="n">
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M100" s="2" t="n">
-        <v>-3.784</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>-8958</v>
-      </c>
-      <c r="O100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="2" t="n">
-        <v>-53747</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>1686</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>-52060</v>
-      </c>
-      <c r="S100" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="M101" s="2" t="n">
+        <v>-3.337</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-7859</v>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>-55013</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>1884</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>-53128</v>
+      </c>
+      <c r="S101" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-      <c r="P102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="D103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D105" t="n">
         <v>2</v>
       </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="n">
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="n">
         <v>7.15</v>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="n">
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="n">
         <v>10.49</v>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="n">
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="n">
         <v>1</v>
       </c>
-      <c r="M104" t="n">
+      <c r="M105" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N104" t="n">
-        <v>-27585</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
-        <v>-55169</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>1059</v>
-      </c>
-      <c r="R104" t="n">
-        <v>-54110</v>
-      </c>
-      <c r="S104" t="n">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="N105" t="n">
+        <v>-27445</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>-54889</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1054</v>
+      </c>
+      <c r="R105" t="n">
+        <v>-53835</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n">
+      <c r="D106" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="n">
+      <c r="E106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="n">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="n">
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M105" s="2" t="n">
+      <c r="M106" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N105" s="2" t="n">
-        <v>-27585</v>
-      </c>
-      <c r="O105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" s="2" t="n">
-        <v>-55169</v>
-      </c>
-      <c r="Q105" s="2" t="n">
-        <v>1059</v>
-      </c>
-      <c r="R105" s="2" t="n">
-        <v>-54110</v>
-      </c>
-      <c r="S105" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="N106" s="2" t="n">
+        <v>-27445</v>
+      </c>
+      <c r="O106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="2" t="n">
+        <v>-54889</v>
+      </c>
+      <c r="Q106" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>-53835</v>
+      </c>
+      <c r="S106" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>13</v>
-      </c>
-      <c r="E107" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="F107" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G107" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="H107" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I107" t="n">
+      <c r="D108" t="n">
+        <v>17</v>
+      </c>
+      <c r="E108" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G108" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I108" t="n">
         <v>16.31</v>
       </c>
-      <c r="J107" t="n">
+      <c r="J108" t="n">
         <v>5.68</v>
       </c>
-      <c r="K107" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M107" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="N107" t="n">
-        <v>3632</v>
-      </c>
-      <c r="O107" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="P107" t="n">
-        <v>138180</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>5941</v>
-      </c>
-      <c r="R107" t="n">
-        <v>144120</v>
-      </c>
-      <c r="S107" t="n">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="K108" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N108" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O108" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P108" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R108" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S108" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I108" s="2" t="n">
+      <c r="D109" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I109" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J108" s="2" t="n">
+      <c r="J109" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K108" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="N108" s="2" t="n">
-        <v>3632</v>
-      </c>
-      <c r="O108" s="2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="P108" s="2" t="n">
-        <v>138180</v>
-      </c>
-      <c r="Q108" s="2" t="n">
-        <v>5941</v>
-      </c>
-      <c r="R108" s="2" t="n">
-        <v>144120</v>
-      </c>
-      <c r="S108" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="K109" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O109" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P109" s="2" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q109" s="2" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S109" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr"/>
-      <c r="P110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="D111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D112" t="n">
+      <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E113" t="n">
         <v>100</v>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="n">
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="n">
         <v>2.1</v>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="n">
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="n">
         <v>2.1</v>
       </c>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="n">
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
         <v>52.73</v>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="n">
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="n">
         <v>2.102</v>
       </c>
-      <c r="N112" t="n">
+      <c r="N113" t="n">
         <v>2341</v>
       </c>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="n">
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="n">
         <v>2341</v>
       </c>
-      <c r="Q112" t="n">
+      <c r="Q113" t="n">
         <v>34</v>
       </c>
-      <c r="R112" t="n">
+      <c r="R113" t="n">
         <v>2375</v>
       </c>
-      <c r="S112" t="n">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="S113" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D113" s="2" t="n">
+      <c r="D114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E113" s="2" t="n">
+      <c r="E114" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="n">
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="n">
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="2" t="n">
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="n">
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N113" s="2" t="n">
+      <c r="N114" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O113" s="2" t="inlineStr"/>
-      <c r="P113" s="2" t="n">
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q113" s="2" t="n">
+      <c r="Q114" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R113" s="2" t="n">
+      <c r="R114" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S113" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>2</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="n">
-        <v>1</v>
-      </c>
-      <c r="M115" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N115" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>513</v>
-      </c>
-      <c r="R115" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S115" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S114" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4959,53 +4975,47 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G116" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I116" t="n">
-        <v>1.37</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K116" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="n">
         <v>1</v>
       </c>
-      <c r="L116" t="n">
-        <v>5.67</v>
-      </c>
       <c r="M116" t="n">
-        <v>-0.217</v>
+        <v>-2.607</v>
       </c>
       <c r="N116" t="n">
-        <v>-13272</v>
+        <v>-8011</v>
       </c>
       <c r="O116" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>-53089</v>
+        <v>-16021</v>
       </c>
       <c r="Q116" t="n">
-        <v>5913</v>
+        <v>513</v>
       </c>
       <c r="R116" t="n">
-        <v>-47176</v>
+        <v>-15508</v>
       </c>
       <c r="S116" t="n">
         <v>1415</v>
@@ -5024,47 +5034,53 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H117" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I117" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J117" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K117" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1</v>
+      </c>
       <c r="L117" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.136</v>
+        <v>-0.217</v>
       </c>
       <c r="N117" t="n">
-        <v>-2389</v>
+        <v>-13272</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P117" t="n">
-        <v>-4777</v>
+        <v>-53089</v>
       </c>
       <c r="Q117" t="n">
-        <v>2924</v>
+        <v>5913</v>
       </c>
       <c r="R117" t="n">
-        <v>-1854</v>
+        <v>-47176</v>
       </c>
       <c r="S117" t="n">
         <v>1415</v>
@@ -5083,43 +5099,47 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>100</v>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="n">
-        <v>14</v>
-      </c>
-      <c r="L118" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M118" t="n">
-        <v>1.042</v>
+        <v>-0.136</v>
       </c>
       <c r="N118" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O118" t="inlineStr"/>
+        <v>-2389</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
       <c r="P118" t="n">
-        <v>48540</v>
+        <v>-4777</v>
       </c>
       <c r="Q118" t="n">
-        <v>4254</v>
+        <v>2924</v>
       </c>
       <c r="R118" t="n">
-        <v>52794</v>
+        <v>-1854</v>
       </c>
       <c r="S118" t="n">
         <v>1415</v>
@@ -5138,50 +5158,46 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D119" t="n">
         <v>3</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="n">
-        <v>4.67</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="n">
+        <v>14</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
       <c r="M119" t="n">
-        <v>-0.864</v>
+        <v>1.042</v>
       </c>
       <c r="N119" t="n">
-        <v>-28997</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O119" t="inlineStr"/>
       <c r="P119" t="n">
-        <v>-86990</v>
+        <v>48540</v>
       </c>
       <c r="Q119" t="n">
-        <v>13787</v>
+        <v>4254</v>
       </c>
       <c r="R119" t="n">
-        <v>-73203</v>
+        <v>52794</v>
       </c>
       <c r="S119" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="120">
@@ -5197,11 +5213,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -5211,161 +5227,159 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>0.87</v>
+        <v>1.53</v>
       </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R120" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
         <v>3</v>
       </c>
-      <c r="M120" t="n">
+      <c r="M121" t="n">
         <v>-0.867</v>
       </c>
-      <c r="N120" t="n">
-        <v>-29337</v>
-      </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>-29337</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>2965</v>
-      </c>
-      <c r="R120" t="n">
-        <v>-26372</v>
-      </c>
-      <c r="S120" t="n">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="N121" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>2950</v>
+      </c>
+      <c r="R121" t="n">
+        <v>-26238</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D121" s="2" t="n">
+      <c r="D122" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E121" s="2" t="n">
+      <c r="E122" s="2" t="n">
         <v>26.7</v>
       </c>
-      <c r="F121" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G121" s="2" t="n">
+      <c r="F122" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G122" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H121" s="2" t="n">
+      <c r="H122" s="2" t="n">
         <v>1.02</v>
       </c>
-      <c r="I121" s="2" t="n">
+      <c r="I122" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J121" s="2" t="n">
+      <c r="J122" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K121" s="2" t="n">
+      <c r="K122" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L121" s="2" t="n">
+      <c r="L122" s="2" t="n">
         <v>4.27</v>
       </c>
-      <c r="M121" s="2" t="n">
+      <c r="M122" s="2" t="n">
         <v>-0.446</v>
       </c>
-      <c r="N121" s="2" t="n">
-        <v>-9445</v>
-      </c>
-      <c r="O121" s="2" t="n">
+      <c r="N122" s="2" t="n">
+        <v>-9435</v>
+      </c>
+      <c r="O122" s="2" t="n">
         <v>0.26</v>
       </c>
-      <c r="P121" s="2" t="n">
-        <v>-141674</v>
-      </c>
-      <c r="Q121" s="2" t="n">
-        <v>30356</v>
-      </c>
-      <c r="R121" s="2" t="n">
-        <v>-111319</v>
-      </c>
-      <c r="S121" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>9</v>
-      </c>
-      <c r="E123" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F123" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G123" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H123" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I123" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J123" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N123" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P123" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R123" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S123" t="n">
-        <v>1415</v>
-      </c>
+      <c r="P122" s="2" t="n">
+        <v>-141525</v>
+      </c>
+      <c r="Q122" s="2" t="n">
+        <v>30341</v>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>-111185</v>
+      </c>
+      <c r="S122" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5380,44 +5394,52 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E124" t="n">
-        <v>100</v>
-      </c>
-      <c r="F124" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G124" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H124" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H124" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I124" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J124" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J124" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N124" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O124" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P124" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q124" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R124" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S124" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="125">
@@ -5433,173 +5455,161 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="n">
-        <v>8.300000000000001</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N125" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>667</v>
+      </c>
+      <c r="R125" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N125" t="n">
+      <c r="N126" t="n">
         <v>-74087</v>
       </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q125" t="n">
+      <c r="Q126" t="n">
         <v>257</v>
       </c>
-      <c r="R125" t="n">
+      <c r="R126" t="n">
         <v>-73830</v>
       </c>
-      <c r="S125" t="n">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="S126" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D126" s="2" t="n">
+      <c r="D127" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E127" s="2" t="n">
         <v>58.3</v>
       </c>
-      <c r="F126" s="2" t="n">
+      <c r="F127" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="G126" s="2" t="n">
+      <c r="G127" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H126" s="2" t="n">
+      <c r="H127" s="2" t="n">
         <v>5.02</v>
       </c>
-      <c r="I126" s="2" t="n">
+      <c r="I127" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J127" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="2" t="n">
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="n">
         <v>-0.175</v>
       </c>
-      <c r="N126" s="2" t="n">
+      <c r="N127" s="2" t="n">
         <v>2846</v>
       </c>
-      <c r="O126" s="2" t="n">
+      <c r="O127" s="2" t="n">
         <v>1.28</v>
       </c>
-      <c r="P126" s="2" t="n">
+      <c r="P127" s="2" t="n">
         <v>34154</v>
       </c>
-      <c r="Q126" s="2" t="n">
+      <c r="Q127" s="2" t="n">
         <v>3063</v>
       </c>
-      <c r="R126" s="2" t="n">
+      <c r="R127" s="2" t="n">
         <v>37217</v>
       </c>
-      <c r="S126" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>9</v>
-      </c>
-      <c r="E128" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H128" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I128" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J128" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K128" t="n">
-        <v>3</v>
-      </c>
-      <c r="L128" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M128" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N128" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O128" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P128" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R128" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S128" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S127" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5614,46 +5624,56 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E129" t="n">
-        <v>100</v>
-      </c>
-      <c r="F129" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G129" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H129" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H129" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I129" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J129" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J129" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K129" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L129" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L129" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M129" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N129" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O129" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P129" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q129" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R129" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S129" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="130">
@@ -5669,196 +5689,251 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="n">
+        <v>100</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N130" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>667</v>
+      </c>
+      <c r="R130" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D130" t="n">
+      <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="n">
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="n">
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="n">
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="n">
         <v>3</v>
       </c>
-      <c r="M130" t="n">
+      <c r="M131" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N130" t="n">
+      <c r="N131" t="n">
         <v>-74087</v>
       </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="n">
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q130" t="n">
+      <c r="Q131" t="n">
         <v>257</v>
       </c>
-      <c r="R130" t="n">
+      <c r="R131" t="n">
         <v>-73830</v>
       </c>
-      <c r="S130" t="n">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="S131" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D132" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E131" s="2" t="n">
+      <c r="E132" s="2" t="n">
         <v>58.3</v>
       </c>
-      <c r="F131" s="2" t="n">
+      <c r="F132" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="G131" s="2" t="n">
+      <c r="G132" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H131" s="2" t="n">
+      <c r="H132" s="2" t="n">
         <v>5.02</v>
       </c>
-      <c r="I131" s="2" t="n">
+      <c r="I132" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J131" s="2" t="n">
+      <c r="J132" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K131" s="2" t="n">
+      <c r="K132" s="2" t="n">
         <v>3.43</v>
       </c>
-      <c r="L131" s="2" t="n">
+      <c r="L132" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M131" s="2" t="n">
+      <c r="M132" s="2" t="n">
         <v>-0.175</v>
       </c>
-      <c r="N131" s="2" t="n">
+      <c r="N132" s="2" t="n">
         <v>2846</v>
       </c>
-      <c r="O131" s="2" t="n">
+      <c r="O132" s="2" t="n">
         <v>1.28</v>
       </c>
-      <c r="P131" s="2" t="n">
+      <c r="P132" s="2" t="n">
         <v>34154</v>
       </c>
-      <c r="Q131" s="2" t="n">
+      <c r="Q132" s="2" t="n">
         <v>3063</v>
       </c>
-      <c r="R131" s="2" t="n">
+      <c r="R132" s="2" t="n">
         <v>37217</v>
       </c>
-      <c r="S131" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="S132" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="2" t="inlineStr"/>
-      <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-      <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="2" t="inlineStr"/>
-      <c r="M133" s="2" t="inlineStr"/>
-      <c r="N133" s="2" t="inlineStr"/>
-      <c r="O133" s="2" t="inlineStr"/>
-      <c r="P133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="D134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr"/>
+      <c r="P134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-      <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="2" t="inlineStr"/>
-      <c r="M135" s="2" t="inlineStr"/>
-      <c r="N135" s="2" t="inlineStr"/>
-      <c r="O135" s="2" t="inlineStr"/>
-      <c r="P135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" s="2" t="inlineStr"/>
+      <c r="D136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S136"/>
+  <dimension ref="A1:S137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1267,13 +1267,13 @@
         <v>0.99</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>64495</v>
+        <v>46269</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>52676</v>
+        <v>52773</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>117172</v>
+        <v>99043</v>
       </c>
       <c r="S13" s="2" t="inlineStr"/>
     </row>
@@ -2404,13 +2404,13 @@
         <v>1.2</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>175011</v>
+        <v>156785</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>11975</v>
+        <v>12072</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>186986</v>
+        <v>168857</v>
       </c>
       <c r="S37" s="2" t="inlineStr"/>
     </row>
@@ -5319,128 +5319,126 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>4</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-18456</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>-68234</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>5788</v>
+      </c>
+      <c r="R122" t="n">
+        <v>-62446</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D122" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G122" s="2" t="n">
+      <c r="D123" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G123" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H122" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I122" s="2" t="n">
+      <c r="H123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J122" s="2" t="n">
+      <c r="J123" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K122" s="2" t="n">
+      <c r="K123" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L122" s="2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>-0.446</v>
-      </c>
-      <c r="N122" s="2" t="n">
-        <v>-9435</v>
-      </c>
-      <c r="O122" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="P122" s="2" t="n">
-        <v>-141525</v>
-      </c>
-      <c r="Q122" s="2" t="n">
-        <v>30341</v>
-      </c>
-      <c r="R122" s="2" t="n">
-        <v>-111185</v>
-      </c>
-      <c r="S122" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>9</v>
-      </c>
-      <c r="E124" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G124" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H124" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I124" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J124" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N124" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P124" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R124" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S124" t="n">
-        <v>1415</v>
-      </c>
+      <c r="L123" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-0.501</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>-10496</v>
+      </c>
+      <c r="O123" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P123" s="2" t="n">
+        <v>-209759</v>
+      </c>
+      <c r="Q123" s="2" t="n">
+        <v>36129</v>
+      </c>
+      <c r="R123" s="2" t="n">
+        <v>-173631</v>
+      </c>
+      <c r="S123" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5455,44 +5453,52 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E125" t="n">
-        <v>100</v>
-      </c>
-      <c r="F125" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G125" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H125" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H125" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I125" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J125" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J125" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N125" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O125" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P125" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q125" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R125" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S125" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="126">
@@ -5508,173 +5514,161 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="n">
-        <v>8.300000000000001</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N126" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>667</v>
+      </c>
+      <c r="R126" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N126" t="n">
+      <c r="N127" t="n">
         <v>-74087</v>
       </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q126" t="n">
+      <c r="Q127" t="n">
         <v>257</v>
       </c>
-      <c r="R126" t="n">
+      <c r="R127" t="n">
         <v>-73830</v>
       </c>
-      <c r="S126" t="n">
+      <c r="S127" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D127" s="2" t="n">
+      <c r="D128" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E128" s="2" t="n">
         <v>58.3</v>
       </c>
-      <c r="F127" s="2" t="n">
+      <c r="F128" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="G127" s="2" t="n">
+      <c r="G128" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H127" s="2" t="n">
+      <c r="H128" s="2" t="n">
         <v>5.02</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J128" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K127" s="2" t="inlineStr"/>
-      <c r="L127" s="2" t="inlineStr"/>
-      <c r="M127" s="2" t="n">
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="n">
         <v>-0.175</v>
       </c>
-      <c r="N127" s="2" t="n">
+      <c r="N128" s="2" t="n">
         <v>2846</v>
       </c>
-      <c r="O127" s="2" t="n">
+      <c r="O128" s="2" t="n">
         <v>1.28</v>
       </c>
-      <c r="P127" s="2" t="n">
+      <c r="P128" s="2" t="n">
         <v>34154</v>
       </c>
-      <c r="Q127" s="2" t="n">
+      <c r="Q128" s="2" t="n">
         <v>3063</v>
       </c>
-      <c r="R127" s="2" t="n">
+      <c r="R128" s="2" t="n">
         <v>37217</v>
       </c>
-      <c r="S127" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>9</v>
-      </c>
-      <c r="E129" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F129" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G129" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H129" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I129" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J129" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K129" t="n">
-        <v>3</v>
-      </c>
-      <c r="L129" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M129" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N129" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P129" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R129" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S129" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S128" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5689,46 +5683,56 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E130" t="n">
-        <v>100</v>
-      </c>
-      <c r="F130" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G130" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H130" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H130" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I130" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J130" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J130" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K130" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L130" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M130" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N130" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O130" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P130" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q130" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R130" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S130" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="131">
@@ -5744,196 +5748,251 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" t="n">
+        <v>100</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N131" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>667</v>
+      </c>
+      <c r="R131" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S131" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D131" t="n">
+      <c r="D132" t="n">
         <v>1</v>
       </c>
-      <c r="E131" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="n">
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="n">
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="n">
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="n">
         <v>3</v>
       </c>
-      <c r="M131" t="n">
+      <c r="M132" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N131" t="n">
+      <c r="N132" t="n">
         <v>-74087</v>
       </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q131" t="n">
+      <c r="Q132" t="n">
         <v>257</v>
       </c>
-      <c r="R131" t="n">
+      <c r="R132" t="n">
         <v>-73830</v>
       </c>
-      <c r="S131" t="n">
+      <c r="S132" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D132" s="2" t="n">
+      <c r="D133" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E132" s="2" t="n">
+      <c r="E133" s="2" t="n">
         <v>58.3</v>
       </c>
-      <c r="F132" s="2" t="n">
+      <c r="F133" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="G132" s="2" t="n">
+      <c r="G133" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H132" s="2" t="n">
+      <c r="H133" s="2" t="n">
         <v>5.02</v>
       </c>
-      <c r="I132" s="2" t="n">
+      <c r="I133" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J132" s="2" t="n">
+      <c r="J133" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K132" s="2" t="n">
+      <c r="K133" s="2" t="n">
         <v>3.43</v>
       </c>
-      <c r="L132" s="2" t="n">
+      <c r="L133" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M132" s="2" t="n">
+      <c r="M133" s="2" t="n">
         <v>-0.175</v>
       </c>
-      <c r="N132" s="2" t="n">
+      <c r="N133" s="2" t="n">
         <v>2846</v>
       </c>
-      <c r="O132" s="2" t="n">
+      <c r="O133" s="2" t="n">
         <v>1.28</v>
       </c>
-      <c r="P132" s="2" t="n">
+      <c r="P133" s="2" t="n">
         <v>34154</v>
       </c>
-      <c r="Q132" s="2" t="n">
+      <c r="Q133" s="2" t="n">
         <v>3063</v>
       </c>
-      <c r="R132" s="2" t="n">
+      <c r="R133" s="2" t="n">
         <v>37217</v>
       </c>
-      <c r="S132" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="S133" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="2" t="inlineStr"/>
-      <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="inlineStr"/>
-      <c r="N134" s="2" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr"/>
-      <c r="P134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="D135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr"/>
+      <c r="O135" s="2" t="inlineStr"/>
+      <c r="P135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" s="2" t="inlineStr"/>
-      <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-      <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="2" t="inlineStr"/>
-      <c r="M136" s="2" t="inlineStr"/>
-      <c r="N136" s="2" t="inlineStr"/>
-      <c r="O136" s="2" t="inlineStr"/>
-      <c r="P136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" s="2" t="inlineStr"/>
+      <c r="D137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr"/>
+      <c r="O137" s="2" t="inlineStr"/>
+      <c r="P137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S137"/>
+  <dimension ref="A1:S139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1219,122 +1219,116 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>통합</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6878</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>-11288</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>909</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-10378</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="H13" s="2" t="n">
+      <c r="D14" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="H14" s="2" t="n">
         <v>2.8</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="n">
-        <v>-0.123</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>-67</v>
-      </c>
-      <c r="O13" s="2" t="n">
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="n">
+        <v>-0.119</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>-39</v>
+      </c>
+      <c r="O14" s="2" t="n">
         <v>0.99</v>
       </c>
-      <c r="P13" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="Q13" s="2" t="n">
-        <v>52773</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>99043</v>
-      </c>
-      <c r="S13" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>주도주</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>06/08~06/12</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-3.964</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-58941</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-176822</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1322</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-175500</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1415</v>
-      </c>
+      <c r="P14" s="2" t="n">
+        <v>53207</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>53585</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>106794</v>
+      </c>
+      <c r="S14" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1349,53 +1343,47 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>06/15~06/19</t>
+          <t>06/08~06/12</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="I16" t="n">
-        <v>19.29</v>
-      </c>
+        <v>3.96</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.71</v>
-      </c>
+        <v>4.35</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.378</v>
+        <v>-3.964</v>
       </c>
       <c r="N16" t="n">
-        <v>16263</v>
+        <v>-58941</v>
       </c>
       <c r="O16" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>227688</v>
+        <v>-176822</v>
       </c>
       <c r="Q16" t="n">
-        <v>2172</v>
+        <v>1322</v>
       </c>
       <c r="R16" t="n">
-        <v>229860</v>
+        <v>-175500</v>
       </c>
       <c r="S16" t="n">
         <v>1415</v>
@@ -1414,47 +1402,53 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>06/22~06/26</t>
+          <t>06/15~06/19</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+        <v>3.69</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7.79</v>
+      </c>
       <c r="H17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>19.29</v>
+      </c>
       <c r="J17" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
+        <v>4.76</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.71</v>
+      </c>
       <c r="L17" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.001</v>
+        <v>2.378</v>
       </c>
       <c r="N17" t="n">
-        <v>-21403</v>
+        <v>16263</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P17" t="n">
-        <v>-235428</v>
+        <v>227688</v>
       </c>
       <c r="Q17" t="n">
-        <v>2878</v>
+        <v>2172</v>
       </c>
       <c r="R17" t="n">
-        <v>-232550</v>
+        <v>229860</v>
       </c>
       <c r="S17" t="n">
         <v>1415</v>
@@ -1473,53 +1467,47 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4.74</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
+        <v>8.44</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>3.33</v>
+        <v>0.91</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.022</v>
+        <v>-3.001</v>
       </c>
       <c r="N18" t="n">
-        <v>14731</v>
+        <v>-21403</v>
       </c>
       <c r="O18" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>58925</v>
+        <v>-235428</v>
       </c>
       <c r="Q18" t="n">
-        <v>1075</v>
+        <v>2878</v>
       </c>
       <c r="R18" t="n">
-        <v>60000</v>
+        <v>-232550</v>
       </c>
       <c r="S18" t="n">
         <v>1415</v>
@@ -1538,53 +1526,53 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
-        <v>0.67</v>
+        <v>7.37</v>
       </c>
       <c r="G19" t="n">
-        <v>1.34</v>
+        <v>4.74</v>
       </c>
       <c r="H19" t="n">
-        <v>1.38</v>
+        <v>2.94</v>
       </c>
       <c r="I19" t="n">
-        <v>4.21</v>
+        <v>4.74</v>
       </c>
       <c r="J19" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.021</v>
+        <v>-1.022</v>
       </c>
       <c r="N19" t="n">
-        <v>-521</v>
+        <v>14731</v>
       </c>
       <c r="O19" t="n">
-        <v>0.67</v>
+        <v>2.46</v>
       </c>
       <c r="P19" t="n">
-        <v>-4171</v>
+        <v>58925</v>
       </c>
       <c r="Q19" t="n">
-        <v>1720</v>
+        <v>1075</v>
       </c>
       <c r="R19" t="n">
-        <v>-2451</v>
+        <v>60000</v>
       </c>
       <c r="S19" t="n">
         <v>1415</v>
@@ -1603,43 +1591,53 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.67</v>
+      </c>
       <c r="G20" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>1.34</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.38</v>
+      </c>
       <c r="I20" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>4.21</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.27</v>
+      </c>
       <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="M20" t="n">
-        <v>8.81</v>
+        <v>-0.021</v>
       </c>
       <c r="N20" t="n">
-        <v>85744</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
+        <v>-521</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.67</v>
+      </c>
       <c r="P20" t="n">
-        <v>342974</v>
+        <v>-4171</v>
       </c>
       <c r="Q20" t="n">
-        <v>1131</v>
+        <v>1720</v>
       </c>
       <c r="R20" t="n">
-        <v>344105</v>
+        <v>-2451</v>
       </c>
       <c r="S20" t="n">
         <v>1415</v>
@@ -1658,53 +1656,43 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.21</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="H21" t="n">
-        <v>9.42</v>
-      </c>
+        <v>8.81</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="J21" t="n">
-        <v>11.77</v>
-      </c>
+        <v>11.03</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>8.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>1.361</v>
+        <v>8.81</v>
       </c>
       <c r="N21" t="n">
-        <v>11916</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.43</v>
-      </c>
+        <v>85744</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>71497</v>
+        <v>342974</v>
       </c>
       <c r="Q21" t="n">
-        <v>583</v>
+        <v>1131</v>
       </c>
       <c r="R21" t="n">
-        <v>72080</v>
+        <v>344105</v>
       </c>
       <c r="S21" t="n">
         <v>1415</v>
@@ -1723,308 +1711,308 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="I22" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="J22" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="N22" t="n">
+        <v>11916</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P22" t="n">
+        <v>71497</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>583</v>
+      </c>
+      <c r="R22" t="n">
+        <v>72080</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>주도주</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>2</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>50</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>1.27</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>4.87</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>4.6</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>4.87</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>4.6</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>3</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>0.133</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>4036</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>1.27</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>8073</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>427</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>8500</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>주도주</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D24" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E24" s="2" t="n">
         <v>40.4</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>6.27</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="I24" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J24" s="2" t="n">
         <v>11.77</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K24" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="L23" s="2" t="n">
+      <c r="L24" s="2" t="n">
         <v>1.52</v>
       </c>
-      <c r="M23" s="2" t="n">
+      <c r="M24" s="2" t="n">
         <v>0.535</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="N24" s="2" t="n">
         <v>5630</v>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="O24" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>292736</v>
       </c>
-      <c r="Q23" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>11308</v>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="R24" s="2" t="n">
         <v>304044</v>
       </c>
-      <c r="S23" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>ROCKET</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>ABC-VCP</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>TV알림</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>27</v>
-      </c>
-      <c r="E31" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I31" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J31" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L31" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N31" t="n">
-        <v>507</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P31" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R31" t="n">
-        <v>15210</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2039,53 +2027,53 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E32" t="n">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="F32" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="G32" t="n">
-        <v>3.01</v>
+        <v>5.47</v>
       </c>
       <c r="H32" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="I32" t="n">
-        <v>13.15</v>
+        <v>17.35</v>
       </c>
       <c r="J32" t="n">
-        <v>5.82</v>
+        <v>20.1</v>
       </c>
       <c r="K32" t="n">
-        <v>313.5</v>
+        <v>185.95</v>
       </c>
       <c r="L32" t="n">
-        <v>175.2</v>
+        <v>187.46</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.703</v>
+        <v>0.274</v>
       </c>
       <c r="N32" t="n">
-        <v>-1271</v>
+        <v>507</v>
       </c>
       <c r="O32" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="P32" t="n">
-        <v>-57188</v>
+        <v>13680</v>
       </c>
       <c r="Q32" t="n">
-        <v>2829</v>
+        <v>1530</v>
       </c>
       <c r="R32" t="n">
-        <v>-54359</v>
+        <v>15210</v>
       </c>
       <c r="S32" t="n">
         <v>1415</v>
@@ -2104,53 +2092,53 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E33" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="F33" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="G33" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="H33" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I33" t="n">
-        <v>8.68</v>
+        <v>13.15</v>
       </c>
       <c r="J33" t="n">
-        <v>9.01</v>
+        <v>5.82</v>
       </c>
       <c r="K33" t="n">
-        <v>247.7</v>
+        <v>313.5</v>
       </c>
       <c r="L33" t="n">
-        <v>174.67</v>
+        <v>175.2</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.288</v>
+        <v>-0.703</v>
       </c>
       <c r="N33" t="n">
-        <v>1187</v>
+        <v>-1271</v>
       </c>
       <c r="O33" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="P33" t="n">
-        <v>36789</v>
+        <v>-57188</v>
       </c>
       <c r="Q33" t="n">
-        <v>3306</v>
+        <v>2829</v>
       </c>
       <c r="R33" t="n">
-        <v>40095</v>
+        <v>-54359</v>
       </c>
       <c r="S33" t="n">
         <v>1415</v>
@@ -2169,53 +2157,53 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E34" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="F34" t="n">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="G34" t="n">
-        <v>6.86</v>
+        <v>3.14</v>
       </c>
       <c r="H34" t="n">
-        <v>4.11</v>
+        <v>2.76</v>
       </c>
       <c r="I34" t="n">
-        <v>11.14</v>
+        <v>8.68</v>
       </c>
       <c r="J34" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="K34" t="n">
-        <v>533.86</v>
+        <v>247.7</v>
       </c>
       <c r="L34" t="n">
-        <v>403.59</v>
+        <v>174.67</v>
       </c>
       <c r="M34" t="n">
-        <v>1.375</v>
+        <v>-0.288</v>
       </c>
       <c r="N34" t="n">
-        <v>8720</v>
+        <v>1187</v>
       </c>
       <c r="O34" t="n">
-        <v>3.53</v>
+        <v>1.3</v>
       </c>
       <c r="P34" t="n">
-        <v>52321</v>
+        <v>36789</v>
       </c>
       <c r="Q34" t="n">
-        <v>523</v>
+        <v>3306</v>
       </c>
       <c r="R34" t="n">
-        <v>52844</v>
+        <v>40095</v>
       </c>
       <c r="S34" t="n">
         <v>1415</v>
@@ -2234,53 +2222,53 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="G35" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="H35" t="n">
-        <v>1.26</v>
+        <v>4.11</v>
       </c>
       <c r="I35" t="n">
-        <v>7.95</v>
+        <v>11.14</v>
       </c>
       <c r="J35" t="n">
-        <v>2.19</v>
+        <v>9.65</v>
       </c>
       <c r="K35" t="n">
-        <v>800.2</v>
+        <v>533.86</v>
       </c>
       <c r="L35" t="n">
-        <v>60.03</v>
+        <v>403.59</v>
       </c>
       <c r="M35" t="n">
-        <v>2.446</v>
+        <v>1.375</v>
       </c>
       <c r="N35" t="n">
-        <v>5075</v>
+        <v>8720</v>
       </c>
       <c r="O35" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P35" t="n">
-        <v>45679</v>
+        <v>52321</v>
       </c>
       <c r="Q35" t="n">
-        <v>661</v>
+        <v>523</v>
       </c>
       <c r="R35" t="n">
-        <v>46340</v>
+        <v>52844</v>
       </c>
       <c r="S35" t="n">
         <v>1415</v>
@@ -2299,295 +2287,301 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F36" t="n">
-        <v>1.14</v>
+        <v>4.39</v>
       </c>
       <c r="G36" t="n">
-        <v>6.04</v>
+        <v>7.08</v>
       </c>
       <c r="H36" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I36" t="n">
-        <v>13.51</v>
+        <v>7.95</v>
       </c>
       <c r="J36" t="n">
-        <v>4.74</v>
+        <v>2.19</v>
       </c>
       <c r="K36" t="n">
-        <v>2281.51</v>
+        <v>800.2</v>
       </c>
       <c r="L36" t="n">
-        <v>27.54</v>
+        <v>60.03</v>
       </c>
       <c r="M36" t="n">
-        <v>1.758</v>
+        <v>2.446</v>
       </c>
       <c r="N36" t="n">
-        <v>851</v>
+        <v>5075</v>
       </c>
       <c r="O36" t="n">
-        <v>1.14</v>
+        <v>3.51</v>
       </c>
       <c r="P36" t="n">
-        <v>13616</v>
+        <v>45679</v>
       </c>
       <c r="Q36" t="n">
-        <v>1561</v>
+        <v>661</v>
       </c>
       <c r="R36" t="n">
-        <v>15177</v>
+        <v>46340</v>
       </c>
       <c r="S36" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>16</v>
+      </c>
+      <c r="E37" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I37" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L37" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N37" t="n">
+        <v>851</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P37" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R37" t="n">
+        <v>15177</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D38" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E38" s="2" t="n">
         <v>41.8</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F38" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>2.87</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="I38" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="J38" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K38" s="2" t="n">
         <v>600.88</v>
       </c>
-      <c r="L37" s="2" t="n">
+      <c r="L38" s="2" t="n">
         <v>163.85</v>
       </c>
-      <c r="M37" s="2" t="n">
+      <c r="M38" s="2" t="n">
         <v>0.188</v>
       </c>
-      <c r="N37" s="2" t="n">
+      <c r="N38" s="2" t="n">
         <v>783</v>
       </c>
-      <c r="O37" s="2" t="n">
+      <c r="O38" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="P37" s="2" t="n">
+      <c r="P38" s="2" t="n">
         <v>156785</v>
       </c>
-      <c r="Q37" s="2" t="n">
+      <c r="Q38" s="2" t="n">
         <v>12072</v>
       </c>
-      <c r="R37" s="2" t="n">
+      <c r="R38" s="2" t="n">
         <v>168857</v>
       </c>
-      <c r="S37" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D40" t="n">
         <v>3</v>
       </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="n">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="n">
         <v>0.34</v>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="n">
         <v>0.49</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
         <v>13.35</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M40" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N40" t="n">
         <v>-4880</v>
       </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q40" t="n">
         <v>1291</v>
       </c>
-      <c r="R39" t="n">
+      <c r="R40" t="n">
         <v>-13350</v>
       </c>
-      <c r="S39" t="n">
+      <c r="S40" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="n">
+      <c r="E41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="n">
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M40" s="2" t="n">
+      <c r="M41" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N40" s="2" t="n">
+      <c r="N41" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="2" t="n">
+      <c r="O41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q40" s="2" t="n">
+      <c r="Q41" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R40" s="2" t="n">
+      <c r="R41" s="2" t="n">
         <v>-13350</v>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M42" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>-138394</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>4519</v>
-      </c>
-      <c r="R42" t="n">
-        <v>-133875</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S41" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2602,11 +2596,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -2616,445 +2610,445 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0.49</v>
+        <v>0.91</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>0.59</v>
+        <v>2.28</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-0.912</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-138394</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4519</v>
+      </c>
+      <c r="R43" t="n">
+        <v>-133875</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="n">
         <v>27.47</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M44" t="n">
         <v>-0.486</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N44" t="n">
         <v>-7995</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>-15989</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q44" t="n">
         <v>989</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R44" t="n">
         <v>-15000</v>
       </c>
-      <c r="S43" t="n">
+      <c r="S44" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D45" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="n">
+      <c r="E45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="n">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="n">
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="n">
         <v>29.57</v>
       </c>
-      <c r="M44" s="2" t="n">
+      <c r="M45" s="2" t="n">
         <v>-0.841</v>
       </c>
-      <c r="N44" s="2" t="n">
+      <c r="N45" s="2" t="n">
         <v>-12865</v>
       </c>
-      <c r="O44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="2" t="n">
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="n">
         <v>-154383</v>
       </c>
-      <c r="Q44" s="2" t="n">
+      <c r="Q45" s="2" t="n">
         <v>5508</v>
       </c>
-      <c r="R44" s="2" t="n">
+      <c r="R45" s="2" t="n">
         <v>-148875</v>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D47" t="n">
         <v>12</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E47" t="n">
         <v>16.7</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F47" t="n">
         <v>0.72</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G47" t="n">
         <v>0.44</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H47" t="n">
         <v>0.64</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I47" t="n">
         <v>0.84</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J47" t="n">
         <v>1.81</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K47" t="n">
         <v>14.12</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L47" t="n">
         <v>26.24</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M47" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N46" t="n">
+      <c r="N47" t="n">
         <v>-6941</v>
       </c>
-      <c r="O46" t="n">
+      <c r="O47" t="n">
         <v>0.14</v>
       </c>
-      <c r="P46" t="n">
+      <c r="P47" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q47" t="n">
         <v>5515</v>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>-77775</v>
       </c>
-      <c r="S46" t="n">
+      <c r="S47" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D48" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E48" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F48" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="H48" s="2" t="n">
         <v>0.64</v>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="I48" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="J48" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K48" s="2" t="n">
         <v>14.12</v>
       </c>
-      <c r="L47" s="2" t="n">
+      <c r="L48" s="2" t="n">
         <v>26.24</v>
       </c>
-      <c r="M47" s="2" t="n">
+      <c r="M48" s="2" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N47" s="2" t="n">
+      <c r="N48" s="2" t="n">
         <v>-6941</v>
       </c>
-      <c r="O47" s="2" t="n">
+      <c r="O48" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="P47" s="2" t="n">
+      <c r="P48" s="2" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q47" s="2" t="n">
+      <c r="Q48" s="2" t="n">
         <v>5515</v>
       </c>
-      <c r="R47" s="2" t="n">
+      <c r="R48" s="2" t="n">
         <v>-77775</v>
       </c>
-      <c r="S47" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="S48" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_미분류</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="D50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>5minHL</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="D52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>5minHL2</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr"/>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="D54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>5minHL_동시</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr"/>
-      <c r="O55" s="2" t="inlineStr"/>
-      <c r="P55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M57" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>26</v>
-      </c>
-      <c r="R57" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3069,53 +3063,47 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2.47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1279.97</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
-        <v>875.09</v>
+        <v>49.85</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.191</v>
+        <v>-2.747</v>
       </c>
       <c r="N58" t="n">
-        <v>4951</v>
+        <v>-2426</v>
       </c>
       <c r="O58" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>29704</v>
+        <v>-2426</v>
       </c>
       <c r="Q58" t="n">
-        <v>756</v>
+        <v>26</v>
       </c>
       <c r="R58" t="n">
-        <v>30460</v>
+        <v>-2400</v>
       </c>
       <c r="S58" t="n">
         <v>1415</v>
@@ -3134,53 +3122,53 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="G59" t="n">
-        <v>0.08</v>
+        <v>2.47</v>
       </c>
       <c r="H59" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="I59" t="n">
-        <v>0.08</v>
+        <v>4.6</v>
       </c>
       <c r="J59" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="K59" t="n">
-        <v>4319.93</v>
+        <v>1279.97</v>
       </c>
       <c r="L59" t="n">
-        <v>1351.81</v>
+        <v>875.09</v>
       </c>
       <c r="M59" t="n">
-        <v>-2.059</v>
+        <v>-0.191</v>
       </c>
       <c r="N59" t="n">
-        <v>-3794</v>
+        <v>4951</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="P59" t="n">
-        <v>-11383</v>
+        <v>29704</v>
       </c>
       <c r="Q59" t="n">
-        <v>153</v>
+        <v>756</v>
       </c>
       <c r="R59" t="n">
-        <v>-11230</v>
+        <v>30460</v>
       </c>
       <c r="S59" t="n">
         <v>1415</v>
@@ -3199,43 +3187,53 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>100</v>
-      </c>
-      <c r="F60" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G60" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3.13</v>
+      </c>
       <c r="I60" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.61</v>
+      </c>
       <c r="K60" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L60" t="inlineStr"/>
+        <v>4319.93</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1351.81</v>
+      </c>
       <c r="M60" t="n">
-        <v>1.678</v>
+        <v>-2.059</v>
       </c>
       <c r="N60" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O60" t="inlineStr"/>
+        <v>-3794</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.01</v>
+      </c>
       <c r="P60" t="n">
-        <v>1670</v>
+        <v>-11383</v>
       </c>
       <c r="Q60" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="R60" t="n">
-        <v>1700</v>
+        <v>-11230</v>
       </c>
       <c r="S60" t="n">
         <v>1415</v>
@@ -3254,609 +3252,605 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="n">
-        <v>5756.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>-6.785</v>
+        <v>1.678</v>
       </c>
       <c r="N61" t="n">
-        <v>-7272</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
+        <v>1670</v>
+      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>-14543</v>
+        <v>1670</v>
       </c>
       <c r="Q61" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="R61" t="n">
-        <v>-14485</v>
+        <v>1700</v>
       </c>
       <c r="S61" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>5756.96</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-7272</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-14543</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>58</v>
+      </c>
+      <c r="R62" t="n">
+        <v>-14485</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D63" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E63" s="2" t="n">
         <v>38.5</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F63" s="2" t="n">
         <v>1.71</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H63" s="2" t="n">
         <v>3.89</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="I63" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J63" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="K62" s="2" t="n">
+      <c r="K63" s="2" t="n">
         <v>1633.99</v>
       </c>
-      <c r="L62" s="2" t="n">
+      <c r="L63" s="2" t="n">
         <v>2111.58</v>
       </c>
-      <c r="M62" s="2" t="n">
+      <c r="M63" s="2" t="n">
         <v>-1.689</v>
       </c>
-      <c r="N62" s="2" t="n">
+      <c r="N63" s="2" t="n">
         <v>232</v>
       </c>
-      <c r="O62" s="2" t="n">
+      <c r="O63" s="2" t="n">
         <v>1.07</v>
       </c>
-      <c r="P62" s="2" t="n">
+      <c r="P63" s="2" t="n">
         <v>3022</v>
       </c>
-      <c r="Q62" s="2" t="n">
+      <c r="Q63" s="2" t="n">
         <v>1023</v>
       </c>
-      <c r="R62" s="2" t="n">
+      <c r="R63" s="2" t="n">
         <v>4045</v>
       </c>
-      <c r="S62" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="S63" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr"/>
-      <c r="P64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="D65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D67" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E67" t="n">
         <v>100</v>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="n">
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
         <v>1.3</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="n">
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
         <v>1.3</v>
       </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="n">
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
         <v>7</v>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="n">
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="n">
         <v>1.299</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N67" t="n">
         <v>6421</v>
       </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="n">
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
         <v>6421</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="Q67" t="n">
         <v>149</v>
       </c>
-      <c r="R66" t="n">
+      <c r="R67" t="n">
         <v>6570</v>
       </c>
-      <c r="S66" t="n">
+      <c r="S67" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E68" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="n">
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="n">
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="n">
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="n">
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="n">
         <v>1.299</v>
       </c>
-      <c r="N67" s="2" t="n">
+      <c r="N68" s="2" t="n">
         <v>6421</v>
       </c>
-      <c r="O67" s="2" t="inlineStr"/>
-      <c r="P67" s="2" t="n">
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="n">
         <v>6421</v>
       </c>
-      <c r="Q67" s="2" t="n">
+      <c r="Q68" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="R67" s="2" t="n">
+      <c r="R68" s="2" t="n">
         <v>6570</v>
       </c>
-      <c r="S67" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="S68" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr"/>
-      <c r="O69" s="2" t="inlineStr"/>
-      <c r="P69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="D70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP1</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr"/>
-      <c r="P71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="D72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP2</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr"/>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="D74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>KR_TR_JEO2</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr"/>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="D76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>KR_TR_MA</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr"/>
-      <c r="O77" s="2" t="inlineStr"/>
-      <c r="P77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="D78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ADD1</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr"/>
-      <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="D80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>미국VCP</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr"/>
-      <c r="O81" s="2" t="inlineStr"/>
-      <c r="P81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_A</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="n">
-        <v>3</v>
-      </c>
-      <c r="M83" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N83" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>949</v>
-      </c>
-      <c r="R83" t="n">
-        <v>-70465</v>
-      </c>
-      <c r="S83" t="n">
-        <v>1411</v>
-      </c>
+      <c r="D82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3871,125 +3865,176 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="n">
+        <v>3</v>
+      </c>
+      <c r="M84" t="n">
+        <v>-10.012</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>-71414</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>949</v>
+      </c>
+      <c r="R84" t="n">
+        <v>-70465</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_A</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D85" t="n">
         <v>10</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E85" t="n">
         <v>50</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F85" t="n">
         <v>0.93</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G85" t="n">
         <v>2.49</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H85" t="n">
         <v>4.28</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I85" t="n">
         <v>7.7</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J85" t="n">
         <v>5.74</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K85" t="n">
         <v>14.2</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L85" t="n">
         <v>5.6</v>
       </c>
-      <c r="M84" t="n">
+      <c r="M85" t="n">
         <v>-0.896</v>
       </c>
-      <c r="N84" t="n">
+      <c r="N85" t="n">
         <v>-471</v>
       </c>
-      <c r="O84" t="n">
+      <c r="O85" t="n">
         <v>0.93</v>
       </c>
-      <c r="P84" t="n">
+      <c r="P85" t="n">
         <v>9429</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="Q85" t="n">
         <v>6892</v>
       </c>
-      <c r="R84" t="n">
+      <c r="R85" t="n">
         <v>16322</v>
       </c>
-      <c r="S84" t="n">
+      <c r="S85" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>-1.725</v>
-      </c>
-      <c r="N85" s="2" t="n">
-        <v>-6921</v>
-      </c>
-      <c r="O85" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P85" s="2" t="n">
-        <v>-61985</v>
-      </c>
-      <c r="Q85" s="2" t="n">
-        <v>7841</v>
-      </c>
-      <c r="R85" s="2" t="n">
-        <v>-54143</v>
-      </c>
-      <c r="S85" s="2" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>100</v>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>14</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="N86" t="n">
+        <v>6878</v>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="n">
+        <v>7070</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>487</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7557</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1384</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_1</t>
+          <t>US_TR_ORD_A</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4003,34 +4048,56 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr"/>
-      <c r="N87" s="2" t="inlineStr"/>
-      <c r="O87" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1.498</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>-5771</v>
+      </c>
+      <c r="O87" s="2" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P87" s="2" t="n">
-        <v>0</v>
+        <v>-54915</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>0</v>
+        <v>8328</v>
       </c>
       <c r="R87" s="2" t="n">
-        <v>0</v>
+        <v>-46586</v>
       </c>
       <c r="S87" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_2</t>
+          <t>US_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4071,7 +4138,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP1</t>
+          <t>US_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4110,981 +4177,898 @@
       <c r="S91" s="2" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP1</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>08/10~08/14</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D95" t="n">
         <v>1</v>
       </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="n">
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="n">
         <v>6.8</v>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="n">
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="n">
         <v>6.8</v>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="n">
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="n">
         <v>5</v>
       </c>
-      <c r="M93" t="n">
+      <c r="M95" t="n">
         <v>-6.802</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N95" t="n">
         <v>-9876</v>
       </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
         <v>-9876</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="Q95" t="n">
         <v>196</v>
       </c>
-      <c r="R93" t="n">
+      <c r="R95" t="n">
         <v>-9679</v>
       </c>
-      <c r="S93" t="n">
+      <c r="S95" t="n">
         <v>1411</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D96" t="n">
         <v>4</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E96" t="n">
         <v>50</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F96" t="n">
         <v>1.67</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G96" t="n">
         <v>3.59</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H96" t="n">
         <v>2.42</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I96" t="n">
         <v>4.34</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J96" t="n">
         <v>4.61</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K96" t="n">
         <v>14</v>
       </c>
-      <c r="L94" t="n">
+      <c r="L96" t="n">
         <v>4.5</v>
       </c>
-      <c r="M94" t="n">
+      <c r="M96" t="n">
         <v>0.587</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N96" t="n">
         <v>2178</v>
       </c>
-      <c r="O94" t="n">
+      <c r="O96" t="n">
         <v>1.67</v>
       </c>
-      <c r="P94" t="n">
+      <c r="P96" t="n">
         <v>5736</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="Q96" t="n">
         <v>3250</v>
       </c>
-      <c r="R94" t="n">
+      <c r="R96" t="n">
         <v>8986</v>
       </c>
-      <c r="S94" t="n">
+      <c r="S96" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n">
+      <c r="D97" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E95" s="2" t="n">
+      <c r="E97" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F95" s="2" t="n">
+      <c r="F97" s="2" t="n">
         <v>1.42</v>
       </c>
-      <c r="G95" s="2" t="n">
+      <c r="G97" s="2" t="n">
         <v>3.59</v>
       </c>
-      <c r="H95" s="2" t="n">
+      <c r="H97" s="2" t="n">
         <v>3.88</v>
       </c>
-      <c r="I95" s="2" t="n">
+      <c r="I97" s="2" t="n">
         <v>4.34</v>
       </c>
-      <c r="J95" s="2" t="n">
+      <c r="J97" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="K95" s="2" t="n">
+      <c r="K97" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="L95" s="2" t="n">
+      <c r="L97" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="M95" s="2" t="n">
+      <c r="M97" s="2" t="n">
         <v>-0.891</v>
       </c>
-      <c r="N95" s="2" t="n">
+      <c r="N97" s="2" t="n">
         <v>-232</v>
       </c>
-      <c r="O95" s="2" t="n">
+      <c r="O97" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="P95" s="2" t="n">
-        <v>-4140</v>
-      </c>
-      <c r="Q95" s="2" t="n">
-        <v>3446</v>
-      </c>
-      <c r="R95" s="2" t="n">
-        <v>-693</v>
-      </c>
-      <c r="S95" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="P97" s="2" t="n">
+        <v>-8386</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>3644</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>-4741</v>
+      </c>
+      <c r="S97" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D99" t="n">
         <v>1</v>
       </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="n">
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
         <v>2.13</v>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="n">
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
         <v>2.13</v>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="n">
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
         <v>1</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M99" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N99" t="n">
         <v>-41586</v>
       </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="Q99" t="n">
         <v>2702</v>
       </c>
-      <c r="R97" t="n">
+      <c r="R99" t="n">
         <v>-38883</v>
       </c>
-      <c r="S97" t="n">
+      <c r="S99" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="n">
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="n">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="n">
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M98" s="2" t="n">
+      <c r="M100" s="2" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N98" s="2" t="n">
+      <c r="N100" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="O98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="2" t="n">
+      <c r="O100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q98" s="2" t="n">
+      <c r="Q100" s="2" t="n">
         <v>2702</v>
       </c>
-      <c r="R98" s="2" t="n">
+      <c r="R100" s="2" t="n">
         <v>-38883</v>
       </c>
-      <c r="S98" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="S100" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D102" t="n">
         <v>7</v>
       </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="n">
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="n">
         <v>3.34</v>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="n">
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="n">
         <v>6.17</v>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="n">
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="n">
         <v>8</v>
       </c>
-      <c r="M100" t="n">
+      <c r="M102" t="n">
         <v>-3.337</v>
       </c>
-      <c r="N100" t="n">
+      <c r="N102" t="n">
         <v>-7859</v>
       </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
         <v>-55013</v>
       </c>
-      <c r="Q100" t="n">
+      <c r="Q102" t="n">
         <v>1884</v>
       </c>
-      <c r="R100" t="n">
+      <c r="R102" t="n">
         <v>-53128</v>
       </c>
-      <c r="S100" t="n">
+      <c r="S102" t="n">
         <v>1373</v>
       </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="2" t="n">
-        <v>-55013</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>-53128</v>
-      </c>
-      <c r="S101" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-3.337</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-7859</v>
+      </c>
+      <c r="O103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="2" t="n">
+        <v>-50898</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>-48886</v>
+      </c>
+      <c r="S103" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
-      <c r="P103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="D105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D107" t="n">
         <v>2</v>
       </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="n">
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="n">
         <v>7.15</v>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="n">
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="n">
         <v>10.49</v>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="n">
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="n">
         <v>1</v>
       </c>
-      <c r="M105" t="n">
+      <c r="M107" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N105" t="n">
+      <c r="N107" t="n">
         <v>-27445</v>
       </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q105" t="n">
+      <c r="Q107" t="n">
         <v>1054</v>
       </c>
-      <c r="R105" t="n">
+      <c r="R107" t="n">
         <v>-53835</v>
       </c>
-      <c r="S105" t="n">
+      <c r="S107" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D106" s="2" t="n">
+      <c r="D108" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="n">
+      <c r="E108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="n">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="n">
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M106" s="2" t="n">
+      <c r="M108" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N106" s="2" t="n">
+      <c r="N108" s="2" t="n">
         <v>-27445</v>
       </c>
-      <c r="O106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" s="2" t="n">
+      <c r="O108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="2" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q106" s="2" t="n">
+      <c r="Q108" s="2" t="n">
         <v>1054</v>
       </c>
-      <c r="R106" s="2" t="n">
+      <c r="R108" s="2" t="n">
         <v>-53835</v>
       </c>
-      <c r="S106" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="S108" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="D110" t="n">
         <v>17</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E110" t="n">
         <v>52.9</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F110" t="n">
         <v>1.87</v>
       </c>
-      <c r="G108" t="n">
+      <c r="G110" t="n">
         <v>7.27</v>
       </c>
-      <c r="H108" t="n">
+      <c r="H110" t="n">
         <v>2.48</v>
       </c>
-      <c r="I108" t="n">
+      <c r="I110" t="n">
         <v>16.31</v>
       </c>
-      <c r="J108" t="n">
+      <c r="J110" t="n">
         <v>5.68</v>
       </c>
-      <c r="K108" t="n">
+      <c r="K110" t="n">
         <v>0.78</v>
       </c>
-      <c r="L108" t="n">
+      <c r="L110" t="n">
         <v>0.75</v>
       </c>
-      <c r="M108" t="n">
+      <c r="M110" t="n">
         <v>2.681</v>
       </c>
-      <c r="N108" t="n">
+      <c r="N110" t="n">
         <v>3410</v>
       </c>
-      <c r="O108" t="n">
+      <c r="O110" t="n">
         <v>2.11</v>
       </c>
-      <c r="P108" t="n">
+      <c r="P110" t="n">
         <v>134658</v>
       </c>
-      <c r="Q108" t="n">
+      <c r="Q110" t="n">
         <v>7271</v>
       </c>
-      <c r="R108" t="n">
+      <c r="R110" t="n">
         <v>141929</v>
       </c>
-      <c r="S108" t="n">
+      <c r="S110" t="n">
         <v>1373</v>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O109" s="2" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P109" s="2" t="n">
-        <v>134658</v>
-      </c>
-      <c r="Q109" s="2" t="n">
-        <v>7271</v>
-      </c>
-      <c r="R109" s="2" t="n">
-        <v>141929</v>
-      </c>
-      <c r="S109" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O111" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P111" s="2" t="n">
+        <v>135541</v>
+      </c>
+      <c r="Q111" s="2" t="n">
+        <v>7304</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>142845</v>
+      </c>
+      <c r="S111" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="2" t="inlineStr"/>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-      <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="2" t="inlineStr"/>
-      <c r="N111" s="2" t="inlineStr"/>
-      <c r="O111" s="2" t="inlineStr"/>
-      <c r="P111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="D113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D115" t="n">
         <v>1</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E115" t="n">
         <v>100</v>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="n">
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="n">
         <v>2.1</v>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="n">
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="n">
         <v>2.1</v>
       </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="n">
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="n">
         <v>52.73</v>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="n">
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="n">
         <v>2.102</v>
       </c>
-      <c r="N113" t="n">
+      <c r="N115" t="n">
         <v>2341</v>
       </c>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="n">
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="n">
         <v>2341</v>
       </c>
-      <c r="Q113" t="n">
+      <c r="Q115" t="n">
         <v>34</v>
       </c>
-      <c r="R113" t="n">
+      <c r="R115" t="n">
         <v>2375</v>
       </c>
-      <c r="S113" t="n">
+      <c r="S115" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E116" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="n">
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="2" t="n">
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="2" t="n">
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="n">
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N114" s="2" t="n">
+      <c r="N116" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O114" s="2" t="inlineStr"/>
-      <c r="P114" s="2" t="n">
+      <c r="O116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q114" s="2" t="n">
+      <c r="Q116" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R114" s="2" t="n">
+      <c r="R116" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S114" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>2</v>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="n">
-        <v>1</v>
-      </c>
-      <c r="M116" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N116" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>513</v>
-      </c>
-      <c r="R116" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S116" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>4</v>
-      </c>
-      <c r="E117" t="n">
-        <v>25</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G117" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I117" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J117" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K117" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M117" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N117" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P117" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R117" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S117" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S116" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5099,7 +5083,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -5113,33 +5097,33 @@
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>0.14</v>
+        <v>2.61</v>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="n">
-        <v>0.16</v>
+        <v>3.49</v>
       </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>-0.136</v>
+        <v>-2.607</v>
       </c>
       <c r="N118" t="n">
-        <v>-2389</v>
+        <v>-8011</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>-4777</v>
+        <v>-16021</v>
       </c>
       <c r="Q118" t="n">
-        <v>2924</v>
+        <v>513</v>
       </c>
       <c r="R118" t="n">
-        <v>-1854</v>
+        <v>-15508</v>
       </c>
       <c r="S118" t="n">
         <v>1415</v>
@@ -5158,43 +5142,53 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E119" t="n">
-        <v>100</v>
-      </c>
-      <c r="F119" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G119" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H119" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I119" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J119" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K119" t="n">
-        <v>14</v>
-      </c>
-      <c r="L119" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L119" t="n">
+        <v>5.67</v>
+      </c>
       <c r="M119" t="n">
-        <v>1.042</v>
+        <v>-0.217</v>
       </c>
       <c r="N119" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O119" t="inlineStr"/>
+        <v>-13272</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.02</v>
+      </c>
       <c r="P119" t="n">
-        <v>48540</v>
+        <v>-53089</v>
       </c>
       <c r="Q119" t="n">
-        <v>4254</v>
+        <v>5913</v>
       </c>
       <c r="R119" t="n">
-        <v>52794</v>
+        <v>-47176</v>
       </c>
       <c r="S119" t="n">
         <v>1415</v>
@@ -5213,11 +5207,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -5227,36 +5221,36 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
-        <v>4.67</v>
+        <v>5.5</v>
       </c>
       <c r="M120" t="n">
-        <v>-0.864</v>
+        <v>-0.136</v>
       </c>
       <c r="N120" t="n">
-        <v>-28997</v>
+        <v>-2389</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>-86990</v>
+        <v>-4777</v>
       </c>
       <c r="Q120" t="n">
-        <v>13787</v>
+        <v>2924</v>
       </c>
       <c r="R120" t="n">
-        <v>-73203</v>
+        <v>-1854</v>
       </c>
       <c r="S120" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="121">
@@ -5272,50 +5266,46 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="n">
-        <v>3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>14</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
       <c r="M121" t="n">
-        <v>-0.867</v>
+        <v>1.042</v>
       </c>
       <c r="N121" t="n">
-        <v>-29188</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>-29188</v>
+        <v>48540</v>
       </c>
       <c r="Q121" t="n">
-        <v>2950</v>
+        <v>4254</v>
       </c>
       <c r="R121" t="n">
-        <v>-26238</v>
+        <v>52794</v>
       </c>
       <c r="S121" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="122">
@@ -5331,11 +5321,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -5345,214 +5335,218 @@
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="n">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R122" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="n">
+        <v>3</v>
+      </c>
+      <c r="M123" t="n">
+        <v>-0.867</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>2950</v>
+      </c>
+      <c r="R123" t="n">
+        <v>-26238</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="n">
         <v>4</v>
       </c>
-      <c r="M122" t="n">
+      <c r="M124" t="n">
         <v>-0.918</v>
       </c>
-      <c r="N122" t="n">
+      <c r="N124" t="n">
         <v>-18456</v>
       </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
         <v>-68234</v>
       </c>
-      <c r="Q122" t="n">
+      <c r="Q124" t="n">
         <v>5788</v>
       </c>
-      <c r="R122" t="n">
+      <c r="R124" t="n">
         <v>-62446</v>
       </c>
-      <c r="S122" t="n">
+      <c r="S124" t="n">
         <v>1384</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D123" s="2" t="n">
+      <c r="D125" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E123" s="2" t="n">
+      <c r="E125" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="F123" s="2" t="n">
+      <c r="F125" s="2" t="n">
         <v>0.71</v>
       </c>
-      <c r="G123" s="2" t="n">
+      <c r="G125" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H123" s="2" t="n">
+      <c r="H125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I123" s="2" t="n">
+      <c r="I125" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J123" s="2" t="n">
+      <c r="J125" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K123" s="2" t="n">
+      <c r="K125" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L123" s="2" t="n">
+      <c r="L125" s="2" t="n">
         <v>4.23</v>
       </c>
-      <c r="M123" s="2" t="n">
+      <c r="M125" s="2" t="n">
         <v>-0.501</v>
       </c>
-      <c r="N123" s="2" t="n">
+      <c r="N125" s="2" t="n">
         <v>-10496</v>
       </c>
-      <c r="O123" s="2" t="n">
+      <c r="O125" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="P123" s="2" t="n">
+      <c r="P125" s="2" t="n">
         <v>-209759</v>
       </c>
-      <c r="Q123" s="2" t="n">
+      <c r="Q125" s="2" t="n">
         <v>36129</v>
       </c>
-      <c r="R123" s="2" t="n">
+      <c r="R125" s="2" t="n">
         <v>-173631</v>
       </c>
-      <c r="S123" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>9</v>
-      </c>
-      <c r="E125" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G125" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H125" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I125" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J125" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N125" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P125" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R125" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S125" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>2</v>
-      </c>
-      <c r="E126" t="n">
-        <v>100</v>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N126" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>667</v>
-      </c>
-      <c r="R126" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S126" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S125" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5567,228 +5561,222 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="inlineStr"/>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1.17</v>
+      </c>
       <c r="H127" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I127" t="inlineStr"/>
+        <v>4.19</v>
+      </c>
+      <c r="I127" t="n">
+        <v>3.38</v>
+      </c>
       <c r="J127" t="n">
-        <v>8.300000000000001</v>
+        <v>7.04</v>
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N127" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P127" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="n">
+        <v>100</v>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N128" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>667</v>
+      </c>
+      <c r="R128" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N127" t="n">
+      <c r="N129" t="n">
         <v>-74087</v>
       </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q127" t="n">
+      <c r="Q129" t="n">
         <v>257</v>
       </c>
-      <c r="R127" t="n">
+      <c r="R129" t="n">
         <v>-73830</v>
       </c>
-      <c r="S127" t="n">
+      <c r="S129" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D128" s="2" t="n">
+      <c r="D130" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E130" s="2" t="n">
         <v>58.3</v>
       </c>
-      <c r="F128" s="2" t="n">
+      <c r="F130" s="2" t="n">
         <v>0.91</v>
       </c>
-      <c r="G128" s="2" t="n">
+      <c r="G130" s="2" t="n">
         <v>3.28</v>
       </c>
-      <c r="H128" s="2" t="n">
+      <c r="H130" s="2" t="n">
         <v>5.02</v>
       </c>
-      <c r="I128" s="2" t="n">
+      <c r="I130" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J128" s="2" t="n">
+      <c r="J130" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="inlineStr"/>
-      <c r="M128" s="2" t="n">
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="n">
         <v>-0.175</v>
       </c>
-      <c r="N128" s="2" t="n">
+      <c r="N130" s="2" t="n">
         <v>2846</v>
       </c>
-      <c r="O128" s="2" t="n">
+      <c r="O130" s="2" t="n">
         <v>1.28</v>
       </c>
-      <c r="P128" s="2" t="n">
+      <c r="P130" s="2" t="n">
         <v>34154</v>
       </c>
-      <c r="Q128" s="2" t="n">
+      <c r="Q130" s="2" t="n">
         <v>3063</v>
       </c>
-      <c r="R128" s="2" t="n">
+      <c r="R130" s="2" t="n">
         <v>37217</v>
       </c>
-      <c r="S128" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>9</v>
-      </c>
-      <c r="E130" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G130" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H130" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I130" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J130" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K130" t="n">
-        <v>3</v>
-      </c>
-      <c r="L130" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M130" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N130" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O130" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P130" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R130" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S130" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>2</v>
-      </c>
-      <c r="E131" t="n">
-        <v>100</v>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N131" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>667</v>
-      </c>
-      <c r="R131" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S131" t="n">
-        <v>1411</v>
-      </c>
+      <c r="S130" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5803,119 +5791,176 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>9</v>
+      </c>
+      <c r="E132" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H132" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I132" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J132" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K132" t="n">
+        <v>3</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M132" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N132" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P132" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R132" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S132" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" t="n">
+        <v>100</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N133" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>667</v>
+      </c>
+      <c r="R133" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D132" t="n">
+      <c r="D134" t="n">
         <v>1</v>
       </c>
-      <c r="E132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="n">
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="n">
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="n">
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="n">
         <v>3</v>
       </c>
-      <c r="M132" t="n">
+      <c r="M134" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N134" t="n">
         <v>-74087</v>
       </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="n">
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q132" t="n">
+      <c r="Q134" t="n">
         <v>257</v>
       </c>
-      <c r="R132" t="n">
+      <c r="R134" t="n">
         <v>-73830</v>
       </c>
-      <c r="S132" t="n">
+      <c r="S134" t="n">
         <v>1373</v>
       </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K133" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M133" s="2" t="n">
-        <v>-0.175</v>
-      </c>
-      <c r="N133" s="2" t="n">
-        <v>2846</v>
-      </c>
-      <c r="O133" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P133" s="2" t="n">
-        <v>34154</v>
-      </c>
-      <c r="Q133" s="2" t="n">
-        <v>3063</v>
-      </c>
-      <c r="R133" s="2" t="n">
-        <v>37217</v>
-      </c>
-      <c r="S133" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -5929,39 +5974,61 @@
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-      <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="2" t="inlineStr"/>
-      <c r="M135" s="2" t="inlineStr"/>
-      <c r="N135" s="2" t="inlineStr"/>
-      <c r="O135" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>-0.175</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>2846</v>
+      </c>
+      <c r="O135" s="2" t="n">
+        <v>1.28</v>
+      </c>
       <c r="P135" s="2" t="n">
-        <v>0</v>
+        <v>34154</v>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>0</v>
+        <v>3063</v>
       </c>
       <c r="R135" s="2" t="n">
-        <v>0</v>
+        <v>37217</v>
       </c>
       <c r="S135" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -5994,6 +6061,47 @@
       </c>
       <c r="S137" s="2" t="inlineStr"/>
     </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr"/>
+      <c r="P139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S139"/>
+  <dimension ref="A1:S141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1255,20 +1255,20 @@
         <v>0.999</v>
       </c>
       <c r="N13" t="n">
-        <v>6878</v>
+        <v>6839</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>-11288</v>
+        <v>-11328</v>
       </c>
       <c r="Q13" t="n">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="R13" t="n">
-        <v>-10378</v>
+        <v>-10423</v>
       </c>
       <c r="S13" t="n">
-        <v>1384</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +1320,13 @@
         <v>0.99</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>53207</v>
+        <v>53167</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>53585</v>
+        <v>53581</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>106794</v>
+        <v>106749</v>
       </c>
       <c r="S14" s="2" t="inlineStr"/>
     </row>
@@ -4015,20 +4015,20 @@
         <v>0.999</v>
       </c>
       <c r="N86" t="n">
-        <v>6878</v>
+        <v>6839</v>
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>7070</v>
+        <v>7029</v>
       </c>
       <c r="Q86" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="R86" t="n">
-        <v>7557</v>
+        <v>7513</v>
       </c>
       <c r="S86" t="n">
-        <v>1384</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="87">
@@ -4078,19 +4078,19 @@
         <v>-1.498</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-5771</v>
+        <v>-5774</v>
       </c>
       <c r="O87" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>-54915</v>
+        <v>-54956</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>8328</v>
+        <v>8325</v>
       </c>
       <c r="R87" s="2" t="n">
-        <v>-46586</v>
+        <v>-46630</v>
       </c>
       <c r="S87" s="2" t="inlineStr"/>
     </row>
@@ -4394,13 +4394,13 @@
         <v>0.95</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>-8386</v>
+        <v>-8362</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="R97" s="2" t="n">
-        <v>-4741</v>
+        <v>-4718</v>
       </c>
       <c r="S97" s="2" t="inlineStr"/>
     </row>
@@ -4626,13 +4626,13 @@
         <v>0</v>
       </c>
       <c r="P103" s="2" t="n">
-        <v>-50898</v>
+        <v>-50922</v>
       </c>
       <c r="Q103" s="2" t="n">
         <v>2011</v>
       </c>
       <c r="R103" s="2" t="n">
-        <v>-48886</v>
+        <v>-48911</v>
       </c>
       <c r="S103" s="2" t="inlineStr"/>
     </row>
@@ -4911,13 +4911,13 @@
         <v>2.11</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>135541</v>
+        <v>135536</v>
       </c>
       <c r="Q111" s="2" t="n">
-        <v>7304</v>
+        <v>7303</v>
       </c>
       <c r="R111" s="2" t="n">
-        <v>142845</v>
+        <v>142839</v>
       </c>
       <c r="S111" s="2" t="inlineStr"/>
     </row>
@@ -5467,22 +5467,22 @@
         <v>-0.918</v>
       </c>
       <c r="N124" t="n">
-        <v>-18456</v>
+        <v>-18350</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>-68234</v>
+        <v>-67839</v>
       </c>
       <c r="Q124" t="n">
-        <v>5788</v>
+        <v>5754</v>
       </c>
       <c r="R124" t="n">
-        <v>-62446</v>
+        <v>-62085</v>
       </c>
       <c r="S124" t="n">
-        <v>1384</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="125">
@@ -5532,19 +5532,19 @@
         <v>-0.501</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-10496</v>
+        <v>-10484</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>-209759</v>
+        <v>-209364</v>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>36129</v>
+        <v>36095</v>
       </c>
       <c r="R125" s="2" t="n">
-        <v>-173631</v>
+        <v>-173270</v>
       </c>
       <c r="S125" s="2" t="inlineStr"/>
     </row>
@@ -5720,128 +5720,116 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>100</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N130" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>269</v>
+      </c>
+      <c r="R130" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D130" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H130" s="2" t="n">
+      <c r="D131" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H131" s="2" t="n">
         <v>5.02</v>
       </c>
-      <c r="I130" s="2" t="n">
+      <c r="I131" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J130" s="2" t="n">
+      <c r="J131" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="inlineStr"/>
-      <c r="M130" s="2" t="n">
-        <v>-0.175</v>
-      </c>
-      <c r="N130" s="2" t="n">
-        <v>2846</v>
-      </c>
-      <c r="O130" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P130" s="2" t="n">
-        <v>34154</v>
-      </c>
-      <c r="Q130" s="2" t="n">
-        <v>3063</v>
-      </c>
-      <c r="R130" s="2" t="n">
-        <v>37217</v>
-      </c>
-      <c r="S130" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>9</v>
-      </c>
-      <c r="E132" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G132" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H132" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I132" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J132" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K132" t="n">
-        <v>3</v>
-      </c>
-      <c r="L132" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M132" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N132" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O132" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P132" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R132" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S132" t="n">
-        <v>1415</v>
-      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>5349</v>
+      </c>
+      <c r="O131" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P131" s="2" t="n">
+        <v>69535</v>
+      </c>
+      <c r="Q131" s="2" t="n">
+        <v>3332</v>
+      </c>
+      <c r="R131" s="2" t="n">
+        <v>72867</v>
+      </c>
+      <c r="S131" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5856,46 +5844,56 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E133" t="n">
-        <v>100</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G133" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H133" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I133" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J133" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J133" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K133" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L133" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M133" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N133" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O133" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P133" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q133" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R133" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S133" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="134">
@@ -5911,119 +5909,166 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>2</v>
+      </c>
+      <c r="E134" t="n">
+        <v>100</v>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N134" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>667</v>
+      </c>
+      <c r="R134" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S134" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D134" t="n">
+      <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="n">
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="n">
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="n">
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="n">
         <v>3</v>
       </c>
-      <c r="M134" t="n">
+      <c r="M135" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N134" t="n">
+      <c r="N135" t="n">
         <v>-74087</v>
       </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q134" t="n">
+      <c r="Q135" t="n">
         <v>257</v>
       </c>
-      <c r="R134" t="n">
+      <c r="R135" t="n">
         <v>-73830</v>
       </c>
-      <c r="S134" t="n">
+      <c r="S135" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K135" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="L135" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M135" s="2" t="n">
-        <v>-0.175</v>
-      </c>
-      <c r="N135" s="2" t="n">
-        <v>2846</v>
-      </c>
-      <c r="O135" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P135" s="2" t="n">
-        <v>34154</v>
-      </c>
-      <c r="Q135" s="2" t="n">
-        <v>3063</v>
-      </c>
-      <c r="R135" s="2" t="n">
-        <v>37217</v>
-      </c>
-      <c r="S135" s="2" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>100</v>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N136" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>269</v>
+      </c>
+      <c r="R136" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1376</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>미국수동</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6037,39 +6082,61 @@
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr"/>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-      <c r="K137" s="2" t="inlineStr"/>
-      <c r="L137" s="2" t="inlineStr"/>
-      <c r="M137" s="2" t="inlineStr"/>
-      <c r="N137" s="2" t="inlineStr"/>
-      <c r="O137" s="2" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>5349</v>
+      </c>
+      <c r="O137" s="2" t="n">
+        <v>1.57</v>
+      </c>
       <c r="P137" s="2" t="n">
-        <v>0</v>
+        <v>69535</v>
       </c>
       <c r="Q137" s="2" t="n">
-        <v>0</v>
+        <v>3332</v>
       </c>
       <c r="R137" s="2" t="n">
-        <v>0</v>
+        <v>72867</v>
       </c>
       <c r="S137" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>기타(8042)</t>
+          <t>미국수동</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -6102,6 +6169,47 @@
       </c>
       <c r="S139" s="2" t="inlineStr"/>
     </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr"/>
+      <c r="P141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1255,20 +1255,20 @@
         <v>0.999</v>
       </c>
       <c r="N13" t="n">
-        <v>6839</v>
+        <v>6873</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>-11328</v>
+        <v>-13285</v>
       </c>
       <c r="Q13" t="n">
-        <v>905</v>
+        <v>1166</v>
       </c>
       <c r="R13" t="n">
-        <v>-10423</v>
+        <v>-12120</v>
       </c>
       <c r="S13" t="n">
-        <v>1376</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +1320,13 @@
         <v>0.99</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>53167</v>
+        <v>51210</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>53581</v>
+        <v>53842</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>106749</v>
+        <v>105052</v>
       </c>
       <c r="S14" s="2" t="inlineStr"/>
     </row>
@@ -4015,20 +4015,20 @@
         <v>0.999</v>
       </c>
       <c r="N86" t="n">
-        <v>6839</v>
+        <v>6873</v>
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>7029</v>
+        <v>7065</v>
       </c>
       <c r="Q86" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="R86" t="n">
-        <v>7513</v>
+        <v>7551</v>
       </c>
       <c r="S86" t="n">
-        <v>1376</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="87">
@@ -4078,19 +4078,19 @@
         <v>-1.498</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-5774</v>
+        <v>-5771</v>
       </c>
       <c r="O87" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>-54956</v>
+        <v>-54920</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>8325</v>
+        <v>8328</v>
       </c>
       <c r="R87" s="2" t="n">
-        <v>-46630</v>
+        <v>-46592</v>
       </c>
       <c r="S87" s="2" t="inlineStr"/>
     </row>
@@ -4394,13 +4394,13 @@
         <v>0.95</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>-8362</v>
+        <v>-12276</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>3643</v>
+        <v>3775</v>
       </c>
       <c r="R97" s="2" t="n">
-        <v>-4718</v>
+        <v>-8500</v>
       </c>
       <c r="S97" s="2" t="inlineStr"/>
     </row>
@@ -4626,13 +4626,13 @@
         <v>0</v>
       </c>
       <c r="P103" s="2" t="n">
-        <v>-50922</v>
+        <v>-49001</v>
       </c>
       <c r="Q103" s="2" t="n">
-        <v>2011</v>
+        <v>2137</v>
       </c>
       <c r="R103" s="2" t="n">
-        <v>-48911</v>
+        <v>-46863</v>
       </c>
       <c r="S103" s="2" t="inlineStr"/>
     </row>
@@ -4911,13 +4911,13 @@
         <v>2.11</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>135536</v>
+        <v>150584</v>
       </c>
       <c r="Q111" s="2" t="n">
-        <v>7303</v>
+        <v>7472</v>
       </c>
       <c r="R111" s="2" t="n">
-        <v>142839</v>
+        <v>158057</v>
       </c>
       <c r="S111" s="2" t="inlineStr"/>
     </row>
@@ -5467,22 +5467,22 @@
         <v>-0.918</v>
       </c>
       <c r="N124" t="n">
-        <v>-18350</v>
+        <v>-18443</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>-67839</v>
+        <v>-68185</v>
       </c>
       <c r="Q124" t="n">
-        <v>5754</v>
+        <v>5784</v>
       </c>
       <c r="R124" t="n">
-        <v>-62085</v>
+        <v>-62401</v>
       </c>
       <c r="S124" t="n">
-        <v>1376</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="125">
@@ -5532,19 +5532,19 @@
         <v>-0.501</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-10484</v>
+        <v>-10495</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>-209364</v>
+        <v>-209710</v>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>36095</v>
+        <v>36125</v>
       </c>
       <c r="R125" s="2" t="n">
-        <v>-173270</v>
+        <v>-173586</v>
       </c>
       <c r="S125" s="2" t="inlineStr"/>
     </row>
@@ -5769,7 +5769,7 @@
         <v>35650</v>
       </c>
       <c r="S130" t="n">
-        <v>1376</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="131">
@@ -6062,7 +6062,7 @@
         <v>35650</v>
       </c>
       <c r="S136" t="n">
-        <v>1376</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="137">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1255,20 +1255,20 @@
         <v>0.999</v>
       </c>
       <c r="N13" t="n">
-        <v>6873</v>
+        <v>6883</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>-13285</v>
+        <v>-13278</v>
       </c>
       <c r="Q13" t="n">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="R13" t="n">
-        <v>-12120</v>
+        <v>-12111</v>
       </c>
       <c r="S13" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +1320,13 @@
         <v>0.99</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>51210</v>
+        <v>51217</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>53842</v>
+        <v>53843</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>105052</v>
+        <v>105061</v>
       </c>
       <c r="S14" s="2" t="inlineStr"/>
     </row>
@@ -4015,20 +4015,20 @@
         <v>0.999</v>
       </c>
       <c r="N86" t="n">
-        <v>6873</v>
+        <v>6883</v>
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>7065</v>
+        <v>7075</v>
       </c>
       <c r="Q86" t="n">
         <v>487</v>
       </c>
       <c r="R86" t="n">
-        <v>7551</v>
+        <v>7562</v>
       </c>
       <c r="S86" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="87">
@@ -4078,19 +4078,19 @@
         <v>-1.498</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-5771</v>
+        <v>-5770</v>
       </c>
       <c r="O87" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>-54920</v>
+        <v>-54910</v>
       </c>
       <c r="Q87" s="2" t="n">
         <v>8328</v>
       </c>
       <c r="R87" s="2" t="n">
-        <v>-46592</v>
+        <v>-46581</v>
       </c>
       <c r="S87" s="2" t="inlineStr"/>
     </row>
@@ -4394,13 +4394,13 @@
         <v>0.95</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>-12276</v>
+        <v>-12288</v>
       </c>
       <c r="Q97" s="2" t="n">
         <v>3775</v>
       </c>
       <c r="R97" s="2" t="n">
-        <v>-8500</v>
+        <v>-8511</v>
       </c>
       <c r="S97" s="2" t="inlineStr"/>
     </row>
@@ -4626,13 +4626,13 @@
         <v>0</v>
       </c>
       <c r="P103" s="2" t="n">
-        <v>-49001</v>
+        <v>-48992</v>
       </c>
       <c r="Q103" s="2" t="n">
         <v>2137</v>
       </c>
       <c r="R103" s="2" t="n">
-        <v>-46863</v>
+        <v>-46854</v>
       </c>
       <c r="S103" s="2" t="inlineStr"/>
     </row>
@@ -4911,13 +4911,13 @@
         <v>2.11</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>150584</v>
+        <v>150607</v>
       </c>
       <c r="Q111" s="2" t="n">
-        <v>7472</v>
+        <v>7473</v>
       </c>
       <c r="R111" s="2" t="n">
-        <v>158057</v>
+        <v>158080</v>
       </c>
       <c r="S111" s="2" t="inlineStr"/>
     </row>
@@ -5467,22 +5467,22 @@
         <v>-0.918</v>
       </c>
       <c r="N124" t="n">
-        <v>-18443</v>
+        <v>-18470</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>-68185</v>
+        <v>-68283</v>
       </c>
       <c r="Q124" t="n">
-        <v>5784</v>
+        <v>5792</v>
       </c>
       <c r="R124" t="n">
-        <v>-62401</v>
+        <v>-62491</v>
       </c>
       <c r="S124" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="125">
@@ -5532,19 +5532,19 @@
         <v>-0.501</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-10495</v>
+        <v>-10498</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>-209710</v>
+        <v>-209808</v>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>36125</v>
+        <v>36133</v>
       </c>
       <c r="R125" s="2" t="n">
-        <v>-173586</v>
+        <v>-173676</v>
       </c>
       <c r="S125" s="2" t="inlineStr"/>
     </row>
@@ -5769,7 +5769,7 @@
         <v>35650</v>
       </c>
       <c r="S130" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="131">
@@ -6062,7 +6062,7 @@
         <v>35650</v>
       </c>
       <c r="S136" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="137">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S141"/>
+  <dimension ref="A1:S144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1235,37 +1235,45 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>71.40000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>4.63</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.18</v>
+      </c>
       <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
+        <v>11.98</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6.38</v>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>0.999</v>
+        <v>2.11</v>
       </c>
       <c r="N13" t="n">
-        <v>6883</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
+        <v>-40119</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.18</v>
+      </c>
       <c r="P13" t="n">
-        <v>-13278</v>
+        <v>-348589</v>
       </c>
       <c r="Q13" t="n">
-        <v>1167</v>
+        <v>11163</v>
       </c>
       <c r="R13" t="n">
-        <v>-12111</v>
+        <v>-337427</v>
       </c>
       <c r="S13" t="n">
         <v>1385</v>
@@ -1288,19 +1296,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>37.2</v>
+        <v>37.8</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>19.29</v>
@@ -1311,22 +1319,22 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="n">
-        <v>-0.119</v>
+        <v>-0.063</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-39</v>
+        <v>-1149</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>51217</v>
+        <v>-284094</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>53843</v>
+        <v>63839</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>105061</v>
+        <v>-220255</v>
       </c>
       <c r="S14" s="2" t="inlineStr"/>
     </row>
@@ -3993,39 +4001,49 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>100</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.09</v>
+      </c>
       <c r="G86" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>2.69</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4.18</v>
+      </c>
       <c r="I86" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" t="inlineStr"/>
+        <v>4.37</v>
+      </c>
+      <c r="J86" t="n">
+        <v>6.38</v>
+      </c>
       <c r="K86" t="n">
-        <v>14</v>
-      </c>
-      <c r="L86" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="L86" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M86" t="n">
-        <v>0.999</v>
+        <v>-0.747</v>
       </c>
       <c r="N86" t="n">
-        <v>6883</v>
-      </c>
-      <c r="O86" t="inlineStr"/>
+        <v>-77911</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.09</v>
+      </c>
       <c r="P86" t="n">
-        <v>7075</v>
+        <v>-342796</v>
       </c>
       <c r="Q86" t="n">
-        <v>487</v>
+        <v>9226</v>
       </c>
       <c r="R86" t="n">
-        <v>7562</v>
+        <v>-333570</v>
       </c>
       <c r="S86" t="n">
         <v>1385</v>
@@ -4048,19 +4066,19 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>5.23</v>
+        <v>4.97</v>
       </c>
       <c r="I87" s="2" t="n">
         <v>7.7</v>
@@ -4069,28 +4087,28 @@
         <v>10.01</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>14.17</v>
+        <v>15.29</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>5.17</v>
+        <v>5.75</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>-1.498</v>
+        <v>-1.464</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-5770</v>
+        <v>-25851</v>
       </c>
       <c r="O87" s="2" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>-54910</v>
+        <v>-404781</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>8328</v>
+        <v>17067</v>
       </c>
       <c r="R87" s="2" t="n">
-        <v>-46581</v>
+        <v>-387713</v>
       </c>
       <c r="S87" s="2" t="inlineStr"/>
     </row>
@@ -4342,690 +4360,765 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>100</v>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>22</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="n">
+        <v>11.981</v>
+      </c>
+      <c r="N97" t="n">
+        <v>20295</v>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="n">
+        <v>-1238</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>469</v>
+      </c>
+      <c r="R97" t="n">
+        <v>-769</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D97" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="H97" s="2" t="n">
+      <c r="D98" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="H98" s="2" t="n">
         <v>3.88</v>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="J97" s="2" t="n">
+      <c r="I98" s="2" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="J98" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="K97" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="L97" s="2" t="n">
+      <c r="K98" s="2" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="L98" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="M97" s="2" t="n">
-        <v>-0.891</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>-232</v>
-      </c>
-      <c r="O97" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="P97" s="2" t="n">
-        <v>-12288</v>
-      </c>
-      <c r="Q97" s="2" t="n">
-        <v>3775</v>
-      </c>
-      <c r="R97" s="2" t="n">
-        <v>-8511</v>
-      </c>
-      <c r="S97" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="M98" s="2" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>3189</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>-5378</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>3915</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>-1462</v>
+      </c>
+      <c r="S98" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D100" t="n">
         <v>1</v>
       </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="n">
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="n">
         <v>2.13</v>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="n">
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="n">
         <v>2.13</v>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="n">
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="n">
         <v>1</v>
       </c>
-      <c r="M99" t="n">
+      <c r="M100" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N99" t="n">
+      <c r="N100" t="n">
         <v>-41586</v>
       </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q99" t="n">
+      <c r="Q100" t="n">
         <v>2702</v>
       </c>
-      <c r="R99" t="n">
+      <c r="R100" t="n">
         <v>-38883</v>
       </c>
-      <c r="S99" t="n">
+      <c r="S100" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n">
+      <c r="D101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="n">
+      <c r="E101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="n">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="n">
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M100" s="2" t="n">
+      <c r="M101" s="2" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N100" s="2" t="n">
+      <c r="N101" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="O100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="2" t="n">
+      <c r="O101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q100" s="2" t="n">
+      <c r="Q101" s="2" t="n">
         <v>2702</v>
       </c>
-      <c r="R100" s="2" t="n">
+      <c r="R101" s="2" t="n">
         <v>-38883</v>
       </c>
-      <c r="S100" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="S101" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D103" t="n">
         <v>7</v>
       </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="n">
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="n">
         <v>3.34</v>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="n">
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="n">
         <v>6.17</v>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="n">
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="n">
         <v>8</v>
       </c>
-      <c r="M102" t="n">
+      <c r="M103" t="n">
         <v>-3.337</v>
       </c>
-      <c r="N102" t="n">
+      <c r="N103" t="n">
         <v>-7859</v>
       </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
         <v>-55013</v>
       </c>
-      <c r="Q102" t="n">
+      <c r="Q103" t="n">
         <v>1884</v>
       </c>
-      <c r="R102" t="n">
+      <c r="R103" t="n">
         <v>-53128</v>
       </c>
-      <c r="S102" t="n">
+      <c r="S103" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N103" s="2" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" s="2" t="n">
-        <v>-48992</v>
-      </c>
-      <c r="Q103" s="2" t="n">
-        <v>2137</v>
-      </c>
-      <c r="R103" s="2" t="n">
-        <v>-46854</v>
-      </c>
-      <c r="S103" s="2" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" t="n">
+        <v>100</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>18</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="n">
+        <v>2.888</v>
+      </c>
+      <c r="N104" t="n">
+        <v>5258</v>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="n">
+        <v>13670</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1371</v>
+      </c>
+      <c r="R104" t="n">
+        <v>15041</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1385</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1.953</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-4944</v>
+      </c>
+      <c r="O105" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P105" s="2" t="n">
+        <v>-41343</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>3255</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>-38087</v>
+      </c>
+      <c r="S105" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
           <t>US_TR_ADD1</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr"/>
-      <c r="O105" s="2" t="inlineStr"/>
-      <c r="P105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="D107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D109" t="n">
         <v>2</v>
       </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="n">
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="n">
         <v>7.15</v>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="n">
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="n">
         <v>10.49</v>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="n">
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="n">
         <v>1</v>
       </c>
-      <c r="M107" t="n">
+      <c r="M109" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N107" t="n">
+      <c r="N109" t="n">
         <v>-27445</v>
       </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q107" t="n">
+      <c r="Q109" t="n">
         <v>1054</v>
       </c>
-      <c r="R107" t="n">
+      <c r="R109" t="n">
         <v>-53835</v>
       </c>
-      <c r="S107" t="n">
+      <c r="S109" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>US_TR_LEGACY</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n">
+      <c r="D110" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="n">
+      <c r="E110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="n">
         <v>7.15</v>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="n">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="n">
         <v>10.49</v>
       </c>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="n">
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M108" s="2" t="n">
+      <c r="M110" s="2" t="n">
         <v>-7.145</v>
       </c>
-      <c r="N108" s="2" t="n">
+      <c r="N110" s="2" t="n">
         <v>-27445</v>
       </c>
-      <c r="O108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" s="2" t="n">
+      <c r="O110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="2" t="n">
         <v>-54889</v>
       </c>
-      <c r="Q108" s="2" t="n">
+      <c r="Q110" s="2" t="n">
         <v>1054</v>
       </c>
-      <c r="R108" s="2" t="n">
+      <c r="R110" s="2" t="n">
         <v>-53835</v>
       </c>
-      <c r="S108" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="S110" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D110" t="n">
+      <c r="D112" t="n">
         <v>17</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E112" t="n">
         <v>52.9</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F112" t="n">
         <v>1.87</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G112" t="n">
         <v>7.27</v>
       </c>
-      <c r="H110" t="n">
+      <c r="H112" t="n">
         <v>2.48</v>
       </c>
-      <c r="I110" t="n">
+      <c r="I112" t="n">
         <v>16.31</v>
       </c>
-      <c r="J110" t="n">
+      <c r="J112" t="n">
         <v>5.68</v>
       </c>
-      <c r="K110" t="n">
+      <c r="K112" t="n">
         <v>0.78</v>
       </c>
-      <c r="L110" t="n">
+      <c r="L112" t="n">
         <v>0.75</v>
       </c>
-      <c r="M110" t="n">
+      <c r="M112" t="n">
         <v>2.681</v>
       </c>
-      <c r="N110" t="n">
+      <c r="N112" t="n">
         <v>3410</v>
       </c>
-      <c r="O110" t="n">
+      <c r="O112" t="n">
         <v>2.11</v>
       </c>
-      <c r="P110" t="n">
+      <c r="P112" t="n">
         <v>134658</v>
       </c>
-      <c r="Q110" t="n">
+      <c r="Q112" t="n">
         <v>7271</v>
       </c>
-      <c r="R110" t="n">
+      <c r="R112" t="n">
         <v>141929</v>
       </c>
-      <c r="S110" t="n">
+      <c r="S112" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" t="n">
+        <v>100</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>9</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>4.703</v>
+      </c>
+      <c r="N113" t="n">
+        <v>13940</v>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="n">
+        <v>37139</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>981</v>
+      </c>
+      <c r="R113" t="n">
+        <v>38121</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H111" s="2" t="n">
+      <c r="D114" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="H114" s="2" t="n">
         <v>2.48</v>
       </c>
-      <c r="I111" s="2" t="n">
+      <c r="I114" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J111" s="2" t="n">
+      <c r="J114" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K111" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L111" s="2" t="n">
+      <c r="K114" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="L114" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="M111" s="2" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O111" s="2" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P111" s="2" t="n">
-        <v>150607</v>
-      </c>
-      <c r="Q111" s="2" t="n">
-        <v>7473</v>
-      </c>
-      <c r="R111" s="2" t="n">
-        <v>158080</v>
-      </c>
-      <c r="S111" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_LOW</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="2" t="inlineStr"/>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-      <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="inlineStr"/>
-      <c r="N113" s="2" t="inlineStr"/>
-      <c r="O113" s="2" t="inlineStr"/>
-      <c r="P113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" t="n">
-        <v>100</v>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N115" t="n">
-        <v>2341</v>
-      </c>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="n">
-        <v>2341</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>34</v>
-      </c>
-      <c r="R115" t="n">
-        <v>2375</v>
-      </c>
-      <c r="S115" t="n">
-        <v>1373</v>
-      </c>
+      <c r="M114" s="2" t="n">
+        <v>2.984</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>4990</v>
+      </c>
+      <c r="O114" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P114" s="2" t="n">
+        <v>171797</v>
+      </c>
+      <c r="Q114" s="2" t="n">
+        <v>8252</v>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>180050</v>
+      </c>
+      <c r="S114" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>저점사다리</t>
+          <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5034,224 +5127,137 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="n">
-        <v>52.73</v>
-      </c>
+      <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N116" s="2" t="n">
-        <v>2341</v>
-      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr"/>
       <c r="P116" s="2" t="n">
-        <v>2341</v>
+        <v>0</v>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R116" s="2" t="n">
-        <v>2375</v>
+        <v>0</v>
       </c>
       <c r="S116" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>저점사다리</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="n">
+        <v>100</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N118" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>34</v>
+      </c>
+      <c r="R118" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M118" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N118" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>513</v>
-      </c>
-      <c r="R118" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S118" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>07/20~07/24</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>4</v>
-      </c>
-      <c r="E119" t="n">
-        <v>25</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G119" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I119" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J119" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K119" t="n">
-        <v>1</v>
-      </c>
-      <c r="L119" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M119" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N119" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P119" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R119" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S119" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>2</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M120" t="n">
-        <v>-0.136</v>
-      </c>
-      <c r="N120" t="n">
-        <v>-2389</v>
-      </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>-4777</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>2924</v>
-      </c>
-      <c r="R120" t="n">
-        <v>-1854</v>
-      </c>
-      <c r="S120" t="n">
-        <v>1415</v>
-      </c>
+      <c r="E119" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q119" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="R119" s="2" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S119" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5266,43 +5272,47 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>100</v>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="n">
-        <v>14</v>
-      </c>
-      <c r="L121" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
+        <v>1</v>
+      </c>
       <c r="M121" t="n">
-        <v>1.042</v>
+        <v>-2.607</v>
       </c>
       <c r="N121" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O121" t="inlineStr"/>
+        <v>-8011</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
       <c r="P121" t="n">
-        <v>48540</v>
+        <v>-16021</v>
       </c>
       <c r="Q121" t="n">
-        <v>4254</v>
+        <v>513</v>
       </c>
       <c r="R121" t="n">
-        <v>52794</v>
+        <v>-15508</v>
       </c>
       <c r="S121" t="n">
         <v>1415</v>
@@ -5321,50 +5331,56 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H122" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I122" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J122" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K122" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1</v>
+      </c>
       <c r="L122" t="n">
-        <v>4.67</v>
+        <v>5.67</v>
       </c>
       <c r="M122" t="n">
-        <v>-0.864</v>
+        <v>-0.217</v>
       </c>
       <c r="N122" t="n">
-        <v>-28997</v>
+        <v>-13272</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P122" t="n">
-        <v>-86990</v>
+        <v>-53089</v>
       </c>
       <c r="Q122" t="n">
-        <v>13787</v>
+        <v>5913</v>
       </c>
       <c r="R122" t="n">
-        <v>-73203</v>
+        <v>-47176</v>
       </c>
       <c r="S122" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="123">
@@ -5380,11 +5396,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -5394,36 +5410,36 @@
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>0.87</v>
+        <v>0.14</v>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
-        <v>0.87</v>
+        <v>0.16</v>
       </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.867</v>
+        <v>-0.136</v>
       </c>
       <c r="N123" t="n">
-        <v>-29188</v>
+        <v>-2389</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>-29188</v>
+        <v>-4777</v>
       </c>
       <c r="Q123" t="n">
-        <v>2950</v>
+        <v>2924</v>
       </c>
       <c r="R123" t="n">
-        <v>-26238</v>
+        <v>-1854</v>
       </c>
       <c r="S123" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="124">
@@ -5439,285 +5455,287 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="n">
-        <v>4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="n">
+        <v>14</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="n">
-        <v>-0.918</v>
+        <v>1.042</v>
       </c>
       <c r="N124" t="n">
-        <v>-18470</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
-        <v>-68283</v>
+        <v>48540</v>
       </c>
       <c r="Q124" t="n">
-        <v>5792</v>
+        <v>4254</v>
       </c>
       <c r="R124" t="n">
-        <v>-62491</v>
+        <v>52794</v>
       </c>
       <c r="S124" t="n">
-        <v>1385</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H125" s="2" t="n">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M125" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R125" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="I125" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-0.501</v>
-      </c>
-      <c r="N125" s="2" t="n">
-        <v>-10498</v>
-      </c>
-      <c r="O125" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="P125" s="2" t="n">
-        <v>-209808</v>
-      </c>
-      <c r="Q125" s="2" t="n">
-        <v>36133</v>
-      </c>
-      <c r="R125" s="2" t="n">
-        <v>-173676</v>
-      </c>
-      <c r="S125" s="2" t="inlineStr"/>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="n">
+        <v>3</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.867</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>2950</v>
+      </c>
+      <c r="R126" t="n">
+        <v>-26238</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1373</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G127" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I127" t="n">
-        <v>3.38</v>
-      </c>
+        <v>0.92</v>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="n">
-        <v>7.04</v>
+        <v>1.07</v>
       </c>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
+      <c r="L127" t="n">
+        <v>4</v>
+      </c>
       <c r="M127" t="n">
-        <v>-1.213</v>
+        <v>-0.918</v>
       </c>
       <c r="N127" t="n">
-        <v>-744</v>
+        <v>-18470</v>
       </c>
       <c r="O127" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>-6692</v>
+        <v>-68283</v>
       </c>
       <c r="Q127" t="n">
-        <v>2139</v>
+        <v>5792</v>
       </c>
       <c r="R127" t="n">
-        <v>-4553</v>
+        <v>-62491</v>
       </c>
       <c r="S127" t="n">
-        <v>1415</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>2</v>
-      </c>
-      <c r="E128" t="n">
-        <v>100</v>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N128" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>667</v>
-      </c>
-      <c r="R128" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S128" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N129" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>257</v>
-      </c>
-      <c r="R129" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S129" t="n">
-        <v>1373</v>
-      </c>
+      <c r="I128" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-0.501</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>-10498</v>
+      </c>
+      <c r="O128" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P128" s="2" t="n">
+        <v>-209808</v>
+      </c>
+      <c r="Q128" s="2" t="n">
+        <v>36133</v>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>-173676</v>
+      </c>
+      <c r="S128" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5732,283 +5750,275 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E130" t="n">
-        <v>100</v>
-      </c>
-      <c r="F130" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G130" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H130" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H130" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I130" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J130" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J130" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="n">
-        <v>4.029</v>
+        <v>-1.213</v>
       </c>
       <c r="N130" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O130" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P130" t="n">
-        <v>35381</v>
+        <v>-6692</v>
       </c>
       <c r="Q130" t="n">
-        <v>269</v>
+        <v>2139</v>
       </c>
       <c r="R130" t="n">
-        <v>35650</v>
+        <v>-4553</v>
       </c>
       <c r="S130" t="n">
-        <v>1385</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="A131" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E131" s="2" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I131" s="2" t="n">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" t="n">
+        <v>100</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="n">
         <v>12.69</v>
       </c>
-      <c r="J131" s="2" t="n">
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N131" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>667</v>
+      </c>
+      <c r="R131" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S131" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K131" s="2" t="inlineStr"/>
-      <c r="L131" s="2" t="inlineStr"/>
-      <c r="M131" s="2" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="N131" s="2" t="n">
-        <v>5349</v>
-      </c>
-      <c r="O131" s="2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P131" s="2" t="n">
-        <v>69535</v>
-      </c>
-      <c r="Q131" s="2" t="n">
-        <v>3332</v>
-      </c>
-      <c r="R131" s="2" t="n">
-        <v>72867</v>
-      </c>
-      <c r="S131" s="2" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N132" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>257</v>
+      </c>
+      <c r="R132" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S132" t="n">
+        <v>1373</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H133" t="n">
-        <v>4.19</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N133" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>269</v>
+      </c>
+      <c r="R133" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G134" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="J133" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K133" t="n">
-        <v>3</v>
-      </c>
-      <c r="L133" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M133" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N133" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P133" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R133" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S133" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>2</v>
-      </c>
-      <c r="E134" t="n">
-        <v>100</v>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="n">
+      <c r="H134" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I134" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N134" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>667</v>
-      </c>
-      <c r="R134" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S134" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="n">
+      <c r="J134" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="n">
-        <v>3</v>
-      </c>
-      <c r="M135" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N135" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>257</v>
-      </c>
-      <c r="R135" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S135" t="n">
-        <v>1373</v>
-      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>5349</v>
+      </c>
+      <c r="O134" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P134" s="2" t="n">
+        <v>69535</v>
+      </c>
+      <c r="Q134" s="2" t="n">
+        <v>3332</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>72867</v>
+      </c>
+      <c r="S134" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6023,192 +6033,371 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>9</v>
+      </c>
+      <c r="E136" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H136" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I136" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J136" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="n">
+        <v>100</v>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N137" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>667</v>
+      </c>
+      <c r="R137" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="n">
+        <v>3</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>257</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D136" t="n">
+      <c r="D139" t="n">
         <v>1</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E139" t="n">
         <v>100</v>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="n">
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="n">
         <v>4.03</v>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="n">
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="n">
         <v>4.03</v>
       </c>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="n">
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="n">
         <v>1</v>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="n">
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="n">
         <v>4.029</v>
       </c>
-      <c r="N136" t="n">
+      <c r="N139" t="n">
         <v>35381</v>
       </c>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="n">
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="n">
         <v>35381</v>
       </c>
-      <c r="Q136" t="n">
+      <c r="Q139" t="n">
         <v>269</v>
       </c>
-      <c r="R136" t="n">
+      <c r="R139" t="n">
         <v>35650</v>
       </c>
-      <c r="S136" t="n">
+      <c r="S139" t="n">
         <v>1385</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D137" s="2" t="n">
+      <c r="D140" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E137" s="2" t="n">
+      <c r="E140" s="2" t="n">
         <v>61.5</v>
       </c>
-      <c r="F137" s="2" t="n">
+      <c r="F140" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="G137" s="2" t="n">
+      <c r="G140" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H137" s="2" t="n">
+      <c r="H140" s="2" t="n">
         <v>5.02</v>
       </c>
-      <c r="I137" s="2" t="n">
+      <c r="I140" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J137" s="2" t="n">
+      <c r="J140" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K137" s="2" t="n">
+      <c r="K140" s="2" t="n">
         <v>3.12</v>
       </c>
-      <c r="L137" s="2" t="n">
+      <c r="L140" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M137" s="2" t="n">
+      <c r="M140" s="2" t="n">
         <v>0.148</v>
       </c>
-      <c r="N137" s="2" t="n">
+      <c r="N140" s="2" t="n">
         <v>5349</v>
       </c>
-      <c r="O137" s="2" t="n">
+      <c r="O140" s="2" t="n">
         <v>1.57</v>
       </c>
-      <c r="P137" s="2" t="n">
+      <c r="P140" s="2" t="n">
         <v>69535</v>
       </c>
-      <c r="Q137" s="2" t="n">
+      <c r="Q140" s="2" t="n">
         <v>3332</v>
       </c>
-      <c r="R137" s="2" t="n">
+      <c r="R140" s="2" t="n">
         <v>72867</v>
       </c>
-      <c r="S137" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="S140" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-      <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="2" t="inlineStr"/>
-      <c r="M139" s="2" t="inlineStr"/>
-      <c r="N139" s="2" t="inlineStr"/>
-      <c r="O139" s="2" t="inlineStr"/>
-      <c r="P139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="D142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr"/>
+      <c r="P142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" s="2" t="inlineStr"/>
-      <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-      <c r="K141" s="2" t="inlineStr"/>
-      <c r="L141" s="2" t="inlineStr"/>
-      <c r="M141" s="2" t="inlineStr"/>
-      <c r="N141" s="2" t="inlineStr"/>
-      <c r="O141" s="2" t="inlineStr"/>
-      <c r="P141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" s="2" t="inlineStr"/>
+      <c r="D144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr"/>
+      <c r="O144" s="2" t="inlineStr"/>
+      <c r="P144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -1261,22 +1261,22 @@
         <v>2.11</v>
       </c>
       <c r="N13" t="n">
-        <v>-40119</v>
+        <v>-40061</v>
       </c>
       <c r="O13" t="n">
         <v>0.18</v>
       </c>
       <c r="P13" t="n">
-        <v>-348589</v>
+        <v>-348112</v>
       </c>
       <c r="Q13" t="n">
-        <v>11163</v>
+        <v>11147</v>
       </c>
       <c r="R13" t="n">
-        <v>-337427</v>
+        <v>-336965</v>
       </c>
       <c r="S13" t="n">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="14">
@@ -1322,19 +1322,19 @@
         <v>-0.063</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1149</v>
+        <v>-1148</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>0.85</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>-284094</v>
+        <v>-283617</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>63839</v>
+        <v>63823</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>-220255</v>
+        <v>-219793</v>
       </c>
       <c r="S14" s="2" t="inlineStr"/>
     </row>
@@ -4031,22 +4031,22 @@
         <v>-0.747</v>
       </c>
       <c r="N86" t="n">
-        <v>-77911</v>
+        <v>-77799</v>
       </c>
       <c r="O86" t="n">
         <v>0.09</v>
       </c>
       <c r="P86" t="n">
-        <v>-342796</v>
+        <v>-342301</v>
       </c>
       <c r="Q86" t="n">
-        <v>9226</v>
+        <v>9212</v>
       </c>
       <c r="R86" t="n">
-        <v>-333570</v>
+        <v>-333089</v>
       </c>
       <c r="S86" t="n">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="87">
@@ -4096,19 +4096,19 @@
         <v>-1.464</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-25851</v>
+        <v>-25821</v>
       </c>
       <c r="O87" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>-404781</v>
+        <v>-404286</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>17067</v>
+        <v>17053</v>
       </c>
       <c r="R87" s="2" t="n">
-        <v>-387713</v>
+        <v>-387232</v>
       </c>
       <c r="S87" s="2" t="inlineStr"/>
     </row>
@@ -4398,20 +4398,20 @@
         <v>11.981</v>
       </c>
       <c r="N97" t="n">
-        <v>20295</v>
+        <v>20266</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
-        <v>-1238</v>
+        <v>-1236</v>
       </c>
       <c r="Q97" t="n">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R97" t="n">
-        <v>-769</v>
+        <v>-768</v>
       </c>
       <c r="S97" t="n">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="98">
@@ -4461,19 +4461,19 @@
         <v>1.254</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>3189</v>
+        <v>3184</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>1.83</v>
       </c>
       <c r="P98" s="2" t="n">
-        <v>-5378</v>
+        <v>-5376</v>
       </c>
       <c r="Q98" s="2" t="n">
-        <v>3915</v>
+        <v>3914</v>
       </c>
       <c r="R98" s="2" t="n">
-        <v>-1462</v>
+        <v>-1461</v>
       </c>
       <c r="S98" s="2" t="inlineStr"/>
     </row>
@@ -4691,20 +4691,20 @@
         <v>2.888</v>
       </c>
       <c r="N104" t="n">
-        <v>5258</v>
+        <v>5250</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="n">
-        <v>13670</v>
+        <v>13650</v>
       </c>
       <c r="Q104" t="n">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="R104" t="n">
-        <v>15041</v>
+        <v>15019</v>
       </c>
       <c r="S104" t="n">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="105">
@@ -4754,19 +4754,19 @@
         <v>-1.953</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-4944</v>
+        <v>-4946</v>
       </c>
       <c r="O105" s="2" t="n">
         <v>0.19</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>-41343</v>
+        <v>-41363</v>
       </c>
       <c r="Q105" s="2" t="n">
-        <v>3255</v>
+        <v>3253</v>
       </c>
       <c r="R105" s="2" t="n">
-        <v>-38087</v>
+        <v>-38109</v>
       </c>
       <c r="S105" s="2" t="inlineStr"/>
     </row>
@@ -5031,20 +5031,20 @@
         <v>4.703</v>
       </c>
       <c r="N113" t="n">
-        <v>13940</v>
+        <v>13920</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
-        <v>37139</v>
+        <v>37086</v>
       </c>
       <c r="Q113" t="n">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="R113" t="n">
-        <v>38121</v>
+        <v>38066</v>
       </c>
       <c r="S113" t="n">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="114">
@@ -5070,7 +5070,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>6.63</v>
@@ -5094,19 +5094,19 @@
         <v>2.984</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>4990</v>
+        <v>4987</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2.9</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>171797</v>
+        <v>171744</v>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>8252</v>
+        <v>8251</v>
       </c>
       <c r="R114" s="2" t="n">
-        <v>180050</v>
+        <v>179995</v>
       </c>
       <c r="S114" s="2" t="inlineStr"/>
     </row>
@@ -5656,22 +5656,22 @@
         <v>-0.918</v>
       </c>
       <c r="N127" t="n">
-        <v>-18470</v>
+        <v>-18443</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>-68283</v>
+        <v>-68185</v>
       </c>
       <c r="Q127" t="n">
-        <v>5792</v>
+        <v>5784</v>
       </c>
       <c r="R127" t="n">
-        <v>-62491</v>
+        <v>-62401</v>
       </c>
       <c r="S127" t="n">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="128">
@@ -5721,19 +5721,19 @@
         <v>-0.501</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-10498</v>
+        <v>-10495</v>
       </c>
       <c r="O128" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="P128" s="2" t="n">
-        <v>-209808</v>
+        <v>-209710</v>
       </c>
       <c r="Q128" s="2" t="n">
-        <v>36133</v>
+        <v>36125</v>
       </c>
       <c r="R128" s="2" t="n">
-        <v>-173676</v>
+        <v>-173586</v>
       </c>
       <c r="S128" s="2" t="inlineStr"/>
     </row>
@@ -5958,7 +5958,7 @@
         <v>35650</v>
       </c>
       <c r="S133" t="n">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="134">
@@ -6251,7 +6251,7 @@
         <v>35650</v>
       </c>
       <c r="S139" t="n">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="140">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S144"/>
+  <dimension ref="A1:S145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1235,19 +1235,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="G13" t="n">
         <v>4.63</v>
       </c>
       <c r="H13" t="n">
-        <v>4.18</v>
+        <v>2.92</v>
       </c>
       <c r="I13" t="n">
         <v>11.98</v>
@@ -1258,22 +1258,22 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>2.11</v>
+        <v>0.852</v>
       </c>
       <c r="N13" t="n">
-        <v>-40061</v>
+        <v>-35733</v>
       </c>
       <c r="O13" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="P13" t="n">
-        <v>-348112</v>
+        <v>-420102</v>
       </c>
       <c r="Q13" t="n">
-        <v>11147</v>
+        <v>15016</v>
       </c>
       <c r="R13" t="n">
-        <v>-336965</v>
+        <v>-405085</v>
       </c>
       <c r="S13" t="n">
         <v>1383</v>
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>4.46</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>19.29</v>
@@ -1319,22 +1319,22 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="n">
-        <v>-0.063</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1148</v>
+        <v>-1428</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>-283617</v>
+        <v>-355607</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>63823</v>
+        <v>67692</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>-219793</v>
+        <v>-287913</v>
       </c>
       <c r="S14" s="2" t="inlineStr"/>
     </row>
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F86" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="G86" t="n">
         <v>2.69</v>
       </c>
       <c r="H86" t="n">
-        <v>4.18</v>
+        <v>3.1</v>
       </c>
       <c r="I86" t="n">
         <v>4.37</v>
@@ -4025,25 +4025,25 @@
         <v>18</v>
       </c>
       <c r="L86" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.747</v>
+        <v>-0.787</v>
       </c>
       <c r="N86" t="n">
-        <v>-77799</v>
+        <v>-62797</v>
       </c>
       <c r="O86" t="n">
         <v>0.09</v>
       </c>
       <c r="P86" t="n">
-        <v>-342301</v>
+        <v>-340821</v>
       </c>
       <c r="Q86" t="n">
-        <v>9212</v>
+        <v>9807</v>
       </c>
       <c r="R86" t="n">
-        <v>-333089</v>
+        <v>-331014</v>
       </c>
       <c r="S86" t="n">
         <v>1383</v>
@@ -4066,19 +4066,19 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>46.7</v>
+        <v>43.8</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>2.54</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>4.97</v>
+        <v>4.52</v>
       </c>
       <c r="I87" s="2" t="n">
         <v>7.7</v>
@@ -4090,25 +4090,25 @@
         <v>15.29</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>5.75</v>
+        <v>6.44</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>-1.464</v>
+        <v>-1.432</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-25821</v>
+        <v>-24382</v>
       </c>
       <c r="O87" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>-404286</v>
+        <v>-402806</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>17053</v>
+        <v>17648</v>
       </c>
       <c r="R87" s="2" t="n">
-        <v>-387232</v>
+        <v>-385157</v>
       </c>
       <c r="S87" s="2" t="inlineStr"/>
     </row>
@@ -4376,39 +4376,49 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>100</v>
-      </c>
-      <c r="F97" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2.51</v>
+      </c>
       <c r="G97" t="n">
         <v>11.98</v>
       </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="n">
+        <v>2.12</v>
+      </c>
       <c r="I97" t="n">
         <v>11.98</v>
       </c>
-      <c r="J97" t="inlineStr"/>
+      <c r="J97" t="n">
+        <v>2.12</v>
+      </c>
       <c r="K97" t="n">
         <v>22</v>
       </c>
-      <c r="L97" t="inlineStr"/>
+      <c r="L97" t="n">
+        <v>12</v>
+      </c>
       <c r="M97" t="n">
-        <v>11.981</v>
+        <v>4.933</v>
       </c>
       <c r="N97" t="n">
-        <v>20266</v>
-      </c>
-      <c r="O97" t="inlineStr"/>
+        <v>6093</v>
+      </c>
+      <c r="O97" t="n">
+        <v>2.51</v>
+      </c>
       <c r="P97" t="n">
-        <v>-1236</v>
+        <v>-8680</v>
       </c>
       <c r="Q97" t="n">
-        <v>468</v>
+        <v>887</v>
       </c>
       <c r="R97" t="n">
-        <v>-768</v>
+        <v>-7793</v>
       </c>
       <c r="S97" t="n">
         <v>1383</v>
@@ -4431,19 +4441,19 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>6.39</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>3.88</v>
+        <v>3.44</v>
       </c>
       <c r="I98" s="2" t="n">
         <v>11.98</v>
@@ -4455,25 +4465,25 @@
         <v>16.67</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>4.67</v>
+        <v>6.5</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1.254</v>
+        <v>0.773</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>3184</v>
+        <v>1575</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="P98" s="2" t="n">
-        <v>-5376</v>
+        <v>-12820</v>
       </c>
       <c r="Q98" s="2" t="n">
-        <v>3914</v>
+        <v>4333</v>
       </c>
       <c r="R98" s="2" t="n">
-        <v>-1461</v>
+        <v>-8486</v>
       </c>
       <c r="S98" s="2" t="inlineStr"/>
     </row>
@@ -4669,39 +4679,49 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>100</v>
-      </c>
-      <c r="F104" t="inlineStr"/>
+        <v>66.7</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.08</v>
+      </c>
       <c r="G104" t="n">
         <v>2.89</v>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>3.18</v>
+      </c>
       <c r="I104" t="n">
         <v>3.32</v>
       </c>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="n">
+        <v>3.18</v>
+      </c>
       <c r="K104" t="n">
         <v>18</v>
       </c>
-      <c r="L104" t="inlineStr"/>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
       <c r="M104" t="n">
-        <v>2.888</v>
+        <v>0.864</v>
       </c>
       <c r="N104" t="n">
-        <v>5250</v>
-      </c>
-      <c r="O104" t="inlineStr"/>
+        <v>-18508</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.16</v>
+      </c>
       <c r="P104" t="n">
-        <v>13650</v>
+        <v>-52375</v>
       </c>
       <c r="Q104" t="n">
-        <v>1369</v>
+        <v>4226</v>
       </c>
       <c r="R104" t="n">
-        <v>15019</v>
+        <v>-48149</v>
       </c>
       <c r="S104" t="n">
         <v>1383</v>
@@ -4724,19 +4744,19 @@
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0.67</v>
+        <v>0.35</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>2.89</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="I105" s="2" t="n">
         <v>3.32</v>
@@ -4748,25 +4768,25 @@
         <v>18</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>-1.953</v>
+        <v>-2.076</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-4946</v>
+        <v>-11054</v>
       </c>
       <c r="O105" s="2" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>-41363</v>
+        <v>-107388</v>
       </c>
       <c r="Q105" s="2" t="n">
-        <v>3253</v>
+        <v>6110</v>
       </c>
       <c r="R105" s="2" t="n">
-        <v>-38109</v>
+        <v>-101277</v>
       </c>
       <c r="S105" s="2" t="inlineStr"/>
     </row>
@@ -5009,39 +5029,39 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E113" t="n">
         <v>100</v>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>4.7</v>
+        <v>6.16</v>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>5.41</v>
+        <v>11.46</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="n">
-        <v>9</v>
+        <v>10.43</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>4.703</v>
+        <v>6.16</v>
       </c>
       <c r="N113" t="n">
-        <v>13920</v>
+        <v>18699</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
-        <v>37086</v>
+        <v>86535</v>
       </c>
       <c r="Q113" t="n">
-        <v>980</v>
+        <v>1828</v>
       </c>
       <c r="R113" t="n">
-        <v>38066</v>
+        <v>88363</v>
       </c>
       <c r="S113" t="n">
         <v>1383</v>
@@ -5064,16 +5084,16 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>6.63</v>
+        <v>6.78</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>2.48</v>
@@ -5085,238 +5105,254 @@
         <v>5.68</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>2.83</v>
+        <v>5</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0.75</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2.984</v>
+        <v>3.695</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>4987</v>
+        <v>7869</v>
       </c>
       <c r="O114" s="2" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>171744</v>
+        <v>221193</v>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>8251</v>
+        <v>9099</v>
       </c>
       <c r="R114" s="2" t="n">
-        <v>179995</v>
+        <v>230292</v>
       </c>
       <c r="S114" s="2" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="n">
+        <v>12</v>
+      </c>
+      <c r="M116" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N116" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>208</v>
+      </c>
+      <c r="R116" t="n">
+        <v>-1072</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_LOW</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr"/>
-      <c r="O116" s="2" t="inlineStr"/>
-      <c r="P116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="D117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="2" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="Q117" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="R117" s="2" t="n">
+        <v>-1072</v>
+      </c>
+      <c r="S117" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D118" t="n">
+      <c r="D119" t="n">
         <v>1</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E119" t="n">
         <v>100</v>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="n">
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="n">
         <v>2.1</v>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="n">
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="n">
         <v>2.1</v>
       </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="n">
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="n">
         <v>52.73</v>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="n">
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
         <v>2.102</v>
       </c>
-      <c r="N118" t="n">
+      <c r="N119" t="n">
         <v>2341</v>
       </c>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="n">
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="n">
         <v>2341</v>
       </c>
-      <c r="Q118" t="n">
+      <c r="Q119" t="n">
         <v>34</v>
       </c>
-      <c r="R118" t="n">
+      <c r="R119" t="n">
         <v>2375</v>
       </c>
-      <c r="S118" t="n">
+      <c r="S119" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>저점사다리</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D119" s="2" t="n">
+      <c r="D120" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E119" s="2" t="n">
+      <c r="E120" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="n">
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="2" t="n">
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="J119" s="2" t="inlineStr"/>
-      <c r="K119" s="2" t="n">
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="n">
         <v>52.73</v>
       </c>
-      <c r="L119" s="2" t="inlineStr"/>
-      <c r="M119" s="2" t="n">
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="n">
         <v>2.102</v>
       </c>
-      <c r="N119" s="2" t="n">
+      <c r="N120" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="O119" s="2" t="inlineStr"/>
-      <c r="P119" s="2" t="n">
+      <c r="O120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="n">
         <v>2341</v>
       </c>
-      <c r="Q119" s="2" t="n">
+      <c r="Q120" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="R119" s="2" t="n">
+      <c r="R120" s="2" t="n">
         <v>2375</v>
       </c>
-      <c r="S119" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>2</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="n">
-        <v>1</v>
-      </c>
-      <c r="M121" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N121" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>513</v>
-      </c>
-      <c r="R121" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S121" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S120" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5331,53 +5367,47 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G122" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I122" t="n">
-        <v>1.37</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K122" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="n">
         <v>1</v>
       </c>
-      <c r="L122" t="n">
-        <v>5.67</v>
-      </c>
       <c r="M122" t="n">
-        <v>-0.217</v>
+        <v>-2.607</v>
       </c>
       <c r="N122" t="n">
-        <v>-13272</v>
+        <v>-8011</v>
       </c>
       <c r="O122" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>-53089</v>
+        <v>-16021</v>
       </c>
       <c r="Q122" t="n">
-        <v>5913</v>
+        <v>513</v>
       </c>
       <c r="R122" t="n">
-        <v>-47176</v>
+        <v>-15508</v>
       </c>
       <c r="S122" t="n">
         <v>1415</v>
@@ -5396,47 +5426,53 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H123" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I123" t="inlineStr"/>
+        <v>0.74</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1.37</v>
+      </c>
       <c r="J123" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K123" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1</v>
+      </c>
       <c r="L123" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.136</v>
+        <v>-0.217</v>
       </c>
       <c r="N123" t="n">
-        <v>-2389</v>
+        <v>-13272</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P123" t="n">
-        <v>-4777</v>
+        <v>-53089</v>
       </c>
       <c r="Q123" t="n">
-        <v>2924</v>
+        <v>5913</v>
       </c>
       <c r="R123" t="n">
-        <v>-1854</v>
+        <v>-47176</v>
       </c>
       <c r="S123" t="n">
         <v>1415</v>
@@ -5455,43 +5491,47 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>100</v>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="n">
-        <v>14</v>
-      </c>
-      <c r="L124" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M124" t="n">
-        <v>1.042</v>
+        <v>-0.136</v>
       </c>
       <c r="N124" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O124" t="inlineStr"/>
+        <v>-2389</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
       <c r="P124" t="n">
-        <v>48540</v>
+        <v>-4777</v>
       </c>
       <c r="Q124" t="n">
-        <v>4254</v>
+        <v>2924</v>
       </c>
       <c r="R124" t="n">
-        <v>52794</v>
+        <v>-1854</v>
       </c>
       <c r="S124" t="n">
         <v>1415</v>
@@ -5510,50 +5550,46 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D125" t="n">
         <v>3</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="n">
-        <v>4.67</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="n">
+        <v>14</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
-        <v>-0.864</v>
+        <v>1.042</v>
       </c>
       <c r="N125" t="n">
-        <v>-28997</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O125" t="inlineStr"/>
       <c r="P125" t="n">
-        <v>-86990</v>
+        <v>48540</v>
       </c>
       <c r="Q125" t="n">
-        <v>13787</v>
+        <v>4254</v>
       </c>
       <c r="R125" t="n">
-        <v>-73203</v>
+        <v>52794</v>
       </c>
       <c r="S125" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="126">
@@ -5569,11 +5605,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -5583,36 +5619,36 @@
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
-        <v>0.87</v>
+        <v>1.53</v>
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
-        <v>3</v>
+        <v>4.67</v>
       </c>
       <c r="M126" t="n">
-        <v>-0.867</v>
+        <v>-0.864</v>
       </c>
       <c r="N126" t="n">
-        <v>-29188</v>
+        <v>-28997</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>-29188</v>
+        <v>-86990</v>
       </c>
       <c r="Q126" t="n">
-        <v>2950</v>
+        <v>13787</v>
       </c>
       <c r="R126" t="n">
-        <v>-26238</v>
+        <v>-73203</v>
       </c>
       <c r="S126" t="n">
-        <v>1373</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="127">
@@ -5628,11 +5664,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -5642,161 +5678,159 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="n">
-        <v>1.07</v>
+        <v>0.87</v>
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
+        <v>3</v>
+      </c>
+      <c r="M127" t="n">
+        <v>-0.867</v>
+      </c>
+      <c r="N127" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>-29188</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>2950</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-26238</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="n">
         <v>4</v>
       </c>
-      <c r="M127" t="n">
+      <c r="M128" t="n">
         <v>-0.918</v>
       </c>
-      <c r="N127" t="n">
+      <c r="N128" t="n">
         <v>-18443</v>
       </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
         <v>-68185</v>
       </c>
-      <c r="Q127" t="n">
+      <c r="Q128" t="n">
         <v>5784</v>
       </c>
-      <c r="R127" t="n">
+      <c r="R128" t="n">
         <v>-62401</v>
       </c>
-      <c r="S127" t="n">
+      <c r="S128" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D128" s="2" t="n">
+      <c r="D129" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="F128" s="2" t="n">
+      <c r="F129" s="2" t="n">
         <v>0.71</v>
       </c>
-      <c r="G128" s="2" t="n">
+      <c r="G129" s="2" t="n">
         <v>1.12</v>
       </c>
-      <c r="H128" s="2" t="n">
+      <c r="H129" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I128" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J128" s="2" t="n">
+      <c r="J129" s="2" t="n">
         <v>3.49</v>
       </c>
-      <c r="K128" s="2" t="n">
+      <c r="K129" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="L128" s="2" t="n">
+      <c r="L129" s="2" t="n">
         <v>4.23</v>
       </c>
-      <c r="M128" s="2" t="n">
+      <c r="M129" s="2" t="n">
         <v>-0.501</v>
       </c>
-      <c r="N128" s="2" t="n">
+      <c r="N129" s="2" t="n">
         <v>-10495</v>
       </c>
-      <c r="O128" s="2" t="n">
+      <c r="O129" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="P128" s="2" t="n">
+      <c r="P129" s="2" t="n">
         <v>-209710</v>
       </c>
-      <c r="Q128" s="2" t="n">
+      <c r="Q129" s="2" t="n">
         <v>36125</v>
       </c>
-      <c r="R128" s="2" t="n">
+      <c r="R129" s="2" t="n">
         <v>-173586</v>
       </c>
-      <c r="S128" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>9</v>
-      </c>
-      <c r="E130" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G130" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H130" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I130" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J130" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N130" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O130" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P130" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R130" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S130" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S129" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5811,44 +5845,52 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E131" t="n">
-        <v>100</v>
-      </c>
-      <c r="F131" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G131" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H131" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I131" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J131" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J131" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N131" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O131" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P131" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q131" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R131" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S131" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="132">
@@ -5864,48 +5906,44 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="n">
-        <v>8.300000000000001</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="n">
-        <v>-8.304</v>
+        <v>8.56</v>
       </c>
       <c r="N132" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
+        <v>57466</v>
+      </c>
+      <c r="O132" t="inlineStr"/>
       <c r="P132" t="n">
-        <v>-74087</v>
+        <v>114933</v>
       </c>
       <c r="Q132" t="n">
-        <v>257</v>
+        <v>667</v>
       </c>
       <c r="R132" t="n">
-        <v>-73830</v>
+        <v>115600</v>
       </c>
       <c r="S132" t="n">
-        <v>1373</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="133">
@@ -5921,169 +5959,161 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D133" t="n">
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>100</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J133" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N133" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>257</v>
+      </c>
+      <c r="R133" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>100</v>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="n">
         <v>4.029</v>
       </c>
-      <c r="N133" t="n">
+      <c r="N134" t="n">
         <v>35381</v>
       </c>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="n">
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="n">
         <v>35381</v>
       </c>
-      <c r="Q133" t="n">
+      <c r="Q134" t="n">
         <v>269</v>
       </c>
-      <c r="R133" t="n">
+      <c r="R134" t="n">
         <v>35650</v>
       </c>
-      <c r="S133" t="n">
+      <c r="S134" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D134" s="2" t="n">
+      <c r="D135" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E134" s="2" t="n">
+      <c r="E135" s="2" t="n">
         <v>61.5</v>
       </c>
-      <c r="F134" s="2" t="n">
+      <c r="F135" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="G134" s="2" t="n">
+      <c r="G135" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H134" s="2" t="n">
+      <c r="H135" s="2" t="n">
         <v>5.02</v>
       </c>
-      <c r="I134" s="2" t="n">
+      <c r="I135" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J134" s="2" t="n">
+      <c r="J135" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="n">
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="n">
         <v>0.148</v>
       </c>
-      <c r="N134" s="2" t="n">
+      <c r="N135" s="2" t="n">
         <v>5349</v>
       </c>
-      <c r="O134" s="2" t="n">
+      <c r="O135" s="2" t="n">
         <v>1.57</v>
       </c>
-      <c r="P134" s="2" t="n">
+      <c r="P135" s="2" t="n">
         <v>69535</v>
       </c>
-      <c r="Q134" s="2" t="n">
+      <c r="Q135" s="2" t="n">
         <v>3332</v>
       </c>
-      <c r="R134" s="2" t="n">
+      <c r="R135" s="2" t="n">
         <v>72867</v>
       </c>
-      <c r="S134" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>9</v>
-      </c>
-      <c r="E136" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F136" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G136" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H136" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I136" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J136" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K136" t="n">
-        <v>3</v>
-      </c>
-      <c r="L136" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M136" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N136" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P136" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R136" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S136" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S135" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6098,46 +6128,56 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E137" t="n">
-        <v>100</v>
-      </c>
-      <c r="F137" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G137" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H137" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H137" t="n">
+        <v>4.19</v>
+      </c>
       <c r="I137" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J137" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="J137" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K137" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L137" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L137" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M137" t="n">
-        <v>8.56</v>
+        <v>-1.213</v>
       </c>
       <c r="N137" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O137" t="inlineStr"/>
+        <v>-744</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.86</v>
+      </c>
       <c r="P137" t="n">
-        <v>114933</v>
+        <v>-6692</v>
       </c>
       <c r="Q137" t="n">
-        <v>667</v>
+        <v>2139</v>
       </c>
       <c r="R137" t="n">
-        <v>115600</v>
+        <v>-4553</v>
       </c>
       <c r="S137" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="138">
@@ -6153,50 +6193,46 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="n">
-        <v>3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
       <c r="M138" t="n">
-        <v>-8.304</v>
+        <v>8.56</v>
       </c>
       <c r="N138" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
+        <v>57466</v>
+      </c>
+      <c r="O138" t="inlineStr"/>
       <c r="P138" t="n">
-        <v>-74087</v>
+        <v>114933</v>
       </c>
       <c r="Q138" t="n">
-        <v>257</v>
+        <v>667</v>
       </c>
       <c r="R138" t="n">
-        <v>-73830</v>
+        <v>115600</v>
       </c>
       <c r="S138" t="n">
-        <v>1373</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="139">
@@ -6212,192 +6248,251 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D139" t="n">
         <v>1</v>
       </c>
       <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="n">
+        <v>3</v>
+      </c>
+      <c r="M139" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N139" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>257</v>
+      </c>
+      <c r="R139" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
         <v>100</v>
       </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="n">
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="n">
         <v>4.03</v>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="n">
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="n">
         <v>4.03</v>
       </c>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="n">
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="n">
         <v>1</v>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="n">
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="n">
         <v>4.029</v>
       </c>
-      <c r="N139" t="n">
+      <c r="N140" t="n">
         <v>35381</v>
       </c>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="n">
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="n">
         <v>35381</v>
       </c>
-      <c r="Q139" t="n">
+      <c r="Q140" t="n">
         <v>269</v>
       </c>
-      <c r="R139" t="n">
+      <c r="R140" t="n">
         <v>35650</v>
       </c>
-      <c r="S139" t="n">
+      <c r="S140" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D140" s="2" t="n">
+      <c r="D141" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E140" s="2" t="n">
+      <c r="E141" s="2" t="n">
         <v>61.5</v>
       </c>
-      <c r="F140" s="2" t="n">
+      <c r="F141" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="G140" s="2" t="n">
+      <c r="G141" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H140" s="2" t="n">
+      <c r="H141" s="2" t="n">
         <v>5.02</v>
       </c>
-      <c r="I140" s="2" t="n">
+      <c r="I141" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J140" s="2" t="n">
+      <c r="J141" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K140" s="2" t="n">
+      <c r="K141" s="2" t="n">
         <v>3.12</v>
       </c>
-      <c r="L140" s="2" t="n">
+      <c r="L141" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M140" s="2" t="n">
+      <c r="M141" s="2" t="n">
         <v>0.148</v>
       </c>
-      <c r="N140" s="2" t="n">
+      <c r="N141" s="2" t="n">
         <v>5349</v>
       </c>
-      <c r="O140" s="2" t="n">
+      <c r="O141" s="2" t="n">
         <v>1.57</v>
       </c>
-      <c r="P140" s="2" t="n">
+      <c r="P141" s="2" t="n">
         <v>69535</v>
       </c>
-      <c r="Q140" s="2" t="n">
+      <c r="Q141" s="2" t="n">
         <v>3332</v>
       </c>
-      <c r="R140" s="2" t="n">
+      <c r="R141" s="2" t="n">
         <v>72867</v>
       </c>
-      <c r="S140" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="S141" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" s="2" t="inlineStr"/>
-      <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-      <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="2" t="inlineStr"/>
-      <c r="M142" s="2" t="inlineStr"/>
-      <c r="N142" s="2" t="inlineStr"/>
-      <c r="O142" s="2" t="inlineStr"/>
-      <c r="P142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="D143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr"/>
+      <c r="O143" s="2" t="inlineStr"/>
+      <c r="P143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" s="2" t="inlineStr"/>
-      <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-      <c r="K144" s="2" t="inlineStr"/>
-      <c r="L144" s="2" t="inlineStr"/>
-      <c r="M144" s="2" t="inlineStr"/>
-      <c r="N144" s="2" t="inlineStr"/>
-      <c r="O144" s="2" t="inlineStr"/>
-      <c r="P144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" s="2" t="inlineStr"/>
+      <c r="D145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr"/>
+      <c r="O145" s="2" t="inlineStr"/>
+      <c r="P145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S145"/>
+  <dimension ref="A1:S142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>8.41</v>
+        <v>10.01</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
@@ -1136,22 +1136,22 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>-8.407</v>
+        <v>-10.012</v>
       </c>
       <c r="N11" t="n">
-        <v>-40645</v>
+        <v>-71414</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-81290</v>
+        <v>-71414</v>
       </c>
       <c r="Q11" t="n">
-        <v>1145</v>
+        <v>949</v>
       </c>
       <c r="R11" t="n">
-        <v>-80145</v>
+        <v>-70465</v>
       </c>
       <c r="S11" t="n">
         <v>1411</v>
@@ -1174,19 +1174,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
       <c r="H12" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="I12" t="n">
         <v>7.7</v>
@@ -1197,22 +1197,22 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>-1.05</v>
+        <v>-1.323</v>
       </c>
       <c r="N12" t="n">
-        <v>-3277</v>
+        <v>-4186</v>
       </c>
       <c r="O12" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="P12" t="n">
-        <v>-10474</v>
+        <v>-16210</v>
       </c>
       <c r="Q12" t="n">
-        <v>17894</v>
+        <v>14644</v>
       </c>
       <c r="R12" t="n">
-        <v>7421</v>
+        <v>-1566</v>
       </c>
       <c r="S12" t="n">
         <v>1373</v>
@@ -1235,22 +1235,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G13" t="n">
-        <v>4.63</v>
+        <v>2.79</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="I13" t="n">
-        <v>11.98</v>
+        <v>4.37</v>
       </c>
       <c r="J13" t="n">
         <v>6.38</v>
@@ -1258,22 +1258,22 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>0.852</v>
+        <v>-0.168</v>
       </c>
       <c r="N13" t="n">
-        <v>-35733</v>
+        <v>-46189</v>
       </c>
       <c r="O13" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="P13" t="n">
-        <v>-420102</v>
+        <v>-411422</v>
       </c>
       <c r="Q13" t="n">
-        <v>15016</v>
+        <v>14130</v>
       </c>
       <c r="R13" t="n">
-        <v>-405085</v>
+        <v>-397292</v>
       </c>
       <c r="S13" t="n">
         <v>1383</v>
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>19.29</v>
@@ -1319,22 +1319,22 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1428</v>
+        <v>-1510</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>-355607</v>
+        <v>-342787</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>67692</v>
+        <v>63360</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>-287913</v>
+        <v>-279427</v>
       </c>
       <c r="S14" s="2" t="inlineStr"/>
     </row>
@@ -4236,133 +4236,50 @@
       <c r="S93" s="2" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="n">
-        <v>5</v>
-      </c>
-      <c r="M95" t="n">
-        <v>-6.802</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>-9876</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>196</v>
-      </c>
-      <c r="R95" t="n">
-        <v>-9679</v>
-      </c>
-      <c r="S95" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>US_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>4</v>
-      </c>
-      <c r="E96" t="n">
-        <v>50</v>
-      </c>
-      <c r="F96" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="G96" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="H96" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I96" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="J96" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="K96" t="n">
-        <v>14</v>
-      </c>
-      <c r="L96" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="N96" t="n">
-        <v>2178</v>
-      </c>
-      <c r="O96" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P96" t="n">
-        <v>5736</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>3250</v>
-      </c>
-      <c r="R96" t="n">
-        <v>8986</v>
-      </c>
-      <c r="S96" t="n">
-        <v>1373</v>
-      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>US_TR_VCP2</t>
+          <t>US_TR_JEO2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4372,62 +4289,56 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="G97" t="n">
-        <v>11.98</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I97" t="n">
-        <v>11.98</v>
-      </c>
+        <v>2.13</v>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="K97" t="n">
-        <v>22</v>
-      </c>
+        <v>2.13</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>4.933</v>
+        <v>-2.131</v>
       </c>
       <c r="N97" t="n">
-        <v>6093</v>
+        <v>-41586</v>
       </c>
       <c r="O97" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>-8680</v>
+        <v>-41586</v>
       </c>
       <c r="Q97" t="n">
-        <v>887</v>
+        <v>2702</v>
       </c>
       <c r="R97" t="n">
-        <v>-7793</v>
+        <v>-38883</v>
       </c>
       <c r="S97" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP2</t>
+          <t>US_TR_JEO2</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4441,56 +4352,50 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>6.39</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>11.98</v>
-      </c>
+        <v>2.13</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>16.67</v>
-      </c>
+        <v>2.13</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>0.773</v>
+        <v>-2.131</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>1575</v>
+        <v>-41586</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P98" s="2" t="n">
-        <v>-12820</v>
+        <v>-41586</v>
       </c>
       <c r="Q98" s="2" t="n">
-        <v>4333</v>
+        <v>2702</v>
       </c>
       <c r="R98" s="2" t="n">
-        <v>-8486</v>
+        <v>-38883</v>
       </c>
       <c r="S98" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>US_TR_JEO2</t>
+          <t>US_TR_MA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4504,7 +4409,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -4514,286 +4419,270 @@
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>2.13</v>
+        <v>3.34</v>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
-        <v>2.13</v>
+        <v>6.17</v>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M100" t="n">
-        <v>-2.131</v>
+        <v>-3.337</v>
       </c>
       <c r="N100" t="n">
-        <v>-41586</v>
+        <v>-7859</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>-41586</v>
+        <v>-55013</v>
       </c>
       <c r="Q100" t="n">
-        <v>2702</v>
+        <v>1884</v>
       </c>
       <c r="R100" t="n">
-        <v>-38883</v>
+        <v>-53128</v>
       </c>
       <c r="S100" t="n">
         <v>1373</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_JEO2</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I101" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J101" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K101" t="n">
+        <v>18</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="N101" t="n">
+        <v>-18508</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P101" t="n">
+        <v>-52375</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>4226</v>
+      </c>
+      <c r="R101" t="n">
+        <v>-48149</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n">
+      <c r="D102" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-2.076</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-11054</v>
+      </c>
+      <c r="O102" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>-107388</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>6110</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>-101277</v>
+      </c>
+      <c r="S102" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_ADD1</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="n">
         <v>1</v>
       </c>
-      <c r="E101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>-2.131</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="O101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="2" t="n">
-        <v>-41586</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>2702</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>-38883</v>
-      </c>
-      <c r="S101" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>7</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="n">
-        <v>8</v>
-      </c>
-      <c r="M103" t="n">
-        <v>-3.337</v>
-      </c>
-      <c r="N103" t="n">
-        <v>-7859</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
-        <v>-55013</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>1884</v>
-      </c>
-      <c r="R103" t="n">
-        <v>-53128</v>
-      </c>
-      <c r="S103" t="n">
+      <c r="M106" t="n">
+        <v>-7.145</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-27445</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>-54889</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1054</v>
+      </c>
+      <c r="R106" t="n">
+        <v>-53835</v>
+      </c>
+      <c r="S106" t="n">
         <v>1373</v>
       </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>3</v>
-      </c>
-      <c r="E104" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G104" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H104" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I104" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J104" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K104" t="n">
-        <v>18</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="N104" t="n">
-        <v>-18508</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P104" t="n">
-        <v>-52375</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>4226</v>
-      </c>
-      <c r="R104" t="n">
-        <v>-48149</v>
-      </c>
-      <c r="S104" t="n">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_MA</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>-2.076</v>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>-11054</v>
-      </c>
-      <c r="O105" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="P105" s="2" t="n">
-        <v>-107388</v>
-      </c>
-      <c r="Q105" s="2" t="n">
-        <v>6110</v>
-      </c>
-      <c r="R105" s="2" t="n">
-        <v>-101277</v>
-      </c>
-      <c r="S105" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>US_TR_ADD1</t>
+          <t>US_TR_LEGACY</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -4807,34 +4696,50 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="n">
+        <v>7.15</v>
+      </c>
       <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="n">
+        <v>10.49</v>
+      </c>
       <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
-      <c r="N107" s="2" t="inlineStr"/>
-      <c r="O107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-7.145</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-27445</v>
+      </c>
+      <c r="O107" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="P107" s="2" t="n">
-        <v>0</v>
+        <v>-54889</v>
       </c>
       <c r="Q107" s="2" t="n">
-        <v>0</v>
+        <v>1054</v>
       </c>
       <c r="R107" s="2" t="n">
-        <v>0</v>
+        <v>-53835</v>
       </c>
       <c r="S107" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY</t>
+          <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4848,174 +4753,176 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>52.9</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" t="inlineStr"/>
+        <v>1.87</v>
+      </c>
+      <c r="G109" t="n">
+        <v>7.27</v>
+      </c>
       <c r="H109" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="I109" t="inlineStr"/>
+        <v>2.48</v>
+      </c>
+      <c r="I109" t="n">
+        <v>16.31</v>
+      </c>
       <c r="J109" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="K109" t="inlineStr"/>
+        <v>5.68</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.78</v>
+      </c>
       <c r="L109" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M109" t="n">
-        <v>-7.145</v>
+        <v>2.681</v>
       </c>
       <c r="N109" t="n">
-        <v>-27445</v>
+        <v>3410</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P109" t="n">
-        <v>-54889</v>
+        <v>134658</v>
       </c>
       <c r="Q109" t="n">
-        <v>1054</v>
+        <v>7271</v>
       </c>
       <c r="R109" t="n">
-        <v>-53835</v>
+        <v>141929</v>
       </c>
       <c r="S109" t="n">
         <v>1373</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>7</v>
+      </c>
+      <c r="E110" t="n">
+        <v>100</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="N110" t="n">
+        <v>18699</v>
+      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="n">
+        <v>86535</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1828</v>
+      </c>
+      <c r="R110" t="n">
+        <v>88363</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>-7.145</v>
-      </c>
-      <c r="N110" s="2" t="n">
-        <v>-27445</v>
-      </c>
-      <c r="O110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" s="2" t="n">
-        <v>-54889</v>
-      </c>
-      <c r="Q110" s="2" t="n">
-        <v>1054</v>
-      </c>
-      <c r="R110" s="2" t="n">
-        <v>-53835</v>
-      </c>
-      <c r="S110" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>17</v>
-      </c>
-      <c r="E112" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F112" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G112" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="H112" t="n">
+      <c r="D111" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="H111" s="2" t="n">
         <v>2.48</v>
       </c>
-      <c r="I112" t="n">
+      <c r="I111" s="2" t="n">
         <v>16.31</v>
       </c>
-      <c r="J112" t="n">
+      <c r="J111" s="2" t="n">
         <v>5.68</v>
       </c>
-      <c r="K112" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="L112" t="n">
+      <c r="K111" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L111" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="M112" t="n">
-        <v>2.681</v>
-      </c>
-      <c r="N112" t="n">
-        <v>3410</v>
-      </c>
-      <c r="O112" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P112" t="n">
-        <v>134658</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>7271</v>
-      </c>
-      <c r="R112" t="n">
-        <v>141929</v>
-      </c>
-      <c r="S112" t="n">
-        <v>1373</v>
-      </c>
+      <c r="M111" s="2" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>7869</v>
+      </c>
+      <c r="O111" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P111" s="2" t="n">
+        <v>221193</v>
+      </c>
+      <c r="Q111" s="2" t="n">
+        <v>9099</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>230292</v>
+      </c>
+      <c r="S111" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_TREND</t>
+          <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5029,39 +4936,43 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>100</v>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="L113" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="n">
+        <v>12</v>
+      </c>
       <c r="M113" t="n">
-        <v>6.16</v>
+        <v>-0.54</v>
       </c>
       <c r="N113" t="n">
-        <v>18699</v>
-      </c>
-      <c r="O113" t="inlineStr"/>
+        <v>-1280</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
       <c r="P113" t="n">
-        <v>86535</v>
+        <v>-1280</v>
       </c>
       <c r="Q113" t="n">
-        <v>1828</v>
+        <v>208</v>
       </c>
       <c r="R113" t="n">
-        <v>88363</v>
+        <v>-1072</v>
       </c>
       <c r="S113" t="n">
         <v>1383</v>
@@ -5070,7 +4981,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_TREND</t>
+          <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5084,120 +4995,110 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>6.78</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>16.31</v>
-      </c>
+        <v>0.54</v>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>5</v>
-      </c>
+        <v>0.54</v>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="n">
-        <v>0.75</v>
+        <v>12</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3.695</v>
+        <v>-0.54</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>7869</v>
+        <v>-1280</v>
       </c>
       <c r="O114" s="2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>221193</v>
+        <v>-1280</v>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>9099</v>
+        <v>208</v>
       </c>
       <c r="R114" s="2" t="n">
-        <v>230292</v>
+        <v>-1072</v>
       </c>
       <c r="S114" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_LOW</t>
+          <t>저점사다리</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D116" t="n">
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="n">
-        <v>12</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="n">
-        <v>-0.54</v>
+        <v>2.102</v>
       </c>
       <c r="N116" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
+        <v>2341</v>
+      </c>
+      <c r="O116" t="inlineStr"/>
       <c r="P116" t="n">
-        <v>-1280</v>
+        <v>2341</v>
       </c>
       <c r="Q116" t="n">
-        <v>208</v>
+        <v>34</v>
       </c>
       <c r="R116" t="n">
-        <v>-1072</v>
+        <v>2375</v>
       </c>
       <c r="S116" t="n">
-        <v>1383</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_LOW</t>
+          <t>저점사다리</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -5209,150 +5110,221 @@
         <v>1</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="n">
-        <v>12</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L117" s="2" t="inlineStr"/>
       <c r="M117" s="2" t="n">
-        <v>-0.54</v>
+        <v>2.102</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="O117" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2341</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr"/>
       <c r="P117" s="2" t="n">
-        <v>-1280</v>
+        <v>2341</v>
       </c>
       <c r="Q117" s="2" t="n">
-        <v>208</v>
+        <v>34</v>
       </c>
       <c r="R117" s="2" t="n">
-        <v>-1072</v>
+        <v>2375</v>
       </c>
       <c r="S117" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>저점사다리</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>분</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="n">
         <v>1</v>
       </c>
-      <c r="E119" t="n">
-        <v>100</v>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="L119" t="inlineStr"/>
       <c r="M119" t="n">
-        <v>2.102</v>
+        <v>-2.607</v>
       </c>
       <c r="N119" t="n">
-        <v>2341</v>
-      </c>
-      <c r="O119" t="inlineStr"/>
+        <v>-8011</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
       <c r="P119" t="n">
-        <v>2341</v>
+        <v>-16021</v>
       </c>
       <c r="Q119" t="n">
-        <v>34</v>
+        <v>513</v>
       </c>
       <c r="R119" t="n">
-        <v>2375</v>
+        <v>-15508</v>
       </c>
       <c r="S119" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="n">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>4</v>
+      </c>
+      <c r="E120" t="n">
+        <v>25</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K120" t="n">
         <v>1</v>
       </c>
-      <c r="E120" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="2" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N120" s="2" t="n">
-        <v>2341</v>
-      </c>
-      <c r="O120" s="2" t="inlineStr"/>
-      <c r="P120" s="2" t="n">
-        <v>2341</v>
-      </c>
-      <c r="Q120" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="R120" s="2" t="n">
-        <v>2375</v>
-      </c>
-      <c r="S120" s="2" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-0.217</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-13272</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P120" t="n">
+        <v>-53089</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>5913</v>
+      </c>
+      <c r="R120" t="n">
+        <v>-47176</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M121" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="N121" t="n">
+        <v>-2389</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>-4777</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>2924</v>
+      </c>
+      <c r="R121" t="n">
+        <v>-1854</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5367,47 +5339,43 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="n">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="n">
+        <v>14</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="n">
-        <v>-2.607</v>
+        <v>1.042</v>
       </c>
       <c r="N122" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
+        <v>16180</v>
+      </c>
+      <c r="O122" t="inlineStr"/>
       <c r="P122" t="n">
-        <v>-16021</v>
+        <v>48540</v>
       </c>
       <c r="Q122" t="n">
-        <v>513</v>
+        <v>4254</v>
       </c>
       <c r="R122" t="n">
-        <v>-15508</v>
+        <v>52794</v>
       </c>
       <c r="S122" t="n">
         <v>1415</v>
@@ -5426,56 +5394,50 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G123" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I123" t="n">
-        <v>1.37</v>
-      </c>
+        <v>0.86</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1</v>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
-        <v>5.67</v>
+        <v>4.67</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.217</v>
+        <v>-0.864</v>
       </c>
       <c r="N123" t="n">
-        <v>-13272</v>
+        <v>-28997</v>
       </c>
       <c r="O123" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>-53089</v>
+        <v>-86990</v>
       </c>
       <c r="Q123" t="n">
-        <v>5913</v>
+        <v>13787</v>
       </c>
       <c r="R123" t="n">
-        <v>-47176</v>
+        <v>-73203</v>
       </c>
       <c r="S123" t="n">
-        <v>1415</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="124">
@@ -5491,11 +5453,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -5505,36 +5467,36 @@
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>0.14</v>
+        <v>0.87</v>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="n">
-        <v>0.16</v>
+        <v>0.87</v>
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="M124" t="n">
-        <v>-0.136</v>
+        <v>-0.867</v>
       </c>
       <c r="N124" t="n">
-        <v>-2389</v>
+        <v>-29188</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>-4777</v>
+        <v>-29188</v>
       </c>
       <c r="Q124" t="n">
-        <v>2924</v>
+        <v>2950</v>
       </c>
       <c r="R124" t="n">
-        <v>-1854</v>
+        <v>-26238</v>
       </c>
       <c r="S124" t="n">
-        <v>1415</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="125">
@@ -5550,287 +5512,285 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>08/03~08/07</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>100</v>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>4</v>
+      </c>
+      <c r="M125" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-18443</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>-68185</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>5784</v>
+      </c>
+      <c r="R125" t="n">
+        <v>-62401</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="n">
-        <v>14</v>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="n">
-        <v>1.042</v>
-      </c>
-      <c r="N125" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="n">
-        <v>48540</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>4254</v>
-      </c>
-      <c r="R125" t="n">
-        <v>52794</v>
-      </c>
-      <c r="S125" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="M126" t="n">
-        <v>-0.864</v>
-      </c>
-      <c r="N126" t="n">
-        <v>-28997</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>-86990</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>13787</v>
-      </c>
-      <c r="R126" t="n">
-        <v>-73203</v>
-      </c>
-      <c r="S126" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="n">
-        <v>3</v>
-      </c>
-      <c r="M127" t="n">
-        <v>-0.867</v>
-      </c>
-      <c r="N127" t="n">
-        <v>-29188</v>
-      </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
-        <v>-29188</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>2950</v>
-      </c>
-      <c r="R127" t="n">
-        <v>-26238</v>
-      </c>
-      <c r="S127" t="n">
-        <v>1373</v>
-      </c>
+      <c r="J126" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-0.501</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-10495</v>
+      </c>
+      <c r="O126" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P126" s="2" t="n">
+        <v>-209710</v>
+      </c>
+      <c r="Q126" s="2" t="n">
+        <v>36125</v>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>-173586</v>
+      </c>
+      <c r="S126" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D128" t="n">
+        <v>9</v>
+      </c>
+      <c r="E128" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I128" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J128" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N128" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P128" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R128" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
         <v>2</v>
       </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="n">
-        <v>4</v>
-      </c>
-      <c r="M128" t="n">
-        <v>-0.918</v>
-      </c>
-      <c r="N128" t="n">
-        <v>-18443</v>
-      </c>
-      <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="n">
-        <v>-68185</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>5784</v>
-      </c>
-      <c r="R128" t="n">
-        <v>-62401</v>
-      </c>
-      <c r="S128" t="n">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E129" s="2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H129" s="2" t="n">
+      <c r="E129" t="n">
+        <v>100</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N129" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>667</v>
+      </c>
+      <c r="R129" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
         <v>1</v>
       </c>
-      <c r="I129" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K129" s="2" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="M129" s="2" t="n">
-        <v>-0.501</v>
-      </c>
-      <c r="N129" s="2" t="n">
-        <v>-10495</v>
-      </c>
-      <c r="O129" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="P129" s="2" t="n">
-        <v>-209710</v>
-      </c>
-      <c r="Q129" s="2" t="n">
-        <v>36125</v>
-      </c>
-      <c r="R129" s="2" t="n">
-        <v>-173586</v>
-      </c>
-      <c r="S129" s="2" t="inlineStr"/>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N130" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>257</v>
+      </c>
+      <c r="R130" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1373</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5845,275 +5805,283 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F131" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H131" t="n">
-        <v>4.19</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J131" t="n">
-        <v>7.04</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="n">
-        <v>-1.213</v>
+        <v>4.029</v>
       </c>
       <c r="N131" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0.86</v>
-      </c>
+        <v>35381</v>
+      </c>
+      <c r="O131" t="inlineStr"/>
       <c r="P131" t="n">
-        <v>-6692</v>
+        <v>35381</v>
       </c>
       <c r="Q131" t="n">
-        <v>2139</v>
+        <v>269</v>
       </c>
       <c r="R131" t="n">
-        <v>-4553</v>
+        <v>35650</v>
       </c>
       <c r="S131" t="n">
-        <v>1415</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>2</v>
-      </c>
-      <c r="E132" t="n">
-        <v>100</v>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="n">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I132" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N132" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>667</v>
-      </c>
-      <c r="R132" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S132" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="n">
+      <c r="J132" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N133" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>257</v>
-      </c>
-      <c r="R133" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S133" t="n">
-        <v>1373</v>
-      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>5349</v>
+      </c>
+      <c r="O132" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P132" s="2" t="n">
+        <v>69535</v>
+      </c>
+      <c r="Q132" s="2" t="n">
+        <v>3332</v>
+      </c>
+      <c r="R132" s="2" t="n">
+        <v>72867</v>
+      </c>
+      <c r="S132" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>수동매매</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D134" t="n">
+        <v>9</v>
+      </c>
+      <c r="E134" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H134" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I134" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J134" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K134" t="n">
+        <v>3</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P134" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R134" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S134" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="n">
+        <v>100</v>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N135" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>667</v>
+      </c>
+      <c r="R135" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S135" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
         <v>1</v>
       </c>
-      <c r="E134" t="n">
-        <v>100</v>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="n">
-        <v>4.029</v>
-      </c>
-      <c r="N134" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="n">
-        <v>35381</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>269</v>
-      </c>
-      <c r="R134" t="n">
-        <v>35650</v>
-      </c>
-      <c r="S134" t="n">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J135" s="2" t="n">
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K135" s="2" t="inlineStr"/>
-      <c r="L135" s="2" t="inlineStr"/>
-      <c r="M135" s="2" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="N135" s="2" t="n">
-        <v>5349</v>
-      </c>
-      <c r="O135" s="2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P135" s="2" t="n">
-        <v>69535</v>
-      </c>
-      <c r="Q135" s="2" t="n">
-        <v>3332</v>
-      </c>
-      <c r="R135" s="2" t="n">
-        <v>72867</v>
-      </c>
-      <c r="S135" s="2" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="n">
+        <v>3</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>257</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1373</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6128,371 +6096,192 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H137" t="n">
-        <v>4.19</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N137" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>269</v>
+      </c>
+      <c r="R137" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G138" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="J137" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K137" t="n">
-        <v>3</v>
-      </c>
-      <c r="L137" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M137" t="n">
-        <v>-1.213</v>
-      </c>
-      <c r="N137" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P137" t="n">
-        <v>-6692</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>2139</v>
-      </c>
-      <c r="R137" t="n">
-        <v>-4553</v>
-      </c>
-      <c r="S137" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
+      <c r="H138" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>5349</v>
+      </c>
+      <c r="O138" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P138" s="2" t="n">
+        <v>69535</v>
+      </c>
+      <c r="Q138" s="2" t="n">
+        <v>3332</v>
+      </c>
+      <c r="R138" s="2" t="n">
+        <v>72867</v>
+      </c>
+      <c r="S138" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>미국수동</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>2</v>
-      </c>
-      <c r="E138" t="n">
-        <v>100</v>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="N138" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="n">
-        <v>114933</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>667</v>
-      </c>
-      <c r="R138" t="n">
-        <v>115600</v>
-      </c>
-      <c r="S138" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="n">
-        <v>3</v>
-      </c>
-      <c r="M139" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N139" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>257</v>
-      </c>
-      <c r="R139" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S139" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" t="n">
-        <v>100</v>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="n">
-        <v>4.029</v>
-      </c>
-      <c r="N140" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="n">
-        <v>35381</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>269</v>
-      </c>
-      <c r="R140" t="n">
-        <v>35650</v>
-      </c>
-      <c r="S140" t="n">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D141" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K141" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M141" s="2" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="N141" s="2" t="n">
-        <v>5349</v>
-      </c>
-      <c r="O141" s="2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P141" s="2" t="n">
-        <v>69535</v>
-      </c>
-      <c r="Q141" s="2" t="n">
-        <v>3332</v>
-      </c>
-      <c r="R141" s="2" t="n">
-        <v>72867</v>
-      </c>
-      <c r="S141" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>미국수동</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="D140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr"/>
+      <c r="P140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>기타(8042)</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" s="2" t="inlineStr"/>
-      <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-      <c r="K143" s="2" t="inlineStr"/>
-      <c r="L143" s="2" t="inlineStr"/>
-      <c r="M143" s="2" t="inlineStr"/>
-      <c r="N143" s="2" t="inlineStr"/>
-      <c r="O143" s="2" t="inlineStr"/>
-      <c r="P143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>기타(8042)</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" s="2" t="inlineStr"/>
-      <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr"/>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-      <c r="K145" s="2" t="inlineStr"/>
-      <c r="L145" s="2" t="inlineStr"/>
-      <c r="M145" s="2" t="inlineStr"/>
-      <c r="N145" s="2" t="inlineStr"/>
-      <c r="O145" s="2" t="inlineStr"/>
-      <c r="P145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" s="2" t="inlineStr"/>
+      <c r="D142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr"/>
+      <c r="P142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S142"/>
+  <dimension ref="A1:S148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3658,7 +3658,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KR_TR_VCP2</t>
+          <t>KR_TR_BASE</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP2</t>
+          <t>US_TR_BASE</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5036,350 +5036,194 @@
       <c r="S114" s="2" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" t="n">
-        <v>100</v>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N116" t="n">
-        <v>2341</v>
-      </c>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="n">
-        <v>2341</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>34</v>
-      </c>
-      <c r="R116" t="n">
-        <v>2375</v>
-      </c>
-      <c r="S116" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D117" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="2" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="L117" s="2" t="inlineStr"/>
-      <c r="M117" s="2" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>2341</v>
-      </c>
-      <c r="O117" s="2" t="inlineStr"/>
-      <c r="P117" s="2" t="n">
-        <v>2341</v>
-      </c>
-      <c r="Q117" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="R117" s="2" t="n">
-        <v>2375</v>
-      </c>
-      <c r="S117" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
+      <c r="D116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>2</v>
-      </c>
-      <c r="E119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="n">
-        <v>1</v>
-      </c>
-      <c r="M119" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N119" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>513</v>
-      </c>
-      <c r="R119" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S119" t="n">
-        <v>1415</v>
-      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>저점사다리</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>25</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0.74</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J120" t="n">
-        <v>1.32</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N120" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>34</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L120" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M120" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N120" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O120" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P120" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R120" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S120" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>2</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M121" t="n">
-        <v>-0.136</v>
-      </c>
-      <c r="N121" t="n">
-        <v>-2389</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>-4777</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>2924</v>
-      </c>
-      <c r="R121" t="n">
-        <v>-1854</v>
-      </c>
-      <c r="S121" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>3</v>
-      </c>
-      <c r="E122" t="n">
+      <c r="E121" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="n">
-        <v>14</v>
-      </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="n">
-        <v>1.042</v>
-      </c>
-      <c r="N122" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="n">
-        <v>48540</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>4254</v>
-      </c>
-      <c r="R122" t="n">
-        <v>52794</v>
-      </c>
-      <c r="S122" t="n">
-        <v>1415</v>
-      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q121" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="R121" s="2" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S121" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5394,11 +5238,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -5408,36 +5252,36 @@
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>0.86</v>
+        <v>2.61</v>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
-        <v>1.53</v>
+        <v>3.49</v>
       </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
-        <v>4.67</v>
+        <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.864</v>
+        <v>-2.607</v>
       </c>
       <c r="N123" t="n">
-        <v>-28997</v>
+        <v>-8011</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>-86990</v>
+        <v>-16021</v>
       </c>
       <c r="Q123" t="n">
-        <v>13787</v>
+        <v>513</v>
       </c>
       <c r="R123" t="n">
-        <v>-73203</v>
+        <v>-15508</v>
       </c>
       <c r="S123" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="124">
@@ -5453,50 +5297,56 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D124" t="n">
+        <v>4</v>
+      </c>
+      <c r="E124" t="n">
+        <v>25</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K124" t="n">
         <v>1</v>
       </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
-        <v>3</v>
+        <v>5.67</v>
       </c>
       <c r="M124" t="n">
-        <v>-0.867</v>
+        <v>-0.217</v>
       </c>
       <c r="N124" t="n">
-        <v>-29188</v>
+        <v>-13272</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P124" t="n">
-        <v>-29188</v>
+        <v>-53089</v>
       </c>
       <c r="Q124" t="n">
-        <v>2950</v>
+        <v>5913</v>
       </c>
       <c r="R124" t="n">
-        <v>-26238</v>
+        <v>-47176</v>
       </c>
       <c r="S124" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="125">
@@ -5512,7 +5362,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -5526,518 +5376,571 @@
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>0.92</v>
+        <v>0.14</v>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
-        <v>1.07</v>
+        <v>0.16</v>
       </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.918</v>
+        <v>-0.136</v>
       </c>
       <c r="N125" t="n">
-        <v>-18443</v>
+        <v>-2389</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>-68185</v>
+        <v>-4777</v>
       </c>
       <c r="Q125" t="n">
-        <v>5784</v>
+        <v>2924</v>
       </c>
       <c r="R125" t="n">
-        <v>-62401</v>
+        <v>-1854</v>
       </c>
       <c r="S125" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I126" s="2" t="n">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E126" t="n">
+        <v>100</v>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="n">
         <v>2.2</v>
       </c>
-      <c r="J126" s="2" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>-0.501</v>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>-10495</v>
-      </c>
-      <c r="O126" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="P126" s="2" t="n">
-        <v>-209710</v>
-      </c>
-      <c r="Q126" s="2" t="n">
-        <v>36125</v>
-      </c>
-      <c r="R126" s="2" t="n">
-        <v>-173586</v>
-      </c>
-      <c r="S126" s="2" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="n">
+        <v>14</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N126" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R126" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M127" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N127" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1411</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I128" t="n">
-        <v>3.38</v>
-      </c>
+        <v>0.87</v>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="n">
-        <v>7.04</v>
+        <v>0.87</v>
       </c>
       <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
+      <c r="L128" t="n">
+        <v>3</v>
+      </c>
       <c r="M128" t="n">
-        <v>-1.213</v>
+        <v>-0.867</v>
       </c>
       <c r="N128" t="n">
-        <v>-744</v>
+        <v>-29188</v>
       </c>
       <c r="O128" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>-6692</v>
+        <v>-29188</v>
       </c>
       <c r="Q128" t="n">
-        <v>2139</v>
+        <v>2950</v>
       </c>
       <c r="R128" t="n">
-        <v>-4553</v>
+        <v>-26238</v>
       </c>
       <c r="S128" t="n">
-        <v>1415</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D129" t="n">
         <v>2</v>
       </c>
       <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="n">
+        <v>4</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-18443</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>-68185</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>5784</v>
+      </c>
+      <c r="R129" t="n">
+        <v>-62401</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-0.501</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>-10495</v>
+      </c>
+      <c r="O130" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P130" s="2" t="n">
+        <v>-209710</v>
+      </c>
+      <c r="Q130" s="2" t="n">
+        <v>36125</v>
+      </c>
+      <c r="R130" s="2" t="n">
+        <v>-173586</v>
+      </c>
+      <c r="S130" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>9</v>
+      </c>
+      <c r="E132" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H132" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I132" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J132" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N132" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P132" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R132" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S132" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" t="n">
         <v>100</v>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="n">
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="n">
         <v>8.56</v>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="n">
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="n">
         <v>12.69</v>
       </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="n">
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="n">
         <v>8.56</v>
       </c>
-      <c r="N129" t="n">
+      <c r="N133" t="n">
         <v>57466</v>
       </c>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="n">
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="n">
         <v>114933</v>
       </c>
-      <c r="Q129" t="n">
+      <c r="Q133" t="n">
         <v>667</v>
       </c>
-      <c r="R129" t="n">
+      <c r="R133" t="n">
         <v>115600</v>
       </c>
-      <c r="S129" t="n">
+      <c r="S133" t="n">
         <v>1411</v>
       </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>1</v>
-      </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N130" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>257</v>
-      </c>
-      <c r="R130" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S130" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" t="n">
-        <v>100</v>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="n">
-        <v>4.029</v>
-      </c>
-      <c r="N131" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="n">
-        <v>35381</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>269</v>
-      </c>
-      <c r="R131" t="n">
-        <v>35650</v>
-      </c>
-      <c r="S131" t="n">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr"/>
-      <c r="M132" s="2" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="N132" s="2" t="n">
-        <v>5349</v>
-      </c>
-      <c r="O132" s="2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P132" s="2" t="n">
-        <v>69535</v>
-      </c>
-      <c r="Q132" s="2" t="n">
-        <v>3332</v>
-      </c>
-      <c r="R132" s="2" t="n">
-        <v>72867</v>
-      </c>
-      <c r="S132" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G134" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I134" t="n">
-        <v>3.38</v>
-      </c>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K134" t="n">
-        <v>3</v>
-      </c>
-      <c r="L134" t="n">
-        <v>1.75</v>
-      </c>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
       <c r="M134" t="n">
-        <v>-1.213</v>
+        <v>-8.304</v>
       </c>
       <c r="N134" t="n">
-        <v>-744</v>
+        <v>-74087</v>
       </c>
       <c r="O134" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>-6692</v>
+        <v>-74087</v>
       </c>
       <c r="Q134" t="n">
-        <v>2139</v>
+        <v>257</v>
       </c>
       <c r="R134" t="n">
-        <v>-4553</v>
+        <v>-73830</v>
       </c>
       <c r="S134" t="n">
-        <v>1415</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
         <v>100</v>
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>8.56</v>
+        <v>4.03</v>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
-        <v>12.69</v>
+        <v>4.03</v>
       </c>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="n">
-        <v>8.56</v>
+        <v>4.029</v>
       </c>
       <c r="N135" t="n">
-        <v>57466</v>
+        <v>35381</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="n">
-        <v>114933</v>
+        <v>35381</v>
       </c>
       <c r="Q135" t="n">
-        <v>667</v>
+        <v>269</v>
       </c>
       <c r="R135" t="n">
-        <v>115600</v>
+        <v>35650</v>
       </c>
       <c r="S135" t="n">
-        <v>1411</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -6051,237 +5954,532 @@
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>8.300000000000001</v>
+        <v>2.96</v>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>-2.963</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-12121</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-12121</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>121</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J137" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="n">
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="n">
+        <v>-0.074</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>4101</v>
+      </c>
+      <c r="O137" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P137" s="2" t="n">
+        <v>57414</v>
+      </c>
+      <c r="Q137" s="2" t="n">
+        <v>3453</v>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>60867</v>
+      </c>
+      <c r="S137" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>9</v>
+      </c>
+      <c r="E139" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H139" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I139" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J139" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K139" t="n">
         <v>3</v>
       </c>
-      <c r="M136" t="n">
+      <c r="L139" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M139" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N139" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P139" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R139" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" t="n">
+        <v>100</v>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N140" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>667</v>
+      </c>
+      <c r="R140" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="n">
+        <v>3</v>
+      </c>
+      <c r="M141" t="n">
         <v>-8.304</v>
       </c>
-      <c r="N136" t="n">
+      <c r="N141" t="n">
         <v>-74087</v>
       </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
         <v>-74087</v>
       </c>
-      <c r="Q136" t="n">
+      <c r="Q141" t="n">
         <v>257</v>
       </c>
-      <c r="R136" t="n">
+      <c r="R141" t="n">
         <v>-73830</v>
       </c>
-      <c r="S136" t="n">
+      <c r="S141" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D137" t="n">
+      <c r="D142" t="n">
         <v>1</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E142" t="n">
         <v>100</v>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="n">
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="n">
         <v>4.03</v>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="n">
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="n">
         <v>4.03</v>
       </c>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="n">
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="n">
         <v>1</v>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="n">
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="n">
         <v>4.029</v>
       </c>
-      <c r="N137" t="n">
+      <c r="N142" t="n">
         <v>35381</v>
       </c>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="n">
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="n">
         <v>35381</v>
       </c>
-      <c r="Q137" t="n">
+      <c r="Q142" t="n">
         <v>269</v>
       </c>
-      <c r="R137" t="n">
+      <c r="R142" t="n">
         <v>35650</v>
       </c>
-      <c r="S137" t="n">
+      <c r="S142" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>수동매매</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="n">
+        <v>5</v>
+      </c>
+      <c r="M143" t="n">
+        <v>-2.963</v>
+      </c>
+      <c r="N143" t="n">
+        <v>-12121</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>-12121</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>121</v>
+      </c>
+      <c r="R143" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="S143" t="n">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D138" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G138" s="2" t="n">
+      <c r="D144" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G144" s="2" t="n">
         <v>3.38</v>
       </c>
-      <c r="H138" s="2" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I138" s="2" t="n">
+      <c r="H144" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I144" s="2" t="n">
         <v>12.69</v>
       </c>
-      <c r="J138" s="2" t="n">
+      <c r="J144" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K138" s="2" t="n">
+      <c r="K144" s="2" t="n">
         <v>3.12</v>
       </c>
-      <c r="L138" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M138" s="2" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="N138" s="2" t="n">
-        <v>5349</v>
-      </c>
-      <c r="O138" s="2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P138" s="2" t="n">
-        <v>69535</v>
-      </c>
-      <c r="Q138" s="2" t="n">
-        <v>3332</v>
-      </c>
-      <c r="R138" s="2" t="n">
-        <v>72867</v>
-      </c>
-      <c r="S138" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="L144" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>-0.074</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>4101</v>
+      </c>
+      <c r="O144" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P144" s="2" t="n">
+        <v>57414</v>
+      </c>
+      <c r="Q144" s="2" t="n">
+        <v>3453</v>
+      </c>
+      <c r="R144" s="2" t="n">
+        <v>60867</v>
+      </c>
+      <c r="S144" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>미국수동</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-      <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="inlineStr"/>
-      <c r="M140" s="2" t="inlineStr"/>
-      <c r="N140" s="2" t="inlineStr"/>
-      <c r="O140" s="2" t="inlineStr"/>
-      <c r="P140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="D146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" s="2" t="inlineStr"/>
+      <c r="P146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" s="2" t="inlineStr"/>
-      <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-      <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="2" t="inlineStr"/>
-      <c r="M142" s="2" t="inlineStr"/>
-      <c r="N142" s="2" t="inlineStr"/>
-      <c r="O142" s="2" t="inlineStr"/>
-      <c r="P142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" s="2" t="inlineStr"/>
+      <c r="D148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr"/>
+      <c r="O148" s="2" t="inlineStr"/>
+      <c r="P148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -5981,7 +5981,7 @@
         <v>-12000</v>
       </c>
       <c r="S136" t="n">
-        <v>1380</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="137">
@@ -6333,7 +6333,7 @@
         <v>-12000</v>
       </c>
       <c r="S143" t="n">
-        <v>1380</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="144">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -5981,7 +5981,7 @@
         <v>-12000</v>
       </c>
       <c r="S136" t="n">
-        <v>1376</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="137">
@@ -6333,7 +6333,7 @@
         <v>-12000</v>
       </c>
       <c r="S143" t="n">
-        <v>1376</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="144">

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S148"/>
+  <dimension ref="A1:S152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1280,122 +1280,120 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>통합</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>-2.291</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-28796</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-178577</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8926</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-169651</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="G14" s="2" t="n">
+      <c r="D15" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="I14" s="2" t="n">
+      <c r="H15" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>-1510</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>-342787</v>
-      </c>
-      <c r="Q14" s="2" t="n">
-        <v>63360</v>
-      </c>
-      <c r="R14" s="2" t="n">
-        <v>-279427</v>
-      </c>
-      <c r="S14" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>주도주</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>06/08~06/12</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-3.964</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-58941</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-176822</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1322</v>
-      </c>
-      <c r="R16" t="n">
-        <v>-175500</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1415</v>
-      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="n">
+        <v>-0.143</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>-1932</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>-521364</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>72286</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>-449078</v>
+      </c>
+      <c r="S15" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1410,53 +1408,47 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>06/15~06/19</t>
+          <t>06/08~06/12</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="I17" t="n">
-        <v>19.29</v>
-      </c>
+        <v>3.96</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.71</v>
-      </c>
+        <v>4.35</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.378</v>
+        <v>-3.964</v>
       </c>
       <c r="N17" t="n">
-        <v>16263</v>
+        <v>-58941</v>
       </c>
       <c r="O17" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>227688</v>
+        <v>-176822</v>
       </c>
       <c r="Q17" t="n">
-        <v>2172</v>
+        <v>1322</v>
       </c>
       <c r="R17" t="n">
-        <v>229860</v>
+        <v>-175500</v>
       </c>
       <c r="S17" t="n">
         <v>1415</v>
@@ -1475,47 +1467,53 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>06/22~06/26</t>
+          <t>06/15~06/19</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+        <v>3.69</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7.79</v>
+      </c>
       <c r="H18" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="I18" t="n">
+        <v>19.29</v>
+      </c>
       <c r="J18" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>4.76</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.71</v>
+      </c>
       <c r="L18" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.001</v>
+        <v>2.378</v>
       </c>
       <c r="N18" t="n">
-        <v>-21403</v>
+        <v>16263</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P18" t="n">
-        <v>-235428</v>
+        <v>227688</v>
       </c>
       <c r="Q18" t="n">
-        <v>2878</v>
+        <v>2172</v>
       </c>
       <c r="R18" t="n">
-        <v>-232550</v>
+        <v>229860</v>
       </c>
       <c r="S18" t="n">
         <v>1415</v>
@@ -1534,53 +1532,47 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4.74</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
+        <v>8.44</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>3.33</v>
+        <v>0.91</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.022</v>
+        <v>-3.001</v>
       </c>
       <c r="N19" t="n">
-        <v>14731</v>
+        <v>-21403</v>
       </c>
       <c r="O19" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>58925</v>
+        <v>-235428</v>
       </c>
       <c r="Q19" t="n">
-        <v>1075</v>
+        <v>2878</v>
       </c>
       <c r="R19" t="n">
-        <v>60000</v>
+        <v>-232550</v>
       </c>
       <c r="S19" t="n">
         <v>1415</v>
@@ -1599,53 +1591,53 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>0.67</v>
+        <v>7.37</v>
       </c>
       <c r="G20" t="n">
-        <v>1.34</v>
+        <v>4.74</v>
       </c>
       <c r="H20" t="n">
-        <v>1.38</v>
+        <v>2.94</v>
       </c>
       <c r="I20" t="n">
-        <v>4.21</v>
+        <v>4.74</v>
       </c>
       <c r="J20" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.021</v>
+        <v>-1.022</v>
       </c>
       <c r="N20" t="n">
-        <v>-521</v>
+        <v>14731</v>
       </c>
       <c r="O20" t="n">
-        <v>0.67</v>
+        <v>2.46</v>
       </c>
       <c r="P20" t="n">
-        <v>-4171</v>
+        <v>58925</v>
       </c>
       <c r="Q20" t="n">
-        <v>1720</v>
+        <v>1075</v>
       </c>
       <c r="R20" t="n">
-        <v>-2451</v>
+        <v>60000</v>
       </c>
       <c r="S20" t="n">
         <v>1415</v>
@@ -1664,43 +1656,53 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.67</v>
+      </c>
       <c r="G21" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>1.34</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.38</v>
+      </c>
       <c r="I21" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>4.21</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.27</v>
+      </c>
       <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="M21" t="n">
-        <v>8.81</v>
+        <v>-0.021</v>
       </c>
       <c r="N21" t="n">
-        <v>85744</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
+        <v>-521</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.67</v>
+      </c>
       <c r="P21" t="n">
-        <v>342974</v>
+        <v>-4171</v>
       </c>
       <c r="Q21" t="n">
-        <v>1131</v>
+        <v>1720</v>
       </c>
       <c r="R21" t="n">
-        <v>344105</v>
+        <v>-2451</v>
       </c>
       <c r="S21" t="n">
         <v>1415</v>
@@ -1719,53 +1721,43 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.21</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="H22" t="n">
-        <v>9.42</v>
-      </c>
+        <v>8.81</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="J22" t="n">
-        <v>11.77</v>
-      </c>
+        <v>11.03</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L22" t="n">
-        <v>8.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>1.361</v>
+        <v>8.81</v>
       </c>
       <c r="N22" t="n">
-        <v>11916</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4.43</v>
-      </c>
+        <v>85744</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>71497</v>
+        <v>342974</v>
       </c>
       <c r="Q22" t="n">
-        <v>583</v>
+        <v>1131</v>
       </c>
       <c r="R22" t="n">
-        <v>72080</v>
+        <v>344105</v>
       </c>
       <c r="S22" t="n">
         <v>1415</v>
@@ -1784,308 +1776,308 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>07/20~07/24</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="J23" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="N23" t="n">
+        <v>11916</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P23" t="n">
+        <v>71497</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>583</v>
+      </c>
+      <c r="R23" t="n">
+        <v>72080</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>주도주</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D24" t="n">
         <v>2</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>50</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>1.27</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>4.87</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>4.6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>4.87</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>4.6</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>0.133</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>4036</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>1.27</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>8073</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>427</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>8500</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>주도주</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D25" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E25" s="2" t="n">
         <v>40.4</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F25" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>6.27</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I25" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J25" s="2" t="n">
         <v>11.77</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K25" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="L25" s="2" t="n">
         <v>1.52</v>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="M25" s="2" t="n">
         <v>0.535</v>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="N25" s="2" t="n">
         <v>5630</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="O25" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="P25" s="2" t="n">
         <v>292736</v>
       </c>
-      <c r="Q24" s="2" t="n">
+      <c r="Q25" s="2" t="n">
         <v>11308</v>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="R25" s="2" t="n">
         <v>304044</v>
       </c>
-      <c r="S24" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>ROCKET</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>ABC-VCP</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>TV알림</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>27</v>
-      </c>
-      <c r="E32" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G32" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I32" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J32" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L32" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N32" t="n">
-        <v>507</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P32" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R32" t="n">
-        <v>15210</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2100,53 +2092,53 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E33" t="n">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="F33" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="G33" t="n">
-        <v>3.01</v>
+        <v>5.47</v>
       </c>
       <c r="H33" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="I33" t="n">
-        <v>13.15</v>
+        <v>17.35</v>
       </c>
       <c r="J33" t="n">
-        <v>5.82</v>
+        <v>20.1</v>
       </c>
       <c r="K33" t="n">
-        <v>313.5</v>
+        <v>185.95</v>
       </c>
       <c r="L33" t="n">
-        <v>175.2</v>
+        <v>187.46</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.703</v>
+        <v>0.274</v>
       </c>
       <c r="N33" t="n">
-        <v>-1271</v>
+        <v>507</v>
       </c>
       <c r="O33" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="P33" t="n">
-        <v>-57188</v>
+        <v>13680</v>
       </c>
       <c r="Q33" t="n">
-        <v>2829</v>
+        <v>1530</v>
       </c>
       <c r="R33" t="n">
-        <v>-54359</v>
+        <v>15210</v>
       </c>
       <c r="S33" t="n">
         <v>1415</v>
@@ -2165,53 +2157,53 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E34" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="F34" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="G34" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="H34" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I34" t="n">
-        <v>8.68</v>
+        <v>13.15</v>
       </c>
       <c r="J34" t="n">
-        <v>9.01</v>
+        <v>5.82</v>
       </c>
       <c r="K34" t="n">
-        <v>247.7</v>
+        <v>313.5</v>
       </c>
       <c r="L34" t="n">
-        <v>174.67</v>
+        <v>175.2</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.288</v>
+        <v>-0.703</v>
       </c>
       <c r="N34" t="n">
-        <v>1187</v>
+        <v>-1271</v>
       </c>
       <c r="O34" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="P34" t="n">
-        <v>36789</v>
+        <v>-57188</v>
       </c>
       <c r="Q34" t="n">
-        <v>3306</v>
+        <v>2829</v>
       </c>
       <c r="R34" t="n">
-        <v>40095</v>
+        <v>-54359</v>
       </c>
       <c r="S34" t="n">
         <v>1415</v>
@@ -2230,53 +2222,53 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E35" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="F35" t="n">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="G35" t="n">
-        <v>6.86</v>
+        <v>3.14</v>
       </c>
       <c r="H35" t="n">
-        <v>4.11</v>
+        <v>2.76</v>
       </c>
       <c r="I35" t="n">
-        <v>11.14</v>
+        <v>8.68</v>
       </c>
       <c r="J35" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="K35" t="n">
-        <v>533.86</v>
+        <v>247.7</v>
       </c>
       <c r="L35" t="n">
-        <v>403.59</v>
+        <v>174.67</v>
       </c>
       <c r="M35" t="n">
-        <v>1.375</v>
+        <v>-0.288</v>
       </c>
       <c r="N35" t="n">
-        <v>8720</v>
+        <v>1187</v>
       </c>
       <c r="O35" t="n">
-        <v>3.53</v>
+        <v>1.3</v>
       </c>
       <c r="P35" t="n">
-        <v>52321</v>
+        <v>36789</v>
       </c>
       <c r="Q35" t="n">
-        <v>523</v>
+        <v>3306</v>
       </c>
       <c r="R35" t="n">
-        <v>52844</v>
+        <v>40095</v>
       </c>
       <c r="S35" t="n">
         <v>1415</v>
@@ -2295,53 +2287,53 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F36" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="G36" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="H36" t="n">
-        <v>1.26</v>
+        <v>4.11</v>
       </c>
       <c r="I36" t="n">
-        <v>7.95</v>
+        <v>11.14</v>
       </c>
       <c r="J36" t="n">
-        <v>2.19</v>
+        <v>9.65</v>
       </c>
       <c r="K36" t="n">
-        <v>800.2</v>
+        <v>533.86</v>
       </c>
       <c r="L36" t="n">
-        <v>60.03</v>
+        <v>403.59</v>
       </c>
       <c r="M36" t="n">
-        <v>2.446</v>
+        <v>1.375</v>
       </c>
       <c r="N36" t="n">
-        <v>5075</v>
+        <v>8720</v>
       </c>
       <c r="O36" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P36" t="n">
-        <v>45679</v>
+        <v>52321</v>
       </c>
       <c r="Q36" t="n">
-        <v>661</v>
+        <v>523</v>
       </c>
       <c r="R36" t="n">
-        <v>46340</v>
+        <v>52844</v>
       </c>
       <c r="S36" t="n">
         <v>1415</v>
@@ -2360,295 +2352,301 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F37" t="n">
-        <v>1.14</v>
+        <v>4.39</v>
       </c>
       <c r="G37" t="n">
-        <v>6.04</v>
+        <v>7.08</v>
       </c>
       <c r="H37" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I37" t="n">
-        <v>13.51</v>
+        <v>7.95</v>
       </c>
       <c r="J37" t="n">
-        <v>4.74</v>
+        <v>2.19</v>
       </c>
       <c r="K37" t="n">
-        <v>2281.51</v>
+        <v>800.2</v>
       </c>
       <c r="L37" t="n">
-        <v>27.54</v>
+        <v>60.03</v>
       </c>
       <c r="M37" t="n">
-        <v>1.758</v>
+        <v>2.446</v>
       </c>
       <c r="N37" t="n">
-        <v>851</v>
+        <v>5075</v>
       </c>
       <c r="O37" t="n">
-        <v>1.14</v>
+        <v>3.51</v>
       </c>
       <c r="P37" t="n">
-        <v>13616</v>
+        <v>45679</v>
       </c>
       <c r="Q37" t="n">
-        <v>1561</v>
+        <v>661</v>
       </c>
       <c r="R37" t="n">
-        <v>15177</v>
+        <v>46340</v>
       </c>
       <c r="S37" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>16</v>
+      </c>
+      <c r="E38" t="n">
+        <v>50</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I38" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L38" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N38" t="n">
+        <v>851</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P38" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R38" t="n">
+        <v>15177</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D39" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E39" s="2" t="n">
         <v>41.8</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F39" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>2.87</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="I39" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J39" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K39" s="2" t="n">
         <v>600.88</v>
       </c>
-      <c r="L38" s="2" t="n">
+      <c r="L39" s="2" t="n">
         <v>163.85</v>
       </c>
-      <c r="M38" s="2" t="n">
+      <c r="M39" s="2" t="n">
         <v>0.188</v>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="N39" s="2" t="n">
         <v>783</v>
       </c>
-      <c r="O38" s="2" t="n">
+      <c r="O39" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="P38" s="2" t="n">
+      <c r="P39" s="2" t="n">
         <v>156785</v>
       </c>
-      <c r="Q38" s="2" t="n">
+      <c r="Q39" s="2" t="n">
         <v>12072</v>
       </c>
-      <c r="R38" s="2" t="n">
+      <c r="R39" s="2" t="n">
         <v>168857</v>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D41" t="n">
         <v>3</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="n">
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="n">
         <v>0.34</v>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
         <v>0.49</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
         <v>13.35</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M41" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N41" t="n">
         <v>-4880</v>
       </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q41" t="n">
         <v>1291</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R41" t="n">
         <v>-13350</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S41" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="n">
+      <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="n">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="n">
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="n">
         <v>13.35</v>
       </c>
-      <c r="M41" s="2" t="n">
+      <c r="M42" s="2" t="n">
         <v>-0.341</v>
       </c>
-      <c r="N41" s="2" t="n">
+      <c r="N42" s="2" t="n">
         <v>-4880</v>
       </c>
-      <c r="O41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2" t="n">
+      <c r="O42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2" t="n">
         <v>-14641</v>
       </c>
-      <c r="Q41" s="2" t="n">
+      <c r="Q42" s="2" t="n">
         <v>1291</v>
       </c>
-      <c r="R41" s="2" t="n">
+      <c r="R42" s="2" t="n">
         <v>-13350</v>
       </c>
-      <c r="S41" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>삼닉v3_추세</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="M43" t="n">
-        <v>-0.912</v>
-      </c>
-      <c r="N43" t="n">
-        <v>-13839</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>-138394</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4519</v>
-      </c>
-      <c r="R43" t="n">
-        <v>-133875</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1415</v>
-      </c>
+      <c r="S42" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2663,11 +2661,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/03~08/07</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2677,445 +2675,445 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0.49</v>
+        <v>0.91</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>0.59</v>
+        <v>2.28</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-0.912</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-13839</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>-138394</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4519</v>
+      </c>
+      <c r="R44" t="n">
+        <v>-133875</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>삼닉v3_추세</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="n">
         <v>27.47</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M45" t="n">
         <v>-0.486</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N45" t="n">
         <v>-7995</v>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
         <v>-15989</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q45" t="n">
         <v>989</v>
       </c>
-      <c r="R44" t="n">
+      <c r="R45" t="n">
         <v>-15000</v>
       </c>
-      <c r="S44" t="n">
+      <c r="S45" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_추세</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D46" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="n">
+      <c r="E46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="n">
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="n">
         <v>29.57</v>
       </c>
-      <c r="M45" s="2" t="n">
+      <c r="M46" s="2" t="n">
         <v>-0.841</v>
       </c>
-      <c r="N45" s="2" t="n">
+      <c r="N46" s="2" t="n">
         <v>-12865</v>
       </c>
-      <c r="O45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2" t="n">
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
         <v>-154383</v>
       </c>
-      <c r="Q45" s="2" t="n">
+      <c r="Q46" s="2" t="n">
         <v>5508</v>
       </c>
-      <c r="R45" s="2" t="n">
+      <c r="R46" s="2" t="n">
         <v>-148875</v>
       </c>
-      <c r="S45" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D48" t="n">
         <v>12</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E48" t="n">
         <v>16.7</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F48" t="n">
         <v>0.72</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G48" t="n">
         <v>0.44</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H48" t="n">
         <v>0.64</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I48" t="n">
         <v>0.84</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J48" t="n">
         <v>1.81</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K48" t="n">
         <v>14.12</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L48" t="n">
         <v>26.24</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M48" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N48" t="n">
         <v>-6941</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O48" t="n">
         <v>0.14</v>
       </c>
-      <c r="P47" t="n">
+      <c r="P48" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q48" t="n">
         <v>5515</v>
       </c>
-      <c r="R47" t="n">
+      <c r="R48" t="n">
         <v>-77775</v>
       </c>
-      <c r="S47" t="n">
+      <c r="S48" t="n">
         <v>1415</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_MA</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D49" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E49" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F49" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="H49" s="2" t="n">
         <v>0.64</v>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="I49" s="2" t="n">
         <v>0.84</v>
       </c>
-      <c r="J48" s="2" t="n">
+      <c r="J49" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="K49" s="2" t="n">
         <v>14.12</v>
       </c>
-      <c r="L48" s="2" t="n">
+      <c r="L49" s="2" t="n">
         <v>26.24</v>
       </c>
-      <c r="M48" s="2" t="n">
+      <c r="M49" s="2" t="n">
         <v>-0.461</v>
       </c>
-      <c r="N48" s="2" t="n">
+      <c r="N49" s="2" t="n">
         <v>-6941</v>
       </c>
-      <c r="O48" s="2" t="n">
+      <c r="O49" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="P48" s="2" t="n">
+      <c r="P49" s="2" t="n">
         <v>-83290</v>
       </c>
-      <c r="Q48" s="2" t="n">
+      <c r="Q49" s="2" t="n">
         <v>5515</v>
       </c>
-      <c r="R48" s="2" t="n">
+      <c r="R49" s="2" t="n">
         <v>-77775</v>
       </c>
-      <c r="S48" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="S49" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>삼닉v3_미분류</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="D51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>5minHL</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="D53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>5minHL2</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="D55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>5minHL_동시</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>5minHL_미분류</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="M58" t="n">
-        <v>-2.747</v>
-      </c>
-      <c r="N58" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>-2426</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>26</v>
-      </c>
-      <c r="R58" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="S58" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3130,53 +3128,47 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G59" t="n">
-        <v>2.47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I59" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1279.97</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
-        <v>875.09</v>
+        <v>49.85</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.191</v>
+        <v>-2.747</v>
       </c>
       <c r="N59" t="n">
-        <v>4951</v>
+        <v>-2426</v>
       </c>
       <c r="O59" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>29704</v>
+        <v>-2426</v>
       </c>
       <c r="Q59" t="n">
-        <v>756</v>
+        <v>26</v>
       </c>
       <c r="R59" t="n">
-        <v>30460</v>
+        <v>-2400</v>
       </c>
       <c r="S59" t="n">
         <v>1415</v>
@@ -3195,53 +3187,53 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="G60" t="n">
-        <v>0.08</v>
+        <v>2.47</v>
       </c>
       <c r="H60" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="I60" t="n">
-        <v>0.08</v>
+        <v>4.6</v>
       </c>
       <c r="J60" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="K60" t="n">
-        <v>4319.93</v>
+        <v>1279.97</v>
       </c>
       <c r="L60" t="n">
-        <v>1351.81</v>
+        <v>875.09</v>
       </c>
       <c r="M60" t="n">
-        <v>-2.059</v>
+        <v>-0.191</v>
       </c>
       <c r="N60" t="n">
-        <v>-3794</v>
+        <v>4951</v>
       </c>
       <c r="O60" t="n">
-        <v>0.01</v>
+        <v>2.93</v>
       </c>
       <c r="P60" t="n">
-        <v>-11383</v>
+        <v>29704</v>
       </c>
       <c r="Q60" t="n">
-        <v>153</v>
+        <v>756</v>
       </c>
       <c r="R60" t="n">
-        <v>-11230</v>
+        <v>30460</v>
       </c>
       <c r="S60" t="n">
         <v>1415</v>
@@ -3260,43 +3252,53 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>100</v>
-      </c>
-      <c r="F61" t="inlineStr"/>
+        <v>33.3</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G61" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3.13</v>
+      </c>
       <c r="I61" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3.61</v>
+      </c>
       <c r="K61" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L61" t="inlineStr"/>
+        <v>4319.93</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1351.81</v>
+      </c>
       <c r="M61" t="n">
-        <v>1.678</v>
+        <v>-2.059</v>
       </c>
       <c r="N61" t="n">
-        <v>1670</v>
-      </c>
-      <c r="O61" t="inlineStr"/>
+        <v>-3794</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.01</v>
+      </c>
       <c r="P61" t="n">
-        <v>1670</v>
+        <v>-11383</v>
       </c>
       <c r="Q61" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="R61" t="n">
-        <v>1700</v>
+        <v>-11230</v>
       </c>
       <c r="S61" t="n">
         <v>1415</v>
@@ -3315,609 +3317,605 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
-        <v>5756.96</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>-6.785</v>
+        <v>1.678</v>
       </c>
       <c r="N62" t="n">
-        <v>-7272</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
+        <v>1670</v>
+      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>-14543</v>
+        <v>1670</v>
       </c>
       <c r="Q62" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="R62" t="n">
-        <v>-14485</v>
+        <v>1700</v>
       </c>
       <c r="S62" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>5minHL_미분류</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="n">
+        <v>5756.96</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-6.785</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-7272</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-14543</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>58</v>
+      </c>
+      <c r="R63" t="n">
+        <v>-14485</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>5minHL_미분류</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D64" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E64" s="2" t="n">
         <v>38.5</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F64" s="2" t="n">
         <v>1.71</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="H64" s="2" t="n">
         <v>3.89</v>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="I64" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="J63" s="2" t="n">
+      <c r="J64" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="K63" s="2" t="n">
+      <c r="K64" s="2" t="n">
         <v>1633.99</v>
       </c>
-      <c r="L63" s="2" t="n">
+      <c r="L64" s="2" t="n">
         <v>2111.58</v>
       </c>
-      <c r="M63" s="2" t="n">
+      <c r="M64" s="2" t="n">
         <v>-1.689</v>
       </c>
-      <c r="N63" s="2" t="n">
+      <c r="N64" s="2" t="n">
         <v>232</v>
       </c>
-      <c r="O63" s="2" t="n">
+      <c r="O64" s="2" t="n">
         <v>1.07</v>
       </c>
-      <c r="P63" s="2" t="n">
+      <c r="P64" s="2" t="n">
         <v>3022</v>
       </c>
-      <c r="Q63" s="2" t="n">
+      <c r="Q64" s="2" t="n">
         <v>1023</v>
       </c>
-      <c r="R63" s="2" t="n">
+      <c r="R64" s="2" t="n">
         <v>4045</v>
       </c>
-      <c r="S63" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="S64" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr"/>
-      <c r="N65" s="2" t="inlineStr"/>
-      <c r="O65" s="2" t="inlineStr"/>
-      <c r="P65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="D66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D68" t="n">
         <v>1</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E68" t="n">
         <v>100</v>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="n">
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
         <v>1.3</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="n">
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
         <v>1.3</v>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="n">
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="n">
         <v>7</v>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="n">
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="n">
         <v>1.299</v>
       </c>
-      <c r="N67" t="n">
+      <c r="N68" t="n">
         <v>6421</v>
       </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="n">
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
         <v>6421</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="Q68" t="n">
         <v>149</v>
       </c>
-      <c r="R67" t="n">
+      <c r="R68" t="n">
         <v>6570</v>
       </c>
-      <c r="S67" t="n">
+      <c r="S68" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_1</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E69" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="n">
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="n">
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="n">
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="n">
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="n">
         <v>1.299</v>
       </c>
-      <c r="N68" s="2" t="n">
+      <c r="N69" s="2" t="n">
         <v>6421</v>
       </c>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="n">
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="n">
         <v>6421</v>
       </c>
-      <c r="Q68" s="2" t="n">
+      <c r="Q69" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="R68" s="2" t="n">
+      <c r="R69" s="2" t="n">
         <v>6570</v>
       </c>
-      <c r="S68" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="S69" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VOLUME_2</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="D71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>KR_TR_VCP1</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="D73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>KR_TR_BASE</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="D75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>KR_TR_JEO2</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="D77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>KR_TR_MA</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="D79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>KR_TR_ADD1</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="D81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>미국VCP</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>US_TR_ORD_A</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>08/10~08/14</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="n">
-        <v>3</v>
-      </c>
-      <c r="M84" t="n">
-        <v>-10.012</v>
-      </c>
-      <c r="N84" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>-71414</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>949</v>
-      </c>
-      <c r="R84" t="n">
-        <v>-70465</v>
-      </c>
-      <c r="S84" t="n">
-        <v>1411</v>
-      </c>
+      <c r="D83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3932,56 +3930,50 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>08/10~08/14</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G85" t="n">
-        <v>2.49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="I85" t="n">
-        <v>7.7</v>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="K85" t="n">
-        <v>14.2</v>
-      </c>
+        <v>10.01</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.896</v>
+        <v>-10.012</v>
       </c>
       <c r="N85" t="n">
-        <v>-471</v>
+        <v>-71414</v>
       </c>
       <c r="O85" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>9429</v>
+        <v>-71414</v>
       </c>
       <c r="Q85" t="n">
-        <v>6892</v>
+        <v>949</v>
       </c>
       <c r="R85" t="n">
-        <v>16322</v>
+        <v>-70465</v>
       </c>
       <c r="S85" t="n">
-        <v>1373</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="86">
@@ -3997,125 +3989,186 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="n">
+        <v>50</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I86" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J86" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="K86" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L86" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M86" t="n">
+        <v>-0.896</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-471</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P86" t="n">
+        <v>9429</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>6892</v>
+      </c>
+      <c r="R86" t="n">
+        <v>16322</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>US_TR_ORD_A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D87" t="n">
         <v>5</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E87" t="n">
         <v>40</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F87" t="n">
         <v>0.14</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G87" t="n">
         <v>2.69</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H87" t="n">
         <v>3.1</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I87" t="n">
         <v>4.37</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J87" t="n">
         <v>6.38</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K87" t="n">
         <v>18</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L87" t="n">
         <v>9</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M87" t="n">
         <v>-0.787</v>
       </c>
-      <c r="N86" t="n">
+      <c r="N87" t="n">
         <v>-62797</v>
       </c>
-      <c r="O86" t="n">
+      <c r="O87" t="n">
         <v>0.09</v>
       </c>
-      <c r="P86" t="n">
+      <c r="P87" t="n">
         <v>-340821</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="Q87" t="n">
         <v>9807</v>
       </c>
-      <c r="R86" t="n">
+      <c r="R87" t="n">
         <v>-331014</v>
       </c>
-      <c r="S86" t="n">
+      <c r="S87" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>US_TR_ORD_A</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>-1.432</v>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>-24382</v>
-      </c>
-      <c r="O87" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P87" s="2" t="n">
-        <v>-402806</v>
-      </c>
-      <c r="Q87" s="2" t="n">
-        <v>17648</v>
-      </c>
-      <c r="R87" s="2" t="n">
-        <v>-385157</v>
-      </c>
-      <c r="S87" s="2" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M88" t="n">
+        <v>-2.712</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-19055</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>-98361</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>4113</v>
+      </c>
+      <c r="R88" t="n">
+        <v>-94248</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1379</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_1</t>
+          <t>US_TR_ORD_A</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4129,34 +4182,56 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
-      <c r="N89" s="2" t="inlineStr"/>
-      <c r="O89" s="2" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1.574</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>-23790</v>
+      </c>
+      <c r="O89" s="2" t="n">
+        <v>0.18</v>
+      </c>
       <c r="P89" s="2" t="n">
-        <v>0</v>
+        <v>-501167</v>
       </c>
       <c r="Q89" s="2" t="n">
-        <v>0</v>
+        <v>21761</v>
       </c>
       <c r="R89" s="2" t="n">
-        <v>0</v>
+        <v>-479405</v>
       </c>
       <c r="S89" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VOLUME_2</t>
+          <t>US_TR_VOLUME_1</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4197,7 +4272,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>US_TR_VCP1</t>
+          <t>US_TR_VOLUME_2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4238,7 +4313,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>US_TR_BASE</t>
+          <t>US_TR_VCP1</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4277,412 +4352,412 @@
       <c r="S95" s="2" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_BASE</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D99" t="n">
         <v>1</v>
       </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="n">
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
         <v>2.13</v>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="n">
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
         <v>2.13</v>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="n">
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
         <v>1</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M99" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N99" t="n">
         <v>-41586</v>
       </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="Q99" t="n">
         <v>2702</v>
       </c>
-      <c r="R97" t="n">
+      <c r="R99" t="n">
         <v>-38883</v>
       </c>
-      <c r="S97" t="n">
+      <c r="S99" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>US_TR_JEO2</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D98" s="2" t="n">
+      <c r="D100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="n">
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="n">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="n">
         <v>2.13</v>
       </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="n">
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M98" s="2" t="n">
+      <c r="M100" s="2" t="n">
         <v>-2.131</v>
       </c>
-      <c r="N98" s="2" t="n">
+      <c r="N100" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="O98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="2" t="n">
+      <c r="O100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="2" t="n">
         <v>-41586</v>
       </c>
-      <c r="Q98" s="2" t="n">
+      <c r="Q100" s="2" t="n">
         <v>2702</v>
       </c>
-      <c r="R98" s="2" t="n">
+      <c r="R100" s="2" t="n">
         <v>-38883</v>
       </c>
-      <c r="S98" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="S100" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>08/17~08/21</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D102" t="n">
         <v>7</v>
       </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="n">
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="n">
         <v>3.34</v>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="n">
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="n">
         <v>6.17</v>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="n">
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="n">
         <v>8</v>
       </c>
-      <c r="M100" t="n">
+      <c r="M102" t="n">
         <v>-3.337</v>
       </c>
-      <c r="N100" t="n">
+      <c r="N102" t="n">
         <v>-7859</v>
       </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
         <v>-55013</v>
       </c>
-      <c r="Q100" t="n">
+      <c r="Q102" t="n">
         <v>1884</v>
       </c>
-      <c r="R100" t="n">
+      <c r="R102" t="n">
         <v>-53128</v>
       </c>
-      <c r="S100" t="n">
+      <c r="S102" t="n">
         <v>1373</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>08/24~08/28</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D103" t="n">
         <v>3</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E103" t="n">
         <v>66.7</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F103" t="n">
         <v>0.08</v>
       </c>
-      <c r="G101" t="n">
+      <c r="G103" t="n">
         <v>2.89</v>
       </c>
-      <c r="H101" t="n">
+      <c r="H103" t="n">
         <v>3.18</v>
       </c>
-      <c r="I101" t="n">
+      <c r="I103" t="n">
         <v>3.32</v>
       </c>
-      <c r="J101" t="n">
+      <c r="J103" t="n">
         <v>3.18</v>
       </c>
-      <c r="K101" t="n">
+      <c r="K103" t="n">
         <v>18</v>
       </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
         <v>0.864</v>
       </c>
-      <c r="N101" t="n">
+      <c r="N103" t="n">
         <v>-18508</v>
       </c>
-      <c r="O101" t="n">
+      <c r="O103" t="n">
         <v>0.16</v>
       </c>
-      <c r="P101" t="n">
+      <c r="P103" t="n">
         <v>-52375</v>
       </c>
-      <c r="Q101" t="n">
+      <c r="Q103" t="n">
         <v>4226</v>
       </c>
-      <c r="R101" t="n">
+      <c r="R103" t="n">
         <v>-48149</v>
       </c>
-      <c r="S101" t="n">
+      <c r="S103" t="n">
         <v>1383</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>US_TR_MA</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M104" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-38538</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>-80216</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>4813</v>
+      </c>
+      <c r="R104" t="n">
+        <v>-75404</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_MA</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G102" s="2" t="n">
+      <c r="D105" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G105" s="2" t="n">
         <v>2.89</v>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="H105" s="2" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I105" s="2" t="n">
         <v>3.32</v>
       </c>
-      <c r="I102" s="2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J102" s="2" t="n">
+      <c r="J105" s="2" t="n">
         <v>6.17</v>
       </c>
-      <c r="K102" s="2" t="n">
+      <c r="K105" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="L102" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>-2.076</v>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>-11054</v>
-      </c>
-      <c r="O102" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="P102" s="2" t="n">
-        <v>-107388</v>
-      </c>
-      <c r="Q102" s="2" t="n">
-        <v>6110</v>
-      </c>
-      <c r="R102" s="2" t="n">
-        <v>-101277</v>
-      </c>
-      <c r="S102" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_ADD1</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr"/>
-      <c r="P104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>2</v>
-      </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="n">
-        <v>10.49</v>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="n">
-        <v>1</v>
-      </c>
-      <c r="M106" t="n">
-        <v>-7.145</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-27445</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>-54889</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>1054</v>
-      </c>
-      <c r="R106" t="n">
-        <v>-53835</v>
-      </c>
-      <c r="S106" t="n">
-        <v>1373</v>
-      </c>
+      <c r="L105" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-2.042</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-15634</v>
+      </c>
+      <c r="O105" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P105" s="2" t="n">
+        <v>-187604</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>10923</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>-176681</v>
+      </c>
+      <c r="S105" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY</t>
+          <t>US_TR_ADD1</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -4696,50 +4771,34 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="n">
-        <v>7.15</v>
-      </c>
+      <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="n">
-        <v>10.49</v>
-      </c>
+      <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>-7.145</v>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>-27445</v>
-      </c>
-      <c r="O107" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="n">
-        <v>-54889</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="2" t="n">
-        <v>1054</v>
+        <v>0</v>
       </c>
       <c r="R107" s="2" t="n">
-        <v>-53835</v>
+        <v>0</v>
       </c>
       <c r="S107" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_TREND</t>
+          <t>US_TR_LEGACY</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4753,176 +4812,174 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G109" t="n">
-        <v>7.27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I109" t="n">
-        <v>16.31</v>
-      </c>
+        <v>7.15</v>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0.78</v>
-      </c>
+        <v>10.49</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>2.681</v>
+        <v>-7.145</v>
       </c>
       <c r="N109" t="n">
-        <v>3410</v>
+        <v>-27445</v>
       </c>
       <c r="O109" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>134658</v>
+        <v>-54889</v>
       </c>
       <c r="Q109" t="n">
-        <v>7271</v>
+        <v>1054</v>
       </c>
       <c r="R109" t="n">
-        <v>141929</v>
+        <v>-53835</v>
       </c>
       <c r="S109" t="n">
         <v>1373</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-7.145</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>-27445</v>
+      </c>
+      <c r="O110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="2" t="n">
+        <v>-54889</v>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>-53835</v>
+      </c>
+      <c r="S110" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>7</v>
-      </c>
-      <c r="E110" t="n">
-        <v>100</v>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="N110" t="n">
-        <v>18699</v>
-      </c>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="n">
-        <v>86535</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>1828</v>
-      </c>
-      <c r="R110" t="n">
-        <v>88363</v>
-      </c>
-      <c r="S110" t="n">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>US_TR_LEGACY_TREND</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="H111" s="2" t="n">
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>17</v>
+      </c>
+      <c r="E112" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G112" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="H112" t="n">
         <v>2.48</v>
       </c>
-      <c r="I111" s="2" t="n">
+      <c r="I112" t="n">
         <v>16.31</v>
       </c>
-      <c r="J111" s="2" t="n">
+      <c r="J112" t="n">
         <v>5.68</v>
       </c>
-      <c r="K111" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L111" s="2" t="n">
+      <c r="K112" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L112" t="n">
         <v>0.75</v>
       </c>
-      <c r="M111" s="2" t="n">
-        <v>3.695</v>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>7869</v>
-      </c>
-      <c r="O111" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P111" s="2" t="n">
-        <v>221193</v>
-      </c>
-      <c r="Q111" s="2" t="n">
-        <v>9099</v>
-      </c>
-      <c r="R111" s="2" t="n">
-        <v>230292</v>
-      </c>
-      <c r="S111" s="2" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="N112" t="n">
+        <v>3410</v>
+      </c>
+      <c r="O112" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P112" t="n">
+        <v>134658</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>7271</v>
+      </c>
+      <c r="R112" t="n">
+        <v>141929</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1373</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>US_TR_LEGACY_LOW</t>
+          <t>US_TR_LEGACY_TREND</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4936,532 +4993,477 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="n">
-        <v>12</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>-0.54</v>
+        <v>6.16</v>
       </c>
       <c r="N113" t="n">
-        <v>-1280</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
+        <v>18699</v>
+      </c>
+      <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
-        <v>-1280</v>
+        <v>86535</v>
       </c>
       <c r="Q113" t="n">
-        <v>208</v>
+        <v>1828</v>
       </c>
       <c r="R113" t="n">
-        <v>-1072</v>
+        <v>88363</v>
       </c>
       <c r="S113" t="n">
         <v>1383</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>2</v>
+      </c>
+      <c r="E114" t="n">
+        <v>50</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G114" t="n">
+        <v>12</v>
+      </c>
+      <c r="H114" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="I114" t="n">
+        <v>12</v>
+      </c>
+      <c r="J114" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="K114" t="n">
+        <v>13</v>
+      </c>
+      <c r="L114" t="n">
+        <v>13</v>
+      </c>
+      <c r="M114" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-3196</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P114" t="n">
+        <v>-11449</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>330</v>
+      </c>
+      <c r="R114" t="n">
+        <v>-11119</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>US_TR_LEGACY_TREND</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>3.683</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>7018</v>
+      </c>
+      <c r="O115" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="P115" s="2" t="n">
+        <v>209744</v>
+      </c>
+      <c r="Q115" s="2" t="n">
+        <v>9429</v>
+      </c>
+      <c r="R115" s="2" t="n">
+        <v>219173</v>
+      </c>
+      <c r="S115" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>US_TR_LEGACY_LOW</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="n">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
         <v>1</v>
       </c>
-      <c r="E114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="n">
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="n">
         <v>0.54</v>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="n">
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="n">
         <v>0.54</v>
       </c>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="n">
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="n">
         <v>12</v>
       </c>
-      <c r="M114" s="2" t="n">
+      <c r="M117" t="n">
         <v>-0.54</v>
       </c>
-      <c r="N114" s="2" t="n">
+      <c r="N117" t="n">
         <v>-1280</v>
       </c>
-      <c r="O114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" s="2" t="n">
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
         <v>-1280</v>
       </c>
-      <c r="Q114" s="2" t="n">
+      <c r="Q117" t="n">
         <v>208</v>
       </c>
-      <c r="R114" s="2" t="n">
+      <c r="R117" t="n">
         <v>-1072</v>
       </c>
-      <c r="S114" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>KR_TR_VCP2</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr"/>
-      <c r="O116" s="2" t="inlineStr"/>
-      <c r="P116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" s="2" t="inlineStr"/>
+      <c r="S117" t="n">
+        <v>1383</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>US_TR_LEGACY_LOW</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="O118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="2" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>-1072</v>
+      </c>
+      <c r="S118" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>KR_TR_VCP2</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
           <t>US_TR_VCP2</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" s="2" t="inlineStr"/>
-      <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
-      <c r="M118" s="2" t="inlineStr"/>
-      <c r="N118" s="2" t="inlineStr"/>
-      <c r="O118" s="2" t="inlineStr"/>
-      <c r="P118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" t="n">
-        <v>100</v>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N120" t="n">
-        <v>2341</v>
-      </c>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="n">
-        <v>2341</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>34</v>
-      </c>
-      <c r="R120" t="n">
-        <v>2375</v>
-      </c>
-      <c r="S120" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>저점사다리</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="2" t="n">
-        <v>52.73</v>
-      </c>
-      <c r="L121" s="2" t="inlineStr"/>
-      <c r="M121" s="2" t="n">
-        <v>2.102</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>2341</v>
-      </c>
-      <c r="O121" s="2" t="inlineStr"/>
-      <c r="P121" s="2" t="n">
-        <v>2341</v>
-      </c>
-      <c r="Q121" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="R121" s="2" t="n">
-        <v>2375</v>
-      </c>
-      <c r="S121" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>07/13~07/17</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>2</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="n">
-        <v>1</v>
-      </c>
-      <c r="M123" t="n">
-        <v>-2.607</v>
-      </c>
-      <c r="N123" t="n">
-        <v>-8011</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>-16021</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>513</v>
-      </c>
-      <c r="R123" t="n">
-        <v>-15508</v>
-      </c>
-      <c r="S123" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>통합ETF</t>
+          <t>저점사다리</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>분</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>25</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0.74</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J124" t="n">
-        <v>1.32</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N124" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>34</v>
+      </c>
+      <c r="R124" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S124" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>저점사다리</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L124" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="M124" t="n">
-        <v>-0.217</v>
-      </c>
-      <c r="N124" t="n">
-        <v>-13272</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P124" t="n">
-        <v>-53089</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>5913</v>
-      </c>
-      <c r="R124" t="n">
-        <v>-47176</v>
-      </c>
-      <c r="S124" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>07/27~07/31</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>2</v>
-      </c>
-      <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M125" t="n">
-        <v>-0.136</v>
-      </c>
-      <c r="N125" t="n">
-        <v>-2389</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>-4777</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>2924</v>
-      </c>
-      <c r="R125" t="n">
-        <v>-1854</v>
-      </c>
-      <c r="S125" t="n">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>통합ETF</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>08/03~08/07</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E126" t="n">
+      <c r="E125" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="n">
-        <v>14</v>
-      </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="n">
-        <v>1.042</v>
-      </c>
-      <c r="N126" t="n">
-        <v>16180</v>
-      </c>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="n">
-        <v>48540</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>4254</v>
-      </c>
-      <c r="R126" t="n">
-        <v>52794</v>
-      </c>
-      <c r="S126" t="n">
-        <v>1415</v>
-      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="n">
+        <v>2341</v>
+      </c>
+      <c r="Q125" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>2375</v>
+      </c>
+      <c r="S125" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5476,11 +5478,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -5490,36 +5492,36 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>0.86</v>
+        <v>2.61</v>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="n">
-        <v>1.53</v>
+        <v>3.49</v>
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
-        <v>4.67</v>
+        <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>-0.864</v>
+        <v>-2.607</v>
       </c>
       <c r="N127" t="n">
-        <v>-28997</v>
+        <v>-8011</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>-86990</v>
+        <v>-16021</v>
       </c>
       <c r="Q127" t="n">
-        <v>13787</v>
+        <v>513</v>
       </c>
       <c r="R127" t="n">
-        <v>-73203</v>
+        <v>-15508</v>
       </c>
       <c r="S127" t="n">
-        <v>1411</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="128">
@@ -5535,50 +5537,56 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>08/17~08/21</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D128" t="n">
+        <v>4</v>
+      </c>
+      <c r="E128" t="n">
+        <v>25</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K128" t="n">
         <v>1</v>
       </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
-        <v>3</v>
+        <v>5.67</v>
       </c>
       <c r="M128" t="n">
-        <v>-0.867</v>
+        <v>-0.217</v>
       </c>
       <c r="N128" t="n">
-        <v>-29188</v>
+        <v>-13272</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="P128" t="n">
-        <v>-29188</v>
+        <v>-53089</v>
       </c>
       <c r="Q128" t="n">
-        <v>2950</v>
+        <v>5913</v>
       </c>
       <c r="R128" t="n">
-        <v>-26238</v>
+        <v>-47176</v>
       </c>
       <c r="S128" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="129">
@@ -5594,7 +5602,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>08/24~08/28</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -5608,324 +5616,332 @@
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>0.92</v>
+        <v>0.14</v>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="n">
-        <v>1.07</v>
+        <v>0.16</v>
       </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="M129" t="n">
-        <v>-0.918</v>
+        <v>-0.136</v>
       </c>
       <c r="N129" t="n">
-        <v>-18443</v>
+        <v>-2389</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>-68185</v>
+        <v>-4777</v>
       </c>
       <c r="Q129" t="n">
-        <v>5784</v>
+        <v>2924</v>
       </c>
       <c r="R129" t="n">
-        <v>-62401</v>
+        <v>-1854</v>
       </c>
       <c r="S129" t="n">
-        <v>1383</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>통합ETF</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I130" s="2" t="n">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>08/03~08/07</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" t="n">
+        <v>100</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="n">
         <v>2.2</v>
       </c>
-      <c r="J130" s="2" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="M130" s="2" t="n">
-        <v>-0.501</v>
-      </c>
-      <c r="N130" s="2" t="n">
-        <v>-10495</v>
-      </c>
-      <c r="O130" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="P130" s="2" t="n">
-        <v>-209710</v>
-      </c>
-      <c r="Q130" s="2" t="n">
-        <v>36125</v>
-      </c>
-      <c r="R130" s="2" t="n">
-        <v>-173586</v>
-      </c>
-      <c r="S130" s="2" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="n">
+        <v>14</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="N130" t="n">
+        <v>16180</v>
+      </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="n">
+        <v>48540</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>4254</v>
+      </c>
+      <c r="R130" t="n">
+        <v>52794</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M131" t="n">
+        <v>-0.864</v>
+      </c>
+      <c r="N131" t="n">
+        <v>-28997</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>-86990</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>13787</v>
+      </c>
+      <c r="R131" t="n">
+        <v>-73203</v>
+      </c>
+      <c r="S131" t="n">
+        <v>1411</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/17~08/21</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G132" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="I132" t="n">
-        <v>3.38</v>
-      </c>
+        <v>0.87</v>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="n">
-        <v>7.04</v>
+        <v>0.87</v>
       </c>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
+      <c r="L132" t="n">
+        <v>3</v>
+      </c>
       <c r="M132" t="n">
-        <v>-1.213</v>
+        <v>-0.867</v>
       </c>
       <c r="N132" t="n">
-        <v>-744</v>
+        <v>-29188</v>
       </c>
       <c r="O132" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>-6692</v>
+        <v>-29188</v>
       </c>
       <c r="Q132" t="n">
-        <v>2139</v>
+        <v>2950</v>
       </c>
       <c r="R132" t="n">
-        <v>-4553</v>
+        <v>-26238</v>
       </c>
       <c r="S132" t="n">
-        <v>1415</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>수동합계</t>
+          <t>통합ETF</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>혼합</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D133" t="n">
         <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>100</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J133" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="n">
+        <v>1.07</v>
+      </c>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
+      <c r="L133" t="n">
+        <v>4</v>
+      </c>
       <c r="M133" t="n">
-        <v>8.56</v>
+        <v>-0.918</v>
       </c>
       <c r="N133" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O133" t="inlineStr"/>
+        <v>-18443</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
       <c r="P133" t="n">
-        <v>114933</v>
+        <v>-68185</v>
       </c>
       <c r="Q133" t="n">
-        <v>667</v>
+        <v>5784</v>
       </c>
       <c r="R133" t="n">
-        <v>115600</v>
+        <v>-62401</v>
       </c>
       <c r="S133" t="n">
-        <v>1411</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>통합ETF</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H134" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N134" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>257</v>
-      </c>
-      <c r="R134" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S134" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>수동합계</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="n">
-        <v>100</v>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="n">
-        <v>4.029</v>
-      </c>
-      <c r="N135" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="n">
-        <v>35381</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>269</v>
-      </c>
-      <c r="R135" t="n">
-        <v>35650</v>
-      </c>
-      <c r="S135" t="n">
-        <v>1383</v>
-      </c>
+      <c r="I134" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>-0.501</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>-10495</v>
+      </c>
+      <c r="O134" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P134" s="2" t="n">
+        <v>-209710</v>
+      </c>
+      <c r="Q134" s="2" t="n">
+        <v>36125</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>-173586</v>
+      </c>
+      <c r="S134" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5940,342 +5956,332 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>08/31~09/04</t>
+          <t>07/27~07/31</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" t="inlineStr"/>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1.17</v>
+      </c>
       <c r="H136" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I136" t="inlineStr"/>
+        <v>4.19</v>
+      </c>
+      <c r="I136" t="n">
+        <v>3.38</v>
+      </c>
       <c r="J136" t="n">
-        <v>2.96</v>
+        <v>7.04</v>
       </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="n">
-        <v>-2.963</v>
+        <v>-1.213</v>
       </c>
       <c r="N136" t="n">
-        <v>-12121</v>
+        <v>-744</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="P136" t="n">
-        <v>-12121</v>
+        <v>-6692</v>
       </c>
       <c r="Q136" t="n">
-        <v>121</v>
+        <v>2139</v>
       </c>
       <c r="R136" t="n">
-        <v>-12000</v>
+        <v>-4553</v>
       </c>
       <c r="S136" t="n">
-        <v>1379</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" t="inlineStr">
         <is>
           <t>수동합계</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>혼합</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E137" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="I137" s="2" t="n">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="n">
+        <v>100</v>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="n">
         <v>12.69</v>
       </c>
-      <c r="J137" s="2" t="n">
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N137" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>667</v>
+      </c>
+      <c r="R137" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K137" s="2" t="inlineStr"/>
-      <c r="L137" s="2" t="inlineStr"/>
-      <c r="M137" s="2" t="n">
-        <v>-0.074</v>
-      </c>
-      <c r="N137" s="2" t="n">
-        <v>4101</v>
-      </c>
-      <c r="O137" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P137" s="2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="Q137" s="2" t="n">
-        <v>3453</v>
-      </c>
-      <c r="R137" s="2" t="n">
-        <v>60867</v>
-      </c>
-      <c r="S137" s="2" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>257</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1373</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>08/24~08/28</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H139" t="n">
-        <v>4.19</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="J139" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K139" t="n">
-        <v>3</v>
-      </c>
-      <c r="L139" t="n">
-        <v>1.75</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
       <c r="M139" t="n">
-        <v>-1.213</v>
+        <v>4.029</v>
       </c>
       <c r="N139" t="n">
-        <v>-744</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0.86</v>
-      </c>
+        <v>35381</v>
+      </c>
+      <c r="O139" t="inlineStr"/>
       <c r="P139" t="n">
-        <v>-6692</v>
+        <v>35381</v>
       </c>
       <c r="Q139" t="n">
-        <v>2139</v>
+        <v>269</v>
       </c>
       <c r="R139" t="n">
-        <v>-4553</v>
+        <v>35650</v>
       </c>
       <c r="S139" t="n">
-        <v>1415</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>수동매매</t>
+          <t>수동합계</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>혼합</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>08/10~08/14</t>
+          <t>08/31~09/04</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>100</v>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="n">
-        <v>4.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="n">
-        <v>8.56</v>
+        <v>-2.963</v>
       </c>
       <c r="N140" t="n">
-        <v>57466</v>
-      </c>
-      <c r="O140" t="inlineStr"/>
+        <v>-12121</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
       <c r="P140" t="n">
-        <v>114933</v>
+        <v>-12121</v>
       </c>
       <c r="Q140" t="n">
-        <v>667</v>
+        <v>121</v>
       </c>
       <c r="R140" t="n">
-        <v>115600</v>
+        <v>-12000</v>
       </c>
       <c r="S140" t="n">
-        <v>1411</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>08/17~08/21</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="n">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>수동합계</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J141" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="n">
-        <v>3</v>
-      </c>
-      <c r="M141" t="n">
-        <v>-8.304</v>
-      </c>
-      <c r="N141" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>-74087</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>257</v>
-      </c>
-      <c r="R141" t="n">
-        <v>-73830</v>
-      </c>
-      <c r="S141" t="n">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>08/24~08/28</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" t="n">
-        <v>100</v>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="n">
-        <v>4.029</v>
-      </c>
-      <c r="N142" t="n">
-        <v>35381</v>
-      </c>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="n">
-        <v>35381</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>269</v>
-      </c>
-      <c r="R142" t="n">
-        <v>35650</v>
-      </c>
-      <c r="S142" t="n">
-        <v>1383</v>
-      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="n">
+        <v>-0.074</v>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>4101</v>
+      </c>
+      <c r="O141" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P141" s="2" t="n">
+        <v>57414</v>
+      </c>
+      <c r="Q141" s="2" t="n">
+        <v>3453</v>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>60867</v>
+      </c>
+      <c r="S141" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6290,196 +6296,430 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>9</v>
+      </c>
+      <c r="E143" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H143" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I143" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J143" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="K143" t="n">
+        <v>3</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M143" t="n">
+        <v>-1.213</v>
+      </c>
+      <c r="N143" t="n">
+        <v>-744</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P143" t="n">
+        <v>-6692</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>2139</v>
+      </c>
+      <c r="R143" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="S143" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>08/10~08/14</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" t="n">
+        <v>100</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N144" t="n">
+        <v>57466</v>
+      </c>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="n">
+        <v>114933</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>667</v>
+      </c>
+      <c r="R144" t="n">
+        <v>115600</v>
+      </c>
+      <c r="S144" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>08/17~08/21</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="n">
+        <v>3</v>
+      </c>
+      <c r="M145" t="n">
+        <v>-8.304</v>
+      </c>
+      <c r="N145" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>-74087</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>257</v>
+      </c>
+      <c r="R145" t="n">
+        <v>-73830</v>
+      </c>
+      <c r="S145" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>08/24~08/28</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>100</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="N146" t="n">
+        <v>35381</v>
+      </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="n">
+        <v>35381</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>269</v>
+      </c>
+      <c r="R146" t="n">
+        <v>35650</v>
+      </c>
+      <c r="S146" t="n">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
           <t>08/31~09/04</t>
         </is>
       </c>
-      <c r="D143" t="n">
+      <c r="D147" t="n">
         <v>1</v>
       </c>
-      <c r="E143" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="n">
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="n">
         <v>2.96</v>
       </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="n">
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="n">
         <v>2.96</v>
       </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="n">
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="n">
         <v>5</v>
       </c>
-      <c r="M143" t="n">
+      <c r="M147" t="n">
         <v>-2.963</v>
       </c>
-      <c r="N143" t="n">
+      <c r="N147" t="n">
         <v>-12121</v>
       </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
         <v>-12121</v>
       </c>
-      <c r="Q143" t="n">
+      <c r="Q147" t="n">
         <v>121</v>
       </c>
-      <c r="R143" t="n">
+      <c r="R147" t="n">
         <v>-12000</v>
       </c>
-      <c r="S143" t="n">
+      <c r="S147" t="n">
         <v>1379</v>
       </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>수동매매</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K144" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L144" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M144" s="2" t="n">
-        <v>-0.074</v>
-      </c>
-      <c r="N144" s="2" t="n">
-        <v>4101</v>
-      </c>
-      <c r="O144" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P144" s="2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="Q144" s="2" t="n">
-        <v>3453</v>
-      </c>
-      <c r="R144" s="2" t="n">
-        <v>60867</v>
-      </c>
-      <c r="S144" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>미국수동</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" s="2" t="inlineStr"/>
-      <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr"/>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-      <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="2" t="inlineStr"/>
-      <c r="M146" s="2" t="inlineStr"/>
-      <c r="N146" s="2" t="inlineStr"/>
-      <c r="O146" s="2" t="inlineStr"/>
-      <c r="P146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>수동매매</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>-0.074</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>4101</v>
+      </c>
+      <c r="O148" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P148" s="2" t="n">
+        <v>57414</v>
+      </c>
+      <c r="Q148" s="2" t="n">
+        <v>3453</v>
+      </c>
+      <c r="R148" s="2" t="n">
+        <v>60867</v>
+      </c>
+      <c r="S148" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>미국수동</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr"/>
+      <c r="O150" s="2" t="inlineStr"/>
+      <c r="P150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
           <t>기타(8042)</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="2" t="inlineStr"/>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-      <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="inlineStr"/>
-      <c r="M148" s="2" t="inlineStr"/>
-      <c r="N148" s="2" t="inlineStr"/>
-      <c r="O148" s="2" t="inlineStr"/>
-      <c r="P148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" s="2" t="inlineStr"/>
+      <c r="D152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr"/>
+      <c r="O152" s="2" t="inlineStr"/>
+      <c r="P152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/weekly_performance.xlsx
+++ b/weekly_performance.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S152"/>
+  <dimension ref="A1:S153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1296,44 +1296,48 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.17</v>
+      </c>
       <c r="H14" t="n">
         <v>2.29</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>0.17</v>
+      </c>
       <c r="J14" t="n">
         <v>3.32</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>-2.291</v>
+        <v>-1.799</v>
       </c>
       <c r="N14" t="n">
-        <v>-28796</v>
+        <v>-23069</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-178577</v>
+        <v>-179059</v>
       </c>
       <c r="Q14" t="n">
-        <v>8926</v>
+        <v>9047</v>
       </c>
       <c r="R14" t="n">
-        <v>-169651</v>
+        <v>-170013</v>
       </c>
       <c r="S14" t="n">
-        <v>1379</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="15">
@@ -1353,16 +1357,16 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>36.7</v>
+        <v>36.9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>2.78</v>
@@ -1376,22 +1380,22 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="n">
-        <v>-0.143</v>
+        <v>-0.142</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1932</v>
+        <v>-1925</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>0.77</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>-521364</v>
+        <v>-521846</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>72286</v>
+        <v>72407</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>-449078</v>
+        <v>-449440</v>
       </c>
       <c r="S15" s="2" t="inlineStr"/>
     </row>
@@ -1894,255 +1898,245 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>주도주</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>08/31~09/04</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="N25" t="n">
+        <v>424</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>424</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>76</v>
+      </c>
+      <c r="R25" t="n">
+        <v>500</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>주도주</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="H25" s="2" t="n">
+      <c r="D26" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="I26" s="2" t="n">
         <v>19.29</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J26" s="2" t="n">
         <v>11.77</v>
       </c>
-      <c r="K25" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="L25" s="2" t="n">
+      <c r="K26" s="2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="L26" s="2" t="n">
         <v>1.52</v>
       </c>
-      <c r="M25" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>5630</v>
-      </c>
-      <c r="O25" s="2" t="n">
+      <c r="M26" s="2" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>5531</v>
+      </c>
+      <c r="O26" s="2" t="n">
         <v>1.49</v>
       </c>
-      <c r="P25" s="2" t="n">
-        <v>292736</v>
-      </c>
-      <c r="Q25" s="2" t="n">
-        <v>11308</v>
-      </c>
-      <c r="R25" s="2" t="n">
-        <v>304044</v>
-      </c>
-      <c r="S25" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="P26" s="2" t="n">
+        <v>293160</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>11384</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>304544</v>
+      </c>
+      <c r="S26" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>ROCKET</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>ABC-VCP</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>TV알림</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2X단타</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>분</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>06/22~06/26</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>27</v>
-      </c>
-      <c r="E33" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="I33" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J33" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>185.95</v>
-      </c>
-      <c r="L33" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="N33" t="n">
-        <v>507</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P33" t="n">
-        <v>13680</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1530</v>
-      </c>
-      <c r="R33" t="n">
-        <v>15210</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1415</v>
-      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2157,53 +2151,53 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>06/29~07/03</t>
+          <t>06/22~06/26</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E34" t="n">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="F34" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="G34" t="n">
-        <v>3.01</v>
+        <v>5.47</v>
       </c>
       <c r="H34" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="I34" t="n">
-        <v>13.15</v>
+        <v>17.35</v>
       </c>
       <c r="J34" t="n">
-        <v>5.82</v>
+        <v>20.1</v>
       </c>
       <c r="K34" t="n">
-        <v>313.5</v>
+        <v>185.95</v>
       </c>
       <c r="L34" t="n">
-        <v>175.2</v>
+        <v>187.46</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.703</v>
+        <v>0.274</v>
       </c>
       <c r="N34" t="n">
-        <v>-1271</v>
+        <v>507</v>
       </c>
       <c r="O34" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="P34" t="n">
-        <v>-57188</v>
+        <v>13680</v>
       </c>
       <c r="Q34" t="n">
-        <v>2829</v>
+        <v>1530</v>
       </c>
       <c r="R34" t="n">
-        <v>-54359</v>
+        <v>15210</v>
       </c>
       <c r="S34" t="n">
         <v>1415</v>
@@ -2222,53 +2216,53 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>07/06~07/10</t>
+          <t>06/29~07/03</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E35" t="n">
-        <v>41.9</v>
+        <v>37.8</v>
       </c>
       <c r="F35" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="G35" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="H35" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I35" t="n">
-        <v>8.68</v>
+        <v>13.15</v>
       </c>
       <c r="J35" t="n">
-        <v>9.01</v>
+        <v>5.82</v>
       </c>
       <c r="K35" t="n">
-        <v>247.7</v>
+        <v>313.5</v>
       </c>
       <c r="L35" t="n">
-        <v>174.67</v>
+        <v>175.2</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.288</v>
+        <v>-0.703</v>
       </c>
       <c r="N35" t="n">
-        <v>1187</v>
+        <v>-1271</v>
       </c>
       <c r="O35" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="P35" t="n">
-        <v>36789</v>
+        <v>-57188</v>
       </c>
       <c r="Q35" t="n">
-        <v>3306</v>
+        <v>2829</v>
       </c>
       <c r="R35" t="n">
-        <v>40095</v>
+        <v>-54359</v>
       </c>
       <c r="S35" t="n">
         <v>1415</v>
@@ -2287,53 +2281,53 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>07/13~07/17</t>
+          <t>07/06~07/10</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="F36" t="n">
-        <v>3.53</v>
+        <v>1.8</v>
       </c>
       <c r="G36" t="n">
-        <v>6.86</v>
+        <v>3.14</v>
       </c>
       <c r="H36" t="n">
-        <v>4.11</v>
+        <v>2.76</v>
       </c>
       <c r="I36" t="n">
-        <v>11.14</v>
+        <v>8.68</v>
       </c>
       <c r="J36" t="n">
-        <v>9.65</v>
+        <v>9.01</v>
       </c>
       <c r="K36" t="n">
-        <v>533.86</v>
+        <v>247.7</v>
       </c>
       <c r="L36" t="n">
-        <v>403.59</v>
+        <v>174.67</v>
       </c>
       <c r="M36" t="n">
-        <v>1.375</v>
+        <v>-0.288</v>
       </c>
       <c r="N36" t="n">
-        <v>8720</v>
+        <v>1187</v>
       </c>
       <c r="O36" t="n">
-        <v>3.53</v>
+        <v>1.3</v>
       </c>
       <c r="P36" t="n">
-        <v>52321</v>
+        <v>36789</v>
       </c>
       <c r="Q36" t="n">
-        <v>523</v>
+        <v>3306</v>
       </c>
       <c r="R36" t="n">
-        <v>52844</v>
+        <v>40095</v>
       </c>
       <c r="S36" t="n">
         <v>1415</v>
@@ -2352,53 +2346,53 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>07/20~07/24</t>
+          <t>07/13~07/17</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="G37" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="H37" t="n">
-        <v>1.26</v>
+        <v>4.11</v>
       </c>
       <c r="I37" t="n">
-        <v>7.95</v>
+        <v>11.14</v>
       </c>
       <c r="J37" t="n">
-        <v>2.19</v>
+        <v>9.65</v>
       </c>
       <c r="K37" t="n">
-        <v>800.2</v>
+        <v>533.86</v>
       </c>
       <c r="L37" t="n">
-        <v>60.03</v>
+        <v>403.59</v>
       </c>
       <c r="M37" t="n">
-        <v>2.446</v>
+        <v>1.375</v>
       </c>
       <c r="N37" t="n">
-        <v>5075</v>
+        <v>8720</v>
       </c>
       <c r="O37" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="P37" t="n">
-        <v>45679</v>
+        <v>52321</v>
       </c>
       <c r="Q37" t="n">
-        <v>661</v>
+        <v>523</v>
       </c>
       <c r="R37" t="n">
-        <v>46340</v>
+        <v>52844</v>
       </c>
       <c r="S37" t="n">
         <v>1415</v>
@@ -2417,295 +2411,301 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>07/27~07/31</t>
+          <t>07/20~07/24</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F38" t="n">
-        <v>1.14</v>
+        <v>4.39</v>
       </c>
       <c r="G38" t="n">
-        <v>6.04</v>
+        <v>7.08</v>
       </c>
       <c r="H38" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>13.51</v>
+        <v>7.95</v>
       </c>
       <c r="J38" t="n">
-        <v>4.74</v>
+        <v>2.19</v>
       </c>
       <c r="K38" t="n">
-        <v>2281.51</v>
+        <v>800.2</v>
       </c>
       <c r="L38" t="n">
-        <v>27.54</v>
+        <v>60.03</v>
       </c>
       <c r="M38" t="n">
-        <v>1.758</v>
+        <v>2.446</v>
       </c>
       <c r="N38" t="n">
-        <v>851</v>
+        <v>5075</v>
       </c>
       <c r="O38" t="n">
-        <v>1.14</v>
+        <v>3.51</v>
       </c>
       <c r="P38" t="n">
-        <v>13616</v>
+        <v>45679</v>
       </c>
       <c r="Q38" t="n">
-        <v>1561</v>
+        <v>661</v>
       </c>
       <c r="R38" t="n">
-        <v>15177</v>
+        <v>46340</v>
       </c>
       <c r="S38" t="n">
         <v>1415</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>2X단타</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>07/27~07/31</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>16</v>
+      </c>
+      <c r="E39" t="n">
+        <v>50</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I39" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="J39" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2281.51</v>
+      </c>
+      <c r="L39" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="N39" t="n">
+        <v>851</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P39" t="n">
+        <v>13616</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R39" t="n">
+        <v>15177</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2X단타</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>분</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D40" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E40" s="2" t="n">
         <v>41.8</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F40" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>4.45</v>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>2.87</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="I40" s="2" t="n">
         <v>17.35</v>
       </c>
-      <c r="J39" s="2" t="n">
+      <c r="J40" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K40" s="2" t="n">
         <v>600.88</v>
       </c>
-      <c r="L39" s="2" t="n">
+      <c r="L40" s="2" t="n">
         <v>163.85</v>
       </c>
-      <c r="M39" s="2" t="n">
+      <c r="M40" s="2" t="n">
         <v>0.188</v>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="N40" s="2" t="n">
         <v>783</v>
       </c>
-      <c r="O39" s="2" t="n">
+      <c r="O40" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="P39" s="2" t="n">
+      <c r="P40" s="2" t="n">
         <v>156785</v>
       </c>
-      <c r="Q39" s="2" t="n">
+      <c r="Q40" s="2" t="n">
         <v>12072</v>
       </c>
-      <c r="R39" s="2" t="n">
+      <c r="R40" s="2" t="n">
         <v>168857</v>
       </c>
-      <c r="S39" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>삼닉v3_저2</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>분</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>08/03~08/07</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D42" t="n">
         <v>3</v>
       </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="n">
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
         <v>0.34</v>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
         <v>0.49</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
         <v>13.35</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M42" t="n">
     